--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulation Data" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Column Definition'!$A$3:$H$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Column Definition'!$A$3:$H$340</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2293,13 +2293,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2309,8 +2309,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23945850" y="2000250"/>
-          <a:ext cx="209550" cy="1562100"/>
+          <a:off x="23945850" y="2762250"/>
+          <a:ext cx="209550" cy="3048000"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2319,7 +2319,7 @@
           <a:cxnLst/>
           <a:rect l="0" t="0" r="r" b="b"/>
           <a:pathLst>
-            <a:path w="209550" h="1562100" fill="none">
+            <a:path w="209550" h="3048000" fill="none">
               <a:moveTo>
                 <a:pt x="0" y="0"/>
               </a:moveTo>
@@ -2327,10 +2327,10 @@
                 <a:pt x="209550" y="0"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="209550" y="1562100"/>
+                <a:pt x="209550" y="3048000"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="0" y="1562100"/>
+                <a:pt x="0" y="3048000"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -2349,13 +2349,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2365,7 +2365,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23974425" y="1876425"/>
+          <a:off x="23974425" y="2638425"/>
           <a:ext cx="228600" cy="104775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2402,13 +2402,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2418,7 +2418,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23974425" y="3438525"/>
+          <a:off x="23974425" y="5686425"/>
           <a:ext cx="228600" cy="104775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2455,13 +2455,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2471,8 +2471,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23945850" y="3562350"/>
-          <a:ext cx="257175" cy="2057400"/>
+          <a:off x="23945850" y="5810250"/>
+          <a:ext cx="257175" cy="2743200"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2481,7 +2481,7 @@
           <a:cxnLst/>
           <a:rect l="0" t="0" r="r" b="b"/>
           <a:pathLst>
-            <a:path w="257175" h="2057400" fill="none">
+            <a:path w="257175" h="2743200" fill="none">
               <a:moveTo>
                 <a:pt x="0" y="0"/>
               </a:moveTo>
@@ -2489,10 +2489,10 @@
                 <a:pt x="257175" y="0"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="257175" y="2057400"/>
+                <a:pt x="257175" y="2743200"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="0" y="2057400"/>
+                <a:pt x="0" y="2743200"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -2511,13 +2511,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2527,7 +2527,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23974425" y="3438525"/>
+          <a:off x="23974425" y="5686425"/>
           <a:ext cx="228600" cy="104775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2564,13 +2564,13 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2580,7 +2580,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23974425" y="5495925"/>
+          <a:off x="23974425" y="8429625"/>
           <a:ext cx="228600" cy="104775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2617,13 +2617,13 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2633,8 +2633,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19954875" y="3562350"/>
-          <a:ext cx="514350" cy="1219200"/>
+          <a:off x="19954875" y="4781550"/>
+          <a:ext cx="514350" cy="1028700"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2643,18 +2643,18 @@
           <a:cxnLst/>
           <a:rect l="0" t="0" r="r" b="b"/>
           <a:pathLst>
-            <a:path w="514350" h="1219200" fill="none">
+            <a:path w="514350" h="1028700" fill="none">
               <a:moveTo>
-                <a:pt x="514350" y="0"/>
+                <a:pt x="514350" y="1028700"/>
               </a:moveTo>
+              <a:lnTo>
+                <a:pt x="304800" y="1028700"/>
+              </a:lnTo>
               <a:lnTo>
                 <a:pt x="304800" y="0"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="304800" y="1219200"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="1219200"/>
+                <a:pt x="0" y="0"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -2673,13 +2673,13 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2689,7 +2689,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20212050" y="3438525"/>
+          <a:off x="20212050" y="5686425"/>
           <a:ext cx="228600" cy="104775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2779,7 +2779,7 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
@@ -2795,8 +2795,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19954875" y="3562350"/>
-          <a:ext cx="514350" cy="4991100"/>
+          <a:off x="19954875" y="5810250"/>
+          <a:ext cx="514350" cy="2743200"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2805,7 +2805,7 @@
           <a:cxnLst/>
           <a:rect l="0" t="0" r="r" b="b"/>
           <a:pathLst>
-            <a:path w="514350" h="4991100" fill="none">
+            <a:path w="514350" h="2743200" fill="none">
               <a:moveTo>
                 <a:pt x="514350" y="0"/>
               </a:moveTo>
@@ -2813,10 +2813,10 @@
                 <a:pt x="209550" y="0"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="209550" y="4991100"/>
+                <a:pt x="209550" y="2743200"/>
               </a:lnTo>
               <a:lnTo>
-                <a:pt x="0" y="4991100"/>
+                <a:pt x="0" y="2743200"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -2835,13 +2835,13 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2851,7 +2851,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20212050" y="3438525"/>
+          <a:off x="20212050" y="5686425"/>
           <a:ext cx="228600" cy="104775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3559,7 +3559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AB54"/>
+  <dimension ref="B1:AB55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3780,21 +3780,17 @@
           <t>PK</t>
         </is>
       </c>
-      <c r="V15" s="15" t="inlineStr">
-        <is>
-          <t>MANIFEST_NO</t>
-        </is>
-      </c>
-      <c r="W15" s="16" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
-      <c r="X15" s="17" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="V15" s="18" t="inlineStr">
+        <is>
+          <t>SUPPLIER_CD</t>
+        </is>
+      </c>
+      <c r="W15" s="18" t="inlineStr">
+        <is>
+          <t>VARCHAR(4+)</t>
+        </is>
+      </c>
+      <c r="X15" s="19" t="inlineStr"/>
       <c r="Z15" s="15" t="inlineStr">
         <is>
           <t>MANIFEST_NO / ASN_NO</t>
@@ -3877,12 +3873,12 @@
       <c r="T16" s="19" t="inlineStr"/>
       <c r="V16" s="18" t="inlineStr">
         <is>
-          <t>PO_NO</t>
+          <t>SUPPLIER_PLANT</t>
         </is>
       </c>
       <c r="W16" s="18" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(1+)</t>
         </is>
       </c>
       <c r="X16" s="19" t="inlineStr"/>
@@ -3964,12 +3960,12 @@
       <c r="T17" s="19" t="inlineStr"/>
       <c r="V17" s="18" t="inlineStr">
         <is>
-          <t>SUPPLIER_CD</t>
+          <t>PO_NO</t>
         </is>
       </c>
       <c r="W17" s="18" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(8+)</t>
         </is>
       </c>
       <c r="X17" s="19" t="inlineStr"/>
@@ -4047,12 +4043,12 @@
       <c r="T18" s="19" t="inlineStr"/>
       <c r="V18" s="18" t="inlineStr">
         <is>
-          <t>SUPPLIER_PLANT</t>
+          <t>PO_DT</t>
         </is>
       </c>
       <c r="W18" s="18" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="X18" s="19" t="inlineStr"/>
@@ -4124,17 +4120,21 @@
         </is>
       </c>
       <c r="T19" s="19" t="inlineStr"/>
-      <c r="V19" s="18" t="inlineStr">
-        <is>
-          <t>PO_ORDER_DT</t>
-        </is>
-      </c>
-      <c r="W19" s="18" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
-      <c r="X19" s="19" t="inlineStr"/>
+      <c r="V19" s="15" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="W19" s="16" t="inlineStr">
+        <is>
+          <t>VARCHAR(10+)</t>
+        </is>
+      </c>
+      <c r="X19" s="17" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="Z19" s="18" t="inlineStr">
         <is>
           <t>RIT / ROUTE</t>
@@ -4192,6 +4192,17 @@
         </is>
       </c>
       <c r="T20" s="19" t="inlineStr"/>
+      <c r="V20" s="18" t="inlineStr">
+        <is>
+          <t>ORDER_TYPE</t>
+        </is>
+      </c>
+      <c r="W20" s="18" t="inlineStr">
+        <is>
+          <t>VARCHAR(1+)</t>
+        </is>
+      </c>
+      <c r="X20" s="19" t="inlineStr"/>
       <c r="Z20" s="18" t="inlineStr">
         <is>
           <t>TOTAL_CASE / TOTAL_QTY</t>
@@ -4246,6 +4257,17 @@
           <t>FK</t>
         </is>
       </c>
+      <c r="V21" s="18" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK_FLAG</t>
+        </is>
+      </c>
+      <c r="W21" s="18" t="inlineStr">
+        <is>
+          <t>VARCHAR(1+)</t>
+        </is>
+      </c>
+      <c r="X21" s="19" t="inlineStr"/>
       <c r="Z21" s="18" t="inlineStr">
         <is>
           <t>STATUS</t>
@@ -4307,13 +4329,17 @@
           <t>FK</t>
         </is>
       </c>
-      <c r="V22" s="14" t="inlineStr">
-        <is>
-          <t>TB_R_PRA_DAILY_ORDER_PART</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="n"/>
-      <c r="X22" s="8" t="n"/>
+      <c r="V22" s="18" t="inlineStr">
+        <is>
+          <t>DOCK_CD</t>
+        </is>
+      </c>
+      <c r="W22" s="18" t="inlineStr">
+        <is>
+          <t>VARCHAR(2+)</t>
+        </is>
+      </c>
+      <c r="X22" s="19" t="inlineStr"/>
       <c r="Z22" s="20" t="inlineStr">
         <is>
           <t>… 1 more columns (sheet Column Definition)</t>
@@ -4382,21 +4408,17 @@
           <t>FK</t>
         </is>
       </c>
-      <c r="V23" s="15" t="inlineStr">
-        <is>
-          <t>MANIFEST_NO</t>
-        </is>
-      </c>
-      <c r="W23" s="16" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
-      <c r="X23" s="17" t="inlineStr">
-        <is>
-          <t>PK, FK</t>
-        </is>
-      </c>
+      <c r="V23" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL_QTY</t>
+        </is>
+      </c>
+      <c r="W23" s="18" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="X23" s="19" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="15" t="inlineStr">
@@ -4466,21 +4488,17 @@
           <t>FK</t>
         </is>
       </c>
-      <c r="V24" s="15" t="inlineStr">
-        <is>
-          <t>MANIFEST_ITEM_NO</t>
-        </is>
-      </c>
-      <c r="W24" s="16" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
-      <c r="X24" s="17" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="V24" s="18" t="inlineStr">
+        <is>
+          <t>DELIVERY_DT</t>
+        </is>
+      </c>
+      <c r="W24" s="18" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="X24" s="19" t="inlineStr"/>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="15" t="inlineStr">
@@ -4548,12 +4566,12 @@
       </c>
       <c r="V25" s="18" t="inlineStr">
         <is>
-          <t>PO_NO</t>
+          <t>SUB_ROUTE_CD</t>
         </is>
       </c>
       <c r="W25" s="18" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(4+)</t>
         </is>
       </c>
       <c r="X25" s="19" t="inlineStr"/>
@@ -4631,12 +4649,12 @@
       </c>
       <c r="V26" s="18" t="inlineStr">
         <is>
-          <t>PART_NO</t>
+          <t>SUB_ROUTE_SEQ</t>
         </is>
       </c>
       <c r="W26" s="18" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="X26" s="19" t="inlineStr"/>
@@ -4718,12 +4736,12 @@
       <c r="T27" s="19" t="inlineStr"/>
       <c r="V27" s="18" t="inlineStr">
         <is>
-          <t>PO_ORDER_QTY</t>
+          <t>STATUS</t>
         </is>
       </c>
       <c r="W27" s="18" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(1+)</t>
         </is>
       </c>
       <c r="X27" s="19" t="inlineStr"/>
@@ -4799,17 +4817,13 @@
         </is>
       </c>
       <c r="T28" s="19" t="inlineStr"/>
-      <c r="V28" s="18" t="inlineStr">
-        <is>
-          <t>CROSSDOCK_FLAG</t>
-        </is>
-      </c>
-      <c r="W28" s="18" t="inlineStr">
-        <is>
-          <t>existing</t>
-        </is>
-      </c>
-      <c r="X28" s="19" t="inlineStr"/>
+      <c r="V28" s="20" t="inlineStr">
+        <is>
+          <t>… 41 more columns (sheet Column Definition)</t>
+        </is>
+      </c>
+      <c r="W28" s="21" t="n"/>
+      <c r="X28" s="21" t="n"/>
       <c r="Z28" s="18" t="inlineStr">
         <is>
           <t>PART_NO</t>
@@ -4904,7 +4918,7 @@
       <c r="H30" s="19" t="inlineStr"/>
       <c r="R30" s="22" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="S30" s="22" t="inlineStr">
@@ -4966,13 +4980,13 @@
         </is>
       </c>
       <c r="T31" s="19" t="inlineStr"/>
-      <c r="V31" s="13" t="inlineStr">
-        <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
-        </is>
-      </c>
-      <c r="W31" s="4" t="n"/>
-      <c r="X31" s="4" t="n"/>
+      <c r="V31" s="14" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="n"/>
+      <c r="X31" s="8" t="n"/>
       <c r="Z31" s="18" t="inlineStr">
         <is>
           <t>PO_NO / MANIFEST_ITEM_NO</t>
@@ -5034,21 +5048,17 @@
           <t>FK</t>
         </is>
       </c>
-      <c r="V32" s="15" t="inlineStr">
+      <c r="V32" s="18" t="inlineStr">
         <is>
           <t>PO_NO</t>
         </is>
       </c>
-      <c r="W32" s="16" t="inlineStr">
-        <is>
-          <t>VARCHAR(TBD)</t>
-        </is>
-      </c>
-      <c r="X32" s="17" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="W32" s="18" t="inlineStr">
+        <is>
+          <t>VARCHAR(8+)</t>
+        </is>
+      </c>
+      <c r="X32" s="19" t="inlineStr"/>
       <c r="Z32" s="20" t="inlineStr">
         <is>
           <t>… 1 more columns (sheet Column Definition)</t>
@@ -5110,21 +5120,17 @@
           <t>FK</t>
         </is>
       </c>
-      <c r="V33" s="15" t="inlineStr">
-        <is>
-          <t>MANIFEST_NO</t>
-        </is>
-      </c>
-      <c r="W33" s="16" t="inlineStr">
-        <is>
-          <t>VARCHAR(TBD)</t>
-        </is>
-      </c>
-      <c r="X33" s="17" t="inlineStr">
-        <is>
-          <t>PK, FK</t>
-        </is>
-      </c>
+      <c r="V33" s="18" t="inlineStr">
+        <is>
+          <t>PO_ITEM</t>
+        </is>
+      </c>
+      <c r="W33" s="18" t="inlineStr">
+        <is>
+          <t>VARCHAR(4+)</t>
+        </is>
+      </c>
+      <c r="X33" s="19" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="J34" s="18" t="inlineStr">
@@ -5162,12 +5168,12 @@
       <c r="T34" s="21" t="n"/>
       <c r="V34" s="15" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_NO</t>
         </is>
       </c>
       <c r="W34" s="16" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>VARCHAR(10+)</t>
         </is>
       </c>
       <c r="X34" s="17" t="inlineStr">
@@ -5203,17 +5209,21 @@
           <t>PK, FK</t>
         </is>
       </c>
-      <c r="V35" s="18" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="W35" s="18" t="inlineStr">
-        <is>
-          <t>VARCHAR(15)</t>
-        </is>
-      </c>
-      <c r="X35" s="19" t="inlineStr"/>
+      <c r="V35" s="15" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="W35" s="16" t="inlineStr">
+        <is>
+          <t>VARCHAR(4+)</t>
+        </is>
+      </c>
+      <c r="X35" s="17" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="J36" s="18" t="inlineStr">
@@ -5244,12 +5254,12 @@
       </c>
       <c r="V36" s="18" t="inlineStr">
         <is>
-          <t>SUPPLIER_CD</t>
+          <t>PART_NO</t>
         </is>
       </c>
       <c r="W36" s="18" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>VARCHAR(12+)</t>
         </is>
       </c>
       <c r="X36" s="19" t="inlineStr"/>
@@ -5290,12 +5300,12 @@
       <c r="T37" s="10" t="n"/>
       <c r="V37" s="18" t="inlineStr">
         <is>
-          <t>SUPPLIER_PLANT</t>
+          <t>QTY_PER_CONTAINER</t>
         </is>
       </c>
       <c r="W37" s="18" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="X37" s="19" t="inlineStr"/>
@@ -5344,12 +5354,12 @@
       </c>
       <c r="V38" s="18" t="inlineStr">
         <is>
-          <t>PO_ORDER_QTY</t>
+          <t>ORDER_QTY</t>
         </is>
       </c>
       <c r="W38" s="18" t="inlineStr">
         <is>
-          <t>NUMBER(TBD)</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="X38" s="19" t="inlineStr"/>
@@ -5398,12 +5408,12 @@
       </c>
       <c r="V39" s="18" t="inlineStr">
         <is>
-          <t>MAPPED_QTY</t>
+          <t>DELIVERY_QTY</t>
         </is>
       </c>
       <c r="W39" s="18" t="inlineStr">
         <is>
-          <t>NUMBER(TBD)</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="X39" s="19" t="inlineStr"/>
@@ -5446,13 +5456,17 @@
           <t>FK</t>
         </is>
       </c>
-      <c r="V40" s="20" t="inlineStr">
-        <is>
-          <t>… 4 more columns (sheet Column Definition)</t>
-        </is>
-      </c>
-      <c r="W40" s="21" t="n"/>
-      <c r="X40" s="21" t="n"/>
+      <c r="V40" s="18" t="inlineStr">
+        <is>
+          <t>REMAIN_QTY</t>
+        </is>
+      </c>
+      <c r="W40" s="18" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="X40" s="19" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="J41" s="18" t="inlineStr">
@@ -5492,6 +5506,17 @@
           <t>FK</t>
         </is>
       </c>
+      <c r="V41" s="18" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="W41" s="18" t="inlineStr">
+        <is>
+          <t>VARCHAR(1+)</t>
+        </is>
+      </c>
+      <c r="X41" s="19" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="J42" s="18" t="inlineStr">
@@ -5531,6 +5556,17 @@
           <t>FK</t>
         </is>
       </c>
+      <c r="V42" s="18" t="inlineStr">
+        <is>
+          <t>DOCK_CD</t>
+        </is>
+      </c>
+      <c r="W42" s="18" t="inlineStr">
+        <is>
+          <t>VARCHAR(2+)</t>
+        </is>
+      </c>
+      <c r="X42" s="19" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="J43" s="20" t="inlineStr">
@@ -5566,6 +5602,13 @@
           <t>FK</t>
         </is>
       </c>
+      <c r="V43" s="20" t="inlineStr">
+        <is>
+          <t>… 27 more columns (sheet Column Definition)</t>
+        </is>
+      </c>
+      <c r="W43" s="21" t="n"/>
+      <c r="X43" s="21" t="n"/>
     </row>
     <row r="44">
       <c r="N44" s="18" t="inlineStr">
@@ -5649,6 +5692,13 @@
         </is>
       </c>
       <c r="T46" s="31" t="inlineStr"/>
+      <c r="V46" s="13" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="W46" s="4" t="n"/>
+      <c r="X46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="J47" s="15" t="inlineStr">
@@ -5688,6 +5738,21 @@
         </is>
       </c>
       <c r="T47" s="31" t="inlineStr"/>
+      <c r="V47" s="15" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="W47" s="16" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="X47" s="17" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="J48" s="15" t="inlineStr">
@@ -5731,6 +5796,21 @@
           <t>FK</t>
         </is>
       </c>
+      <c r="V48" s="15" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="W48" s="16" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="X48" s="17" t="inlineStr">
+        <is>
+          <t>PK, FK</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="J49" s="18" t="inlineStr">
@@ -5757,7 +5837,7 @@
       <c r="P49" s="19" t="inlineStr"/>
       <c r="R49" s="28" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="S49" s="28" t="inlineStr">
@@ -5768,6 +5848,21 @@
       <c r="T49" s="29" t="inlineStr">
         <is>
           <t>FK</t>
+        </is>
+      </c>
+      <c r="V49" s="15" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="W49" s="16" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="X49" s="17" t="inlineStr">
+        <is>
+          <t>PK, FK</t>
         </is>
       </c>
     </row>
@@ -5805,6 +5900,17 @@
         </is>
       </c>
       <c r="T50" s="31" t="inlineStr"/>
+      <c r="V50" s="18" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="W50" s="18" t="inlineStr">
+        <is>
+          <t>VARCHAR(15)</t>
+        </is>
+      </c>
+      <c r="X50" s="19" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="J51" s="18" t="inlineStr">
@@ -5832,6 +5938,17 @@
       </c>
       <c r="S51" s="21" t="n"/>
       <c r="T51" s="21" t="n"/>
+      <c r="V51" s="18" t="inlineStr">
+        <is>
+          <t>SUPPLIER_CD</t>
+        </is>
+      </c>
+      <c r="W51" s="18" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="X51" s="19" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="J52" s="18" t="inlineStr">
@@ -5845,6 +5962,17 @@
         </is>
       </c>
       <c r="L52" s="19" t="inlineStr"/>
+      <c r="V52" s="18" t="inlineStr">
+        <is>
+          <t>SUPPLIER_PLANT</t>
+        </is>
+      </c>
+      <c r="W52" s="18" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="X52" s="19" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="J53" s="18" t="inlineStr">
@@ -5858,6 +5986,17 @@
         </is>
       </c>
       <c r="L53" s="19" t="inlineStr"/>
+      <c r="V53" s="18" t="inlineStr">
+        <is>
+          <t>ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="W53" s="18" t="inlineStr">
+        <is>
+          <t>NUMBER(TBD)</t>
+        </is>
+      </c>
+      <c r="X53" s="19" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="J54" s="20" t="inlineStr">
@@ -5867,14 +6006,35 @@
       </c>
       <c r="K54" s="21" t="n"/>
       <c r="L54" s="21" t="n"/>
-    </row>
-    <row r="55"/>
+      <c r="V54" s="18" t="inlineStr">
+        <is>
+          <t>MAPPED_QTY</t>
+        </is>
+      </c>
+      <c r="W54" s="18" t="inlineStr">
+        <is>
+          <t>NUMBER(TBD)</t>
+        </is>
+      </c>
+      <c r="X54" s="19" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="V55" s="20" t="inlineStr">
+        <is>
+          <t>… 4 more columns (sheet Column Definition)</t>
+        </is>
+      </c>
+      <c r="W55" s="21" t="n"/>
+      <c r="X55" s="21" t="n"/>
+    </row>
     <row r="56"/>
     <row r="57"/>
     <row r="58"/>
     <row r="59"/>
+    <row r="60"/>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="36">
+    <mergeCell ref="V28:X28"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="Z22:AB22"/>
     <mergeCell ref="B23:D23"/>
@@ -5882,7 +6042,6 @@
     <mergeCell ref="R37:T37"/>
     <mergeCell ref="N14:P14"/>
     <mergeCell ref="V31:X31"/>
-    <mergeCell ref="V40:X40"/>
     <mergeCell ref="R51:T51"/>
     <mergeCell ref="N29:P29"/>
     <mergeCell ref="J54:L54"/>
@@ -5893,9 +6052,11 @@
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="J46:L46"/>
-    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="V46:X46"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="R14:T14"/>
+    <mergeCell ref="V43:X43"/>
+    <mergeCell ref="V55:X55"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="F19:H19"/>
@@ -6296,7 +6457,7 @@
       </c>
       <c r="D15" s="34" t="inlineStr">
         <is>
-          <t>Existing Pra Daily Order manifest (supplier PO header). Only the columns used by Crossdock are listed.</t>
+          <t>Existing Pra Daily Order manifest (supplier PO per manifest, 391 sample rows). MANIFEST_NO is unique; one PO_NO can have several manifests. CROSS_DOCK_FLAG is on the manifest. Types inferred from the sample data (confirm with the DDL).</t>
         </is>
       </c>
       <c r="E15" s="34" t="inlineStr">
@@ -6324,7 +6485,7 @@
       </c>
       <c r="D16" s="34" t="inlineStr">
         <is>
-          <t>Existing Pra Daily Order part (supplier PO line). Only the columns used by Crossdock are listed.</t>
+          <t>Existing Pra Daily Order part (one row per manifest item, 2353 sample rows). Key MANIFEST_NO + MANIFEST_ITEM (also PO_NO + PO_ITEM is unique; PO_ITEM can differ from MANIFEST_ITEM). Types inferred from the sample data (confirm with the DDL).</t>
         </is>
       </c>
       <c r="E16" s="34" t="inlineStr">
@@ -6939,7 +7100,7 @@
       </c>
       <c r="G16" s="34" t="inlineStr">
         <is>
-          <t>PO lines of a manifest (existing)</t>
+          <t>Items of a manifest (existing); crossdock when the manifest has CROSS_DOCK_FLAG X</t>
         </is>
       </c>
     </row>
@@ -6954,7 +7115,7 @@
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_NO + MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_NO + MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="D17" s="34" t="inlineStr">
@@ -6964,7 +7125,7 @@
       </c>
       <c r="E17" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_NO + MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_NO + MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="F17" s="34" t="inlineStr">
@@ -6989,7 +7150,7 @@
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_NO + MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_NO + MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="D18" s="34" t="inlineStr">
@@ -6999,7 +7160,7 @@
       </c>
       <c r="E18" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_NO + MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_NO + MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="F18" s="34" t="inlineStr">
@@ -7024,7 +7185,7 @@
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_NO + MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_NO + MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="D19" s="34" t="inlineStr">
@@ -7034,7 +7195,7 @@
       </c>
       <c r="E19" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_NO + MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_NO + MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="F19" s="34" t="inlineStr">
@@ -7130,7 +7291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13243,7 +13404,7 @@
       </c>
       <c r="C186" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="D186" s="34" t="inlineStr">
@@ -13264,7 +13425,7 @@
       </c>
       <c r="H186" s="34" t="inlineStr">
         <is>
-          <t>Manifest item number</t>
+          <t>Manifest item number (renamed from MANIFEST_ITEM_NO of the UISS to the name of the existing Pra Daily Order column)</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13440,7 @@
       </c>
       <c r="C187" s="34" t="inlineStr">
         <is>
-          <t>PO_ORDER_QTY</t>
+          <t>ORDER_QTY</t>
         </is>
       </c>
       <c r="D187" s="34" t="inlineStr">
@@ -13296,7 +13457,7 @@
       </c>
       <c r="H187" s="34" t="inlineStr">
         <is>
-          <t>PO qty</t>
+          <t>PO qty (renamed from PO_ORDER_QTY of the UISS to the name of the existing Pra Daily Order column)</t>
         </is>
       </c>
     </row>
@@ -14087,7 +14248,7 @@
       </c>
       <c r="C211" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="D211" s="34" t="inlineStr">
@@ -14108,7 +14269,7 @@
       </c>
       <c r="H211" s="34" t="inlineStr">
         <is>
-          <t>Manifest item number (Pra Daily Order Part)</t>
+          <t>Manifest item number (Pra Daily Order Part) (renamed from MANIFEST_ITEM_NO of the UISS to the name of the existing Pra Daily Order column)</t>
         </is>
       </c>
     </row>
@@ -14123,7 +14284,7 @@
       </c>
       <c r="C212" s="34" t="inlineStr">
         <is>
-          <t>PO_ORDER_DT</t>
+          <t>PO_DT</t>
         </is>
       </c>
       <c r="D212" s="34" t="inlineStr">
@@ -14140,7 +14301,7 @@
       </c>
       <c r="H212" s="34" t="inlineStr">
         <is>
-          <t>Order date of the PO (PO Date)</t>
+          <t>Order date of the PO (PO Date) (renamed from PO_ORDER_DT of the UISS to the name of the existing Pra Daily Order column)</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14316,7 @@
       </c>
       <c r="C213" s="34" t="inlineStr">
         <is>
-          <t>PO_ORDER_QTY</t>
+          <t>ORDER_QTY</t>
         </is>
       </c>
       <c r="D213" s="34" t="inlineStr">
@@ -14172,7 +14333,7 @@
       </c>
       <c r="H213" s="34" t="inlineStr">
         <is>
-          <t>Order qty of the PO part</t>
+          <t>Order qty of the PO part (renamed from PO_ORDER_QTY of the UISS to the name of the existing Pra Daily Order column)</t>
         </is>
       </c>
     </row>
@@ -14443,19 +14604,15 @@
       </c>
       <c r="C222" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_NO</t>
+          <t>DEPOT_CD</t>
         </is>
       </c>
       <c r="D222" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
-        </is>
-      </c>
-      <c r="E222" s="34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>VARCHAR(2+)</t>
+        </is>
+      </c>
+      <c r="E222" s="34" t="inlineStr"/>
       <c r="F222" s="34" t="inlineStr"/>
       <c r="G222" s="34" t="inlineStr">
         <is>
@@ -14464,7 +14621,7 @@
       </c>
       <c r="H222" s="34" t="inlineStr">
         <is>
-          <t>Manifest number</t>
+          <t>values: 01</t>
         </is>
       </c>
     </row>
@@ -14479,12 +14636,12 @@
       </c>
       <c r="C223" s="34" t="inlineStr">
         <is>
-          <t>PO_NO</t>
+          <t>SUPPLIER_CD</t>
         </is>
       </c>
       <c r="D223" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(4+)</t>
         </is>
       </c>
       <c r="E223" s="34" t="inlineStr"/>
@@ -14496,7 +14653,7 @@
       </c>
       <c r="H223" s="34" t="inlineStr">
         <is>
-          <t>PO number</t>
+          <t>Supplier code (4 characters in the sample)</t>
         </is>
       </c>
     </row>
@@ -14511,12 +14668,12 @@
       </c>
       <c r="C224" s="34" t="inlineStr">
         <is>
-          <t>SUPPLIER_CD</t>
+          <t>SUPPLIER_PLANT</t>
         </is>
       </c>
       <c r="D224" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(1+)</t>
         </is>
       </c>
       <c r="E224" s="34" t="inlineStr"/>
@@ -14528,7 +14685,7 @@
       </c>
       <c r="H224" s="34" t="inlineStr">
         <is>
-          <t>Supplier code</t>
+          <t>Supplier plant</t>
         </is>
       </c>
     </row>
@@ -14543,26 +14700,22 @@
       </c>
       <c r="C225" s="34" t="inlineStr">
         <is>
-          <t>SUPPLIER_PLANT</t>
+          <t>SUB_SUPP_CD</t>
         </is>
       </c>
       <c r="D225" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(4+)</t>
         </is>
       </c>
       <c r="E225" s="34" t="inlineStr"/>
       <c r="F225" s="34" t="inlineStr"/>
       <c r="G225" s="34" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H225" s="34" t="inlineStr">
-        <is>
-          <t>Supplier plant</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H225" s="34" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="34" t="inlineStr">
@@ -14575,91 +14728,71 @@
       </c>
       <c r="C226" s="34" t="inlineStr">
         <is>
-          <t>PO_ORDER_DT</t>
+          <t>SUB_SUPP_PLANT</t>
         </is>
       </c>
       <c r="D226" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(1+)</t>
         </is>
       </c>
       <c r="E226" s="34" t="inlineStr"/>
       <c r="F226" s="34" t="inlineStr"/>
       <c r="G226" s="34" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H226" s="34" t="inlineStr">
-        <is>
-          <t>PO date</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H226" s="34" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B227" s="33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C227" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_NO</t>
+          <t>SUPPLIER_NAME</t>
         </is>
       </c>
       <c r="D227" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
-        </is>
-      </c>
-      <c r="E227" s="34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F227" s="34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>VARCHAR(49+)</t>
+        </is>
+      </c>
+      <c r="E227" s="34" t="inlineStr"/>
+      <c r="F227" s="34" t="inlineStr"/>
       <c r="G227" s="34" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H227" s="34" t="inlineStr">
-        <is>
-          <t>Manifest number (TB_R_PRA_DAILY_ORDER_MANIFEST)</t>
-        </is>
-      </c>
+      <c r="H227" s="34" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B228" s="33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C228" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM_NO</t>
+          <t>PO_NO</t>
         </is>
       </c>
       <c r="D228" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
-        </is>
-      </c>
-      <c r="E228" s="34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>VARCHAR(8+)</t>
+        </is>
+      </c>
+      <c r="E228" s="34" t="inlineStr"/>
       <c r="F228" s="34" t="inlineStr"/>
       <c r="G228" s="34" t="inlineStr">
         <is>
@@ -14668,27 +14801,27 @@
       </c>
       <c r="H228" s="34" t="inlineStr">
         <is>
-          <t>Manifest item number</t>
+          <t>PO number; one PO can be split over several manifests</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B229" s="33" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C229" s="34" t="inlineStr">
         <is>
-          <t>PO_NO</t>
+          <t>PO_DT</t>
         </is>
       </c>
       <c r="D229" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E229" s="34" t="inlineStr"/>
@@ -14700,30 +14833,34 @@
       </c>
       <c r="H229" s="34" t="inlineStr">
         <is>
-          <t>PO number</t>
+          <t>PO date</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B230" s="33" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C230" s="34" t="inlineStr">
         <is>
-          <t>PART_NO</t>
+          <t>MANIFEST_NO</t>
         </is>
       </c>
       <c r="D230" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
-        </is>
-      </c>
-      <c r="E230" s="34" t="inlineStr"/>
+          <t>VARCHAR(10+)</t>
+        </is>
+      </c>
+      <c r="E230" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F230" s="34" t="inlineStr"/>
       <c r="G230" s="34" t="inlineStr">
         <is>
@@ -14732,27 +14869,27 @@
       </c>
       <c r="H230" s="34" t="inlineStr">
         <is>
-          <t>Part number</t>
+          <t>Manifest number (unique in the sample)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B231" s="33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C231" s="34" t="inlineStr">
         <is>
-          <t>PO_ORDER_QTY</t>
+          <t>MAKER_CODE</t>
         </is>
       </c>
       <c r="D231" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(1+)</t>
         </is>
       </c>
       <c r="E231" s="34" t="inlineStr"/>
@@ -14764,27 +14901,27 @@
       </c>
       <c r="H231" s="34" t="inlineStr">
         <is>
-          <t>PO qty (pcs)</t>
+          <t>values: A</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B232" s="33" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C232" s="34" t="inlineStr">
         <is>
-          <t>CROSSDOCK_FLAG</t>
+          <t>PO_TRANSPORT_CD</t>
         </is>
       </c>
       <c r="D232" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(1+)</t>
         </is>
       </c>
       <c r="E232" s="34" t="inlineStr"/>
@@ -14796,34 +14933,30 @@
       </c>
       <c r="H232" s="34" t="inlineStr">
         <is>
-          <t>'X' = crossdock PO part (taken by XD09)</t>
+          <t>values: 3</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B233" s="33" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C233" s="34" t="inlineStr">
         <is>
-          <t>PO_NO</t>
+          <t>ORDER_TYPE</t>
         </is>
       </c>
       <c r="D233" s="34" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
-        </is>
-      </c>
-      <c r="E233" s="34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>VARCHAR(1+)</t>
+        </is>
+      </c>
+      <c r="E233" s="34" t="inlineStr"/>
       <c r="F233" s="34" t="inlineStr"/>
       <c r="G233" s="34" t="inlineStr">
         <is>
@@ -14832,79 +14965,63 @@
       </c>
       <c r="H233" s="34" t="inlineStr">
         <is>
-          <t>PO number (Pra Daily Order Manifest)</t>
+          <t>Order type ('3', 'C' in the sample); values: 3, C</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B234" s="33" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C234" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_NO</t>
+          <t>CROSS_DOCK_FLAG</t>
         </is>
       </c>
       <c r="D234" s="34" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
-        </is>
-      </c>
-      <c r="E234" s="34" t="inlineStr">
+          <t>VARCHAR(1+)</t>
+        </is>
+      </c>
+      <c r="E234" s="34" t="inlineStr"/>
+      <c r="F234" s="34" t="inlineStr"/>
+      <c r="G234" s="34" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F234" s="34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G234" s="34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="H234" s="34" t="inlineStr">
         <is>
-          <t>Manifest number</t>
+          <t>'X' = crossdock manifest (its parts are taken by XD09); NULL otherwise; values: X</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B235" s="33" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C235" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM_NO</t>
+          <t>COMPANY_CD</t>
         </is>
       </c>
       <c r="D235" s="34" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
-        </is>
-      </c>
-      <c r="E235" s="34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F235" s="34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>VARCHAR(4+)</t>
+        </is>
+      </c>
+      <c r="E235" s="34" t="inlineStr"/>
+      <c r="F235" s="34" t="inlineStr"/>
       <c r="G235" s="34" t="inlineStr">
         <is>
           <t>N</t>
@@ -14912,27 +15029,27 @@
       </c>
       <c r="H235" s="34" t="inlineStr">
         <is>
-          <t>Manifest item number (Pra Daily Order Part)</t>
+          <t>values: 807B</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B236" s="33" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C236" s="34" t="inlineStr">
         <is>
-          <t>PART_NO</t>
+          <t>RCV_PLANT_CD</t>
         </is>
       </c>
       <c r="D236" s="34" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
+          <t>VARCHAR(1+)</t>
         </is>
       </c>
       <c r="E236" s="34" t="inlineStr"/>
@@ -14944,27 +15061,27 @@
       </c>
       <c r="H236" s="34" t="inlineStr">
         <is>
-          <t>Part number</t>
+          <t>values: 1</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B237" s="33" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C237" s="34" t="inlineStr">
         <is>
-          <t>SUPPLIER_CD</t>
+          <t>DOCK_CD</t>
         </is>
       </c>
       <c r="D237" s="34" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>VARCHAR(2+)</t>
         </is>
       </c>
       <c r="E237" s="34" t="inlineStr"/>
@@ -14976,27 +15093,27 @@
       </c>
       <c r="H237" s="34" t="inlineStr">
         <is>
-          <t>Supplier code</t>
+          <t>Receiving dock; values: S1, S2, S3</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B238" s="33" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C238" s="34" t="inlineStr">
         <is>
-          <t>SUPPLIER_PLANT</t>
+          <t>TOTAL_ITEM</t>
         </is>
       </c>
       <c r="D238" s="34" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="E238" s="34" t="inlineStr"/>
@@ -15008,27 +15125,27 @@
       </c>
       <c r="H238" s="34" t="inlineStr">
         <is>
-          <t>Supplier plant</t>
+          <t>Number of items of the manifest</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B239" s="33" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C239" s="34" t="inlineStr">
         <is>
-          <t>PO_ORDER_QTY</t>
+          <t>TOTAL_QTY</t>
         </is>
       </c>
       <c r="D239" s="34" t="inlineStr">
         <is>
-          <t>NUMBER(TBD)</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="E239" s="34" t="inlineStr"/>
@@ -15040,27 +15157,27 @@
       </c>
       <c r="H239" s="34" t="inlineStr">
         <is>
-          <t>PO qty of the part</t>
+          <t>Total order qty of the manifest</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B240" s="33" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C240" s="34" t="inlineStr">
         <is>
-          <t>MAPPED_QTY</t>
+          <t>TOTAL_QTY_DELIVERY</t>
         </is>
       </c>
       <c r="D240" s="34" t="inlineStr">
         <is>
-          <t>NUMBER(TBD)</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="E240" s="34" t="inlineStr"/>
@@ -15070,29 +15187,25 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H240" s="34" t="inlineStr">
-        <is>
-          <t>Qty already mapped to customer orders by [Create ASN]; open qty = PO_ORDER_QTY - MAPPED_QTY</t>
-        </is>
-      </c>
+      <c r="H240" s="34" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B241" s="33" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C241" s="34" t="inlineStr">
         <is>
-          <t>CREATED_BY</t>
+          <t>RECEIVED_QTY</t>
         </is>
       </c>
       <c r="D241" s="34" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="E241" s="34" t="inlineStr"/>
@@ -15104,27 +15217,27 @@
       </c>
       <c r="H241" s="34" t="inlineStr">
         <is>
-          <t>User who created the record</t>
+          <t>values: 0</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B242" s="33" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C242" s="34" t="inlineStr">
         <is>
-          <t>CREATED_DT</t>
+          <t>TOTAL_QTY_REMAIN</t>
         </is>
       </c>
       <c r="D242" s="34" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="E242" s="34" t="inlineStr"/>
@@ -15134,29 +15247,25 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H242" s="34" t="inlineStr">
-        <is>
-          <t>Created date and time</t>
-        </is>
-      </c>
+      <c r="H242" s="34" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B243" s="33" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C243" s="34" t="inlineStr">
         <is>
-          <t>CHANGED_BY</t>
+          <t>DELIVERY_DT</t>
         </is>
       </c>
       <c r="D243" s="34" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E243" s="34" t="inlineStr"/>
@@ -15168,22 +15277,22 @@
       </c>
       <c r="H243" s="34" t="inlineStr">
         <is>
-          <t>User who last changed the record</t>
+          <t>Delivery date</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="34" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B244" s="33" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C244" s="34" t="inlineStr">
         <is>
-          <t>CHANGED_DT</t>
+          <t>DELIVERY_DT_ACTUAL</t>
         </is>
       </c>
       <c r="D244" s="34" t="inlineStr">
@@ -15195,100 +15304,88 @@
       <c r="F244" s="34" t="inlineStr"/>
       <c r="G244" s="34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H244" s="34" t="inlineStr">
         <is>
-          <t>Last changed date and time</t>
+          <t>values: 2026-10-06 06:30:21.103</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B245" s="33" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C245" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_NO / ASN_NO</t>
+          <t>SHIPPING_DOCK</t>
         </is>
       </c>
       <c r="D245" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
-        </is>
-      </c>
-      <c r="E245" s="34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E245" s="34" t="inlineStr"/>
       <c r="F245" s="34" t="inlineStr"/>
       <c r="G245" s="34" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H245" s="34" t="inlineStr">
-        <is>
-          <t>ASN number (auto generated as today, existing numbering)</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H245" s="34" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B246" s="33" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C246" s="34" t="inlineStr">
         <is>
-          <t>SUPPLIER_CD</t>
+          <t>SHIPPING_DT</t>
         </is>
       </c>
       <c r="D246" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E246" s="34" t="inlineStr"/>
       <c r="F246" s="34" t="inlineStr"/>
       <c r="G246" s="34" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H246" s="34" t="inlineStr">
-        <is>
-          <t>Supplier code</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H246" s="34" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B247" s="33" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C247" s="34" t="inlineStr">
         <is>
-          <t>SUPPLIER_PLANT</t>
+          <t>SUB_ROUTE_CD</t>
         </is>
       </c>
       <c r="D247" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(4+)</t>
         </is>
       </c>
       <c r="E247" s="34" t="inlineStr"/>
@@ -15300,27 +15397,27 @@
       </c>
       <c r="H247" s="34" t="inlineStr">
         <is>
-          <t>Supplier plant</t>
+          <t>Route of the delivery (e.g. DS18)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B248" s="33" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C248" s="34" t="inlineStr">
         <is>
-          <t>DELIVERY_DT</t>
+          <t>SUB_ROUTE_SEQ</t>
         </is>
       </c>
       <c r="D248" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="E248" s="34" t="inlineStr"/>
@@ -15332,327 +15429,283 @@
       </c>
       <c r="H248" s="34" t="inlineStr">
         <is>
-          <t>Delivery Date</t>
+          <t>Sequence (rit) of the route; values: 1, 2, 5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B249" s="33" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C249" s="34" t="inlineStr">
         <is>
-          <t>RIT / ROUTE</t>
+          <t>SUB_ROUTE_DT</t>
         </is>
       </c>
       <c r="D249" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E249" s="34" t="inlineStr"/>
       <c r="F249" s="34" t="inlineStr"/>
       <c r="G249" s="34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H249" s="34" t="inlineStr">
         <is>
-          <t>Rit and route (route master, existing)</t>
+          <t>Date and time of the route</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B250" s="33" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C250" s="34" t="inlineStr">
         <is>
-          <t>TOTAL_CASE / TOTAL_QTY</t>
+          <t>FST_X_DOC_CD</t>
         </is>
       </c>
       <c r="D250" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>? (no data)</t>
         </is>
       </c>
       <c r="E250" s="34" t="inlineStr"/>
       <c r="F250" s="34" t="inlineStr"/>
       <c r="G250" s="34" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H250" s="34" t="inlineStr">
-        <is>
-          <t>Number of cases / Delivery Qty</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H250" s="34" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B251" s="33" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C251" s="34" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>FST_X_PLANT_CD</t>
         </is>
       </c>
       <c r="D251" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>? (no data)</t>
         </is>
       </c>
       <c r="E251" s="34" t="inlineStr"/>
       <c r="F251" s="34" t="inlineStr"/>
       <c r="G251" s="34" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H251" s="34" t="inlineStr">
-        <is>
-          <t>Created</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H251" s="34" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B252" s="33" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C252" s="34" t="inlineStr">
         <is>
-          <t>CREATED_BY / CREATED_DT</t>
+          <t>FST_X_SHIPPING_DOCK_CD</t>
         </is>
       </c>
       <c r="D252" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>? (no data)</t>
         </is>
       </c>
       <c r="E252" s="34" t="inlineStr"/>
       <c r="F252" s="34" t="inlineStr"/>
       <c r="G252" s="34" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H252" s="34" t="inlineStr">
-        <is>
-          <t>User and date-time of submit</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H252" s="34" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B253" s="33" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C253" s="34" t="inlineStr">
         <is>
-          <t>MANIFEST_NO / ASN_NO</t>
+          <t>FST_X_DOCK_ARRIVAL_DT</t>
         </is>
       </c>
       <c r="D253" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
-        </is>
-      </c>
-      <c r="E253" s="34" t="inlineStr">
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E253" s="34" t="inlineStr"/>
+      <c r="F253" s="34" t="inlineStr"/>
+      <c r="G253" s="34" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F253" s="34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G253" s="34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H253" s="34" t="inlineStr">
-        <is>
-          <t>ASN number</t>
-        </is>
-      </c>
+      <c r="H253" s="34" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B254" s="33" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C254" s="34" t="inlineStr">
         <is>
-          <t>CASE_NO</t>
+          <t>FST_X_DOCK_DEPART_DT</t>
         </is>
       </c>
       <c r="D254" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
-        </is>
-      </c>
-      <c r="E254" s="34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E254" s="34" t="inlineStr"/>
       <c r="F254" s="34" t="inlineStr"/>
       <c r="G254" s="34" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H254" s="34" t="inlineStr">
-        <is>
-          <t>Case number, auto generated with the existing last sequence</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H254" s="34" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B255" s="33" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C255" s="34" t="inlineStr">
         <is>
-          <t>PART_NO</t>
+          <t>FST_X_DOCK_ROUTE_GRP_CD</t>
         </is>
       </c>
       <c r="D255" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>? (no data)</t>
         </is>
       </c>
       <c r="E255" s="34" t="inlineStr"/>
       <c r="F255" s="34" t="inlineStr"/>
       <c r="G255" s="34" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H255" s="34" t="inlineStr">
-        <is>
-          <t>Part number of the case</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H255" s="34" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B256" s="33" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="C256" s="34" t="inlineStr">
         <is>
-          <t>DESTINATION_CD</t>
+          <t>FST_X_DOCK_SEQ_NO</t>
         </is>
       </c>
       <c r="D256" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>? (no data)</t>
         </is>
       </c>
       <c r="E256" s="34" t="inlineStr"/>
       <c r="F256" s="34" t="inlineStr"/>
       <c r="G256" s="34" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H256" s="34" t="inlineStr">
-        <is>
-          <t>Destination of the case</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H256" s="34" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B257" s="33" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="C257" s="34" t="inlineStr">
         <is>
-          <t>QTY</t>
+          <t>FST_X_ROUTE_DT</t>
         </is>
       </c>
       <c r="D257" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E257" s="34" t="inlineStr"/>
       <c r="F257" s="34" t="inlineStr"/>
       <c r="G257" s="34" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H257" s="34" t="inlineStr">
-        <is>
-          <t>Qty of the case</t>
-        </is>
-      </c>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H257" s="34" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B258" s="33" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="C258" s="34" t="inlineStr">
         <is>
-          <t>PO_NO / MANIFEST_ITEM_NO</t>
+          <t>FTP_FLAG</t>
         </is>
       </c>
       <c r="D258" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(1+)</t>
         </is>
       </c>
       <c r="E258" s="34" t="inlineStr"/>
@@ -15664,27 +15717,27 @@
       </c>
       <c r="H258" s="34" t="inlineStr">
         <is>
-          <t>PO reference of the Pra Daily Order</t>
+          <t>values: 0</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="34" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B259" s="33" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C259" s="34" t="inlineStr">
         <is>
-          <t>CREATED_BY / CREATED_DT</t>
+          <t>STATUS</t>
         </is>
       </c>
       <c r="D259" s="34" t="inlineStr">
         <is>
-          <t>existing</t>
+          <t>VARCHAR(1+)</t>
         </is>
       </c>
       <c r="E259" s="34" t="inlineStr"/>
@@ -15696,12 +15749,2520 @@
       </c>
       <c r="H259" s="34" t="inlineStr">
         <is>
+          <t>Manifest status ('0', '2' in the sample); values: 0, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B260" s="33" t="n">
+        <v>39</v>
+      </c>
+      <c r="C260" s="34" t="inlineStr">
+        <is>
+          <t>REMARK</t>
+        </is>
+      </c>
+      <c r="D260" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E260" s="34" t="inlineStr"/>
+      <c r="F260" s="34" t="inlineStr"/>
+      <c r="G260" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H260" s="34" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B261" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="C261" s="34" t="inlineStr">
+        <is>
+          <t>DOWNLOAD_FLAG</t>
+        </is>
+      </c>
+      <c r="D261" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E261" s="34" t="inlineStr"/>
+      <c r="F261" s="34" t="inlineStr"/>
+      <c r="G261" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H261" s="34" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B262" s="33" t="n">
+        <v>41</v>
+      </c>
+      <c r="C262" s="34" t="inlineStr">
+        <is>
+          <t>DOWNLOADED_BY</t>
+        </is>
+      </c>
+      <c r="D262" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E262" s="34" t="inlineStr"/>
+      <c r="F262" s="34" t="inlineStr"/>
+      <c r="G262" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H262" s="34" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B263" s="33" t="n">
+        <v>42</v>
+      </c>
+      <c r="C263" s="34" t="inlineStr">
+        <is>
+          <t>DOWNLOADED_DT</t>
+        </is>
+      </c>
+      <c r="D263" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E263" s="34" t="inlineStr"/>
+      <c r="F263" s="34" t="inlineStr"/>
+      <c r="G263" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H263" s="34" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B264" s="33" t="n">
+        <v>43</v>
+      </c>
+      <c r="C264" s="34" t="inlineStr">
+        <is>
+          <t>SEND_PO_ADM_FLAG</t>
+        </is>
+      </c>
+      <c r="D264" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(1+)</t>
+        </is>
+      </c>
+      <c r="E264" s="34" t="inlineStr"/>
+      <c r="F264" s="34" t="inlineStr"/>
+      <c r="G264" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H264" s="34" t="inlineStr">
+        <is>
+          <t>values: Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B265" s="33" t="n">
+        <v>44</v>
+      </c>
+      <c r="C265" s="34" t="inlineStr">
+        <is>
+          <t>SEND_PO_ADM_DT</t>
+        </is>
+      </c>
+      <c r="D265" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E265" s="34" t="inlineStr"/>
+      <c r="F265" s="34" t="inlineStr"/>
+      <c r="G265" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H265" s="34" t="inlineStr">
+        <is>
+          <t>values: 2026-10-06 05:30:17.083</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B266" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="C266" s="34" t="inlineStr">
+        <is>
+          <t>CREATED_BY</t>
+        </is>
+      </c>
+      <c r="D266" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(6+)</t>
+        </is>
+      </c>
+      <c r="E266" s="34" t="inlineStr"/>
+      <c r="F266" s="34" t="inlineStr"/>
+      <c r="G266" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H266" s="34" t="inlineStr">
+        <is>
+          <t>values: SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B267" s="33" t="n">
+        <v>46</v>
+      </c>
+      <c r="C267" s="34" t="inlineStr">
+        <is>
+          <t>CREATED_DT</t>
+        </is>
+      </c>
+      <c r="D267" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E267" s="34" t="inlineStr"/>
+      <c r="F267" s="34" t="inlineStr"/>
+      <c r="G267" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H267" s="34" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B268" s="33" t="n">
+        <v>47</v>
+      </c>
+      <c r="C268" s="34" t="inlineStr">
+        <is>
+          <t>CHANGED_BY</t>
+        </is>
+      </c>
+      <c r="D268" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(9+)</t>
+        </is>
+      </c>
+      <c r="E268" s="34" t="inlineStr"/>
+      <c r="F268" s="34" t="inlineStr"/>
+      <c r="G268" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H268" s="34" t="inlineStr">
+        <is>
+          <t>values: SCHEDULER, SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B269" s="33" t="n">
+        <v>48</v>
+      </c>
+      <c r="C269" s="34" t="inlineStr">
+        <is>
+          <t>CHANGED_DT</t>
+        </is>
+      </c>
+      <c r="D269" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E269" s="34" t="inlineStr"/>
+      <c r="F269" s="34" t="inlineStr"/>
+      <c r="G269" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H269" s="34" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B270" s="33" t="n">
+        <v>49</v>
+      </c>
+      <c r="C270" s="34" t="inlineStr">
+        <is>
+          <t>RECEIVED_DT</t>
+        </is>
+      </c>
+      <c r="D270" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E270" s="34" t="inlineStr"/>
+      <c r="F270" s="34" t="inlineStr"/>
+      <c r="G270" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H270" s="34" t="inlineStr">
+        <is>
+          <t>values: 2026-10-06 06:30:21.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B271" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="C271" s="34" t="inlineStr">
+        <is>
+          <t>MANIFEST_LAST_SEQ</t>
+        </is>
+      </c>
+      <c r="D271" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(2+)</t>
+        </is>
+      </c>
+      <c r="E271" s="34" t="inlineStr"/>
+      <c r="F271" s="34" t="inlineStr"/>
+      <c r="G271" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H271" s="34" t="inlineStr">
+        <is>
+          <t>values: A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B272" s="33" t="n">
+        <v>51</v>
+      </c>
+      <c r="C272" s="34" t="inlineStr">
+        <is>
+          <t>CANCEL_QTY</t>
+        </is>
+      </c>
+      <c r="D272" s="34" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="E272" s="34" t="inlineStr"/>
+      <c r="F272" s="34" t="inlineStr"/>
+      <c r="G272" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H272" s="34" t="inlineStr">
+        <is>
+          <t>values: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B273" s="33" t="n">
+        <v>52</v>
+      </c>
+      <c r="C273" s="34" t="inlineStr">
+        <is>
+          <t>CANCEL_DT</t>
+        </is>
+      </c>
+      <c r="D273" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E273" s="34" t="inlineStr"/>
+      <c r="F273" s="34" t="inlineStr"/>
+      <c r="G273" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H273" s="34" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B274" s="33" t="n">
+        <v>53</v>
+      </c>
+      <c r="C274" s="34" t="inlineStr">
+        <is>
+          <t>SEND_FLAG_MDI</t>
+        </is>
+      </c>
+      <c r="D274" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E274" s="34" t="inlineStr"/>
+      <c r="F274" s="34" t="inlineStr"/>
+      <c r="G274" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H274" s="34" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B275" s="33" t="n">
+        <v>54</v>
+      </c>
+      <c r="C275" s="34" t="inlineStr">
+        <is>
+          <t>SEND_DATE_MDI</t>
+        </is>
+      </c>
+      <c r="D275" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E275" s="34" t="inlineStr"/>
+      <c r="F275" s="34" t="inlineStr"/>
+      <c r="G275" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H275" s="34" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B276" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C276" s="34" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="D276" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(8+)</t>
+        </is>
+      </c>
+      <c r="E276" s="34" t="inlineStr"/>
+      <c r="F276" s="34" t="inlineStr"/>
+      <c r="G276" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H276" s="34" t="inlineStr">
+        <is>
+          <t>PO number</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B277" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C277" s="34" t="inlineStr">
+        <is>
+          <t>PO_ITEM</t>
+        </is>
+      </c>
+      <c r="D277" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(4+)</t>
+        </is>
+      </c>
+      <c r="E277" s="34" t="inlineStr"/>
+      <c r="F277" s="34" t="inlineStr"/>
+      <c r="G277" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H277" s="34" t="inlineStr">
+        <is>
+          <t>Item of the PO (can differ from MANIFEST_ITEM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B278" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C278" s="34" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="D278" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(10+)</t>
+        </is>
+      </c>
+      <c r="E278" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F278" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G278" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H278" s="34" t="inlineStr">
+        <is>
+          <t>Manifest number (TB_R_PRA_DAILY_ORDER_MANIFEST)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B279" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C279" s="34" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="D279" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(4+)</t>
+        </is>
+      </c>
+      <c r="E279" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F279" s="34" t="inlineStr"/>
+      <c r="G279" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H279" s="34" t="inlineStr">
+        <is>
+          <t>Item of the manifest (0001 ...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B280" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C280" s="34" t="inlineStr">
+        <is>
+          <t>ORI_PART_NO</t>
+        </is>
+      </c>
+      <c r="D280" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(12+)</t>
+        </is>
+      </c>
+      <c r="E280" s="34" t="inlineStr"/>
+      <c r="F280" s="34" t="inlineStr"/>
+      <c r="G280" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H280" s="34" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B281" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="C281" s="34" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="D281" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(12+)</t>
+        </is>
+      </c>
+      <c r="E281" s="34" t="inlineStr"/>
+      <c r="F281" s="34" t="inlineStr"/>
+      <c r="G281" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H281" s="34" t="inlineStr">
+        <is>
+          <t>Part number</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B282" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C282" s="34" t="inlineStr">
+        <is>
+          <t>PART_NAME</t>
+        </is>
+      </c>
+      <c r="D282" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(40+)</t>
+        </is>
+      </c>
+      <c r="E282" s="34" t="inlineStr"/>
+      <c r="F282" s="34" t="inlineStr"/>
+      <c r="G282" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H282" s="34" t="inlineStr">
+        <is>
+          <t>Part name</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B283" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C283" s="34" t="inlineStr">
+        <is>
+          <t>QTY_PER_CONTAINER</t>
+        </is>
+      </c>
+      <c r="D283" s="34" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="E283" s="34" t="inlineStr"/>
+      <c r="F283" s="34" t="inlineStr"/>
+      <c r="G283" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H283" s="34" t="inlineStr">
+        <is>
+          <t>Qty per container of the PO (mostly 1; not the crossdock pcs/case)</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B284" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="C284" s="34" t="inlineStr">
+        <is>
+          <t>ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="D284" s="34" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="E284" s="34" t="inlineStr"/>
+      <c r="F284" s="34" t="inlineStr"/>
+      <c r="G284" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H284" s="34" t="inlineStr">
+        <is>
+          <t>PO qty (pcs) — basis of the open qty for XD09 (ORDER_QTY - MAPPED_QTY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B285" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="C285" s="34" t="inlineStr">
+        <is>
+          <t>ORDER_PLAN_QTY_LOT</t>
+        </is>
+      </c>
+      <c r="D285" s="34" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="E285" s="34" t="inlineStr"/>
+      <c r="F285" s="34" t="inlineStr"/>
+      <c r="G285" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H285" s="34" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B286" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="C286" s="34" t="inlineStr">
+        <is>
+          <t>DELIVERY_QTY</t>
+        </is>
+      </c>
+      <c r="D286" s="34" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="E286" s="34" t="inlineStr"/>
+      <c r="F286" s="34" t="inlineStr"/>
+      <c r="G286" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H286" s="34" t="inlineStr">
+        <is>
+          <t>Delivered qty</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B287" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C287" s="34" t="inlineStr">
+        <is>
+          <t>RECEIVED_QTY</t>
+        </is>
+      </c>
+      <c r="D287" s="34" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="E287" s="34" t="inlineStr"/>
+      <c r="F287" s="34" t="inlineStr"/>
+      <c r="G287" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H287" s="34" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B288" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="C288" s="34" t="inlineStr">
+        <is>
+          <t>REMAIN_QTY</t>
+        </is>
+      </c>
+      <c r="D288" s="34" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="E288" s="34" t="inlineStr"/>
+      <c r="F288" s="34" t="inlineStr"/>
+      <c r="G288" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H288" s="34" t="inlineStr">
+        <is>
+          <t>Remaining qty</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B289" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="C289" s="34" t="inlineStr">
+        <is>
+          <t>DELIVERY_DT</t>
+        </is>
+      </c>
+      <c r="D289" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E289" s="34" t="inlineStr"/>
+      <c r="F289" s="34" t="inlineStr"/>
+      <c r="G289" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H289" s="34" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B290" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="C290" s="34" t="inlineStr">
+        <is>
+          <t>RECEIVED_DT</t>
+        </is>
+      </c>
+      <c r="D290" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E290" s="34" t="inlineStr"/>
+      <c r="F290" s="34" t="inlineStr"/>
+      <c r="G290" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H290" s="34" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B291" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="C291" s="34" t="inlineStr">
+        <is>
+          <t>KANBAN_NO</t>
+        </is>
+      </c>
+      <c r="D291" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(4+)</t>
+        </is>
+      </c>
+      <c r="E291" s="34" t="inlineStr"/>
+      <c r="F291" s="34" t="inlineStr"/>
+      <c r="G291" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H291" s="34" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B292" s="33" t="n">
+        <v>17</v>
+      </c>
+      <c r="C292" s="34" t="inlineStr">
+        <is>
+          <t>PART_BARCODE</t>
+        </is>
+      </c>
+      <c r="D292" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(13+)</t>
+        </is>
+      </c>
+      <c r="E292" s="34" t="inlineStr"/>
+      <c r="F292" s="34" t="inlineStr"/>
+      <c r="G292" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H292" s="34" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B293" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="C293" s="34" t="inlineStr">
+        <is>
+          <t>RECEIVE_PLANT_NAME</t>
+        </is>
+      </c>
+      <c r="D293" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(8+)</t>
+        </is>
+      </c>
+      <c r="E293" s="34" t="inlineStr"/>
+      <c r="F293" s="34" t="inlineStr"/>
+      <c r="G293" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H293" s="34" t="inlineStr">
+        <is>
+          <t>values: SUNTER 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B294" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="C294" s="34" t="inlineStr">
+        <is>
+          <t>SUPPLIER_INFO1</t>
+        </is>
+      </c>
+      <c r="D294" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E294" s="34" t="inlineStr"/>
+      <c r="F294" s="34" t="inlineStr"/>
+      <c r="G294" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H294" s="34" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B295" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="C295" s="34" t="inlineStr">
+        <is>
+          <t>SUPPLIER_INFO2</t>
+        </is>
+      </c>
+      <c r="D295" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E295" s="34" t="inlineStr"/>
+      <c r="F295" s="34" t="inlineStr"/>
+      <c r="G295" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H295" s="34" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B296" s="33" t="n">
+        <v>21</v>
+      </c>
+      <c r="C296" s="34" t="inlineStr">
+        <is>
+          <t>SUPPLIER_INFO3</t>
+        </is>
+      </c>
+      <c r="D296" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E296" s="34" t="inlineStr"/>
+      <c r="F296" s="34" t="inlineStr"/>
+      <c r="G296" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H296" s="34" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B297" s="33" t="n">
+        <v>22</v>
+      </c>
+      <c r="C297" s="34" t="inlineStr">
+        <is>
+          <t>IMPORTIR_INFO</t>
+        </is>
+      </c>
+      <c r="D297" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E297" s="34" t="inlineStr"/>
+      <c r="F297" s="34" t="inlineStr"/>
+      <c r="G297" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H297" s="34" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B298" s="33" t="n">
+        <v>23</v>
+      </c>
+      <c r="C298" s="34" t="inlineStr">
+        <is>
+          <t>IMPORTIR_INFO2</t>
+        </is>
+      </c>
+      <c r="D298" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E298" s="34" t="inlineStr"/>
+      <c r="F298" s="34" t="inlineStr"/>
+      <c r="G298" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H298" s="34" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B299" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="C299" s="34" t="inlineStr">
+        <is>
+          <t>IMPORTIR_INFO3</t>
+        </is>
+      </c>
+      <c r="D299" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E299" s="34" t="inlineStr"/>
+      <c r="F299" s="34" t="inlineStr"/>
+      <c r="G299" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H299" s="34" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B300" s="33" t="n">
+        <v>25</v>
+      </c>
+      <c r="C300" s="34" t="inlineStr">
+        <is>
+          <t>IMPORTIR_INFO4</t>
+        </is>
+      </c>
+      <c r="D300" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E300" s="34" t="inlineStr"/>
+      <c r="F300" s="34" t="inlineStr"/>
+      <c r="G300" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H300" s="34" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B301" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="C301" s="34" t="inlineStr">
+        <is>
+          <t>MOD_DST_CD</t>
+        </is>
+      </c>
+      <c r="D301" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E301" s="34" t="inlineStr"/>
+      <c r="F301" s="34" t="inlineStr"/>
+      <c r="G301" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H301" s="34" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B302" s="33" t="n">
+        <v>27</v>
+      </c>
+      <c r="C302" s="34" t="inlineStr">
+        <is>
+          <t>PLN_PCK_DT</t>
+        </is>
+      </c>
+      <c r="D302" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E302" s="34" t="inlineStr"/>
+      <c r="F302" s="34" t="inlineStr"/>
+      <c r="G302" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H302" s="34" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B303" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="C303" s="34" t="inlineStr">
+        <is>
+          <t>PART_ADDRESS</t>
+        </is>
+      </c>
+      <c r="D303" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(8+)</t>
+        </is>
+      </c>
+      <c r="E303" s="34" t="inlineStr"/>
+      <c r="F303" s="34" t="inlineStr"/>
+      <c r="G303" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H303" s="34" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B304" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="C304" s="34" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="D304" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(1+)</t>
+        </is>
+      </c>
+      <c r="E304" s="34" t="inlineStr"/>
+      <c r="F304" s="34" t="inlineStr"/>
+      <c r="G304" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H304" s="34" t="inlineStr">
+        <is>
+          <t>Status ('0' in the sample); values: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B305" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="C305" s="34" t="inlineStr">
+        <is>
+          <t>CREATED_BY</t>
+        </is>
+      </c>
+      <c r="D305" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E305" s="34" t="inlineStr"/>
+      <c r="F305" s="34" t="inlineStr"/>
+      <c r="G305" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H305" s="34" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B306" s="33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C306" s="34" t="inlineStr">
+        <is>
+          <t>CREATED_DT</t>
+        </is>
+      </c>
+      <c r="D306" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E306" s="34" t="inlineStr"/>
+      <c r="F306" s="34" t="inlineStr"/>
+      <c r="G306" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H306" s="34" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B307" s="33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C307" s="34" t="inlineStr">
+        <is>
+          <t>CHANGED_BY</t>
+        </is>
+      </c>
+      <c r="D307" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E307" s="34" t="inlineStr"/>
+      <c r="F307" s="34" t="inlineStr"/>
+      <c r="G307" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H307" s="34" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B308" s="33" t="n">
+        <v>33</v>
+      </c>
+      <c r="C308" s="34" t="inlineStr">
+        <is>
+          <t>CHANGED_DT</t>
+        </is>
+      </c>
+      <c r="D308" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E308" s="34" t="inlineStr"/>
+      <c r="F308" s="34" t="inlineStr"/>
+      <c r="G308" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H308" s="34" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B309" s="33" t="n">
+        <v>34</v>
+      </c>
+      <c r="C309" s="34" t="inlineStr">
+        <is>
+          <t>DOCK_CD</t>
+        </is>
+      </c>
+      <c r="D309" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(2+)</t>
+        </is>
+      </c>
+      <c r="E309" s="34" t="inlineStr"/>
+      <c r="F309" s="34" t="inlineStr"/>
+      <c r="G309" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H309" s="34" t="inlineStr">
+        <is>
+          <t>Receiving dock; values: S1, S2, S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B310" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="C310" s="34" t="inlineStr">
+        <is>
+          <t>CANCEL_QTY</t>
+        </is>
+      </c>
+      <c r="D310" s="34" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="E310" s="34" t="inlineStr"/>
+      <c r="F310" s="34" t="inlineStr"/>
+      <c r="G310" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H310" s="34" t="inlineStr">
+        <is>
+          <t>values: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B311" s="33" t="n">
+        <v>36</v>
+      </c>
+      <c r="C311" s="34" t="inlineStr">
+        <is>
+          <t>CANCEL_DT</t>
+        </is>
+      </c>
+      <c r="D311" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E311" s="34" t="inlineStr"/>
+      <c r="F311" s="34" t="inlineStr"/>
+      <c r="G311" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H311" s="34" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B312" s="33" t="n">
+        <v>37</v>
+      </c>
+      <c r="C312" s="34" t="inlineStr">
+        <is>
+          <t>SEND_FLAG_MDI</t>
+        </is>
+      </c>
+      <c r="D312" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E312" s="34" t="inlineStr"/>
+      <c r="F312" s="34" t="inlineStr"/>
+      <c r="G312" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H312" s="34" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B313" s="33" t="n">
+        <v>38</v>
+      </c>
+      <c r="C313" s="34" t="inlineStr">
+        <is>
+          <t>SEND_DATE_MDI</t>
+        </is>
+      </c>
+      <c r="D313" s="34" t="inlineStr">
+        <is>
+          <t>? (no data)</t>
+        </is>
+      </c>
+      <c r="E313" s="34" t="inlineStr"/>
+      <c r="F313" s="34" t="inlineStr"/>
+      <c r="G313" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H313" s="34" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="B314" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C314" s="34" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="D314" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="E314" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F314" s="34" t="inlineStr"/>
+      <c r="G314" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H314" s="34" t="inlineStr">
+        <is>
+          <t>PO number (Pra Daily Order Manifest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="B315" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C315" s="34" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="D315" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="E315" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F315" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G315" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H315" s="34" t="inlineStr">
+        <is>
+          <t>Manifest number</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="B316" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C316" s="34" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="D316" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="E316" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F316" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G316" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H316" s="34" t="inlineStr">
+        <is>
+          <t>Manifest item number (Pra Daily Order Part) (renamed from MANIFEST_ITEM_NO of the UISS to the name of the existing Pra Daily Order column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="B317" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C317" s="34" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="D317" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(15)</t>
+        </is>
+      </c>
+      <c r="E317" s="34" t="inlineStr"/>
+      <c r="F317" s="34" t="inlineStr"/>
+      <c r="G317" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H317" s="34" t="inlineStr">
+        <is>
+          <t>Part number</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="B318" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C318" s="34" t="inlineStr">
+        <is>
+          <t>SUPPLIER_CD</t>
+        </is>
+      </c>
+      <c r="D318" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="E318" s="34" t="inlineStr"/>
+      <c r="F318" s="34" t="inlineStr"/>
+      <c r="G318" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H318" s="34" t="inlineStr">
+        <is>
+          <t>Supplier code</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="B319" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="C319" s="34" t="inlineStr">
+        <is>
+          <t>SUPPLIER_PLANT</t>
+        </is>
+      </c>
+      <c r="D319" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="E319" s="34" t="inlineStr"/>
+      <c r="F319" s="34" t="inlineStr"/>
+      <c r="G319" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H319" s="34" t="inlineStr">
+        <is>
+          <t>Supplier plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="B320" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C320" s="34" t="inlineStr">
+        <is>
+          <t>ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="D320" s="34" t="inlineStr">
+        <is>
+          <t>NUMBER(TBD)</t>
+        </is>
+      </c>
+      <c r="E320" s="34" t="inlineStr"/>
+      <c r="F320" s="34" t="inlineStr"/>
+      <c r="G320" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H320" s="34" t="inlineStr">
+        <is>
+          <t>PO qty of the part (renamed from PO_ORDER_QTY of the UISS to the name of the existing Pra Daily Order column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="B321" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C321" s="34" t="inlineStr">
+        <is>
+          <t>MAPPED_QTY</t>
+        </is>
+      </c>
+      <c r="D321" s="34" t="inlineStr">
+        <is>
+          <t>NUMBER(TBD)</t>
+        </is>
+      </c>
+      <c r="E321" s="34" t="inlineStr"/>
+      <c r="F321" s="34" t="inlineStr"/>
+      <c r="G321" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H321" s="34" t="inlineStr">
+        <is>
+          <t>Qty already mapped to customer orders by [Create ASN]; open qty = PO_ORDER_QTY - MAPPED_QTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="B322" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="C322" s="34" t="inlineStr">
+        <is>
+          <t>CREATED_BY</t>
+        </is>
+      </c>
+      <c r="D322" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="E322" s="34" t="inlineStr"/>
+      <c r="F322" s="34" t="inlineStr"/>
+      <c r="G322" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H322" s="34" t="inlineStr">
+        <is>
+          <t>User who created the record</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="B323" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="C323" s="34" t="inlineStr">
+        <is>
+          <t>CREATED_DT</t>
+        </is>
+      </c>
+      <c r="D323" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E323" s="34" t="inlineStr"/>
+      <c r="F323" s="34" t="inlineStr"/>
+      <c r="G323" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H323" s="34" t="inlineStr">
+        <is>
+          <t>Created date and time</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="B324" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="C324" s="34" t="inlineStr">
+        <is>
+          <t>CHANGED_BY</t>
+        </is>
+      </c>
+      <c r="D324" s="34" t="inlineStr">
+        <is>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="E324" s="34" t="inlineStr"/>
+      <c r="F324" s="34" t="inlineStr"/>
+      <c r="G324" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H324" s="34" t="inlineStr">
+        <is>
+          <t>User who last changed the record</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="B325" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C325" s="34" t="inlineStr">
+        <is>
+          <t>CHANGED_DT</t>
+        </is>
+      </c>
+      <c r="D325" s="34" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E325" s="34" t="inlineStr"/>
+      <c r="F325" s="34" t="inlineStr"/>
+      <c r="G325" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H325" s="34" t="inlineStr">
+        <is>
+          <t>Last changed date and time</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B326" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C326" s="34" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO / ASN_NO</t>
+        </is>
+      </c>
+      <c r="D326" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E326" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F326" s="34" t="inlineStr"/>
+      <c r="G326" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H326" s="34" t="inlineStr">
+        <is>
+          <t>ASN number (auto generated as today, existing numbering)</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B327" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C327" s="34" t="inlineStr">
+        <is>
+          <t>SUPPLIER_CD</t>
+        </is>
+      </c>
+      <c r="D327" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E327" s="34" t="inlineStr"/>
+      <c r="F327" s="34" t="inlineStr"/>
+      <c r="G327" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H327" s="34" t="inlineStr">
+        <is>
+          <t>Supplier code</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B328" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C328" s="34" t="inlineStr">
+        <is>
+          <t>SUPPLIER_PLANT</t>
+        </is>
+      </c>
+      <c r="D328" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E328" s="34" t="inlineStr"/>
+      <c r="F328" s="34" t="inlineStr"/>
+      <c r="G328" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H328" s="34" t="inlineStr">
+        <is>
+          <t>Supplier plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B329" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C329" s="34" t="inlineStr">
+        <is>
+          <t>DELIVERY_DT</t>
+        </is>
+      </c>
+      <c r="D329" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E329" s="34" t="inlineStr"/>
+      <c r="F329" s="34" t="inlineStr"/>
+      <c r="G329" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H329" s="34" t="inlineStr">
+        <is>
+          <t>Delivery Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B330" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C330" s="34" t="inlineStr">
+        <is>
+          <t>RIT / ROUTE</t>
+        </is>
+      </c>
+      <c r="D330" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E330" s="34" t="inlineStr"/>
+      <c r="F330" s="34" t="inlineStr"/>
+      <c r="G330" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H330" s="34" t="inlineStr">
+        <is>
+          <t>Rit and route (route master, existing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B331" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="C331" s="34" t="inlineStr">
+        <is>
+          <t>TOTAL_CASE / TOTAL_QTY</t>
+        </is>
+      </c>
+      <c r="D331" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E331" s="34" t="inlineStr"/>
+      <c r="F331" s="34" t="inlineStr"/>
+      <c r="G331" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H331" s="34" t="inlineStr">
+        <is>
+          <t>Number of cases / Delivery Qty</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B332" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C332" s="34" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="D332" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E332" s="34" t="inlineStr"/>
+      <c r="F332" s="34" t="inlineStr"/>
+      <c r="G332" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H332" s="34" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+        </is>
+      </c>
+      <c r="B333" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C333" s="34" t="inlineStr">
+        <is>
+          <t>CREATED_BY / CREATED_DT</t>
+        </is>
+      </c>
+      <c r="D333" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E333" s="34" t="inlineStr"/>
+      <c r="F333" s="34" t="inlineStr"/>
+      <c r="G333" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H333" s="34" t="inlineStr">
+        <is>
           <t>User and date-time of submit</t>
         </is>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B334" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C334" s="34" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO / ASN_NO</t>
+        </is>
+      </c>
+      <c r="D334" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E334" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F334" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G334" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H334" s="34" t="inlineStr">
+        <is>
+          <t>ASN number</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B335" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C335" s="34" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="D335" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E335" s="34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F335" s="34" t="inlineStr"/>
+      <c r="G335" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H335" s="34" t="inlineStr">
+        <is>
+          <t>Case number, auto generated with the existing last sequence</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B336" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C336" s="34" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="D336" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E336" s="34" t="inlineStr"/>
+      <c r="F336" s="34" t="inlineStr"/>
+      <c r="G336" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H336" s="34" t="inlineStr">
+        <is>
+          <t>Part number of the case</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B337" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C337" s="34" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="D337" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E337" s="34" t="inlineStr"/>
+      <c r="F337" s="34" t="inlineStr"/>
+      <c r="G337" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H337" s="34" t="inlineStr">
+        <is>
+          <t>Destination of the case</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B338" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C338" s="34" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="D338" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E338" s="34" t="inlineStr"/>
+      <c r="F338" s="34" t="inlineStr"/>
+      <c r="G338" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H338" s="34" t="inlineStr">
+        <is>
+          <t>Qty of the case</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B339" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="C339" s="34" t="inlineStr">
+        <is>
+          <t>PO_NO / MANIFEST_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="D339" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E339" s="34" t="inlineStr"/>
+      <c r="F339" s="34" t="inlineStr"/>
+      <c r="G339" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H339" s="34" t="inlineStr">
+        <is>
+          <t>PO reference of the Pra Daily Order</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="34" t="inlineStr">
+        <is>
+          <t>TB_R_DAILY_ORDER_PART</t>
+        </is>
+      </c>
+      <c r="B340" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C340" s="34" t="inlineStr">
+        <is>
+          <t>CREATED_BY / CREATED_DT</t>
+        </is>
+      </c>
+      <c r="D340" s="34" t="inlineStr">
+        <is>
+          <t>existing</t>
+        </is>
+      </c>
+      <c r="E340" s="34" t="inlineStr"/>
+      <c r="F340" s="34" t="inlineStr"/>
+      <c r="G340" s="34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H340" s="34" t="inlineStr">
+        <is>
+          <t>User and date-time of submit</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:H259"/>
+  <autoFilter ref="A3:H340"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -18137,7 +20698,7 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>Written by: Existing daily order (supplier PO)</t>
+          <t>Written by: Existing daily order (supplier PO per manifest); CROSS_DOCK_FLAG X = crossdock manifest</t>
         </is>
       </c>
     </row>
@@ -18164,19 +20725,64 @@
       </c>
       <c r="E79" s="38" t="inlineStr">
         <is>
-          <t>PO_ORDER_DT</t>
+          <t>PO_DT</t>
+        </is>
+      </c>
+      <c r="F79" s="38" t="inlineStr">
+        <is>
+          <t>ORDER_TYPE</t>
+        </is>
+      </c>
+      <c r="G79" s="38" t="inlineStr">
+        <is>
+          <t>CROSS_DOCK_FLAG</t>
+        </is>
+      </c>
+      <c r="H79" s="38" t="inlineStr">
+        <is>
+          <t>DOCK_CD</t>
+        </is>
+      </c>
+      <c r="I79" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL_ITEM</t>
+        </is>
+      </c>
+      <c r="J79" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL_QTY</t>
+        </is>
+      </c>
+      <c r="K79" s="38" t="inlineStr">
+        <is>
+          <t>DELIVERY_DT</t>
+        </is>
+      </c>
+      <c r="L79" s="38" t="inlineStr">
+        <is>
+          <t>SUB_ROUTE_CD</t>
+        </is>
+      </c>
+      <c r="M79" s="38" t="inlineStr">
+        <is>
+          <t>SUB_ROUTE_SEQ</t>
+        </is>
+      </c>
+      <c r="N79" s="38" t="inlineStr">
+        <is>
+          <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="34" t="inlineStr">
         <is>
-          <t>M500</t>
+          <t>3126035901</t>
         </is>
       </c>
       <c r="B80" s="34" t="inlineStr">
         <is>
-          <t>PO-X1</t>
+          <t>T0409001</t>
         </is>
       </c>
       <c r="C80" s="34" t="inlineStr">
@@ -18192,18 +20798,59 @@
       <c r="E80" s="34" t="inlineStr">
         <is>
           <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="F80" s="34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G80" s="34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="I80" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="K80" s="34" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L80" s="34" t="inlineStr">
+        <is>
+          <t>SD01</t>
+        </is>
+      </c>
+      <c r="M80" s="34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N80" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="34" t="inlineStr">
         <is>
-          <t>M501</t>
+          <t>3126035902</t>
         </is>
       </c>
       <c r="B81" s="34" t="inlineStr">
         <is>
-          <t>PO-X2</t>
+          <t>T0409002</t>
         </is>
       </c>
       <c r="C81" s="34" t="inlineStr">
@@ -18219,18 +20866,59 @@
       <c r="E81" s="34" t="inlineStr">
         <is>
           <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="F81" s="34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G81" s="34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="I81" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="K81" s="34" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L81" s="34" t="inlineStr">
+        <is>
+          <t>SD01</t>
+        </is>
+      </c>
+      <c r="M81" s="34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N81" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="34" t="inlineStr">
         <is>
-          <t>M502</t>
+          <t>3126035903</t>
         </is>
       </c>
       <c r="B82" s="34" t="inlineStr">
         <is>
-          <t>PO-Y1</t>
+          <t>T0409003</t>
         </is>
       </c>
       <c r="C82" s="34" t="inlineStr">
@@ -18246,6 +20934,47 @@
       <c r="E82" s="34" t="inlineStr">
         <is>
           <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="F82" s="34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G82" s="34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="I82" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K82" s="34" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L82" s="34" t="inlineStr">
+        <is>
+          <t>SD01</t>
+        </is>
+      </c>
+      <c r="M82" s="34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N82" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -18257,7 +20986,7 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>Written by: Existing daily order (supplier PO line)</t>
+          <t>Written by: Existing daily order (one row per manifest item)</t>
         </is>
       </c>
     </row>
@@ -18269,7 +20998,7 @@
       </c>
       <c r="B85" s="38" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="C85" s="38" t="inlineStr">
@@ -18279,107 +21008,209 @@
       </c>
       <c r="D85" s="38" t="inlineStr">
         <is>
+          <t>PO_ITEM</t>
+        </is>
+      </c>
+      <c r="E85" s="38" t="inlineStr">
+        <is>
           <t>PART_NO</t>
         </is>
       </c>
-      <c r="E85" s="38" t="inlineStr">
-        <is>
-          <t>PO_ORDER_QTY</t>
-        </is>
-      </c>
       <c r="F85" s="38" t="inlineStr">
         <is>
-          <t>CROSSDOCK_FLAG</t>
+          <t>PART_NAME</t>
+        </is>
+      </c>
+      <c r="G85" s="38" t="inlineStr">
+        <is>
+          <t>QTY_PER_CONTAINER</t>
+        </is>
+      </c>
+      <c r="H85" s="38" t="inlineStr">
+        <is>
+          <t>ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="I85" s="38" t="inlineStr">
+        <is>
+          <t>DELIVERY_QTY</t>
+        </is>
+      </c>
+      <c r="J85" s="38" t="inlineStr">
+        <is>
+          <t>REMAIN_QTY</t>
+        </is>
+      </c>
+      <c r="K85" s="38" t="inlineStr">
+        <is>
+          <t>DOCK_CD</t>
+        </is>
+      </c>
+      <c r="L85" s="38" t="inlineStr">
+        <is>
+          <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="34" t="inlineStr">
         <is>
-          <t>M500</t>
+          <t>3126035901</t>
         </is>
       </c>
       <c r="B86" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="C86" s="34" t="inlineStr">
         <is>
-          <t>PO-X1</t>
+          <t>T0409001</t>
         </is>
       </c>
       <c r="D86" s="34" t="inlineStr">
         <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E86" s="34" t="inlineStr">
+        <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="E86" s="33" t="n">
+      <c r="F86" s="34" t="inlineStr">
+        <is>
+          <t>DUMMY PART X</t>
+        </is>
+      </c>
+      <c r="G86" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="F86" s="34" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="I86" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="K86" s="34" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="L86" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="34" t="inlineStr">
         <is>
-          <t>M501</t>
+          <t>3126035902</t>
         </is>
       </c>
       <c r="B87" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="C87" s="34" t="inlineStr">
         <is>
-          <t>PO-X2</t>
+          <t>T0409002</t>
         </is>
       </c>
       <c r="D87" s="34" t="inlineStr">
         <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E87" s="34" t="inlineStr">
+        <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="E87" s="33" t="n">
+      <c r="F87" s="34" t="inlineStr">
+        <is>
+          <t>DUMMY PART X</t>
+        </is>
+      </c>
+      <c r="G87" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="F87" s="34" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="I87" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="K87" s="34" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="L87" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="34" t="inlineStr">
         <is>
-          <t>M502</t>
+          <t>3126035903</t>
         </is>
       </c>
       <c r="B88" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="C88" s="34" t="inlineStr">
         <is>
-          <t>PO-Y1</t>
+          <t>T0409003</t>
         </is>
       </c>
       <c r="D88" s="34" t="inlineStr">
         <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E88" s="34" t="inlineStr">
+        <is>
           <t>PART-Y</t>
         </is>
       </c>
-      <c r="E88" s="33" t="n">
+      <c r="F88" s="34" t="inlineStr">
+        <is>
+          <t>DUMMY PART Y</t>
+        </is>
+      </c>
+      <c r="G88" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="F88" s="34" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="I88" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K88" s="34" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="L88" s="34" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -18448,7 +21279,7 @@
       </c>
       <c r="K91" s="39" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="L91" s="39" t="inlineStr">
@@ -18494,17 +21325,17 @@
       </c>
       <c r="I92" s="34" t="inlineStr">
         <is>
-          <t>PO-X1</t>
+          <t>T0409001</t>
         </is>
       </c>
       <c r="J92" s="34" t="inlineStr">
         <is>
-          <t>M500</t>
+          <t>3126035901</t>
         </is>
       </c>
       <c r="K92" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="L92" s="34" t="inlineStr">
@@ -18550,17 +21381,17 @@
       </c>
       <c r="I93" s="34" t="inlineStr">
         <is>
-          <t>PO-X1</t>
+          <t>T0409001</t>
         </is>
       </c>
       <c r="J93" s="34" t="inlineStr">
         <is>
-          <t>M500</t>
+          <t>3126035901</t>
         </is>
       </c>
       <c r="K93" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="L93" s="34" t="inlineStr">
@@ -18606,17 +21437,17 @@
       </c>
       <c r="I94" s="34" t="inlineStr">
         <is>
-          <t>PO-X2</t>
+          <t>T0409002</t>
         </is>
       </c>
       <c r="J94" s="34" t="inlineStr">
         <is>
-          <t>M501</t>
+          <t>3126035902</t>
         </is>
       </c>
       <c r="K94" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="L94" s="34" t="inlineStr">
@@ -18662,17 +21493,17 @@
       </c>
       <c r="I95" s="34" t="inlineStr">
         <is>
-          <t>PO-X2</t>
+          <t>T0409002</t>
         </is>
       </c>
       <c r="J95" s="34" t="inlineStr">
         <is>
-          <t>M501</t>
+          <t>3126035902</t>
         </is>
       </c>
       <c r="K95" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="L95" s="34" t="inlineStr">
@@ -18718,17 +21549,17 @@
       </c>
       <c r="I96" s="34" t="inlineStr">
         <is>
-          <t>PO-X2</t>
+          <t>T0409002</t>
         </is>
       </c>
       <c r="J96" s="34" t="inlineStr">
         <is>
-          <t>M501</t>
+          <t>3126035902</t>
         </is>
       </c>
       <c r="K96" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="L96" s="34" t="inlineStr">
@@ -18774,17 +21605,17 @@
       </c>
       <c r="I97" s="34" t="inlineStr">
         <is>
-          <t>PO-Y1</t>
+          <t>T0409003</t>
         </is>
       </c>
       <c r="J97" s="34" t="inlineStr">
         <is>
-          <t>M502</t>
+          <t>3126035903</t>
         </is>
       </c>
       <c r="K97" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="L97" s="34" t="inlineStr">
@@ -18873,7 +21704,7 @@
       </c>
       <c r="N100" s="32" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="O100" s="32" t="inlineStr">
@@ -18952,17 +21783,17 @@
       </c>
       <c r="L101" s="34" t="inlineStr">
         <is>
-          <t>PO-X1</t>
+          <t>T0409001</t>
         </is>
       </c>
       <c r="M101" s="34" t="inlineStr">
         <is>
-          <t>M500</t>
+          <t>3126035901</t>
         </is>
       </c>
       <c r="N101" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="O101" s="34" t="inlineStr">
@@ -19041,17 +21872,17 @@
       </c>
       <c r="L102" s="34" t="inlineStr">
         <is>
-          <t>PO-X1</t>
+          <t>T0409001</t>
         </is>
       </c>
       <c r="M102" s="34" t="inlineStr">
         <is>
-          <t>M500</t>
+          <t>3126035901</t>
         </is>
       </c>
       <c r="N102" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="O102" s="34" t="inlineStr">
@@ -19130,17 +21961,17 @@
       </c>
       <c r="L103" s="34" t="inlineStr">
         <is>
-          <t>PO-X1</t>
+          <t>T0409001</t>
         </is>
       </c>
       <c r="M103" s="34" t="inlineStr">
         <is>
-          <t>M500</t>
+          <t>3126035901</t>
         </is>
       </c>
       <c r="N103" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="O103" s="34" t="inlineStr">
@@ -19219,17 +22050,17 @@
       </c>
       <c r="L104" s="34" t="inlineStr">
         <is>
-          <t>PO-X2</t>
+          <t>T0409002</t>
         </is>
       </c>
       <c r="M104" s="34" t="inlineStr">
         <is>
-          <t>M501</t>
+          <t>3126035902</t>
         </is>
       </c>
       <c r="N104" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="O104" s="34" t="inlineStr">
@@ -19308,17 +22139,17 @@
       </c>
       <c r="L105" s="34" t="inlineStr">
         <is>
-          <t>PO-X2</t>
+          <t>T0409002</t>
         </is>
       </c>
       <c r="M105" s="34" t="inlineStr">
         <is>
-          <t>M501</t>
+          <t>3126035902</t>
         </is>
       </c>
       <c r="N105" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="O105" s="34" t="inlineStr">
@@ -19397,17 +22228,17 @@
       </c>
       <c r="L106" s="34" t="inlineStr">
         <is>
-          <t>PO-X2</t>
+          <t>T0409002</t>
         </is>
       </c>
       <c r="M106" s="34" t="inlineStr">
         <is>
-          <t>M501</t>
+          <t>3126035902</t>
         </is>
       </c>
       <c r="N106" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="O106" s="34" t="inlineStr">
@@ -19486,17 +22317,17 @@
       </c>
       <c r="L107" s="34" t="inlineStr">
         <is>
-          <t>PO-Y1</t>
+          <t>T0409003</t>
         </is>
       </c>
       <c r="M107" s="34" t="inlineStr">
         <is>
-          <t>M502</t>
+          <t>3126035903</t>
         </is>
       </c>
       <c r="N107" s="34" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="O107" s="34" t="inlineStr">
@@ -19550,7 +22381,7 @@
       </c>
       <c r="C110" s="32" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM_NO</t>
+          <t>MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="D110" s="32" t="inlineStr">
@@ -19570,7 +22401,7 @@
       </c>
       <c r="G110" s="32" t="inlineStr">
         <is>
-          <t>PO_ORDER_QTY</t>
+          <t>ORDER_QTY</t>
         </is>
       </c>
       <c r="H110" s="32" t="inlineStr">
@@ -19582,12 +22413,12 @@
     <row r="111">
       <c r="A111" s="34" t="inlineStr">
         <is>
-          <t>PO-X1</t>
+          <t>T0409001</t>
         </is>
       </c>
       <c r="B111" s="34" t="inlineStr">
         <is>
-          <t>M500</t>
+          <t>3126035901</t>
         </is>
       </c>
       <c r="C111" s="34" t="inlineStr">
@@ -19620,12 +22451,12 @@
     <row r="112">
       <c r="A112" s="34" t="inlineStr">
         <is>
-          <t>PO-X2</t>
+          <t>T0409002</t>
         </is>
       </c>
       <c r="B112" s="34" t="inlineStr">
         <is>
-          <t>M501</t>
+          <t>3126035902</t>
         </is>
       </c>
       <c r="C112" s="34" t="inlineStr">
@@ -19658,12 +22489,12 @@
     <row r="113">
       <c r="A113" s="34" t="inlineStr">
         <is>
-          <t>PO-Y1</t>
+          <t>T0409003</t>
         </is>
       </c>
       <c r="B113" s="34" t="inlineStr">
         <is>
-          <t>M502</t>
+          <t>3126035903</t>
         </is>
       </c>
       <c r="C113" s="34" t="inlineStr">
@@ -19849,7 +22680,7 @@
       </c>
       <c r="F121" s="34" t="inlineStr">
         <is>
-          <t>PO-X1 / 001</t>
+          <t>T0409001 / 0001</t>
         </is>
       </c>
     </row>
@@ -19879,7 +22710,7 @@
       </c>
       <c r="F122" s="34" t="inlineStr">
         <is>
-          <t>PO-X1 / 001</t>
+          <t>T0409001 / 0001</t>
         </is>
       </c>
     </row>
@@ -19909,7 +22740,7 @@
       </c>
       <c r="F123" s="34" t="inlineStr">
         <is>
-          <t>PO-X2 / 001</t>
+          <t>T0409002 / 0001</t>
         </is>
       </c>
     </row>
@@ -19939,7 +22770,7 @@
       </c>
       <c r="F124" s="34" t="inlineStr">
         <is>
-          <t>PO-X2 / 001</t>
+          <t>T0409002 / 0001</t>
         </is>
       </c>
     </row>
@@ -19969,7 +22800,7 @@
       </c>
       <c r="F125" s="34" t="inlineStr">
         <is>
-          <t>PO-Y1 / 001</t>
+          <t>T0409003 / 0001</t>
         </is>
       </c>
     </row>

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -4298,7 +4298,7 @@
       <c r="D3" s="4" t="n"/>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
       <c r="G3" s="6" t="n"/>
@@ -10053,7 +10053,7 @@
     <row r="2">
       <c r="A2" s="33" t="inlineStr">
         <is>
-          <t>BPF F4 · Functions: G-TOPAS, XD12, XD11, XD08</t>
+          <t>BPF F4 · Functions: G-System, XD12, XD11, XD08</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10067,7 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>• G-TOPAS cancels 6 pcs: the line is split into serial 0000001 (status 7, 6 pcs) and serial 0000002 (status 2, 6 pcs).</t>
+          <t>• G-System cancels 6 pcs: the line is split into serial 0000001 (status 7, 6 pcs) and serial 0000002 (status 2, 6 pcs).</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="D20" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="D35" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
@@ -11363,7 +11363,7 @@
       </c>
       <c r="D45" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
     <row r="2">
       <c r="A2" s="33" t="inlineStr">
         <is>
-          <t>BPF F4 / AB16 · Functions: G-TOPAS, XD12, XD11, Log Monitoring</t>
+          <t>BPF F4 / AB16 · Functions: G-System, XD12, XD11, Log Monitoring</t>
         </is>
       </c>
     </row>
@@ -11555,7 +11555,7 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>• G-TOPAS cancels the line although it is in an ASN (SOP not followed): status 2.</t>
+          <t>• G-System cancels the line although it is in an ASN (SOP not followed): status 2.</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="D15" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="M17" s="58" t="inlineStr">
         <is>
-          <t>Cancelled in G-TOPAS</t>
+          <t>Cancelled in G-System</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="D28" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="C4" s="32" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
       <c r="D4" s="32" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="D6" s="32" t="inlineStr">
         <is>
-          <t>Existing part master (MST-03); only PART_NAME is used (by PART_NO). Full structure: GTOPAS_SPS_DB_Structure_20240423 sheet MST-03.</t>
+          <t>Existing part master (MST-03); only PART_NAME is used (by PART_NO). Full structure: GSystem_SPS_DB_Structure_20240423 sheet MST-03.</t>
         </is>
       </c>
       <c r="E6" s="32" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="D11" s="32" t="inlineStr">
         <is>
-          <t>Dummy table (proposed): send status of the cross dock master per part and target system (XD06 GTOPAS, XD07 AP POLE). The real output is the interface data sent to the target (AP POLE: file by SFTP; G-TOPAS: existing interface). The overall Sync Status of the part stays in TB_M_PART_CANDIDATE.</t>
+          <t>Dummy table (proposed): send status of the cross dock master per part and target system (XD06 G-System, XD07 AP POLE). The real output is the interface data sent to the target (AP POLE: file by SFTP; G-System: existing interface). The overall Sync Status of the part stays in TB_M_PART_CANDIDATE.</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr">
@@ -12827,12 +12827,12 @@
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
         <is>
-          <t>Order control data, pre-order picking info (I/F H02-53, DVJO950) replicated from DB Surrounding by XD08 / XD12. Structure from the G-TOPAS I/F layout; physical names follow the existing table. Key (PK) = unique key of the I/F layout. NSP keeps the rows with status 7, 6 and 2 (insert / update); rows with status 6 / 2 are kept for tracking only (retention optional, TBC). CANCEL_STATUS is a new NSP column (proposed).</t>
+          <t>Order control data, pre-order picking info (I/F H02-53, DVJO950) replicated from DB Surrounding by XD08 / XD12. Structure from the G-System I/F layout; physical names follow the existing table. Key (PK) = unique key of the I/F layout. NSP keeps the rows with status 7, 6 and 2 (insert / update); rows with status 6 / 2 are kept for tracking only (retention optional, TBC). CANCEL_STATUS is a new NSP column (proposed).</t>
         </is>
       </c>
       <c r="E12" s="32" t="inlineStr">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>Existing Pra Daily Order manifest (supplier PO per manifest, 391 sample rows). MANIFEST_NO is unique; one PO_NO can have several manifests. CROSS_DOCK_FLAG is on the manifest. Columns from the data export (20-Oct), types from GTOPAS_SPS_DB_Structure_20240423.</t>
+          <t>Existing Pra Daily Order manifest (supplier PO per manifest, 391 sample rows). MANIFEST_NO is unique; one PO_NO can have several manifests. CROSS_DOCK_FLAG is on the manifest. Columns from the data export (20-Oct), types from GSystem_SPS_DB_Structure_20240423.</t>
         </is>
       </c>
       <c r="E16" s="32" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="D17" s="32" t="inlineStr">
         <is>
-          <t>Existing Pra Daily Order part (one row per manifest item, 2353 sample rows). Key MANIFEST_NO + MANIFEST_ITEM (also PO_NO + PO_ITEM is unique; PO_ITEM can differ from MANIFEST_ITEM). Columns from the data export (20-Oct), types from GTOPAS_SPS_DB_Structure_20240423.</t>
+          <t>Existing Pra Daily Order part (one row per manifest item, 2353 sample rows). Key MANIFEST_NO + MANIFEST_ITEM (also PO_NO + PO_ITEM is unique; PO_ITEM can differ from MANIFEST_ITEM). Columns from the data export (20-Oct), types from GSystem_SPS_DB_Structure_20240423.</t>
         </is>
       </c>
       <c r="E17" s="32" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="D19" s="32" t="inlineStr">
         <is>
-          <t>Existing ASN manifest (GTOPAS SPS DB structure TR-01). Submit ASN: one row per Pra Daily Order manifest of the cases, all with the same ASN_NO. Only the columns used are listed. Full structure: GTOPAS_SPS_DB_Structure_20240423 sheet TR-01.</t>
+          <t>Existing ASN manifest (G-System SPS DB structure TR-01). Submit ASN: one row per Pra Daily Order manifest of the cases, all with the same ASN_NO. Only the columns used are listed. Full structure: GSystem_SPS_DB_Structure_20240423 sheet TR-01.</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
-          <t>Existing ASN part (TR-02). Submit ASN: one row per manifest item and case (a case can hold several manifest items). Only the columns used are listed. Full structure: GTOPAS_SPS_DB_Structure_20240423 sheet TR-02.</t>
+          <t>Existing ASN part (TR-02). Submit ASN: one row per manifest item and case (a case can hold several manifest items). Only the columns used are listed. Full structure: GSystem_SPS_DB_Structure_20240423 sheet TR-02.</t>
         </is>
       </c>
       <c r="E20" s="32" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="D21" s="32" t="inlineStr">
         <is>
-          <t>Existing last sequence per supplier + plant (TR-06): the case number (case label) and the ASN number are auto generated from it and the new last sequence is saved here. Full structure: GTOPAS_SPS_DB_Structure_20240423 sheet TR-06.</t>
+          <t>Existing last sequence per supplier + plant (TR-06): the case number (case label) and the ASN number are auto generated from it and the new last sequence is saved here. Full structure: GSystem_SPS_DB_Structure_20240423 sheet TR-06.</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="G9" s="32" t="inlineStr">
         <is>
-          <t>Send status per target system (GTOPAS / APPOLE)</t>
+          <t>Send status per target system (G-System / APPOLE)</t>
         </is>
       </c>
     </row>
@@ -17849,7 +17849,7 @@
       </c>
       <c r="H120" s="32" t="inlineStr">
         <is>
-          <t>'GTOPAS' (XD06) / 'APPOLE' (XD07)</t>
+          <t>'G-System' (XD06) / 'APPOLE' (XD07)</t>
         </is>
       </c>
     </row>
@@ -17977,7 +17977,7 @@
       </c>
       <c r="H124" s="32" t="inlineStr">
         <is>
-          <t>Name of the interface file (AP POLE) or send ID (G-TOPAS)</t>
+          <t>Name of the interface file (AP POLE) or send ID (G-System)</t>
         </is>
       </c>
     </row>
@@ -29087,7 +29087,7 @@
       </c>
       <c r="F6" s="32" t="inlineStr">
         <is>
-          <t>G-TOPAS releases crossdock orders 14-Oct (status 7); the supplier POs of 15-Oct are crossdock manifests (CROSS_DOCK_FLAG X). Supplier searches delivery 16-Oct Rit 1: PART-X (VN 18 pcs = 3 cases, TH 6 = 1 case) and PART-Y (PH 6 = 1 case) are Ready; Create ASN and Submit. Result: one ASN with 5 cases / 30 pcs, 3 ASN manifests (one per Pra manifest), 5 ASN part rows (manifest item x case).</t>
+          <t>G-System releases crossdock orders 14-Oct (status 7); the supplier POs of 15-Oct are crossdock manifests (CROSS_DOCK_FLAG X). Supplier searches delivery 16-Oct Rit 1: PART-X (VN 18 pcs = 3 cases, TH 6 = 1 case) and PART-Y (PH 6 = 1 case) are Ready; Create ASN and Submit. Result: one ASN with 5 cases / 30 pcs, 3 ASN manifests (one per Pra manifest), 5 ASN part rows (manifest item x case).</t>
         </is>
       </c>
     </row>
@@ -29173,7 +29173,7 @@
       </c>
       <c r="D9" s="32" t="inlineStr">
         <is>
-          <t>G-TOPAS, XD12, XD11, XD08</t>
+          <t>G-System, XD12, XD11, XD08</t>
         </is>
       </c>
       <c r="E9" s="32" t="inlineStr">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>CO-14110 (PART-Y, Philippines, 12 pcs) is in an open Case List (Create ASN done, not submitted). G-TOPAS cancels 6 pcs: the line is split into serial 0000001 (status 7, 6 pcs) and serial 0000002 (status 2, 6 pcs). XD12 marks the cancel (P); XD11: CANCEL 6, VALID 6, IN ASN 0, OPEN 12 → the open mapping is released → CANCELLED; XD08 updates serial 1.</t>
+          <t>CO-14110 (PART-Y, Philippines, 12 pcs) is in an open Case List (Create ASN done, not submitted). G-System cancels 6 pcs: the line is split into serial 0000001 (status 7, 6 pcs) and serial 0000002 (status 2, 6 pcs). XD12 marks the cancel (P); XD11: CANCEL 6, VALID 6, IN ASN 0, OPEN 12 → the open mapping is released → CANCELLED; XD08 updates serial 1.</t>
         </is>
       </c>
     </row>
@@ -29205,7 +29205,7 @@
       </c>
       <c r="D10" s="32" t="inlineStr">
         <is>
-          <t>G-TOPAS, XD12, XD11, Log Monitoring</t>
+          <t>G-System, XD12, XD11, Log Monitoring</t>
         </is>
       </c>
       <c r="E10" s="32" t="inlineStr">
@@ -29215,7 +29215,7 @@
       </c>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>CO-14103 (PART-X, Vietnam, 4 pcs) is already in ASN-50221-261016-001, case C-0003. G-TOPAS cancels the line although it is in an ASN (SOP not followed): status 2. XD11: CANCEL 4, VALID 0, IN ASN 4 → CONFLICT 4; the ASN is not changed (no Cancel ASN); D/S handles case C-0003 at receiving.</t>
+          <t>CO-14103 (PART-X, Vietnam, 4 pcs) is already in ASN-50221-261016-001, case C-0003. G-System cancels the line although it is in an ASN (SOP not followed): status 2. XD11: CANCEL 4, VALID 0, IN ASN 4 → CONFLICT 4; the ASN is not changed (no Cancel ASN); D/S handles case C-0003 at receiving.</t>
         </is>
       </c>
     </row>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="D10" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
@@ -29902,7 +29902,7 @@
       </c>
       <c r="D30" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
@@ -31345,7 +31345,7 @@
     <row r="75">
       <c r="A75" s="45" t="inlineStr">
         <is>
-          <t>6. D/S [Sync] → XD06 (G-TOPAS) / XD07 (AP POLE)</t>
+          <t>6. D/S [Sync] → XD06 (G-System) / XD07 (AP POLE)</t>
         </is>
       </c>
       <c r="B75" s="46" t="n"/>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="C78" s="49" t="inlineStr">
         <is>
-          <t>GTOPAS</t>
+          <t>G-System</t>
         </is>
       </c>
       <c r="D78" s="49" t="inlineStr">
@@ -31503,7 +31503,7 @@
       </c>
       <c r="C80" s="49" t="inlineStr">
         <is>
-          <t>GTOPAS</t>
+          <t>G-System</t>
         </is>
       </c>
       <c r="D80" s="49" t="inlineStr">
@@ -31729,7 +31729,7 @@
       </c>
       <c r="K86" s="58" t="inlineStr">
         <is>
-          <t>No Sync → Success (inactive in G-TOPAS / AP POLE)</t>
+          <t>No Sync → Success (inactive in G-System / AP POLE)</t>
         </is>
       </c>
     </row>
@@ -31782,7 +31782,7 @@
     <row r="3">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>• G-TOPAS releases crossdock orders 14-Oct (status 7); the supplier POs of 15-Oct are crossdock manifests (CROSS_DOCK_FLAG X).</t>
+          <t>• G-System releases crossdock orders 14-Oct (status 7); the supplier POs of 15-Oct are crossdock manifests (CROSS_DOCK_FLAG X).</t>
         </is>
       </c>
     </row>
@@ -31886,7 +31886,7 @@
       </c>
       <c r="D10" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
@@ -33805,7 +33805,7 @@
       </c>
       <c r="D58" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
@@ -36688,7 +36688,7 @@
       </c>
       <c r="D10" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
@@ -37516,7 +37516,7 @@
       </c>
       <c r="D31" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-TOPAS)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-5" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-6" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-7" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-8" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Column Definition'!$A$3:$H$467</definedName>
@@ -15272,6 +15273,2185 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SIM-8 SORT_SEQ: H0253 lines into scan order, partial send and re-cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>BPF F2 · Functions: XD09, XD10 (ASN Option, Create ASN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>• PART-B, 6 pcs/case. H0253 is stored in any order; XD09 numbers the lines of a unit by the scan keys (SORT_SEQ): Customer Code, Customer Order No, Order Date, Order Time, Destination, Detailed Item No, Serial No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>• Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>• 15-Oct: PO1 20 pcs → blocks 1-2 Ready, block 3 (case 4) only 2 of 6 pcs with PO → Not Ready. The supplier sends option 1 case only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>• 16-Oct: PO2 10 pcs. The open qty (24) is cut again from case 1 in the same SORT_SEQ: the cases are the same as before. Unit 15-Oct (A-0201) comes after unit 14-Oct (way B), so it gets no PO yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>NEW row</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>UPD row</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="inlineStr">
+        <is>
+          <t>DEL row</t>
+        </is>
+      </c>
+      <c r="E8" s="39" t="inlineStr">
+        <is>
+          <t>READ row</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>TEMP row</t>
+        </is>
+      </c>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>Changed cell</t>
+        </is>
+      </c>
+      <c r="H8" s="42" t="inlineStr">
+        <is>
+          <t>PK column</t>
+        </is>
+      </c>
+      <c r="I8" s="36" t="inlineStr">
+        <is>
+          <t>Status OK</t>
+        </is>
+      </c>
+      <c r="J8" s="43" t="inlineStr">
+        <is>
+          <t>Status attention</t>
+        </is>
+      </c>
+      <c r="K8" s="44" t="inlineStr">
+        <is>
+          <t>Status NG / cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>1. H0253 lines as stored (not sorted)</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="n"/>
+      <c r="C10" s="46" t="n"/>
+      <c r="D10" s="46" t="n"/>
+      <c r="E10" s="46" t="n"/>
+      <c r="F10" s="46" t="n"/>
+      <c r="G10" s="46" t="n"/>
+      <c r="H10" s="46" t="n"/>
+      <c r="I10" s="46" t="n"/>
+      <c r="J10" s="46" t="n"/>
+      <c r="K10" s="46" t="n"/>
+      <c r="L10" s="46" t="n"/>
+      <c r="M10" s="46" t="n"/>
+      <c r="N10" s="46" t="n"/>
+      <c r="O10" s="46" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D11" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B12" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C12" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E12" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F12" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G12" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>CANCEL_STATUS</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E13" s="51" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H13" s="51" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="I13" s="52" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" s="51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L13" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M13" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="51" t="inlineStr">
+        <is>
+          <t>Order time 07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t>9722D00</t>
+        </is>
+      </c>
+      <c r="C14" s="51" t="inlineStr">
+        <is>
+          <t>B-0102</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E14" s="51" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F14" s="51" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G14" s="51" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H14" s="51" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="I14" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K14" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L14" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M14" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="51" t="inlineStr">
+        <is>
+          <t>Order time 09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B15" s="51" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C15" s="51" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E15" s="51" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F15" s="51" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G15" s="51" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H15" s="51" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="I15" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K15" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L15" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M15" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="51" t="inlineStr">
+        <is>
+          <t>Order time 08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E16" s="51" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G16" s="51" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H16" s="51" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="I16" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" s="51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L16" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M16" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="51" t="inlineStr">
+        <is>
+          <t>Order time 08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B17" s="51" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C17" s="51" t="inlineStr">
+        <is>
+          <t>A-0201</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E17" s="51" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G17" s="51" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H17" s="51" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="I17" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" s="51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K17" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L17" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M17" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="51" t="inlineStr">
+        <is>
+          <t>Next unit (15-Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>2. [Search] 15-Oct (PO1 20 pcs) → XD09: SORT_SEQ, cases, blocks</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="n"/>
+      <c r="C19" s="46" t="n"/>
+      <c r="D19" s="46" t="n"/>
+      <c r="E19" s="46" t="n"/>
+      <c r="F19" s="46" t="n"/>
+      <c r="G19" s="46" t="n"/>
+      <c r="H19" s="46" t="n"/>
+      <c r="I19" s="46" t="n"/>
+      <c r="J19" s="46" t="n"/>
+      <c r="K19" s="46" t="n"/>
+      <c r="L19" s="46" t="n"/>
+      <c r="M19" s="46" t="n"/>
+      <c r="N19" s="46" t="n"/>
+      <c r="O19" s="46" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>#TEMP_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D20" s="47" t="inlineStr">
+        <is>
+          <t>Temporary (session)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>SORT_SEQ</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>OPEN_ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>ASSIGNED_QTY</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>CUM_DEST_QTY</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>CUT_FLAG</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>GROUP_SEQ</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>CROSSDOCK_STATUS</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B22" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D22" s="64" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="E22" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F22" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G22" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I22" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L22" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M22" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O22" s="64" t="inlineStr">
+        <is>
+          <t>SORT_SEQ 1 = 9715300 / A-0101 / item 001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B23" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D23" s="64" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="E23" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F23" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G23" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I23" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M23" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O23" s="64" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B24" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D24" s="64" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="E24" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F24" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G24" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I24" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="L24" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M24" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O24" s="64" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B25" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="64" t="inlineStr">
+        <is>
+          <t>9722D00</t>
+        </is>
+      </c>
+      <c r="D25" s="64" t="inlineStr">
+        <is>
+          <t>B-0102</t>
+        </is>
+      </c>
+      <c r="E25" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F25" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G25" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I25" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M25" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O25" s="64" t="inlineStr">
+        <is>
+          <t>Case 2 = VN 2 + VN 2 + TH 2: no cut (VN 10, TH 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B26" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="64" t="inlineStr">
+        <is>
+          <t>9722D00</t>
+        </is>
+      </c>
+      <c r="D26" s="64" t="inlineStr">
+        <is>
+          <t>B-0102</t>
+        </is>
+      </c>
+      <c r="E26" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F26" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G26" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I26" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M26" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O26" s="64" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B27" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D27" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E27" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F27" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G27" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I27" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="L27" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M27" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O27" s="64" t="inlineStr">
+        <is>
+          <t>Cut: VN 12, TH 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B28" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D28" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E28" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F28" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G28" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H28" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I28" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="L28" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M28" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" s="66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O28" s="64" t="inlineStr">
+        <is>
+          <t>Case 4: only 2 of 6 pcs with PO1 → block 3 Not Ready, block 4 too</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B29" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D29" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E29" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F29" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G29" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" s="64" t="n"/>
+      <c r="I29" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="63" t="n">
+        <v>18</v>
+      </c>
+      <c r="L29" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M29" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" s="66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O29" s="64" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B30" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D30" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E30" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F30" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" s="64" t="n"/>
+      <c r="I30" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="63" t="n">
+        <v>24</v>
+      </c>
+      <c r="L30" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M30" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" s="66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O30" s="64" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="inlineStr">
+        <is>
+          <t>3. Supplier chooses option 1 case → [Create ASN]</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n"/>
+      <c r="C32" s="46" t="n"/>
+      <c r="D32" s="46" t="n"/>
+      <c r="E32" s="46" t="n"/>
+      <c r="F32" s="46" t="n"/>
+      <c r="G32" s="46" t="n"/>
+      <c r="H32" s="46" t="n"/>
+      <c r="I32" s="46" t="n"/>
+      <c r="J32" s="46" t="n"/>
+      <c r="K32" s="46" t="n"/>
+      <c r="L32" s="46" t="n"/>
+      <c r="M32" s="46" t="n"/>
+      <c r="N32" s="46" t="n"/>
+      <c r="O32" s="46" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D33" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B34" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>LINE_SEQ</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B35" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="49" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="F35" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G35" s="49" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="H35" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I35" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" s="49" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="K35" s="49" t="inlineStr">
+        <is>
+          <t>3126035921</t>
+        </is>
+      </c>
+      <c r="L35" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M35" s="49" t="n"/>
+      <c r="N35" s="49" t="n"/>
+      <c r="O35" s="49" t="inlineStr">
+        <is>
+          <t>Item 001: 6 of 8, open 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="D37" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B38" s="42" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>MAPPED_QTY</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="C39" s="49" t="inlineStr">
+        <is>
+          <t>3126035921</t>
+        </is>
+      </c>
+      <c r="D39" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E39" s="49" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="F39" s="53" t="n">
+        <v>20</v>
+      </c>
+      <c r="G39" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="49" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="45" t="inlineStr">
+        <is>
+          <t>4. [Search] 16-Oct (PO1 open 14 + PO2 10) → open qty cut again from case 1</t>
+        </is>
+      </c>
+      <c r="B41" s="46" t="n"/>
+      <c r="C41" s="46" t="n"/>
+      <c r="D41" s="46" t="n"/>
+      <c r="E41" s="46" t="n"/>
+      <c r="F41" s="46" t="n"/>
+      <c r="G41" s="46" t="n"/>
+      <c r="H41" s="46" t="n"/>
+      <c r="I41" s="46" t="n"/>
+      <c r="J41" s="46" t="n"/>
+      <c r="K41" s="46" t="n"/>
+      <c r="L41" s="46" t="n"/>
+      <c r="M41" s="46" t="n"/>
+      <c r="N41" s="46" t="n"/>
+      <c r="O41" s="46" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>#TEMP_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D42" s="47" t="inlineStr">
+        <is>
+          <t>Temporary (session)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>SORT_SEQ</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>OPEN_ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>ASSIGNED_QTY</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>CUM_DEST_QTY</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>CUT_FLAG</t>
+        </is>
+      </c>
+      <c r="M43" s="9" t="inlineStr">
+        <is>
+          <t>GROUP_SEQ</t>
+        </is>
+      </c>
+      <c r="N43" s="9" t="inlineStr">
+        <is>
+          <t>CROSSDOCK_STATUS</t>
+        </is>
+      </c>
+      <c r="O43" s="9" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B44" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D44" s="64" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="E44" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F44" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G44" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I44" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M44" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O44" s="64" t="inlineStr">
+        <is>
+          <t>Open qty 8 - 6 = 2; case 1 = the same physical case as case 2 on 15-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B45" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D45" s="64" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="E45" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F45" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G45" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I45" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="L45" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M45" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O45" s="64" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B46" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" s="64" t="inlineStr">
+        <is>
+          <t>9722D00</t>
+        </is>
+      </c>
+      <c r="D46" s="64" t="inlineStr">
+        <is>
+          <t>B-0102</t>
+        </is>
+      </c>
+      <c r="E46" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F46" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G46" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I46" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M46" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O46" s="64" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B47" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="64" t="inlineStr">
+        <is>
+          <t>9722D00</t>
+        </is>
+      </c>
+      <c r="D47" s="64" t="inlineStr">
+        <is>
+          <t>B-0102</t>
+        </is>
+      </c>
+      <c r="E47" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F47" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G47" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I47" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L47" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M47" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O47" s="64" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B48" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D48" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E48" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F48" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G48" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H48" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I48" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L48" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M48" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O48" s="64" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B49" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D49" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E49" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F49" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G49" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H49" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I49" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K49" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="L49" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M49" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O49" s="64" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B50" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D50" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E50" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F50" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G50" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H50" s="64" t="inlineStr">
+        <is>
+          <t>T0410021</t>
+        </is>
+      </c>
+      <c r="I50" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="L50" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M50" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N50" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O50" s="64" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B51" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D51" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E51" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F51" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G51" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H51" s="64" t="inlineStr">
+        <is>
+          <t>T0410021</t>
+        </is>
+      </c>
+      <c r="I51" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J51" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="K51" s="63" t="n">
+        <v>18</v>
+      </c>
+      <c r="L51" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M51" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="N51" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O51" s="64" t="inlineStr">
+        <is>
+          <t>Unit 14-Oct: all 3 blocks Ready (options 2 / 3 / 4 cases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B52" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D52" s="64" t="inlineStr">
+        <is>
+          <t>A-0201</t>
+        </is>
+      </c>
+      <c r="E52" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F52" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G52" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" s="64" t="n"/>
+      <c r="I52" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J52" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L52" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M52" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O52" s="64" t="inlineStr">
+        <is>
+          <t>Unit 15-Oct after unit 14-Oct (way B): no PO left</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -15594,7 +17774,7 @@
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-4, SIM-5, SIM-6, SIM-7</t>
+          <t>SIM-2, SIM-4, SIM-5, SIM-6, SIM-7, SIM-8</t>
         </is>
       </c>
     </row>
@@ -15654,7 +17834,7 @@
       </c>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-4, SIM-5, SIM-6, SIM-7</t>
+          <t>SIM-2, SIM-4, SIM-5, SIM-6, SIM-7, SIM-8</t>
         </is>
       </c>
     </row>
@@ -15684,7 +17864,7 @@
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-3, SIM-4, SIM-7</t>
+          <t>SIM-2, SIM-3, SIM-4, SIM-7, SIM-8</t>
         </is>
       </c>
     </row>
@@ -15774,7 +17954,7 @@
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-5, SIM-6, SIM-7</t>
+          <t>SIM-2, SIM-5, SIM-6, SIM-7, SIM-8</t>
         </is>
       </c>
     </row>
@@ -31978,7 +34158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -32256,6 +34436,38 @@
       <c r="F11" s="32" t="inlineStr">
         <is>
           <t>PART-A 14-Oct, 6 pcs/case: V01 VN 10, T01 TH 6, V02 VN 14 (dummy customer codes CUST-A / B / C give this scan order). p1 (24 pcs) is released 15-Oct, p2 (6 pcs) 16-Oct. Cuts are valid after cases 1, 3, 4 and 5 (VN / TH multiples of 6): blocks case 1 | 2-3 | 4 | 5. 15-Oct: blocks 1-3 Ready, the supplier chooses option 4 cases (blocks 1-3, 24 pcs). 16-Oct: the open 6 pcs of V02 get p2 and go in a second ASN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>SIM-8</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>SORT_SEQ: H0253 lines into scan order, partial send and re-cut</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>BPF F2</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>XD09, XD10 (ASN Option, Create ASN)</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE, #TEMP_INSTRUCTION, TB_R_INSTRUCTION, TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>PART-B, 6 pcs/case. H0253 is stored in any order; XD09 numbers the lines of a unit by the scan keys (SORT_SEQ): Customer Code, Customer Order No, Order Date, Order Time, Destination, Detailed Item No, Serial No. Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. 15-Oct: PO1 20 pcs → blocks 1-2 Ready, block 3 (case 4) only 2 of 6 pcs with PO → Not Ready. The supplier sends option 1 case only. 16-Oct: PO2 10 pcs. The open qty (24) is cut again from case 1 in the same SORT_SEQ: the cases are the same as before. Unit 15-Oct (A-0201) comes after unit 14-Oct (way B), so it gets no PO yet.</t>
         </is>
       </c>
     </row>

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -15316,7 +15316,7 @@
     <row r="3">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>• PART-B, 6 pcs/case. H0253 is stored in any order; XD09 numbers the lines of a unit by the scan keys (SORT_SEQ): Customer Code, Customer Order No, Order Date, Order Time, Destination, Detailed Item No, Serial No.</t>
+          <t>• PART-B, 6 pcs/case. The PK of the H0253 replicate is the 7 scan keys (Customer Code, Customer Order No, Order Date, Order Time, Destination, Detailed Item No, Serial No), so the rows are kept in scan order; the order of the whole table is global (all parts and dates), so XD09 filters the unit and reads it with ORDER BY Part, Order Date + the PK columns. SORT_SEQ = row number in this order.</t>
         </is>
       </c>
     </row>
@@ -15401,7 +15401,7 @@
     <row r="10">
       <c r="A10" s="45" t="inlineStr">
         <is>
-          <t>1. H0253 lines as stored (not sorted)</t>
+          <t>1. H0253 lines in PK order (PK = the 7 scan keys)</t>
         </is>
       </c>
       <c r="B10" s="46" t="n"/>
@@ -15511,12 +15511,12 @@
       </c>
       <c r="B13" s="51" t="inlineStr">
         <is>
-          <t>9730000</t>
+          <t>9715300</t>
         </is>
       </c>
       <c r="C13" s="51" t="inlineStr">
         <is>
-          <t>C-0103</t>
+          <t>A-0101</t>
         </is>
       </c>
       <c r="D13" s="51" t="inlineStr">
@@ -15545,7 +15545,7 @@
         </is>
       </c>
       <c r="I13" s="52" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J13" s="51" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="N13" s="51" t="inlineStr">
         <is>
-          <t>Order time 07:00</t>
+          <t>Order time 08:00</t>
         </is>
       </c>
     </row>
@@ -15581,12 +15581,12 @@
       </c>
       <c r="B14" s="51" t="inlineStr">
         <is>
-          <t>9722D00</t>
+          <t>9715300</t>
         </is>
       </c>
       <c r="C14" s="51" t="inlineStr">
         <is>
-          <t>B-0102</t>
+          <t>A-0101</t>
         </is>
       </c>
       <c r="D14" s="51" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="E14" s="51" t="inlineStr">
         <is>
-          <t>9722D10</t>
+          <t>9715310</t>
         </is>
       </c>
       <c r="F14" s="51" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>002</t>
         </is>
       </c>
       <c r="G14" s="51" t="inlineStr">
@@ -15615,7 +15615,7 @@
         </is>
       </c>
       <c r="I14" s="52" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J14" s="51" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
       </c>
       <c r="N14" s="51" t="inlineStr">
         <is>
-          <t>Order time 09:00</t>
+          <t>Order time 08:00</t>
         </is>
       </c>
     </row>
@@ -15656,12 +15656,12 @@
       </c>
       <c r="C15" s="51" t="inlineStr">
         <is>
-          <t>A-0101</t>
+          <t>A-0201</t>
         </is>
       </c>
       <c r="D15" s="51" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E15" s="51" t="inlineStr">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="F15" s="51" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>001</t>
         </is>
       </c>
       <c r="G15" s="51" t="inlineStr">
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="I15" s="52" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J15" s="51" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
       </c>
       <c r="N15" s="51" t="inlineStr">
         <is>
-          <t>Order time 08:00</t>
+          <t>Other unit (15-Oct) between the lines: XD09 splits per unit</t>
         </is>
       </c>
     </row>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B16" s="51" t="inlineStr">
         <is>
-          <t>9715300</t>
+          <t>9722D00</t>
         </is>
       </c>
       <c r="C16" s="51" t="inlineStr">
         <is>
-          <t>A-0101</t>
+          <t>B-0102</t>
         </is>
       </c>
       <c r="D16" s="51" t="inlineStr">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="E16" s="51" t="inlineStr">
         <is>
-          <t>9715310</t>
+          <t>9722D10</t>
         </is>
       </c>
       <c r="F16" s="51" t="inlineStr">
@@ -15755,7 +15755,7 @@
         </is>
       </c>
       <c r="I16" s="52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J16" s="51" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="N16" s="51" t="inlineStr">
         <is>
-          <t>Order time 08:00</t>
+          <t>Order time 09:00</t>
         </is>
       </c>
     </row>
@@ -15791,17 +15791,17 @@
       </c>
       <c r="B17" s="51" t="inlineStr">
         <is>
-          <t>9715300</t>
+          <t>9730000</t>
         </is>
       </c>
       <c r="C17" s="51" t="inlineStr">
         <is>
-          <t>A-0201</t>
+          <t>C-0103</t>
         </is>
       </c>
       <c r="D17" s="51" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E17" s="51" t="inlineStr">
@@ -15825,7 +15825,7 @@
         </is>
       </c>
       <c r="I17" s="52" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J17" s="51" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="N17" s="51" t="inlineStr">
         <is>
-          <t>Next unit (15-Oct)</t>
+          <t>Order time 07:00: still last (Customer Code first)</t>
         </is>
       </c>
     </row>
@@ -34467,7 +34467,7 @@
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>PART-B, 6 pcs/case. H0253 is stored in any order; XD09 numbers the lines of a unit by the scan keys (SORT_SEQ): Customer Code, Customer Order No, Order Date, Order Time, Destination, Detailed Item No, Serial No. Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. 15-Oct: PO1 20 pcs → blocks 1-2 Ready, block 3 (case 4) only 2 of 6 pcs with PO → Not Ready. The supplier sends option 1 case only. 16-Oct: PO2 10 pcs. The open qty (24) is cut again from case 1 in the same SORT_SEQ: the cases are the same as before. Unit 15-Oct (A-0201) comes after unit 14-Oct (way B), so it gets no PO yet.</t>
+          <t>PART-B, 6 pcs/case. The PK of the H0253 replicate is the 7 scan keys (Customer Code, Customer Order No, Order Date, Order Time, Destination, Detailed Item No, Serial No), so the rows are kept in scan order; the order of the whole table is global (all parts and dates), so XD09 filters the unit and reads it with ORDER BY Part, Order Date + the PK columns. SORT_SEQ = row number in this order. Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. 15-Oct: PO1 20 pcs → blocks 1-2 Ready, block 3 (case 4) only 2 of 6 pcs with PO → Not Ready. The supplier sends option 1 case only. 16-Oct: PO2 10 pcs. The open qty (24) is cut again from case 1 in the same SORT_SEQ: the cases are the same as before. Unit 15-Oct (A-0201) comes after unit 14-Oct (way B), so it gets no PO yet.</t>
         </is>
       </c>
     </row>

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -15279,7 +15279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -15316,14 +15316,14 @@
     <row r="3">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>• PART-B, 6 pcs/case. The PK of the H0253 replicate is the 7 scan keys (Customer Code, Customer Order No, Order Date, Order Time, Destination, Detailed Item No, Serial No), so the rows are kept in scan order; the order of the whole table is global (all parts and dates), so XD09 filters the unit and reads it with ORDER BY Part, Order Date + the PK columns. SORT_SEQ = row number in this order.</t>
+          <t>• PART-B, 6 pcs/case. Scan order = G-System allocation order with Allocation Priority = Customer Order Date: 1) Allocation Priority, 2) Customer Code, 3) Customer Order No, 4) Order Date, 5) Order Time, 6) Destination, 7) Detailed Item No, 8) Serial No. Keys 2-8 are the PK of the H0253 replicate; XD09 reads with ORDER BY Part, Allocation Priority + the PK columns (query in XD09 Appendix). SORT_SEQ = row number per unit.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>• Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first.</t>
+          <t>• Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. A-0201 (15-Oct) is in the middle of the PK order but after all 14-Oct lines in the scan order (Allocation Priority).</t>
         </is>
       </c>
     </row>
@@ -15709,7 +15709,7 @@
       </c>
       <c r="N15" s="51" t="inlineStr">
         <is>
-          <t>Other unit (15-Oct) between the lines: XD09 splits per unit</t>
+          <t>15-Oct between the 14-Oct lines in PK order: moved down by the Allocation Priority (1b)</t>
         </is>
       </c>
     </row>
@@ -15856,7 +15856,7 @@
     <row r="19">
       <c r="A19" s="45" t="inlineStr">
         <is>
-          <t>2. [Search] 15-Oct (PO1 20 pcs) → XD09: SORT_SEQ, cases, blocks</t>
+          <t>1b. XD09 read order: ORDER BY Part, Allocation Priority (= Order Date), PK columns</t>
         </is>
       </c>
       <c r="B19" s="46" t="n"/>
@@ -15877,912 +15877,1108 @@
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D20" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C21" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E21" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F21" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G21" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>CANCEL_STATUS</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B22" s="51" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C22" s="51" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="D22" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E22" s="51" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F22" s="51" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G22" s="51" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H22" s="51" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="I22" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" s="51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K22" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L22" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M22" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="51" t="inlineStr">
+        <is>
+          <t>Priority 14-Oct · SORT_SEQ 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B23" s="51" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C23" s="51" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="D23" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E23" s="51" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F23" s="51" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G23" s="51" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H23" s="51" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="I23" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K23" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L23" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M23" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="51" t="inlineStr">
+        <is>
+          <t>Priority 14-Oct · SORT_SEQ 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B24" s="51" t="inlineStr">
+        <is>
+          <t>9722D00</t>
+        </is>
+      </c>
+      <c r="C24" s="51" t="inlineStr">
+        <is>
+          <t>B-0102</t>
+        </is>
+      </c>
+      <c r="D24" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E24" s="51" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F24" s="51" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G24" s="51" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H24" s="51" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="I24" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" s="51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K24" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L24" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M24" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="51" t="inlineStr">
+        <is>
+          <t>Priority 14-Oct · SORT_SEQ 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B25" s="51" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="C25" s="51" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="D25" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E25" s="51" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F25" s="51" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G25" s="51" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H25" s="51" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="I25" s="52" t="n">
+        <v>14</v>
+      </c>
+      <c r="J25" s="51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K25" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L25" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M25" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="51" t="inlineStr">
+        <is>
+          <t>Priority 14-Oct · SORT_SEQ 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B26" s="51" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C26" s="51" t="inlineStr">
+        <is>
+          <t>A-0201</t>
+        </is>
+      </c>
+      <c r="D26" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E26" s="51" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F26" s="51" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G26" s="51" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H26" s="51" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="I26" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" s="51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K26" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L26" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M26" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="51" t="inlineStr">
+        <is>
+          <t>Priority 15-Oct: after all 14-Oct lines (unit 15-Oct, SORT_SEQ 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="inlineStr">
+        <is>
+          <t>2. [Search] 15-Oct (PO1 20 pcs) → XD09: SORT_SEQ, cases, blocks</t>
+        </is>
+      </c>
+      <c r="B28" s="46" t="n"/>
+      <c r="C28" s="46" t="n"/>
+      <c r="D28" s="46" t="n"/>
+      <c r="E28" s="46" t="n"/>
+      <c r="F28" s="46" t="n"/>
+      <c r="G28" s="46" t="n"/>
+      <c r="H28" s="46" t="n"/>
+      <c r="I28" s="46" t="n"/>
+      <c r="J28" s="46" t="n"/>
+      <c r="K28" s="46" t="n"/>
+      <c r="L28" s="46" t="n"/>
+      <c r="M28" s="46" t="n"/>
+      <c r="N28" s="46" t="n"/>
+      <c r="O28" s="46" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="inlineStr">
+        <is>
           <t>#TEMP_INSTRUCTION</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D29" s="47" t="inlineStr">
         <is>
           <t>Temporary (session)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>SORT_SEQ</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>CUSTOMER_CD</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>CUSTOMER_ORDER_NO</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>DESTINATION_CD</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>PART_NO</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>OPEN_ORDER_QTY</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>PO_NO</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>ASSIGNED_QTY</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>CASE_SEQ</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>CUM_DEST_QTY</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>CUT_FLAG</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>GROUP_SEQ</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>CROSSDOCK_STATUS</t>
         </is>
       </c>
-      <c r="O21" s="9" t="inlineStr">
+      <c r="O30" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="62" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B22" s="63" t="n">
+      <c r="B31" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="64" t="inlineStr">
+      <c r="C31" s="64" t="inlineStr">
         <is>
           <t>9715300</t>
         </is>
       </c>
-      <c r="D22" s="64" t="inlineStr">
+      <c r="D31" s="64" t="inlineStr">
         <is>
           <t>A-0101</t>
         </is>
       </c>
-      <c r="E22" s="64" t="inlineStr">
+      <c r="E31" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F22" s="64" t="inlineStr">
+      <c r="F31" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G22" s="63" t="n">
+      <c r="G31" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="H22" s="64" t="inlineStr">
+      <c r="H31" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I22" s="63" t="n">
+      <c r="I31" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="J22" s="63" t="n">
+      <c r="J31" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="K22" s="63" t="n">
+      <c r="K31" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L22" s="65" t="inlineStr">
+      <c r="L31" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M22" s="63" t="n">
+      <c r="M31" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="49" t="inlineStr">
+      <c r="N31" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O22" s="64" t="inlineStr">
+      <c r="O31" s="64" t="inlineStr">
         <is>
           <t>SORT_SEQ 1 = 9715300 / A-0101 / item 001</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="62" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B23" s="63" t="n">
+      <c r="B32" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="64" t="inlineStr">
+      <c r="C32" s="64" t="inlineStr">
         <is>
           <t>9715300</t>
         </is>
       </c>
-      <c r="D23" s="64" t="inlineStr">
+      <c r="D32" s="64" t="inlineStr">
         <is>
           <t>A-0101</t>
         </is>
       </c>
-      <c r="E23" s="64" t="inlineStr">
+      <c r="E32" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F23" s="64" t="inlineStr">
+      <c r="F32" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G23" s="63" t="n">
+      <c r="G32" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="H23" s="64" t="inlineStr">
+      <c r="H32" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I23" s="63" t="n">
+      <c r="I32" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="63" t="n">
+      <c r="J32" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="K23" s="63" t="n">
+      <c r="K32" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="L23" s="64" t="inlineStr">
+      <c r="L32" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M23" s="63" t="n">
+      <c r="M32" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N23" s="49" t="inlineStr">
+      <c r="N32" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O23" s="64" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="62" t="inlineStr">
+      <c r="O32" s="64" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B24" s="63" t="n">
+      <c r="B33" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="64" t="inlineStr">
+      <c r="C33" s="64" t="inlineStr">
         <is>
           <t>9715300</t>
         </is>
       </c>
-      <c r="D24" s="64" t="inlineStr">
+      <c r="D33" s="64" t="inlineStr">
         <is>
           <t>A-0101</t>
         </is>
       </c>
-      <c r="E24" s="64" t="inlineStr">
+      <c r="E33" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F24" s="64" t="inlineStr">
+      <c r="F33" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G24" s="63" t="n">
+      <c r="G33" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="64" t="inlineStr">
+      <c r="H33" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I24" s="63" t="n">
+      <c r="I33" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="J24" s="63" t="n">
+      <c r="J33" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="K24" s="63" t="n">
+      <c r="K33" s="63" t="n">
         <v>10</v>
       </c>
-      <c r="L24" s="64" t="inlineStr">
+      <c r="L33" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M24" s="63" t="n">
+      <c r="M33" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N24" s="49" t="inlineStr">
+      <c r="N33" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O24" s="64" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="62" t="inlineStr">
+      <c r="O33" s="64" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B25" s="63" t="n">
+      <c r="B34" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="64" t="inlineStr">
+      <c r="C34" s="64" t="inlineStr">
         <is>
           <t>9722D00</t>
         </is>
       </c>
-      <c r="D25" s="64" t="inlineStr">
+      <c r="D34" s="64" t="inlineStr">
         <is>
           <t>B-0102</t>
         </is>
       </c>
-      <c r="E25" s="64" t="inlineStr">
+      <c r="E34" s="64" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="F25" s="64" t="inlineStr">
+      <c r="F34" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G25" s="63" t="n">
+      <c r="G34" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="H25" s="64" t="inlineStr">
+      <c r="H34" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I25" s="63" t="n">
+      <c r="I34" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="63" t="n">
+      <c r="J34" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="K25" s="63" t="n">
+      <c r="K34" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="L25" s="64" t="inlineStr">
+      <c r="L34" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M25" s="63" t="n">
+      <c r="M34" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="49" t="inlineStr">
+      <c r="N34" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O25" s="64" t="inlineStr">
+      <c r="O34" s="64" t="inlineStr">
         <is>
           <t>Case 2 = VN 2 + VN 2 + TH 2: no cut (VN 10, TH 2)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="62" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B26" s="63" t="n">
+      <c r="B35" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="64" t="inlineStr">
+      <c r="C35" s="64" t="inlineStr">
         <is>
           <t>9722D00</t>
         </is>
       </c>
-      <c r="D26" s="64" t="inlineStr">
+      <c r="D35" s="64" t="inlineStr">
         <is>
           <t>B-0102</t>
         </is>
       </c>
-      <c r="E26" s="64" t="inlineStr">
+      <c r="E35" s="64" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="F26" s="64" t="inlineStr">
+      <c r="F35" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G26" s="63" t="n">
+      <c r="G35" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="H26" s="64" t="inlineStr">
+      <c r="H35" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I26" s="63" t="n">
+      <c r="I35" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="J26" s="63" t="n">
+      <c r="J35" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="K26" s="63" t="n">
+      <c r="K35" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L26" s="64" t="inlineStr">
+      <c r="L35" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M26" s="63" t="n">
+      <c r="M35" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N26" s="49" t="inlineStr">
+      <c r="N35" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O26" s="64" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="62" t="inlineStr">
+      <c r="O35" s="64" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B27" s="63" t="n">
+      <c r="B36" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="C27" s="64" t="inlineStr">
+      <c r="C36" s="64" t="inlineStr">
         <is>
           <t>9730000</t>
         </is>
       </c>
-      <c r="D27" s="64" t="inlineStr">
+      <c r="D36" s="64" t="inlineStr">
         <is>
           <t>C-0103</t>
         </is>
       </c>
-      <c r="E27" s="64" t="inlineStr">
+      <c r="E36" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F27" s="64" t="inlineStr">
+      <c r="F36" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G27" s="63" t="n">
+      <c r="G36" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="H27" s="64" t="inlineStr">
+      <c r="H36" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I27" s="63" t="n">
+      <c r="I36" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="63" t="n">
+      <c r="J36" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="K27" s="63" t="n">
+      <c r="K36" s="63" t="n">
         <v>12</v>
       </c>
-      <c r="L27" s="65" t="inlineStr">
+      <c r="L36" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M27" s="63" t="n">
+      <c r="M36" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N27" s="49" t="inlineStr">
+      <c r="N36" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O27" s="64" t="inlineStr">
+      <c r="O36" s="64" t="inlineStr">
         <is>
           <t>Cut: VN 12, TH 6</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="62" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B28" s="63" t="n">
+      <c r="B37" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="64" t="inlineStr">
+      <c r="C37" s="64" t="inlineStr">
         <is>
           <t>9730000</t>
         </is>
       </c>
-      <c r="D28" s="64" t="inlineStr">
+      <c r="D37" s="64" t="inlineStr">
         <is>
           <t>C-0103</t>
         </is>
       </c>
-      <c r="E28" s="64" t="inlineStr">
+      <c r="E37" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F28" s="64" t="inlineStr">
+      <c r="F37" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G28" s="63" t="n">
+      <c r="G37" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="H28" s="64" t="inlineStr">
+      <c r="H37" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I28" s="63" t="n">
+      <c r="I37" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="63" t="n">
+      <c r="J37" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="K28" s="63" t="n">
+      <c r="K37" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="L28" s="64" t="inlineStr">
+      <c r="L37" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M28" s="63" t="n">
+      <c r="M37" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N28" s="66" t="inlineStr">
+      <c r="N37" s="66" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O28" s="64" t="inlineStr">
+      <c r="O37" s="64" t="inlineStr">
         <is>
           <t>Case 4: only 2 of 6 pcs with PO1 → block 3 Not Ready, block 4 too</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="62" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B29" s="63" t="n">
+      <c r="B38" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="C29" s="64" t="inlineStr">
+      <c r="C38" s="64" t="inlineStr">
         <is>
           <t>9730000</t>
         </is>
       </c>
-      <c r="D29" s="64" t="inlineStr">
+      <c r="D38" s="64" t="inlineStr">
         <is>
           <t>C-0103</t>
         </is>
       </c>
-      <c r="E29" s="64" t="inlineStr">
+      <c r="E38" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F29" s="64" t="inlineStr">
+      <c r="F38" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G29" s="63" t="n">
+      <c r="G38" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="H29" s="64" t="n"/>
-      <c r="I29" s="63" t="n">
+      <c r="H38" s="64" t="n"/>
+      <c r="I38" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="J29" s="63" t="n">
+      <c r="J38" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="K29" s="63" t="n">
+      <c r="K38" s="63" t="n">
         <v>18</v>
       </c>
-      <c r="L29" s="65" t="inlineStr">
+      <c r="L38" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M29" s="63" t="n">
+      <c r="M38" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N29" s="66" t="inlineStr">
+      <c r="N38" s="66" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O29" s="64" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="62" t="inlineStr">
+      <c r="O38" s="64" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B30" s="63" t="n">
+      <c r="B39" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="C30" s="64" t="inlineStr">
+      <c r="C39" s="64" t="inlineStr">
         <is>
           <t>9730000</t>
         </is>
       </c>
-      <c r="D30" s="64" t="inlineStr">
+      <c r="D39" s="64" t="inlineStr">
         <is>
           <t>C-0103</t>
         </is>
       </c>
-      <c r="E30" s="64" t="inlineStr">
+      <c r="E39" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F30" s="64" t="inlineStr">
+      <c r="F39" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G30" s="63" t="n">
+      <c r="G39" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="H30" s="64" t="n"/>
-      <c r="I30" s="63" t="n">
+      <c r="H39" s="64" t="n"/>
+      <c r="I39" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="J30" s="63" t="n">
+      <c r="J39" s="63" t="n">
         <v>5</v>
       </c>
-      <c r="K30" s="63" t="n">
+      <c r="K39" s="63" t="n">
         <v>24</v>
       </c>
-      <c r="L30" s="65" t="inlineStr">
+      <c r="L39" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M30" s="63" t="n">
+      <c r="M39" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="N30" s="66" t="inlineStr">
+      <c r="N39" s="66" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O30" s="64" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="45" t="inlineStr">
-        <is>
-          <t>3. Supplier chooses option 1 case → [Create ASN]</t>
-        </is>
-      </c>
-      <c r="B32" s="46" t="n"/>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="46" t="n"/>
-      <c r="E32" s="46" t="n"/>
-      <c r="F32" s="46" t="n"/>
-      <c r="G32" s="46" t="n"/>
-      <c r="H32" s="46" t="n"/>
-      <c r="I32" s="46" t="n"/>
-      <c r="J32" s="46" t="n"/>
-      <c r="K32" s="46" t="n"/>
-      <c r="L32" s="46" t="n"/>
-      <c r="M32" s="46" t="n"/>
-      <c r="N32" s="46" t="n"/>
-      <c r="O32" s="46" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_INSTRUCTION</t>
-        </is>
-      </c>
-      <c r="D33" s="47" t="inlineStr">
-        <is>
-          <t>New table (Crossdock)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B34" s="42" t="inlineStr">
-        <is>
-          <t>INSTRUCTION_ID</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>CASE_SEQ</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>LINE_SEQ</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>SERIAL_NO</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>QTY</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>PO_NO</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_NO</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_ITEM</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>ASN_NO</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t>CASE_NO</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B35" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="49" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="F35" s="49" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="G35" s="49" t="inlineStr">
-        <is>
-          <t>A-0101</t>
-        </is>
-      </c>
-      <c r="H35" s="49" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="I35" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="J35" s="49" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="K35" s="49" t="inlineStr">
-        <is>
-          <t>3126035921</t>
-        </is>
-      </c>
-      <c r="L35" s="49" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="M35" s="49" t="n"/>
-      <c r="N35" s="49" t="n"/>
-      <c r="O35" s="49" t="inlineStr">
-        <is>
-          <t>Item 001: 6 of 8, open 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
-        </is>
-      </c>
-      <c r="D37" s="47" t="inlineStr">
-        <is>
-          <t>New table (Crossdock)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B38" s="42" t="inlineStr">
-        <is>
-          <t>PO_NO</t>
-        </is>
-      </c>
-      <c r="C38" s="42" t="inlineStr">
-        <is>
-          <t>MANIFEST_NO</t>
-        </is>
-      </c>
-      <c r="D38" s="42" t="inlineStr">
-        <is>
-          <t>MANIFEST_ITEM</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>ORDER_QTY</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>MAPPED_QTY</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B39" s="49" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="C39" s="49" t="inlineStr">
-        <is>
-          <t>3126035921</t>
-        </is>
-      </c>
-      <c r="D39" s="49" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="E39" s="49" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="F39" s="53" t="n">
-        <v>20</v>
-      </c>
-      <c r="G39" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="H39" s="49" t="inlineStr"/>
+      <c r="O39" s="64" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="45" t="inlineStr">
         <is>
-          <t>4. [Search] 16-Oct (PO1 open 14 + PO2 10) → open qty cut again from case 1</t>
+          <t>3. Supplier chooses option 1 case → [Create ASN]</t>
         </is>
       </c>
       <c r="B41" s="46" t="n"/>
@@ -16803,644 +16999,903 @@
     <row r="42">
       <c r="A42" s="35" t="inlineStr">
         <is>
+          <t>TB_R_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D42" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B43" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>LINE_SEQ</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B44" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="49" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="F44" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G44" s="49" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="H44" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I44" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J44" s="49" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="K44" s="49" t="inlineStr">
+        <is>
+          <t>3126035921</t>
+        </is>
+      </c>
+      <c r="L44" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M44" s="49" t="n"/>
+      <c r="N44" s="49" t="n"/>
+      <c r="O44" s="49" t="inlineStr">
+        <is>
+          <t>Item 001: 6 of 8, open 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="D46" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B47" s="42" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="C47" s="42" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="D47" s="42" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>MAPPED_QTY</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B48" s="49" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="C48" s="49" t="inlineStr">
+        <is>
+          <t>3126035921</t>
+        </is>
+      </c>
+      <c r="D48" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E48" s="49" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="F48" s="53" t="n">
+        <v>20</v>
+      </c>
+      <c r="G48" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="H48" s="49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="45" t="inlineStr">
+        <is>
+          <t>4. [Search] 16-Oct (PO1 open 14 + PO2 10) → open qty cut again from case 1</t>
+        </is>
+      </c>
+      <c r="B50" s="46" t="n"/>
+      <c r="C50" s="46" t="n"/>
+      <c r="D50" s="46" t="n"/>
+      <c r="E50" s="46" t="n"/>
+      <c r="F50" s="46" t="n"/>
+      <c r="G50" s="46" t="n"/>
+      <c r="H50" s="46" t="n"/>
+      <c r="I50" s="46" t="n"/>
+      <c r="J50" s="46" t="n"/>
+      <c r="K50" s="46" t="n"/>
+      <c r="L50" s="46" t="n"/>
+      <c r="M50" s="46" t="n"/>
+      <c r="N50" s="46" t="n"/>
+      <c r="O50" s="46" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="35" t="inlineStr">
+        <is>
           <t>#TEMP_INSTRUCTION</t>
         </is>
       </c>
-      <c r="D42" s="47" t="inlineStr">
+      <c r="D51" s="47" t="inlineStr">
         <is>
           <t>Temporary (session)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>SORT_SEQ</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>CUSTOMER_CD</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>CUSTOMER_ORDER_NO</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>DESTINATION_CD</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F52" s="9" t="inlineStr">
         <is>
           <t>PART_NO</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G52" s="9" t="inlineStr">
         <is>
           <t>OPEN_ORDER_QTY</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H52" s="9" t="inlineStr">
         <is>
           <t>PO_NO</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I52" s="9" t="inlineStr">
         <is>
           <t>ASSIGNED_QTY</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr">
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>CASE_SEQ</t>
         </is>
       </c>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="K52" s="9" t="inlineStr">
         <is>
           <t>CUM_DEST_QTY</t>
         </is>
       </c>
-      <c r="L43" s="9" t="inlineStr">
+      <c r="L52" s="9" t="inlineStr">
         <is>
           <t>CUT_FLAG</t>
         </is>
       </c>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="M52" s="9" t="inlineStr">
         <is>
           <t>GROUP_SEQ</t>
         </is>
       </c>
-      <c r="N43" s="9" t="inlineStr">
+      <c r="N52" s="9" t="inlineStr">
         <is>
           <t>CROSSDOCK_STATUS</t>
         </is>
       </c>
-      <c r="O43" s="9" t="inlineStr">
+      <c r="O52" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="62" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B44" s="63" t="n">
+      <c r="B53" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="64" t="inlineStr">
+      <c r="C53" s="64" t="inlineStr">
         <is>
           <t>9715300</t>
         </is>
       </c>
-      <c r="D44" s="64" t="inlineStr">
+      <c r="D53" s="64" t="inlineStr">
         <is>
           <t>A-0101</t>
         </is>
       </c>
-      <c r="E44" s="64" t="inlineStr">
+      <c r="E53" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F44" s="64" t="inlineStr">
+      <c r="F53" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G44" s="63" t="n">
+      <c r="G53" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="H44" s="64" t="inlineStr">
+      <c r="H53" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I44" s="63" t="n">
+      <c r="I53" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="J44" s="63" t="n">
+      <c r="J53" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="K44" s="63" t="n">
+      <c r="K53" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="L44" s="64" t="inlineStr">
+      <c r="L53" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M44" s="63" t="n">
+      <c r="M53" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N44" s="49" t="inlineStr">
+      <c r="N53" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O44" s="64" t="inlineStr">
+      <c r="O53" s="64" t="inlineStr">
         <is>
           <t>Open qty 8 - 6 = 2; case 1 = the same physical case as case 2 on 15-Oct</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="62" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B45" s="63" t="n">
+      <c r="B54" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="C45" s="64" t="inlineStr">
+      <c r="C54" s="64" t="inlineStr">
         <is>
           <t>9715300</t>
         </is>
       </c>
-      <c r="D45" s="64" t="inlineStr">
+      <c r="D54" s="64" t="inlineStr">
         <is>
           <t>A-0101</t>
         </is>
       </c>
-      <c r="E45" s="64" t="inlineStr">
+      <c r="E54" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F45" s="64" t="inlineStr">
+      <c r="F54" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G45" s="63" t="n">
+      <c r="G54" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="H45" s="64" t="inlineStr">
+      <c r="H54" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I45" s="63" t="n">
+      <c r="I54" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="63" t="n">
+      <c r="J54" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="K45" s="63" t="n">
+      <c r="K54" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="L45" s="64" t="inlineStr">
+      <c r="L54" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M45" s="63" t="n">
+      <c r="M54" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N45" s="49" t="inlineStr">
+      <c r="N54" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O45" s="64" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="62" t="inlineStr">
+      <c r="O54" s="64" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B46" s="63" t="n">
+      <c r="B55" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="C46" s="64" t="inlineStr">
+      <c r="C55" s="64" t="inlineStr">
         <is>
           <t>9722D00</t>
         </is>
       </c>
-      <c r="D46" s="64" t="inlineStr">
+      <c r="D55" s="64" t="inlineStr">
         <is>
           <t>B-0102</t>
         </is>
       </c>
-      <c r="E46" s="64" t="inlineStr">
+      <c r="E55" s="64" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="F46" s="64" t="inlineStr">
+      <c r="F55" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G46" s="63" t="n">
+      <c r="G55" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="H46" s="64" t="inlineStr">
+      <c r="H55" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I46" s="63" t="n">
+      <c r="I55" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="J46" s="63" t="n">
+      <c r="J55" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="K46" s="63" t="n">
+      <c r="K55" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="L46" s="64" t="inlineStr">
+      <c r="L55" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M46" s="63" t="n">
+      <c r="M55" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="49" t="inlineStr">
+      <c r="N55" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O46" s="64" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="62" t="inlineStr">
+      <c r="O55" s="64" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B47" s="63" t="n">
+      <c r="B56" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="C47" s="64" t="inlineStr">
+      <c r="C56" s="64" t="inlineStr">
         <is>
           <t>9722D00</t>
         </is>
       </c>
-      <c r="D47" s="64" t="inlineStr">
+      <c r="D56" s="64" t="inlineStr">
         <is>
           <t>B-0102</t>
         </is>
       </c>
-      <c r="E47" s="64" t="inlineStr">
+      <c r="E56" s="64" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="F47" s="64" t="inlineStr">
+      <c r="F56" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G47" s="63" t="n">
+      <c r="G56" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="H47" s="64" t="inlineStr">
+      <c r="H56" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I47" s="63" t="n">
+      <c r="I56" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="J47" s="63" t="n">
+      <c r="J56" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="K47" s="63" t="n">
+      <c r="K56" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L47" s="64" t="inlineStr">
+      <c r="L56" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M47" s="63" t="n">
+      <c r="M56" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="49" t="inlineStr">
+      <c r="N56" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O47" s="64" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="62" t="inlineStr">
+      <c r="O56" s="64" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B48" s="63" t="n">
+      <c r="B57" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="C48" s="64" t="inlineStr">
+      <c r="C57" s="64" t="inlineStr">
         <is>
           <t>9730000</t>
         </is>
       </c>
-      <c r="D48" s="64" t="inlineStr">
+      <c r="D57" s="64" t="inlineStr">
         <is>
           <t>C-0103</t>
         </is>
       </c>
-      <c r="E48" s="64" t="inlineStr">
+      <c r="E57" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F48" s="64" t="inlineStr">
+      <c r="F57" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G48" s="63" t="n">
+      <c r="G57" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="H48" s="64" t="inlineStr">
+      <c r="H57" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I48" s="63" t="n">
+      <c r="I57" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="63" t="n">
+      <c r="J57" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="K48" s="63" t="n">
+      <c r="K57" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L48" s="65" t="inlineStr">
+      <c r="L57" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M48" s="63" t="n">
+      <c r="M57" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N48" s="49" t="inlineStr">
+      <c r="N57" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O48" s="64" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="62" t="inlineStr">
+      <c r="O57" s="64" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B49" s="63" t="n">
+      <c r="B58" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="C49" s="64" t="inlineStr">
+      <c r="C58" s="64" t="inlineStr">
         <is>
           <t>9730000</t>
         </is>
       </c>
-      <c r="D49" s="64" t="inlineStr">
+      <c r="D58" s="64" t="inlineStr">
         <is>
           <t>C-0103</t>
         </is>
       </c>
-      <c r="E49" s="64" t="inlineStr">
+      <c r="E58" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F49" s="64" t="inlineStr">
+      <c r="F58" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G49" s="63" t="n">
+      <c r="G58" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="H49" s="64" t="inlineStr">
+      <c r="H58" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="I49" s="63" t="n">
+      <c r="I58" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="J49" s="63" t="n">
+      <c r="J58" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="K49" s="63" t="n">
+      <c r="K58" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="L49" s="64" t="inlineStr">
+      <c r="L58" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M49" s="63" t="n">
+      <c r="M58" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N49" s="49" t="inlineStr">
+      <c r="N58" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O49" s="64" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="62" t="inlineStr">
+      <c r="O58" s="64" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B50" s="63" t="n">
+      <c r="B59" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="C50" s="64" t="inlineStr">
+      <c r="C59" s="64" t="inlineStr">
         <is>
           <t>9730000</t>
         </is>
       </c>
-      <c r="D50" s="64" t="inlineStr">
+      <c r="D59" s="64" t="inlineStr">
         <is>
           <t>C-0103</t>
         </is>
       </c>
-      <c r="E50" s="64" t="inlineStr">
+      <c r="E59" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F50" s="64" t="inlineStr">
+      <c r="F59" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G50" s="63" t="n">
+      <c r="G59" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="H50" s="64" t="inlineStr">
+      <c r="H59" s="64" t="inlineStr">
         <is>
           <t>T0410021</t>
         </is>
       </c>
-      <c r="I50" s="63" t="n">
+      <c r="I59" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="J50" s="63" t="n">
+      <c r="J59" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="K50" s="63" t="n">
+      <c r="K59" s="63" t="n">
         <v>12</v>
       </c>
-      <c r="L50" s="65" t="inlineStr">
+      <c r="L59" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M50" s="63" t="n">
+      <c r="M59" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N50" s="49" t="inlineStr">
+      <c r="N59" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O50" s="64" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="62" t="inlineStr">
+      <c r="O59" s="64" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B51" s="63" t="n">
+      <c r="B60" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="C51" s="64" t="inlineStr">
+      <c r="C60" s="64" t="inlineStr">
         <is>
           <t>9730000</t>
         </is>
       </c>
-      <c r="D51" s="64" t="inlineStr">
+      <c r="D60" s="64" t="inlineStr">
         <is>
           <t>C-0103</t>
         </is>
       </c>
-      <c r="E51" s="64" t="inlineStr">
+      <c r="E60" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F51" s="64" t="inlineStr">
+      <c r="F60" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G51" s="63" t="n">
+      <c r="G60" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="H51" s="64" t="inlineStr">
+      <c r="H60" s="64" t="inlineStr">
         <is>
           <t>T0410021</t>
         </is>
       </c>
-      <c r="I51" s="63" t="n">
+      <c r="I60" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="J51" s="63" t="n">
+      <c r="J60" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="K51" s="63" t="n">
+      <c r="K60" s="63" t="n">
         <v>18</v>
       </c>
-      <c r="L51" s="65" t="inlineStr">
+      <c r="L60" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M51" s="63" t="n">
+      <c r="M60" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N51" s="49" t="inlineStr">
+      <c r="N60" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O51" s="64" t="inlineStr">
+      <c r="O60" s="64" t="inlineStr">
         <is>
           <t>Unit 14-Oct: all 3 blocks Ready (options 2 / 3 / 4 cases)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="62" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B52" s="63" t="n">
+      <c r="B61" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="64" t="inlineStr">
+      <c r="C61" s="64" t="inlineStr">
         <is>
           <t>9715300</t>
         </is>
       </c>
-      <c r="D52" s="64" t="inlineStr">
+      <c r="D61" s="64" t="inlineStr">
         <is>
           <t>A-0201</t>
         </is>
       </c>
-      <c r="E52" s="64" t="inlineStr">
+      <c r="E61" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F52" s="64" t="inlineStr">
+      <c r="F61" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G52" s="63" t="n">
+      <c r="G61" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="H52" s="64" t="n"/>
-      <c r="I52" s="63" t="n">
+      <c r="H61" s="64" t="n"/>
+      <c r="I61" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="J52" s="63" t="n">
+      <c r="J61" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="K52" s="63" t="n">
+      <c r="K61" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L52" s="65" t="inlineStr">
+      <c r="L61" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M52" s="63" t="n">
+      <c r="M61" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N52" s="66" t="inlineStr">
+      <c r="N61" s="66" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O52" s="64" t="inlineStr">
+      <c r="O61" s="64" t="inlineStr">
         <is>
           <t>Unit 15-Oct after unit 14-Oct (way B): no PO left</t>
         </is>
@@ -34467,7 +34922,7 @@
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>PART-B, 6 pcs/case. The PK of the H0253 replicate is the 7 scan keys (Customer Code, Customer Order No, Order Date, Order Time, Destination, Detailed Item No, Serial No), so the rows are kept in scan order; the order of the whole table is global (all parts and dates), so XD09 filters the unit and reads it with ORDER BY Part, Order Date + the PK columns. SORT_SEQ = row number in this order. Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. 15-Oct: PO1 20 pcs → blocks 1-2 Ready, block 3 (case 4) only 2 of 6 pcs with PO → Not Ready. The supplier sends option 1 case only. 16-Oct: PO2 10 pcs. The open qty (24) is cut again from case 1 in the same SORT_SEQ: the cases are the same as before. Unit 15-Oct (A-0201) comes after unit 14-Oct (way B), so it gets no PO yet.</t>
+          <t>PART-B, 6 pcs/case. Scan order = G-System allocation order with Allocation Priority = Customer Order Date: 1) Allocation Priority, 2) Customer Code, 3) Customer Order No, 4) Order Date, 5) Order Time, 6) Destination, 7) Detailed Item No, 8) Serial No. Keys 2-8 are the PK of the H0253 replicate; XD09 reads with ORDER BY Part, Allocation Priority + the PK columns (query in XD09 Appendix). SORT_SEQ = row number per unit. Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. A-0201 (15-Oct) is in the middle of the PK order but after all 14-Oct lines in the scan order (Allocation Priority). 15-Oct: PO1 20 pcs → blocks 1-2 Ready, block 3 (case 4) only 2 of 6 pcs with PO → Not Ready. The supplier sends option 1 case only. 16-Oct: PO2 10 pcs. The open qty (24) is cut again from case 1 in the same SORT_SEQ: the cases are the same as before. Unit 15-Oct (A-0201) comes after unit 14-Oct (way B), so it gets no PO yet.</t>
         </is>
       </c>
     </row>

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -15279,7 +15279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -15323,7 +15323,7 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>• Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. A-0201 (15-Oct) is in the middle of the PK order but after all 14-Oct lines in the scan order (Allocation Priority).</t>
+          <t>• Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. A-0201 (15-Oct) comes after all 14-Oct lines (Allocation Priority) and is the next unit.</t>
         </is>
       </c>
     </row>
@@ -15401,7 +15401,7 @@
     <row r="10">
       <c r="A10" s="45" t="inlineStr">
         <is>
-          <t>1. H0253 lines in PK order (PK = the 7 scan keys)</t>
+          <t>1. H0253 lines in scan order: ORDER BY Part, Allocation Priority (= Order Date), PK columns</t>
         </is>
       </c>
       <c r="B10" s="46" t="n"/>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="N13" s="51" t="inlineStr">
         <is>
-          <t>Order time 08:00</t>
+          <t>Priority 14-Oct · SORT_SEQ 1</t>
         </is>
       </c>
     </row>
@@ -15639,7 +15639,7 @@
       </c>
       <c r="N14" s="51" t="inlineStr">
         <is>
-          <t>Order time 08:00</t>
+          <t>Priority 14-Oct · SORT_SEQ 2</t>
         </is>
       </c>
     </row>
@@ -15651,22 +15651,22 @@
       </c>
       <c r="B15" s="51" t="inlineStr">
         <is>
-          <t>9715300</t>
+          <t>9722D00</t>
         </is>
       </c>
       <c r="C15" s="51" t="inlineStr">
         <is>
-          <t>A-0201</t>
+          <t>B-0102</t>
         </is>
       </c>
       <c r="D15" s="51" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E15" s="51" t="inlineStr">
         <is>
-          <t>9715310</t>
+          <t>9722D10</t>
         </is>
       </c>
       <c r="F15" s="51" t="inlineStr">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="N15" s="51" t="inlineStr">
         <is>
-          <t>15-Oct between the 14-Oct lines in PK order: moved down by the Allocation Priority (1b)</t>
+          <t>Priority 14-Oct · SORT_SEQ 3</t>
         </is>
       </c>
     </row>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B16" s="51" t="inlineStr">
         <is>
-          <t>9722D00</t>
+          <t>9730000</t>
         </is>
       </c>
       <c r="C16" s="51" t="inlineStr">
         <is>
-          <t>B-0102</t>
+          <t>C-0103</t>
         </is>
       </c>
       <c r="D16" s="51" t="inlineStr">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="E16" s="51" t="inlineStr">
         <is>
-          <t>9722D10</t>
+          <t>9715310</t>
         </is>
       </c>
       <c r="F16" s="51" t="inlineStr">
@@ -15755,7 +15755,7 @@
         </is>
       </c>
       <c r="I16" s="52" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J16" s="51" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="N16" s="51" t="inlineStr">
         <is>
-          <t>Order time 09:00</t>
+          <t>Priority 14-Oct · SORT_SEQ 4</t>
         </is>
       </c>
     </row>
@@ -15791,17 +15791,17 @@
       </c>
       <c r="B17" s="51" t="inlineStr">
         <is>
-          <t>9730000</t>
+          <t>9715300</t>
         </is>
       </c>
       <c r="C17" s="51" t="inlineStr">
         <is>
-          <t>C-0103</t>
+          <t>A-0201</t>
         </is>
       </c>
       <c r="D17" s="51" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E17" s="51" t="inlineStr">
@@ -15825,7 +15825,7 @@
         </is>
       </c>
       <c r="I17" s="52" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J17" s="51" t="inlineStr">
         <is>
@@ -15849,14 +15849,14 @@
       </c>
       <c r="N17" s="51" t="inlineStr">
         <is>
-          <t>Order time 07:00: still last (Customer Code first)</t>
+          <t>Priority 15-Oct: after all 14-Oct lines (unit 15-Oct, SORT_SEQ 1)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="45" t="inlineStr">
         <is>
-          <t>1b. XD09 read order: ORDER BY Part, Allocation Priority (= Order Date), PK columns</t>
+          <t>2. [Search] 15-Oct (PO1 20 pcs) → XD09: SORT_SEQ, cases, blocks</t>
         </is>
       </c>
       <c r="B19" s="46" t="n"/>
@@ -15877,1108 +15877,912 @@
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+          <t>#TEMP_INSTRUCTION</t>
         </is>
       </c>
       <c r="D20" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Temporary (session)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>SORT_SEQ</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>CUSTOMER_CD</t>
         </is>
       </c>
-      <c r="C21" s="42" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>CUSTOMER_ORDER_NO</t>
         </is>
       </c>
-      <c r="D21" s="42" t="inlineStr">
-        <is>
-          <t>ORDER_DT</t>
-        </is>
-      </c>
-      <c r="E21" s="42" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>DESTINATION_CD</t>
         </is>
       </c>
-      <c r="F21" s="42" t="inlineStr">
-        <is>
-          <t>DETAILED_ITEM_NO</t>
-        </is>
-      </c>
-      <c r="G21" s="42" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>OPEN_ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>ASSIGNED_QTY</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>CUM_DEST_QTY</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>CUT_FLAG</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>GROUP_SEQ</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>CROSSDOCK_STATUS</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B22" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D22" s="64" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="E22" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F22" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G22" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I22" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L22" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M22" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O22" s="64" t="inlineStr">
+        <is>
+          <t>SORT_SEQ 1 = 9715300 / A-0101 / item 001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B23" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D23" s="64" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="E23" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F23" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G23" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I23" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M23" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O23" s="64" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B24" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D24" s="64" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="E24" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F24" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G24" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I24" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="L24" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M24" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O24" s="64" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B25" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="64" t="inlineStr">
+        <is>
+          <t>9722D00</t>
+        </is>
+      </c>
+      <c r="D25" s="64" t="inlineStr">
+        <is>
+          <t>B-0102</t>
+        </is>
+      </c>
+      <c r="E25" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F25" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G25" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I25" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M25" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O25" s="64" t="inlineStr">
+        <is>
+          <t>Case 2 = VN 2 + VN 2 + TH 2: no cut (VN 10, TH 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B26" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="64" t="inlineStr">
+        <is>
+          <t>9722D00</t>
+        </is>
+      </c>
+      <c r="D26" s="64" t="inlineStr">
+        <is>
+          <t>B-0102</t>
+        </is>
+      </c>
+      <c r="E26" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F26" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G26" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I26" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L26" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M26" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O26" s="64" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B27" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D27" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E27" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F27" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G27" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I27" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="L27" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M27" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O27" s="64" t="inlineStr">
+        <is>
+          <t>Cut: VN 12, TH 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B28" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D28" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E28" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F28" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G28" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H28" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I28" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="L28" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M28" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" s="66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O28" s="64" t="inlineStr">
+        <is>
+          <t>Case 4: only 2 of 6 pcs with PO1 → block 3 Not Ready, block 4 too</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B29" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D29" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E29" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F29" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G29" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" s="64" t="n"/>
+      <c r="I29" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="63" t="n">
+        <v>18</v>
+      </c>
+      <c r="L29" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M29" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" s="66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O29" s="64" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B30" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D30" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E30" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F30" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" s="64" t="n"/>
+      <c r="I30" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="63" t="n">
+        <v>24</v>
+      </c>
+      <c r="L30" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M30" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" s="66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O30" s="64" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="45" t="inlineStr">
+        <is>
+          <t>3. Supplier chooses option 1 case → [Create ASN]</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n"/>
+      <c r="C32" s="46" t="n"/>
+      <c r="D32" s="46" t="n"/>
+      <c r="E32" s="46" t="n"/>
+      <c r="F32" s="46" t="n"/>
+      <c r="G32" s="46" t="n"/>
+      <c r="H32" s="46" t="n"/>
+      <c r="I32" s="46" t="n"/>
+      <c r="J32" s="46" t="n"/>
+      <c r="K32" s="46" t="n"/>
+      <c r="L32" s="46" t="n"/>
+      <c r="M32" s="46" t="n"/>
+      <c r="N32" s="46" t="n"/>
+      <c r="O32" s="46" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D33" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B34" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>LINE_SEQ</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>SERIAL_NO</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>SHIPPING_PART_NO</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS_QTY</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>HOLD_FLAG</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>PO_MAPPED_FLAG</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>CANCEL_STATUS</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="50" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-      <c r="B22" s="51" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="C22" s="51" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B35" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="49" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="F35" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G35" s="49" t="inlineStr">
         <is>
           <t>A-0101</t>
         </is>
       </c>
-      <c r="D22" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="E22" s="51" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F22" s="51" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G22" s="51" t="inlineStr">
+      <c r="H35" s="49" t="inlineStr">
         <is>
           <t>0000001</t>
         </is>
       </c>
-      <c r="H22" s="51" t="inlineStr">
+      <c r="I35" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" s="49" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="K35" s="49" t="inlineStr">
+        <is>
+          <t>3126035921</t>
+        </is>
+      </c>
+      <c r="L35" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M35" s="49" t="n"/>
+      <c r="N35" s="49" t="n"/>
+      <c r="O35" s="49" t="inlineStr">
+        <is>
+          <t>Item 001: 6 of 8, open 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="D37" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B38" s="42" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>MAPPED_QTY</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="C39" s="49" t="inlineStr">
+        <is>
+          <t>3126035921</t>
+        </is>
+      </c>
+      <c r="D39" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E39" s="49" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="I22" s="52" t="n">
-        <v>8</v>
-      </c>
-      <c r="J22" s="51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K22" s="51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L22" s="51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M22" s="51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N22" s="51" t="inlineStr">
-        <is>
-          <t>Priority 14-Oct · SORT_SEQ 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="50" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-      <c r="B23" s="51" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="C23" s="51" t="inlineStr">
-        <is>
-          <t>A-0101</t>
-        </is>
-      </c>
-      <c r="D23" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="E23" s="51" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F23" s="51" t="inlineStr">
-        <is>
-          <t>002</t>
-        </is>
-      </c>
-      <c r="G23" s="51" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H23" s="51" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="I23" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K23" s="51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L23" s="51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M23" s="51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N23" s="51" t="inlineStr">
-        <is>
-          <t>Priority 14-Oct · SORT_SEQ 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="50" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-      <c r="B24" s="51" t="inlineStr">
-        <is>
-          <t>9722D00</t>
-        </is>
-      </c>
-      <c r="C24" s="51" t="inlineStr">
-        <is>
-          <t>B-0102</t>
-        </is>
-      </c>
-      <c r="D24" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="E24" s="51" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F24" s="51" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G24" s="51" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H24" s="51" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="I24" s="52" t="n">
+      <c r="F39" s="53" t="n">
+        <v>20</v>
+      </c>
+      <c r="G39" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="J24" s="51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K24" s="51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L24" s="51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M24" s="51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N24" s="51" t="inlineStr">
-        <is>
-          <t>Priority 14-Oct · SORT_SEQ 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="50" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-      <c r="B25" s="51" t="inlineStr">
-        <is>
-          <t>9730000</t>
-        </is>
-      </c>
-      <c r="C25" s="51" t="inlineStr">
-        <is>
-          <t>C-0103</t>
-        </is>
-      </c>
-      <c r="D25" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="E25" s="51" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F25" s="51" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G25" s="51" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H25" s="51" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="I25" s="52" t="n">
-        <v>14</v>
-      </c>
-      <c r="J25" s="51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K25" s="51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L25" s="51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M25" s="51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N25" s="51" t="inlineStr">
-        <is>
-          <t>Priority 14-Oct · SORT_SEQ 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="50" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-      <c r="B26" s="51" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="C26" s="51" t="inlineStr">
-        <is>
-          <t>A-0201</t>
-        </is>
-      </c>
-      <c r="D26" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="E26" s="51" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F26" s="51" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G26" s="51" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H26" s="51" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="I26" s="52" t="n">
-        <v>6</v>
-      </c>
-      <c r="J26" s="51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K26" s="51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L26" s="51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M26" s="51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N26" s="51" t="inlineStr">
-        <is>
-          <t>Priority 15-Oct: after all 14-Oct lines (unit 15-Oct, SORT_SEQ 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="45" t="inlineStr">
-        <is>
-          <t>2. [Search] 15-Oct (PO1 20 pcs) → XD09: SORT_SEQ, cases, blocks</t>
-        </is>
-      </c>
-      <c r="B28" s="46" t="n"/>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="46" t="n"/>
-      <c r="E28" s="46" t="n"/>
-      <c r="F28" s="46" t="n"/>
-      <c r="G28" s="46" t="n"/>
-      <c r="H28" s="46" t="n"/>
-      <c r="I28" s="46" t="n"/>
-      <c r="J28" s="46" t="n"/>
-      <c r="K28" s="46" t="n"/>
-      <c r="L28" s="46" t="n"/>
-      <c r="M28" s="46" t="n"/>
-      <c r="N28" s="46" t="n"/>
-      <c r="O28" s="46" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="35" t="inlineStr">
-        <is>
-          <t>#TEMP_INSTRUCTION</t>
-        </is>
-      </c>
-      <c r="D29" s="47" t="inlineStr">
-        <is>
-          <t>Temporary (session)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>SORT_SEQ</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>CUSTOMER_CD</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>OPEN_ORDER_QTY</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>PO_NO</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>ASSIGNED_QTY</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t>CASE_SEQ</t>
-        </is>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>CUM_DEST_QTY</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>CUT_FLAG</t>
-        </is>
-      </c>
-      <c r="M30" s="9" t="inlineStr">
-        <is>
-          <t>GROUP_SEQ</t>
-        </is>
-      </c>
-      <c r="N30" s="9" t="inlineStr">
-        <is>
-          <t>CROSSDOCK_STATUS</t>
-        </is>
-      </c>
-      <c r="O30" s="9" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B31" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="64" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="D31" s="64" t="inlineStr">
-        <is>
-          <t>A-0101</t>
-        </is>
-      </c>
-      <c r="E31" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F31" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G31" s="63" t="n">
-        <v>8</v>
-      </c>
-      <c r="H31" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I31" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="L31" s="65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M31" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O31" s="64" t="inlineStr">
-        <is>
-          <t>SORT_SEQ 1 = 9715300 / A-0101 / item 001</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B32" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="64" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="D32" s="64" t="inlineStr">
-        <is>
-          <t>A-0101</t>
-        </is>
-      </c>
-      <c r="E32" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F32" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G32" s="63" t="n">
-        <v>8</v>
-      </c>
-      <c r="H32" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I32" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" s="63" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M32" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="N32" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O32" s="64" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B33" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" s="64" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="D33" s="64" t="inlineStr">
-        <is>
-          <t>A-0101</t>
-        </is>
-      </c>
-      <c r="E33" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F33" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G33" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I33" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" s="63" t="n">
-        <v>10</v>
-      </c>
-      <c r="L33" s="64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M33" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="N33" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O33" s="64" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B34" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" s="64" t="inlineStr">
-        <is>
-          <t>9722D00</t>
-        </is>
-      </c>
-      <c r="D34" s="64" t="inlineStr">
-        <is>
-          <t>B-0102</t>
-        </is>
-      </c>
-      <c r="E34" s="64" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F34" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G34" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="H34" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I34" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" s="64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M34" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O34" s="64" t="inlineStr">
-        <is>
-          <t>Case 2 = VN 2 + VN 2 + TH 2: no cut (VN 10, TH 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B35" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" s="64" t="inlineStr">
-        <is>
-          <t>9722D00</t>
-        </is>
-      </c>
-      <c r="D35" s="64" t="inlineStr">
-        <is>
-          <t>B-0102</t>
-        </is>
-      </c>
-      <c r="E35" s="64" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F35" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G35" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="H35" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I35" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="J35" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="L35" s="64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M35" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="N35" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O35" s="64" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B36" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="C36" s="64" t="inlineStr">
-        <is>
-          <t>9730000</t>
-        </is>
-      </c>
-      <c r="D36" s="64" t="inlineStr">
-        <is>
-          <t>C-0103</t>
-        </is>
-      </c>
-      <c r="E36" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F36" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G36" s="63" t="n">
-        <v>14</v>
-      </c>
-      <c r="H36" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I36" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="K36" s="63" t="n">
-        <v>12</v>
-      </c>
-      <c r="L36" s="65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M36" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="N36" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O36" s="64" t="inlineStr">
-        <is>
-          <t>Cut: VN 12, TH 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B37" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="C37" s="64" t="inlineStr">
-        <is>
-          <t>9730000</t>
-        </is>
-      </c>
-      <c r="D37" s="64" t="inlineStr">
-        <is>
-          <t>C-0103</t>
-        </is>
-      </c>
-      <c r="E37" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F37" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G37" s="63" t="n">
-        <v>14</v>
-      </c>
-      <c r="H37" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I37" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="K37" s="63" t="n">
-        <v>14</v>
-      </c>
-      <c r="L37" s="64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M37" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="N37" s="66" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O37" s="64" t="inlineStr">
-        <is>
-          <t>Case 4: only 2 of 6 pcs with PO1 → block 3 Not Ready, block 4 too</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B38" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="C38" s="64" t="inlineStr">
-        <is>
-          <t>9730000</t>
-        </is>
-      </c>
-      <c r="D38" s="64" t="inlineStr">
-        <is>
-          <t>C-0103</t>
-        </is>
-      </c>
-      <c r="E38" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F38" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G38" s="63" t="n">
-        <v>14</v>
-      </c>
-      <c r="H38" s="64" t="n"/>
-      <c r="I38" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="J38" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="K38" s="63" t="n">
-        <v>18</v>
-      </c>
-      <c r="L38" s="65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M38" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="N38" s="66" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O38" s="64" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B39" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" s="64" t="inlineStr">
-        <is>
-          <t>9730000</t>
-        </is>
-      </c>
-      <c r="D39" s="64" t="inlineStr">
-        <is>
-          <t>C-0103</t>
-        </is>
-      </c>
-      <c r="E39" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F39" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G39" s="63" t="n">
-        <v>14</v>
-      </c>
-      <c r="H39" s="64" t="n"/>
-      <c r="I39" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="J39" s="63" t="n">
-        <v>5</v>
-      </c>
-      <c r="K39" s="63" t="n">
-        <v>24</v>
-      </c>
-      <c r="L39" s="65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M39" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="N39" s="66" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O39" s="64" t="inlineStr"/>
+      <c r="H39" s="49" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="45" t="inlineStr">
         <is>
-          <t>3. Supplier chooses option 1 case → [Create ASN]</t>
+          <t>4. [Search] 16-Oct (PO1 open 14 + PO2 10) → open qty cut again from case 1</t>
         </is>
       </c>
       <c r="B41" s="46" t="n"/>
@@ -16999,903 +16803,644 @@
     <row r="42">
       <c r="A42" s="35" t="inlineStr">
         <is>
-          <t>TB_R_INSTRUCTION</t>
+          <t>#TEMP_INSTRUCTION</t>
         </is>
       </c>
       <c r="D42" s="47" t="inlineStr">
         <is>
-          <t>New table (Crossdock)</t>
+          <t>Temporary (session)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B43" s="42" t="inlineStr">
-        <is>
-          <t>INSTRUCTION_ID</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>SORT_SEQ</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>OPEN_ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>ASSIGNED_QTY</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>CASE_SEQ</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>LINE_SEQ</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>SERIAL_NO</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>QTY</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>PO_NO</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_NO</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_ITEM</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>ASN_NO</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>CASE_NO</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>CUM_DEST_QTY</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>CUT_FLAG</t>
+        </is>
+      </c>
+      <c r="M43" s="9" t="inlineStr">
+        <is>
+          <t>GROUP_SEQ</t>
+        </is>
+      </c>
+      <c r="N43" s="9" t="inlineStr">
+        <is>
+          <t>CROSSDOCK_STATUS</t>
+        </is>
+      </c>
+      <c r="O43" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B44" s="53" t="n">
+      <c r="A44" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B44" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="53" t="n">
+      <c r="C44" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D44" s="64" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="E44" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F44" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G44" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I44" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="53" t="n">
+      <c r="K44" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M44" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="49" t="inlineStr">
+      <c r="N44" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O44" s="64" t="inlineStr">
+        <is>
+          <t>Open qty 8 - 6 = 2; case 1 = the same physical case as case 2 on 15-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B45" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D45" s="64" t="inlineStr">
+        <is>
+          <t>A-0101</t>
+        </is>
+      </c>
+      <c r="E45" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F45" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="F44" s="49" t="inlineStr">
+      <c r="G45" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I45" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="L45" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M45" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O45" s="64" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B46" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" s="64" t="inlineStr">
+        <is>
+          <t>9722D00</t>
+        </is>
+      </c>
+      <c r="D46" s="64" t="inlineStr">
+        <is>
+          <t>B-0102</t>
+        </is>
+      </c>
+      <c r="E46" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F46" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G46" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I46" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M46" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O46" s="64" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B47" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="64" t="inlineStr">
+        <is>
+          <t>9722D00</t>
+        </is>
+      </c>
+      <c r="D47" s="64" t="inlineStr">
+        <is>
+          <t>B-0102</t>
+        </is>
+      </c>
+      <c r="E47" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F47" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G47" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H47" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I47" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L47" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M47" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O47" s="64" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B48" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D48" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E48" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="G44" s="49" t="inlineStr">
-        <is>
-          <t>A-0101</t>
-        </is>
-      </c>
-      <c r="H44" s="49" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="I44" s="53" t="n">
+      <c r="F48" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G48" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H48" s="64" t="inlineStr">
+        <is>
+          <t>T0409021</t>
+        </is>
+      </c>
+      <c r="I48" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="J44" s="49" t="inlineStr">
+      <c r="L48" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M48" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O48" s="64" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B49" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D49" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E49" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F49" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G49" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H49" s="64" t="inlineStr">
         <is>
           <t>T0409021</t>
         </is>
       </c>
-      <c r="K44" s="49" t="inlineStr">
-        <is>
-          <t>3126035921</t>
-        </is>
-      </c>
-      <c r="L44" s="49" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="M44" s="49" t="n"/>
-      <c r="N44" s="49" t="n"/>
-      <c r="O44" s="49" t="inlineStr">
-        <is>
-          <t>Item 001: 6 of 8, open 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
-        </is>
-      </c>
-      <c r="D46" s="47" t="inlineStr">
-        <is>
-          <t>New table (Crossdock)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B47" s="42" t="inlineStr">
-        <is>
-          <t>PO_NO</t>
-        </is>
-      </c>
-      <c r="C47" s="42" t="inlineStr">
-        <is>
-          <t>MANIFEST_NO</t>
-        </is>
-      </c>
-      <c r="D47" s="42" t="inlineStr">
-        <is>
-          <t>MANIFEST_ITEM</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>ORDER_QTY</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>MAPPED_QTY</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B48" s="49" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="C48" s="49" t="inlineStr">
-        <is>
-          <t>3126035921</t>
-        </is>
-      </c>
-      <c r="D48" s="49" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="E48" s="49" t="inlineStr">
+      <c r="I49" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K49" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="L49" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M49" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O49" s="64" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B50" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D50" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E50" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F50" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="F48" s="53" t="n">
-        <v>20</v>
-      </c>
-      <c r="G48" s="53" t="n">
+      <c r="G50" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H50" s="64" t="inlineStr">
+        <is>
+          <t>T0410021</t>
+        </is>
+      </c>
+      <c r="I50" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="L50" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M50" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N50" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O50" s="64" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B51" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" s="64" t="inlineStr">
+        <is>
+          <t>9730000</t>
+        </is>
+      </c>
+      <c r="D51" s="64" t="inlineStr">
+        <is>
+          <t>C-0103</t>
+        </is>
+      </c>
+      <c r="E51" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F51" s="64" t="inlineStr">
+        <is>
+          <t>PART-B</t>
+        </is>
+      </c>
+      <c r="G51" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H51" s="64" t="inlineStr">
+        <is>
+          <t>T0410021</t>
+        </is>
+      </c>
+      <c r="I51" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="H48" s="49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="45" t="inlineStr">
-        <is>
-          <t>4. [Search] 16-Oct (PO1 open 14 + PO2 10) → open qty cut again from case 1</t>
-        </is>
-      </c>
-      <c r="B50" s="46" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
-      <c r="E50" s="46" t="n"/>
-      <c r="F50" s="46" t="n"/>
-      <c r="G50" s="46" t="n"/>
-      <c r="H50" s="46" t="n"/>
-      <c r="I50" s="46" t="n"/>
-      <c r="J50" s="46" t="n"/>
-      <c r="K50" s="46" t="n"/>
-      <c r="L50" s="46" t="n"/>
-      <c r="M50" s="46" t="n"/>
-      <c r="N50" s="46" t="n"/>
-      <c r="O50" s="46" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="35" t="inlineStr">
-        <is>
-          <t>#TEMP_INSTRUCTION</t>
-        </is>
-      </c>
-      <c r="D51" s="47" t="inlineStr">
-        <is>
-          <t>Temporary (session)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>SORT_SEQ</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>CUSTOMER_CD</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>OPEN_ORDER_QTY</t>
-        </is>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>PO_NO</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>ASSIGNED_QTY</t>
-        </is>
-      </c>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t>CASE_SEQ</t>
-        </is>
-      </c>
-      <c r="K52" s="9" t="inlineStr">
-        <is>
-          <t>CUM_DEST_QTY</t>
-        </is>
-      </c>
-      <c r="L52" s="9" t="inlineStr">
-        <is>
-          <t>CUT_FLAG</t>
-        </is>
-      </c>
-      <c r="M52" s="9" t="inlineStr">
-        <is>
-          <t>GROUP_SEQ</t>
-        </is>
-      </c>
-      <c r="N52" s="9" t="inlineStr">
-        <is>
-          <t>CROSSDOCK_STATUS</t>
-        </is>
-      </c>
-      <c r="O52" s="9" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="62" t="inlineStr">
+      <c r="J51" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="K51" s="63" t="n">
+        <v>18</v>
+      </c>
+      <c r="L51" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M51" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="N51" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O51" s="64" t="inlineStr">
+        <is>
+          <t>Unit 14-Oct: all 3 blocks Ready (options 2 / 3 / 4 cases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="62" t="inlineStr">
         <is>
           <t>TEMP</t>
         </is>
       </c>
-      <c r="B53" s="63" t="n">
+      <c r="B52" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="64" t="inlineStr">
+      <c r="C52" s="64" t="inlineStr">
         <is>
           <t>9715300</t>
         </is>
       </c>
-      <c r="D53" s="64" t="inlineStr">
-        <is>
-          <t>A-0101</t>
-        </is>
-      </c>
-      <c r="E53" s="64" t="inlineStr">
+      <c r="D52" s="64" t="inlineStr">
+        <is>
+          <t>A-0201</t>
+        </is>
+      </c>
+      <c r="E52" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F53" s="64" t="inlineStr">
+      <c r="F52" s="64" t="inlineStr">
         <is>
           <t>PART-B</t>
         </is>
       </c>
-      <c r="G53" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="H53" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I53" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J53" s="63" t="n">
+      <c r="G52" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" s="64" t="n"/>
+      <c r="I52" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J52" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="K53" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="L53" s="64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M53" s="63" t="n">
+      <c r="K52" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L52" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M52" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N53" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O53" s="64" t="inlineStr">
-        <is>
-          <t>Open qty 8 - 6 = 2; case 1 = the same physical case as case 2 on 15-Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B54" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" s="64" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="D54" s="64" t="inlineStr">
-        <is>
-          <t>A-0101</t>
-        </is>
-      </c>
-      <c r="E54" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F54" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G54" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I54" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="L54" s="64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M54" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O54" s="64" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B55" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="C55" s="64" t="inlineStr">
-        <is>
-          <t>9722D00</t>
-        </is>
-      </c>
-      <c r="D55" s="64" t="inlineStr">
-        <is>
-          <t>B-0102</t>
-        </is>
-      </c>
-      <c r="E55" s="64" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F55" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G55" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="H55" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I55" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="L55" s="64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M55" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O55" s="64" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B56" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="C56" s="64" t="inlineStr">
-        <is>
-          <t>9722D00</t>
-        </is>
-      </c>
-      <c r="D56" s="64" t="inlineStr">
-        <is>
-          <t>B-0102</t>
-        </is>
-      </c>
-      <c r="E56" s="64" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F56" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G56" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="H56" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I56" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="J56" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="K56" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="L56" s="64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M56" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O56" s="64" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B57" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="C57" s="64" t="inlineStr">
-        <is>
-          <t>9730000</t>
-        </is>
-      </c>
-      <c r="D57" s="64" t="inlineStr">
-        <is>
-          <t>C-0103</t>
-        </is>
-      </c>
-      <c r="E57" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F57" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G57" s="63" t="n">
-        <v>14</v>
-      </c>
-      <c r="H57" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I57" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="K57" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="L57" s="65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M57" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O57" s="64" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B58" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="C58" s="64" t="inlineStr">
-        <is>
-          <t>9730000</t>
-        </is>
-      </c>
-      <c r="D58" s="64" t="inlineStr">
-        <is>
-          <t>C-0103</t>
-        </is>
-      </c>
-      <c r="E58" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F58" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G58" s="63" t="n">
-        <v>14</v>
-      </c>
-      <c r="H58" s="64" t="inlineStr">
-        <is>
-          <t>T0409021</t>
-        </is>
-      </c>
-      <c r="I58" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="K58" s="63" t="n">
-        <v>8</v>
-      </c>
-      <c r="L58" s="64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M58" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="N58" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O58" s="64" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B59" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="C59" s="64" t="inlineStr">
-        <is>
-          <t>9730000</t>
-        </is>
-      </c>
-      <c r="D59" s="64" t="inlineStr">
-        <is>
-          <t>C-0103</t>
-        </is>
-      </c>
-      <c r="E59" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F59" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G59" s="63" t="n">
-        <v>14</v>
-      </c>
-      <c r="H59" s="64" t="inlineStr">
-        <is>
-          <t>T0410021</t>
-        </is>
-      </c>
-      <c r="I59" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="J59" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="K59" s="63" t="n">
-        <v>12</v>
-      </c>
-      <c r="L59" s="65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M59" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="N59" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O59" s="64" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B60" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="C60" s="64" t="inlineStr">
-        <is>
-          <t>9730000</t>
-        </is>
-      </c>
-      <c r="D60" s="64" t="inlineStr">
-        <is>
-          <t>C-0103</t>
-        </is>
-      </c>
-      <c r="E60" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F60" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G60" s="63" t="n">
-        <v>14</v>
-      </c>
-      <c r="H60" s="64" t="inlineStr">
-        <is>
-          <t>T0410021</t>
-        </is>
-      </c>
-      <c r="I60" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="J60" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="K60" s="63" t="n">
-        <v>18</v>
-      </c>
-      <c r="L60" s="65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M60" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="N60" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O60" s="64" t="inlineStr">
-        <is>
-          <t>Unit 14-Oct: all 3 blocks Ready (options 2 / 3 / 4 cases)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B61" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="64" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="D61" s="64" t="inlineStr">
-        <is>
-          <t>A-0201</t>
-        </is>
-      </c>
-      <c r="E61" s="64" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F61" s="64" t="inlineStr">
-        <is>
-          <t>PART-B</t>
-        </is>
-      </c>
-      <c r="G61" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="H61" s="64" t="n"/>
-      <c r="I61" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="J61" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="L61" s="65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M61" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N61" s="66" t="inlineStr">
+      <c r="N52" s="66" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O61" s="64" t="inlineStr">
+      <c r="O52" s="64" t="inlineStr">
         <is>
           <t>Unit 15-Oct after unit 14-Oct (way B): no PO left</t>
         </is>
@@ -34922,7 +34467,7 @@
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>PART-B, 6 pcs/case. Scan order = G-System allocation order with Allocation Priority = Customer Order Date: 1) Allocation Priority, 2) Customer Code, 3) Customer Order No, 4) Order Date, 5) Order Time, 6) Destination, 7) Detailed Item No, 8) Serial No. Keys 2-8 are the PK of the H0253 replicate; XD09 reads with ORDER BY Part, Allocation Priority + the PK columns (query in XD09 Appendix). SORT_SEQ = row number per unit. Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. A-0201 (15-Oct) is in the middle of the PK order but after all 14-Oct lines in the scan order (Allocation Priority). 15-Oct: PO1 20 pcs → blocks 1-2 Ready, block 3 (case 4) only 2 of 6 pcs with PO → Not Ready. The supplier sends option 1 case only. 16-Oct: PO2 10 pcs. The open qty (24) is cut again from case 1 in the same SORT_SEQ: the cases are the same as before. Unit 15-Oct (A-0201) comes after unit 14-Oct (way B), so it gets no PO yet.</t>
+          <t>PART-B, 6 pcs/case. Scan order = G-System allocation order with Allocation Priority = Customer Order Date: 1) Allocation Priority, 2) Customer Code, 3) Customer Order No, 4) Order Date, 5) Order Time, 6) Destination, 7) Detailed Item No, 8) Serial No. Keys 2-8 are the PK of the H0253 replicate; XD09 reads with ORDER BY Part, Allocation Priority + the PK columns (query in XD09 Appendix). SORT_SEQ = row number per unit. Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. A-0201 (15-Oct) comes after all 14-Oct lines (Allocation Priority) and is the next unit. 15-Oct: PO1 20 pcs → blocks 1-2 Ready, block 3 (case 4) only 2 of 6 pcs with PO → Not Ready. The supplier sends option 1 case only. 16-Oct: PO2 10 pcs. The open qty (24) is cut again from case 1 in the same SORT_SEQ: the cases are the same as before. Unit 15-Oct (A-0201) comes after unit 14-Oct (way B), so it gets no PO yet.</t>
         </is>
       </c>
     </row>

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-8" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Column Definition'!$A$3:$H$467</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Column Definition'!$A$3:$H$468</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8701,12 +8701,12 @@
       </c>
       <c r="R74" s="26" t="inlineStr">
         <is>
-          <t>CUT_FLAG</t>
+          <t>SEQ_QTY</t>
         </is>
       </c>
       <c r="S74" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(1)</t>
+          <t>NUMBER(4)</t>
         </is>
       </c>
       <c r="T74" s="27" t="inlineStr"/>
@@ -8744,12 +8744,12 @@
       </c>
       <c r="R75" s="26" t="inlineStr">
         <is>
-          <t>GROUP_SEQ</t>
+          <t>CUT_FLAG</t>
         </is>
       </c>
       <c r="S75" s="26" t="inlineStr">
         <is>
-          <t>NUMBER(4)</t>
+          <t>VARCHAR(1)</t>
         </is>
       </c>
       <c r="T75" s="27" t="inlineStr"/>
@@ -8783,12 +8783,12 @@
       <c r="P76" s="19" t="inlineStr"/>
       <c r="R76" s="26" t="inlineStr">
         <is>
-          <t>CROSSDOCK_STATUS</t>
+          <t>GROUP_SEQ</t>
         </is>
       </c>
       <c r="S76" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR(1)</t>
+          <t>NUMBER(4)</t>
         </is>
       </c>
       <c r="T76" s="27" t="inlineStr"/>
@@ -8823,6 +8823,17 @@
         </is>
       </c>
       <c r="P77" s="19" t="inlineStr"/>
+      <c r="R77" s="26" t="inlineStr">
+        <is>
+          <t>CROSSDOCK_STATUS</t>
+        </is>
+      </c>
+      <c r="S77" s="26" t="inlineStr">
+        <is>
+          <t>VARCHAR(1)</t>
+        </is>
+      </c>
+      <c r="T77" s="27" t="inlineStr"/>
       <c r="V77" s="18" t="inlineStr">
         <is>
           <t>PART_NO</t>
@@ -12684,7 +12695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -12701,7 +12712,8 @@
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12816,6 +12828,7 @@
       <c r="M9" s="46" t="n"/>
       <c r="N9" s="46" t="n"/>
       <c r="O9" s="46" t="n"/>
+      <c r="P9" s="46" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -13213,6 +13226,7 @@
       <c r="M20" s="46" t="n"/>
       <c r="N20" s="46" t="n"/>
       <c r="O20" s="46" t="n"/>
+      <c r="P20" s="46" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
@@ -13284,20 +13298,25 @@
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
+          <t>SEQ_QTY</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
           <t>CUT_FLAG</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="N22" s="9" t="inlineStr">
         <is>
           <t>GROUP_SEQ</t>
         </is>
       </c>
-      <c r="N22" s="9" t="inlineStr">
+      <c r="O22" s="9" t="inlineStr">
         <is>
           <t>CROSSDOCK_STATUS</t>
         </is>
       </c>
-      <c r="O22" s="9" t="inlineStr">
+      <c r="P22" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -13349,20 +13368,23 @@
       <c r="K23" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L23" s="65" t="inlineStr">
+      <c r="L23" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M23" s="63" t="n">
+      <c r="N23" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="49" t="inlineStr">
+      <c r="O23" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O23" s="64" t="inlineStr"/>
+      <c r="P23" s="64" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="62" t="inlineStr">
@@ -13410,20 +13432,23 @@
       <c r="K24" s="63" t="n">
         <v>10</v>
       </c>
-      <c r="L24" s="64" t="inlineStr">
+      <c r="L24" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M24" s="63" t="n">
+      <c r="N24" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N24" s="49" t="inlineStr">
+      <c r="O24" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O24" s="64" t="inlineStr">
+      <c r="P24" s="64" t="inlineStr">
         <is>
           <t>Case 2 = VN 4 + TH 2: no cut (VN 10, TH 2)</t>
         </is>
@@ -13475,20 +13500,23 @@
       <c r="K25" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="L25" s="64" t="inlineStr">
+      <c r="L25" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M25" s="63" t="n">
+      <c r="N25" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="49" t="inlineStr">
+      <c r="O25" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O25" s="64" t="inlineStr"/>
+      <c r="P25" s="64" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="62" t="inlineStr">
@@ -13536,20 +13564,23 @@
       <c r="K26" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L26" s="64" t="inlineStr">
+      <c r="L26" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M26" s="63" t="n">
+      <c r="N26" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N26" s="49" t="inlineStr">
+      <c r="O26" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O26" s="64" t="inlineStr"/>
+      <c r="P26" s="64" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="62" t="inlineStr">
@@ -13597,20 +13628,23 @@
       <c r="K27" s="63" t="n">
         <v>12</v>
       </c>
-      <c r="L27" s="65" t="inlineStr">
+      <c r="L27" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M27" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M27" s="63" t="n">
+      <c r="N27" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N27" s="49" t="inlineStr">
+      <c r="O27" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O27" s="64" t="inlineStr">
+      <c r="P27" s="64" t="inlineStr">
         <is>
           <t>Cut: VN 12, TH 6</t>
         </is>
@@ -13662,20 +13696,23 @@
       <c r="K28" s="63" t="n">
         <v>18</v>
       </c>
-      <c r="L28" s="65" t="inlineStr">
+      <c r="L28" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M28" s="63" t="n">
+      <c r="N28" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N28" s="49" t="inlineStr">
+      <c r="O28" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O28" s="64" t="inlineStr"/>
+      <c r="P28" s="64" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="62" t="inlineStr">
@@ -13719,20 +13756,23 @@
       <c r="K29" s="63" t="n">
         <v>24</v>
       </c>
-      <c r="L29" s="65" t="inlineStr">
+      <c r="L29" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M29" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M29" s="63" t="n">
+      <c r="N29" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="N29" s="66" t="inlineStr">
+      <c r="O29" s="66" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O29" s="64" t="inlineStr">
+      <c r="P29" s="64" t="inlineStr">
         <is>
           <t>No PO yet: block 4 Not Ready</t>
         </is>
@@ -13758,6 +13798,7 @@
       <c r="M31" s="46" t="n"/>
       <c r="N31" s="46" t="n"/>
       <c r="O31" s="46" t="n"/>
+      <c r="P31" s="46" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="35" t="inlineStr">
@@ -14592,6 +14633,7 @@
       <c r="M51" s="46" t="n"/>
       <c r="N51" s="46" t="n"/>
       <c r="O51" s="46" t="n"/>
+      <c r="P51" s="46" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="35" t="inlineStr">
@@ -14703,6 +14745,7 @@
       <c r="M56" s="46" t="n"/>
       <c r="N56" s="46" t="n"/>
       <c r="O56" s="46" t="n"/>
+      <c r="P56" s="46" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="35" t="inlineStr">
@@ -14774,20 +14817,25 @@
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
+          <t>SEQ_QTY</t>
+        </is>
+      </c>
+      <c r="M58" s="9" t="inlineStr">
+        <is>
           <t>CUT_FLAG</t>
         </is>
       </c>
-      <c r="M58" s="9" t="inlineStr">
+      <c r="N58" s="9" t="inlineStr">
         <is>
           <t>GROUP_SEQ</t>
         </is>
       </c>
-      <c r="N58" s="9" t="inlineStr">
+      <c r="O58" s="9" t="inlineStr">
         <is>
           <t>CROSSDOCK_STATUS</t>
         </is>
       </c>
-      <c r="O58" s="9" t="inlineStr">
+      <c r="P58" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -14839,20 +14887,23 @@
       <c r="K59" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L59" s="65" t="inlineStr">
+      <c r="L59" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M59" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M59" s="63" t="n">
+      <c r="N59" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N59" s="49" t="inlineStr">
+      <c r="O59" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O59" s="64" t="inlineStr">
+      <c r="P59" s="64" t="inlineStr">
         <is>
           <t>OPEN_ORDER_QTY = 14 - 8 in TB_R_INSTRUCTION</t>
         </is>
@@ -14878,6 +14929,7 @@
       <c r="M61" s="46" t="n"/>
       <c r="N61" s="46" t="n"/>
       <c r="O61" s="46" t="n"/>
+      <c r="P61" s="46" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="35" t="inlineStr">
@@ -15279,7 +15331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -15296,7 +15348,8 @@
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15418,6 +15471,7 @@
       <c r="M10" s="46" t="n"/>
       <c r="N10" s="46" t="n"/>
       <c r="O10" s="46" t="n"/>
+      <c r="P10" s="46" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -15873,6 +15927,7 @@
       <c r="M19" s="46" t="n"/>
       <c r="N19" s="46" t="n"/>
       <c r="O19" s="46" t="n"/>
+      <c r="P19" s="46" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
@@ -15944,20 +15999,25 @@
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
+          <t>SEQ_QTY</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
           <t>CUT_FLAG</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>GROUP_SEQ</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="O21" s="9" t="inlineStr">
         <is>
           <t>CROSSDOCK_STATUS</t>
         </is>
       </c>
-      <c r="O21" s="9" t="inlineStr">
+      <c r="P21" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -16009,20 +16069,23 @@
       <c r="K22" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L22" s="65" t="inlineStr">
+      <c r="L22" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M22" s="63" t="n">
+      <c r="N22" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="49" t="inlineStr">
+      <c r="O22" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O22" s="64" t="inlineStr">
+      <c r="P22" s="64" t="inlineStr">
         <is>
           <t>SORT_SEQ 1 = 9715300 / A-0101 / item 001</t>
         </is>
@@ -16074,20 +16137,23 @@
       <c r="K23" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="L23" s="64" t="inlineStr">
+      <c r="L23" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M23" s="63" t="n">
+      <c r="N23" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N23" s="49" t="inlineStr">
+      <c r="O23" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O23" s="64" t="inlineStr"/>
+      <c r="P23" s="64" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="62" t="inlineStr">
@@ -16135,20 +16201,23 @@
       <c r="K24" s="63" t="n">
         <v>10</v>
       </c>
-      <c r="L24" s="64" t="inlineStr">
+      <c r="L24" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M24" s="63" t="n">
+      <c r="N24" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N24" s="49" t="inlineStr">
+      <c r="O24" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O24" s="64" t="inlineStr"/>
+      <c r="P24" s="64" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="62" t="inlineStr">
@@ -16196,20 +16265,23 @@
       <c r="K25" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="L25" s="64" t="inlineStr">
+      <c r="L25" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M25" s="63" t="n">
+      <c r="N25" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="49" t="inlineStr">
+      <c r="O25" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O25" s="64" t="inlineStr">
+      <c r="P25" s="64" t="inlineStr">
         <is>
           <t>Case 2 = VN 2 + VN 2 + TH 2: no cut (VN 10, TH 2)</t>
         </is>
@@ -16261,20 +16333,23 @@
       <c r="K26" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L26" s="64" t="inlineStr">
+      <c r="L26" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M26" s="63" t="n">
+      <c r="N26" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N26" s="49" t="inlineStr">
+      <c r="O26" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O26" s="64" t="inlineStr"/>
+      <c r="P26" s="64" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="62" t="inlineStr">
@@ -16322,20 +16397,23 @@
       <c r="K27" s="63" t="n">
         <v>12</v>
       </c>
-      <c r="L27" s="65" t="inlineStr">
+      <c r="L27" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M27" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M27" s="63" t="n">
+      <c r="N27" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N27" s="49" t="inlineStr">
+      <c r="O27" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O27" s="64" t="inlineStr">
+      <c r="P27" s="64" t="inlineStr">
         <is>
           <t>Cut: VN 12, TH 6</t>
         </is>
@@ -16387,20 +16465,23 @@
       <c r="K28" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="L28" s="64" t="inlineStr">
+      <c r="L28" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M28" s="63" t="n">
+      <c r="N28" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N28" s="66" t="inlineStr">
+      <c r="O28" s="66" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O28" s="64" t="inlineStr">
+      <c r="P28" s="64" t="inlineStr">
         <is>
           <t>Case 4: only 2 of 6 pcs with PO1 → block 3 Not Ready, block 4 too</t>
         </is>
@@ -16448,20 +16529,23 @@
       <c r="K29" s="63" t="n">
         <v>18</v>
       </c>
-      <c r="L29" s="65" t="inlineStr">
+      <c r="L29" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M29" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M29" s="63" t="n">
+      <c r="N29" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N29" s="66" t="inlineStr">
+      <c r="O29" s="66" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O29" s="64" t="inlineStr"/>
+      <c r="P29" s="64" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="62" t="inlineStr">
@@ -16505,20 +16589,23 @@
       <c r="K30" s="63" t="n">
         <v>24</v>
       </c>
-      <c r="L30" s="65" t="inlineStr">
+      <c r="L30" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M30" s="63" t="n">
+      <c r="N30" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="N30" s="66" t="inlineStr">
+      <c r="O30" s="66" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O30" s="64" t="inlineStr"/>
+      <c r="P30" s="64" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="45" t="inlineStr">
@@ -16540,6 +16627,7 @@
       <c r="M32" s="46" t="n"/>
       <c r="N32" s="46" t="n"/>
       <c r="O32" s="46" t="n"/>
+      <c r="P32" s="46" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="35" t="inlineStr">
@@ -16799,6 +16887,7 @@
       <c r="M41" s="46" t="n"/>
       <c r="N41" s="46" t="n"/>
       <c r="O41" s="46" t="n"/>
+      <c r="P41" s="46" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="35" t="inlineStr">
@@ -16870,20 +16959,25 @@
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
+          <t>SEQ_QTY</t>
+        </is>
+      </c>
+      <c r="M43" s="9" t="inlineStr">
+        <is>
           <t>CUT_FLAG</t>
         </is>
       </c>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="N43" s="9" t="inlineStr">
         <is>
           <t>GROUP_SEQ</t>
         </is>
       </c>
-      <c r="N43" s="9" t="inlineStr">
+      <c r="O43" s="9" t="inlineStr">
         <is>
           <t>CROSSDOCK_STATUS</t>
         </is>
       </c>
-      <c r="O43" s="9" t="inlineStr">
+      <c r="P43" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -16935,20 +17029,23 @@
       <c r="K44" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="L44" s="64" t="inlineStr">
+      <c r="L44" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M44" s="63" t="n">
+      <c r="N44" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N44" s="49" t="inlineStr">
+      <c r="O44" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O44" s="64" t="inlineStr">
+      <c r="P44" s="64" t="inlineStr">
         <is>
           <t>Open qty 8 - 6 = 2; case 1 = the same physical case as case 2 on 15-Oct</t>
         </is>
@@ -17000,20 +17097,23 @@
       <c r="K45" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="L45" s="64" t="inlineStr">
+      <c r="L45" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="M45" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M45" s="63" t="n">
+      <c r="N45" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N45" s="49" t="inlineStr">
+      <c r="O45" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O45" s="64" t="inlineStr"/>
+      <c r="P45" s="64" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="62" t="inlineStr">
@@ -17061,20 +17161,23 @@
       <c r="K46" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="L46" s="64" t="inlineStr">
+      <c r="L46" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M46" s="63" t="n">
+      <c r="N46" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N46" s="49" t="inlineStr">
+      <c r="O46" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O46" s="64" t="inlineStr"/>
+      <c r="P46" s="64" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="62" t="inlineStr">
@@ -17122,20 +17225,23 @@
       <c r="K47" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L47" s="64" t="inlineStr">
+      <c r="L47" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M47" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M47" s="63" t="n">
+      <c r="N47" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="49" t="inlineStr">
+      <c r="O47" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O47" s="64" t="inlineStr"/>
+      <c r="P47" s="64" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="62" t="inlineStr">
@@ -17183,20 +17289,23 @@
       <c r="K48" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L48" s="65" t="inlineStr">
+      <c r="L48" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M48" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M48" s="63" t="n">
+      <c r="N48" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N48" s="49" t="inlineStr">
+      <c r="O48" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O48" s="64" t="inlineStr"/>
+      <c r="P48" s="64" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="62" t="inlineStr">
@@ -17244,20 +17353,23 @@
       <c r="K49" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="L49" s="64" t="inlineStr">
+      <c r="L49" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M49" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M49" s="63" t="n">
+      <c r="N49" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N49" s="49" t="inlineStr">
+      <c r="O49" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O49" s="64" t="inlineStr"/>
+      <c r="P49" s="64" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="62" t="inlineStr">
@@ -17305,20 +17417,23 @@
       <c r="K50" s="63" t="n">
         <v>12</v>
       </c>
-      <c r="L50" s="65" t="inlineStr">
+      <c r="L50" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M50" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M50" s="63" t="n">
+      <c r="N50" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N50" s="49" t="inlineStr">
+      <c r="O50" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O50" s="64" t="inlineStr"/>
+      <c r="P50" s="64" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="62" t="inlineStr">
@@ -17366,20 +17481,23 @@
       <c r="K51" s="63" t="n">
         <v>18</v>
       </c>
-      <c r="L51" s="65" t="inlineStr">
+      <c r="L51" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M51" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M51" s="63" t="n">
+      <c r="N51" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N51" s="49" t="inlineStr">
+      <c r="O51" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O51" s="64" t="inlineStr">
+      <c r="P51" s="64" t="inlineStr">
         <is>
           <t>Unit 14-Oct: all 3 blocks Ready (options 2 / 3 / 4 cases)</t>
         </is>
@@ -17427,20 +17545,23 @@
       <c r="K52" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L52" s="65" t="inlineStr">
+      <c r="L52" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M52" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M52" s="63" t="n">
+      <c r="N52" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N52" s="66" t="inlineStr">
+      <c r="O52" s="66" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O52" s="64" t="inlineStr">
+      <c r="P52" s="64" t="inlineStr">
         <is>
           <t>Unit 15-Oct after unit 14-Oct (way B): no PO left</t>
         </is>
@@ -18863,7 +18984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H467"/>
+  <dimension ref="A1:H468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -27316,12 +27437,12 @@
       </c>
       <c r="C257" s="32" t="inlineStr">
         <is>
-          <t>CUT_FLAG</t>
+          <t>SEQ_QTY</t>
         </is>
       </c>
       <c r="D257" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(1)</t>
+          <t>NUMBER(4)</t>
         </is>
       </c>
       <c r="E257" s="32" t="inlineStr"/>
@@ -27333,7 +27454,7 @@
       </c>
       <c r="H257" s="32" t="inlineStr">
         <is>
-          <t>'Y' on the last slice of a case after which the ASN may stop (every destination a multiple of PCS_CASE)</t>
+          <t>Fill of the warehouse case (1 case = 1 destination) of the destination after this slice: 1..PCS_CASE, starts again after PCS_CASE</t>
         </is>
       </c>
     </row>
@@ -27348,12 +27469,12 @@
       </c>
       <c r="C258" s="32" t="inlineStr">
         <is>
-          <t>GROUP_SEQ</t>
+          <t>CUT_FLAG</t>
         </is>
       </c>
       <c r="D258" s="32" t="inlineStr">
         <is>
-          <t>NUMBER(4)</t>
+          <t>VARCHAR(1)</t>
         </is>
       </c>
       <c r="E258" s="32" t="inlineStr"/>
@@ -27365,7 +27486,7 @@
       </c>
       <c r="H258" s="32" t="inlineStr">
         <is>
-          <t>Block (ASN option) of the slice: the cases up to and including a valid cut</t>
+          <t>'Y' on the last slice of a case after which the ASN may stop (every destination a multiple of PCS_CASE)</t>
         </is>
       </c>
     </row>
@@ -27380,12 +27501,12 @@
       </c>
       <c r="C259" s="32" t="inlineStr">
         <is>
-          <t>CROSSDOCK_STATUS</t>
+          <t>GROUP_SEQ</t>
         </is>
       </c>
       <c r="D259" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(1)</t>
+          <t>NUMBER(4)</t>
         </is>
       </c>
       <c r="E259" s="32" t="inlineStr"/>
@@ -27397,39 +27518,39 @@
       </c>
       <c r="H259" s="32" t="inlineStr">
         <is>
-          <t>Status of the block: '6' Ready (the block and every earlier block have a PO) / '7' Not Ready</t>
+          <t>Block (ASN option) of the slice: the cases up to and including a valid cut</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="32" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
+          <t>#TEMP_INSTRUCTION</t>
         </is>
       </c>
       <c r="B260" s="31" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="C260" s="32" t="inlineStr">
         <is>
-          <t>DEPOT_CD</t>
+          <t>CROSSDOCK_STATUS</t>
         </is>
       </c>
       <c r="D260" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(2)</t>
+          <t>VARCHAR(1)</t>
         </is>
       </c>
       <c r="E260" s="32" t="inlineStr"/>
       <c r="F260" s="32" t="inlineStr"/>
       <c r="G260" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H260" s="32" t="inlineStr">
         <is>
-          <t>DEPOT CD; values: 01</t>
+          <t>Status of the block: '6' Ready (the block and every earlier block have a PO) / '7' Not Ready</t>
         </is>
       </c>
     </row>
@@ -27440,28 +27561,28 @@
         </is>
       </c>
       <c r="B261" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C261" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_CD</t>
+          <t>DEPOT_CD</t>
         </is>
       </c>
       <c r="D261" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(4)</t>
+          <t>VARCHAR(2)</t>
         </is>
       </c>
       <c r="E261" s="32" t="inlineStr"/>
       <c r="F261" s="32" t="inlineStr"/>
       <c r="G261" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H261" s="32" t="inlineStr">
         <is>
-          <t>Supplier code (4 characters in the sample); SUPPLIER CD</t>
+          <t>DEPOT CD; values: 01</t>
         </is>
       </c>
     </row>
@@ -27472,16 +27593,16 @@
         </is>
       </c>
       <c r="B262" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C262" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_PLANT</t>
+          <t>SUPPLIER_CD</t>
         </is>
       </c>
       <c r="D262" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(1)</t>
+          <t>VARCHAR(4)</t>
         </is>
       </c>
       <c r="E262" s="32" t="inlineStr"/>
@@ -27493,7 +27614,7 @@
       </c>
       <c r="H262" s="32" t="inlineStr">
         <is>
-          <t>Supplier plant; SUPPLIER PLANT</t>
+          <t>Supplier code (4 characters in the sample); SUPPLIER CD</t>
         </is>
       </c>
     </row>
@@ -27504,28 +27625,28 @@
         </is>
       </c>
       <c r="B263" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C263" s="32" t="inlineStr">
         <is>
-          <t>SUB_SUPP_CD</t>
+          <t>SUPPLIER_PLANT</t>
         </is>
       </c>
       <c r="D263" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(4)</t>
+          <t>VARCHAR(1)</t>
         </is>
       </c>
       <c r="E263" s="32" t="inlineStr"/>
       <c r="F263" s="32" t="inlineStr"/>
       <c r="G263" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H263" s="32" t="inlineStr">
         <is>
-          <t>SUB SUPP CD</t>
+          <t>Supplier plant; SUPPLIER PLANT</t>
         </is>
       </c>
     </row>
@@ -27536,16 +27657,16 @@
         </is>
       </c>
       <c r="B264" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C264" s="32" t="inlineStr">
         <is>
-          <t>SUB_SUPP_PLANT</t>
+          <t>SUB_SUPP_CD</t>
         </is>
       </c>
       <c r="D264" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(1)</t>
+          <t>VARCHAR(4)</t>
         </is>
       </c>
       <c r="E264" s="32" t="inlineStr"/>
@@ -27557,7 +27678,7 @@
       </c>
       <c r="H264" s="32" t="inlineStr">
         <is>
-          <t>SUB SUPP PLANT</t>
+          <t>SUB SUPP CD</t>
         </is>
       </c>
     </row>
@@ -27568,16 +27689,16 @@
         </is>
       </c>
       <c r="B265" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C265" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_NAME</t>
+          <t>SUB_SUPP_PLANT</t>
         </is>
       </c>
       <c r="D265" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(1)</t>
         </is>
       </c>
       <c r="E265" s="32" t="inlineStr"/>
@@ -27589,7 +27710,7 @@
       </c>
       <c r="H265" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER NAME</t>
+          <t>SUB SUPP PLANT</t>
         </is>
       </c>
     </row>
@@ -27600,28 +27721,28 @@
         </is>
       </c>
       <c r="B266" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C266" s="32" t="inlineStr">
         <is>
-          <t>PO_NO</t>
+          <t>SUPPLIER_NAME</t>
         </is>
       </c>
       <c r="D266" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E266" s="32" t="inlineStr"/>
       <c r="F266" s="32" t="inlineStr"/>
       <c r="G266" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H266" s="32" t="inlineStr">
         <is>
-          <t>PO number; one PO can be split over several manifests; PO NO</t>
+          <t>SUPPLIER NAME</t>
         </is>
       </c>
     </row>
@@ -27632,16 +27753,16 @@
         </is>
       </c>
       <c r="B267" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C267" s="32" t="inlineStr">
         <is>
-          <t>PO_DT</t>
+          <t>PO_NO</t>
         </is>
       </c>
       <c r="D267" s="32" t="inlineStr">
         <is>
-          <t>DATETIME (inferred)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E267" s="32" t="inlineStr"/>
@@ -27653,7 +27774,7 @@
       </c>
       <c r="H267" s="32" t="inlineStr">
         <is>
-          <t>PO date; not in the DB structure document</t>
+          <t>PO number; one PO can be split over several manifests; PO NO</t>
         </is>
       </c>
     </row>
@@ -27664,23 +27785,19 @@
         </is>
       </c>
       <c r="B268" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C268" s="32" t="inlineStr">
         <is>
-          <t>MANIFEST_NO</t>
+          <t>PO_DT</t>
         </is>
       </c>
       <c r="D268" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="E268" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>DATETIME (inferred)</t>
+        </is>
+      </c>
+      <c r="E268" s="32" t="inlineStr"/>
       <c r="F268" s="32" t="inlineStr"/>
       <c r="G268" s="32" t="inlineStr">
         <is>
@@ -27689,7 +27806,7 @@
       </c>
       <c r="H268" s="32" t="inlineStr">
         <is>
-          <t>Manifest number (unique in the sample); MANIFEST NO</t>
+          <t>PO date; not in the DB structure document</t>
         </is>
       </c>
     </row>
@@ -27700,11 +27817,11 @@
         </is>
       </c>
       <c r="B269" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C269" s="32" t="inlineStr">
         <is>
-          <t>MAKER_CODE</t>
+          <t>MANIFEST_NO</t>
         </is>
       </c>
       <c r="D269" s="32" t="inlineStr">
@@ -27712,16 +27829,20 @@
           <t>VARCHAR(20)</t>
         </is>
       </c>
-      <c r="E269" s="32" t="inlineStr"/>
+      <c r="E269" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F269" s="32" t="inlineStr"/>
       <c r="G269" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H269" s="32" t="inlineStr">
         <is>
-          <t>MAKER CODE; values: A</t>
+          <t>Manifest number (unique in the sample); MANIFEST NO</t>
         </is>
       </c>
     </row>
@@ -27732,11 +27853,11 @@
         </is>
       </c>
       <c r="B270" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C270" s="32" t="inlineStr">
         <is>
-          <t>PO_TRANSPORT_CD</t>
+          <t>MAKER_CODE</t>
         </is>
       </c>
       <c r="D270" s="32" t="inlineStr">
@@ -27753,7 +27874,7 @@
       </c>
       <c r="H270" s="32" t="inlineStr">
         <is>
-          <t>PO TRANSPORT CD; values: 3</t>
+          <t>MAKER CODE; values: A</t>
         </is>
       </c>
     </row>
@@ -27764,16 +27885,16 @@
         </is>
       </c>
       <c r="B271" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C271" s="32" t="inlineStr">
         <is>
-          <t>ORDER_TYPE</t>
+          <t>PO_TRANSPORT_CD</t>
         </is>
       </c>
       <c r="D271" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(2)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E271" s="32" t="inlineStr"/>
@@ -27785,7 +27906,7 @@
       </c>
       <c r="H271" s="32" t="inlineStr">
         <is>
-          <t>Order type ('3', 'C' in the sample); ORDER TYPE; values: 3, C</t>
+          <t>PO TRANSPORT CD; values: 3</t>
         </is>
       </c>
     </row>
@@ -27796,16 +27917,16 @@
         </is>
       </c>
       <c r="B272" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C272" s="32" t="inlineStr">
         <is>
-          <t>CROSS_DOCK_FLAG</t>
+          <t>ORDER_TYPE</t>
         </is>
       </c>
       <c r="D272" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>VARCHAR(2)</t>
         </is>
       </c>
       <c r="E272" s="32" t="inlineStr"/>
@@ -27817,7 +27938,7 @@
       </c>
       <c r="H272" s="32" t="inlineStr">
         <is>
-          <t>'X' = crossdock manifest (its parts are taken by XD09); NULL otherwise; CROSS DOCK FLAG; values: X</t>
+          <t>Order type ('3', 'C' in the sample); ORDER TYPE; values: 3, C</t>
         </is>
       </c>
     </row>
@@ -27828,11 +27949,11 @@
         </is>
       </c>
       <c r="B273" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C273" s="32" t="inlineStr">
         <is>
-          <t>COMPANY_CD</t>
+          <t>CROSS_DOCK_FLAG</t>
         </is>
       </c>
       <c r="D273" s="32" t="inlineStr">
@@ -27844,12 +27965,12 @@
       <c r="F273" s="32" t="inlineStr"/>
       <c r="G273" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H273" s="32" t="inlineStr">
         <is>
-          <t>COMPANY CD; values: 807B</t>
+          <t>'X' = crossdock manifest (its parts are taken by XD09); NULL otherwise; CROSS DOCK FLAG; values: X</t>
         </is>
       </c>
     </row>
@@ -27860,11 +27981,11 @@
         </is>
       </c>
       <c r="B274" s="31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C274" s="32" t="inlineStr">
         <is>
-          <t>RCV_PLANT_CD</t>
+          <t>COMPANY_CD</t>
         </is>
       </c>
       <c r="D274" s="32" t="inlineStr">
@@ -27876,12 +27997,12 @@
       <c r="F274" s="32" t="inlineStr"/>
       <c r="G274" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H274" s="32" t="inlineStr">
         <is>
-          <t>RCV PLANT CD; values: 1</t>
+          <t>COMPANY CD; values: 807B</t>
         </is>
       </c>
     </row>
@@ -27892,16 +28013,16 @@
         </is>
       </c>
       <c r="B275" s="31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C275" s="32" t="inlineStr">
         <is>
-          <t>DOCK_CD</t>
+          <t>RCV_PLANT_CD</t>
         </is>
       </c>
       <c r="D275" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(4)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E275" s="32" t="inlineStr"/>
@@ -27913,7 +28034,7 @@
       </c>
       <c r="H275" s="32" t="inlineStr">
         <is>
-          <t>Receiving dock; DOCK CD; values: S1, S2, S3</t>
+          <t>RCV PLANT CD; values: 1</t>
         </is>
       </c>
     </row>
@@ -27924,28 +28045,28 @@
         </is>
       </c>
       <c r="B276" s="31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C276" s="32" t="inlineStr">
         <is>
-          <t>TOTAL_ITEM</t>
+          <t>DOCK_CD</t>
         </is>
       </c>
       <c r="D276" s="32" t="inlineStr">
         <is>
-          <t>NUMERIC</t>
+          <t>VARCHAR(4)</t>
         </is>
       </c>
       <c r="E276" s="32" t="inlineStr"/>
       <c r="F276" s="32" t="inlineStr"/>
       <c r="G276" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H276" s="32" t="inlineStr">
         <is>
-          <t>Number of items of the manifest; TOTAL ITEM</t>
+          <t>Receiving dock; DOCK CD; values: S1, S2, S3</t>
         </is>
       </c>
     </row>
@@ -27956,11 +28077,11 @@
         </is>
       </c>
       <c r="B277" s="31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C277" s="32" t="inlineStr">
         <is>
-          <t>TOTAL_QTY</t>
+          <t>TOTAL_ITEM</t>
         </is>
       </c>
       <c r="D277" s="32" t="inlineStr">
@@ -27977,7 +28098,7 @@
       </c>
       <c r="H277" s="32" t="inlineStr">
         <is>
-          <t>Total order qty of the manifest; TOTAL QTY</t>
+          <t>Number of items of the manifest; TOTAL ITEM</t>
         </is>
       </c>
     </row>
@@ -27988,11 +28109,11 @@
         </is>
       </c>
       <c r="B278" s="31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C278" s="32" t="inlineStr">
         <is>
-          <t>TOTAL_QTY_DELIVERY</t>
+          <t>TOTAL_QTY</t>
         </is>
       </c>
       <c r="D278" s="32" t="inlineStr">
@@ -28004,12 +28125,12 @@
       <c r="F278" s="32" t="inlineStr"/>
       <c r="G278" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H278" s="32" t="inlineStr">
         <is>
-          <t>TOTAL QTY DELIVERY</t>
+          <t>Total order qty of the manifest; TOTAL QTY</t>
         </is>
       </c>
     </row>
@@ -28020,11 +28141,11 @@
         </is>
       </c>
       <c r="B279" s="31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C279" s="32" t="inlineStr">
         <is>
-          <t>RECEIVED_QTY</t>
+          <t>TOTAL_QTY_DELIVERY</t>
         </is>
       </c>
       <c r="D279" s="32" t="inlineStr">
@@ -28041,7 +28162,7 @@
       </c>
       <c r="H279" s="32" t="inlineStr">
         <is>
-          <t>RECEIVED QTY; values: 0</t>
+          <t>TOTAL QTY DELIVERY</t>
         </is>
       </c>
     </row>
@@ -28052,11 +28173,11 @@
         </is>
       </c>
       <c r="B280" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C280" s="32" t="inlineStr">
         <is>
-          <t>TOTAL_QTY_REMAIN</t>
+          <t>RECEIVED_QTY</t>
         </is>
       </c>
       <c r="D280" s="32" t="inlineStr">
@@ -28073,7 +28194,7 @@
       </c>
       <c r="H280" s="32" t="inlineStr">
         <is>
-          <t>TOTAL QTY REMAIN</t>
+          <t>RECEIVED QTY; values: 0</t>
         </is>
       </c>
     </row>
@@ -28084,28 +28205,28 @@
         </is>
       </c>
       <c r="B281" s="31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C281" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY_DT</t>
+          <t>TOTAL_QTY_REMAIN</t>
         </is>
       </c>
       <c r="D281" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="E281" s="32" t="inlineStr"/>
       <c r="F281" s="32" t="inlineStr"/>
       <c r="G281" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H281" s="32" t="inlineStr">
         <is>
-          <t>Delivery date; DELIVERY DT</t>
+          <t>TOTAL QTY REMAIN</t>
         </is>
       </c>
     </row>
@@ -28116,11 +28237,11 @@
         </is>
       </c>
       <c r="B282" s="31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C282" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY_DT_ACTUAL</t>
+          <t>DELIVERY_DT</t>
         </is>
       </c>
       <c r="D282" s="32" t="inlineStr">
@@ -28132,12 +28253,12 @@
       <c r="F282" s="32" t="inlineStr"/>
       <c r="G282" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H282" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY DT ACTUAL; values: 2026-10-06 06:30:21.103</t>
+          <t>Delivery date; DELIVERY DT</t>
         </is>
       </c>
     </row>
@@ -28148,16 +28269,16 @@
         </is>
       </c>
       <c r="B283" s="31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C283" s="32" t="inlineStr">
         <is>
-          <t>SHIPPING_DOCK</t>
+          <t>DELIVERY_DT_ACTUAL</t>
         </is>
       </c>
       <c r="D283" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(5)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E283" s="32" t="inlineStr"/>
@@ -28169,7 +28290,7 @@
       </c>
       <c r="H283" s="32" t="inlineStr">
         <is>
-          <t>SHIPPING DOCK</t>
+          <t>DELIVERY DT ACTUAL; values: 2026-10-06 06:30:21.103</t>
         </is>
       </c>
     </row>
@@ -28180,16 +28301,16 @@
         </is>
       </c>
       <c r="B284" s="31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C284" s="32" t="inlineStr">
         <is>
-          <t>SHIPPING_DT</t>
+          <t>SHIPPING_DOCK</t>
         </is>
       </c>
       <c r="D284" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(5)</t>
         </is>
       </c>
       <c r="E284" s="32" t="inlineStr"/>
@@ -28201,7 +28322,7 @@
       </c>
       <c r="H284" s="32" t="inlineStr">
         <is>
-          <t>SHIPPING DT</t>
+          <t>SHIPPING DOCK</t>
         </is>
       </c>
     </row>
@@ -28212,16 +28333,16 @@
         </is>
       </c>
       <c r="B285" s="31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C285" s="32" t="inlineStr">
         <is>
-          <t>SUB_ROUTE_CD</t>
+          <t>SHIPPING_DT</t>
         </is>
       </c>
       <c r="D285" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E285" s="32" t="inlineStr"/>
@@ -28233,7 +28354,7 @@
       </c>
       <c r="H285" s="32" t="inlineStr">
         <is>
-          <t>Route of the delivery (e.g. DS18); SUB ROUTE CD</t>
+          <t>SHIPPING DT</t>
         </is>
       </c>
     </row>
@@ -28244,11 +28365,11 @@
         </is>
       </c>
       <c r="B286" s="31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C286" s="32" t="inlineStr">
         <is>
-          <t>SUB_ROUTE_SEQ</t>
+          <t>SUB_ROUTE_CD</t>
         </is>
       </c>
       <c r="D286" s="32" t="inlineStr">
@@ -28265,7 +28386,7 @@
       </c>
       <c r="H286" s="32" t="inlineStr">
         <is>
-          <t>Sequence (rit) of the route; SUB ROUTE SEQ; values: 1, 2, 5</t>
+          <t>Route of the delivery (e.g. DS18); SUB ROUTE CD</t>
         </is>
       </c>
     </row>
@@ -28276,16 +28397,16 @@
         </is>
       </c>
       <c r="B287" s="31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C287" s="32" t="inlineStr">
         <is>
-          <t>SUB_ROUTE_DT</t>
+          <t>SUB_ROUTE_SEQ</t>
         </is>
       </c>
       <c r="D287" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E287" s="32" t="inlineStr"/>
@@ -28297,7 +28418,7 @@
       </c>
       <c r="H287" s="32" t="inlineStr">
         <is>
-          <t>Date and time of the route; SUB ROUTE DT</t>
+          <t>Sequence (rit) of the route; SUB ROUTE SEQ; values: 1, 2, 5</t>
         </is>
       </c>
     </row>
@@ -28308,16 +28429,16 @@
         </is>
       </c>
       <c r="B288" s="31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C288" s="32" t="inlineStr">
         <is>
-          <t>FST_X_DOC_CD</t>
+          <t>SUB_ROUTE_DT</t>
         </is>
       </c>
       <c r="D288" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(5)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E288" s="32" t="inlineStr"/>
@@ -28329,7 +28450,7 @@
       </c>
       <c r="H288" s="32" t="inlineStr">
         <is>
-          <t>FST X DOC CD</t>
+          <t>Date and time of the route; SUB ROUTE DT</t>
         </is>
       </c>
     </row>
@@ -28340,11 +28461,11 @@
         </is>
       </c>
       <c r="B289" s="31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C289" s="32" t="inlineStr">
         <is>
-          <t>FST_X_PLANT_CD</t>
+          <t>FST_X_DOC_CD</t>
         </is>
       </c>
       <c r="D289" s="32" t="inlineStr">
@@ -28361,7 +28482,7 @@
       </c>
       <c r="H289" s="32" t="inlineStr">
         <is>
-          <t>FST X PLANT CD</t>
+          <t>FST X DOC CD</t>
         </is>
       </c>
     </row>
@@ -28372,11 +28493,11 @@
         </is>
       </c>
       <c r="B290" s="31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C290" s="32" t="inlineStr">
         <is>
-          <t>FST_X_SHIPPING_DOCK_CD</t>
+          <t>FST_X_PLANT_CD</t>
         </is>
       </c>
       <c r="D290" s="32" t="inlineStr">
@@ -28393,7 +28514,7 @@
       </c>
       <c r="H290" s="32" t="inlineStr">
         <is>
-          <t>FST X SHIPPING DOCK CD</t>
+          <t>FST X PLANT CD</t>
         </is>
       </c>
     </row>
@@ -28404,16 +28525,16 @@
         </is>
       </c>
       <c r="B291" s="31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C291" s="32" t="inlineStr">
         <is>
-          <t>FST_X_DOCK_ARRIVAL_DT</t>
+          <t>FST_X_SHIPPING_DOCK_CD</t>
         </is>
       </c>
       <c r="D291" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(5)</t>
         </is>
       </c>
       <c r="E291" s="32" t="inlineStr"/>
@@ -28425,7 +28546,7 @@
       </c>
       <c r="H291" s="32" t="inlineStr">
         <is>
-          <t>FST X DOCK ARRIVAL DT</t>
+          <t>FST X SHIPPING DOCK CD</t>
         </is>
       </c>
     </row>
@@ -28436,11 +28557,11 @@
         </is>
       </c>
       <c r="B292" s="31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C292" s="32" t="inlineStr">
         <is>
-          <t>FST_X_DOCK_DEPART_DT</t>
+          <t>FST_X_DOCK_ARRIVAL_DT</t>
         </is>
       </c>
       <c r="D292" s="32" t="inlineStr">
@@ -28457,7 +28578,7 @@
       </c>
       <c r="H292" s="32" t="inlineStr">
         <is>
-          <t>FST X DOCK DEPART DT</t>
+          <t>FST X DOCK ARRIVAL DT</t>
         </is>
       </c>
     </row>
@@ -28468,16 +28589,16 @@
         </is>
       </c>
       <c r="B293" s="31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C293" s="32" t="inlineStr">
         <is>
-          <t>FST_X_DOCK_ROUTE_GRP_CD</t>
+          <t>FST_X_DOCK_DEPART_DT</t>
         </is>
       </c>
       <c r="D293" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E293" s="32" t="inlineStr"/>
@@ -28489,7 +28610,7 @@
       </c>
       <c r="H293" s="32" t="inlineStr">
         <is>
-          <t>FST X DOCK ROUTE GRP CD</t>
+          <t>FST X DOCK DEPART DT</t>
         </is>
       </c>
     </row>
@@ -28500,16 +28621,16 @@
         </is>
       </c>
       <c r="B294" s="31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C294" s="32" t="inlineStr">
         <is>
-          <t>FST_X_DOCK_SEQ_NO</t>
+          <t>FST_X_DOCK_ROUTE_GRP_CD</t>
         </is>
       </c>
       <c r="D294" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>VARCHAR(15)</t>
         </is>
       </c>
       <c r="E294" s="32" t="inlineStr"/>
@@ -28521,7 +28642,7 @@
       </c>
       <c r="H294" s="32" t="inlineStr">
         <is>
-          <t>FST X DOCK SEQ NO</t>
+          <t>FST X DOCK ROUTE GRP CD</t>
         </is>
       </c>
     </row>
@@ -28532,16 +28653,16 @@
         </is>
       </c>
       <c r="B295" s="31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C295" s="32" t="inlineStr">
         <is>
-          <t>FST_X_ROUTE_DT</t>
+          <t>FST_X_DOCK_SEQ_NO</t>
         </is>
       </c>
       <c r="D295" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E295" s="32" t="inlineStr"/>
@@ -28553,7 +28674,7 @@
       </c>
       <c r="H295" s="32" t="inlineStr">
         <is>
-          <t>FST X ROUTE DT</t>
+          <t>FST X DOCK SEQ NO</t>
         </is>
       </c>
     </row>
@@ -28564,16 +28685,16 @@
         </is>
       </c>
       <c r="B296" s="31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C296" s="32" t="inlineStr">
         <is>
-          <t>FTP_FLAG</t>
+          <t>FST_X_ROUTE_DT</t>
         </is>
       </c>
       <c r="D296" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(4)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E296" s="32" t="inlineStr"/>
@@ -28585,7 +28706,7 @@
       </c>
       <c r="H296" s="32" t="inlineStr">
         <is>
-          <t>FTP FLAG; values: 0</t>
+          <t>FST X ROUTE DT</t>
         </is>
       </c>
     </row>
@@ -28596,16 +28717,16 @@
         </is>
       </c>
       <c r="B297" s="31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C297" s="32" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>FTP_FLAG</t>
         </is>
       </c>
       <c r="D297" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(1)</t>
+          <t>VARCHAR(4)</t>
         </is>
       </c>
       <c r="E297" s="32" t="inlineStr"/>
@@ -28617,7 +28738,7 @@
       </c>
       <c r="H297" s="32" t="inlineStr">
         <is>
-          <t>Manifest status ('0', '2' in the sample); STATUS; values: 0, 2</t>
+          <t>FTP FLAG; values: 0</t>
         </is>
       </c>
     </row>
@@ -28628,16 +28749,16 @@
         </is>
       </c>
       <c r="B298" s="31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C298" s="32" t="inlineStr">
         <is>
-          <t>REMARK</t>
+          <t>STATUS</t>
         </is>
       </c>
       <c r="D298" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>VARCHAR(1)</t>
         </is>
       </c>
       <c r="E298" s="32" t="inlineStr"/>
@@ -28649,7 +28770,7 @@
       </c>
       <c r="H298" s="32" t="inlineStr">
         <is>
-          <t>REMARK</t>
+          <t>Manifest status ('0', '2' in the sample); STATUS; values: 0, 2</t>
         </is>
       </c>
     </row>
@@ -28660,16 +28781,16 @@
         </is>
       </c>
       <c r="B299" s="31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C299" s="32" t="inlineStr">
         <is>
-          <t>DOWNLOAD_FLAG</t>
+          <t>REMARK</t>
         </is>
       </c>
       <c r="D299" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(2)</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="E299" s="32" t="inlineStr"/>
@@ -28681,7 +28802,7 @@
       </c>
       <c r="H299" s="32" t="inlineStr">
         <is>
-          <t>DOWNLOAD FLAG</t>
+          <t>REMARK</t>
         </is>
       </c>
     </row>
@@ -28692,16 +28813,16 @@
         </is>
       </c>
       <c r="B300" s="31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C300" s="32" t="inlineStr">
         <is>
-          <t>DOWNLOADED_BY</t>
+          <t>DOWNLOAD_FLAG</t>
         </is>
       </c>
       <c r="D300" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(2)</t>
         </is>
       </c>
       <c r="E300" s="32" t="inlineStr"/>
@@ -28713,7 +28834,7 @@
       </c>
       <c r="H300" s="32" t="inlineStr">
         <is>
-          <t>DOWNLOADED BY</t>
+          <t>DOWNLOAD FLAG</t>
         </is>
       </c>
     </row>
@@ -28724,16 +28845,16 @@
         </is>
       </c>
       <c r="B301" s="31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C301" s="32" t="inlineStr">
         <is>
-          <t>DOWNLOADED_DT</t>
+          <t>DOWNLOADED_BY</t>
         </is>
       </c>
       <c r="D301" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E301" s="32" t="inlineStr"/>
@@ -28745,7 +28866,7 @@
       </c>
       <c r="H301" s="32" t="inlineStr">
         <is>
-          <t>DOWNLOADED DT</t>
+          <t>DOWNLOADED BY</t>
         </is>
       </c>
     </row>
@@ -28756,16 +28877,16 @@
         </is>
       </c>
       <c r="B302" s="31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C302" s="32" t="inlineStr">
         <is>
-          <t>SEND_PO_ADM_FLAG</t>
+          <t>DOWNLOADED_DT</t>
         </is>
       </c>
       <c r="D302" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(2)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E302" s="32" t="inlineStr"/>
@@ -28777,7 +28898,7 @@
       </c>
       <c r="H302" s="32" t="inlineStr">
         <is>
-          <t>SEND PO ADM FLAG; values: Y</t>
+          <t>DOWNLOADED DT</t>
         </is>
       </c>
     </row>
@@ -28788,16 +28909,16 @@
         </is>
       </c>
       <c r="B303" s="31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C303" s="32" t="inlineStr">
         <is>
-          <t>SEND_PO_ADM_DT</t>
+          <t>SEND_PO_ADM_FLAG</t>
         </is>
       </c>
       <c r="D303" s="32" t="inlineStr">
         <is>
-          <t>DATETIME (inferred)</t>
+          <t>VARCHAR(2)</t>
         </is>
       </c>
       <c r="E303" s="32" t="inlineStr"/>
@@ -28809,7 +28930,7 @@
       </c>
       <c r="H303" s="32" t="inlineStr">
         <is>
-          <t>not in the DB structure document; values: 2026-10-06 05:30:17.083</t>
+          <t>SEND PO ADM FLAG; values: Y</t>
         </is>
       </c>
     </row>
@@ -28820,28 +28941,28 @@
         </is>
       </c>
       <c r="B304" s="31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C304" s="32" t="inlineStr">
         <is>
-          <t>CREATED_BY</t>
+          <t>SEND_PO_ADM_DT</t>
         </is>
       </c>
       <c r="D304" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DATETIME (inferred)</t>
         </is>
       </c>
       <c r="E304" s="32" t="inlineStr"/>
       <c r="F304" s="32" t="inlineStr"/>
       <c r="G304" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H304" s="32" t="inlineStr">
         <is>
-          <t>CREATED BY; values: SYSTEM</t>
+          <t>not in the DB structure document; values: 2026-10-06 05:30:17.083</t>
         </is>
       </c>
     </row>
@@ -28852,16 +28973,16 @@
         </is>
       </c>
       <c r="B305" s="31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C305" s="32" t="inlineStr">
         <is>
-          <t>CREATED_DT</t>
+          <t>CREATED_BY</t>
         </is>
       </c>
       <c r="D305" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E305" s="32" t="inlineStr"/>
@@ -28873,7 +28994,7 @@
       </c>
       <c r="H305" s="32" t="inlineStr">
         <is>
-          <t>CREATED DT</t>
+          <t>CREATED BY; values: SYSTEM</t>
         </is>
       </c>
     </row>
@@ -28884,28 +29005,28 @@
         </is>
       </c>
       <c r="B306" s="31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C306" s="32" t="inlineStr">
         <is>
-          <t>CHANGED_BY</t>
+          <t>CREATED_DT</t>
         </is>
       </c>
       <c r="D306" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E306" s="32" t="inlineStr"/>
       <c r="F306" s="32" t="inlineStr"/>
       <c r="G306" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H306" s="32" t="inlineStr">
         <is>
-          <t>CHANGED BY; values: SCHEDULER, SYSTEM</t>
+          <t>CREATED DT</t>
         </is>
       </c>
     </row>
@@ -28916,16 +29037,16 @@
         </is>
       </c>
       <c r="B307" s="31" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C307" s="32" t="inlineStr">
         <is>
-          <t>CHANGED_DT</t>
+          <t>CHANGED_BY</t>
         </is>
       </c>
       <c r="D307" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E307" s="32" t="inlineStr"/>
@@ -28937,7 +29058,7 @@
       </c>
       <c r="H307" s="32" t="inlineStr">
         <is>
-          <t>CHANGED DT</t>
+          <t>CHANGED BY; values: SCHEDULER, SYSTEM</t>
         </is>
       </c>
     </row>
@@ -28948,11 +29069,11 @@
         </is>
       </c>
       <c r="B308" s="31" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C308" s="32" t="inlineStr">
         <is>
-          <t>RECEIVED_DT</t>
+          <t>CHANGED_DT</t>
         </is>
       </c>
       <c r="D308" s="32" t="inlineStr">
@@ -28969,7 +29090,7 @@
       </c>
       <c r="H308" s="32" t="inlineStr">
         <is>
-          <t>RECEIVED_DT; values: 2026-10-06 06:30:21.103</t>
+          <t>CHANGED DT</t>
         </is>
       </c>
     </row>
@@ -28980,16 +29101,16 @@
         </is>
       </c>
       <c r="B309" s="31" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C309" s="32" t="inlineStr">
         <is>
-          <t>MANIFEST_LAST_SEQ</t>
+          <t>RECEIVED_DT</t>
         </is>
       </c>
       <c r="D309" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(2+) (inferred)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E309" s="32" t="inlineStr"/>
@@ -29001,7 +29122,7 @@
       </c>
       <c r="H309" s="32" t="inlineStr">
         <is>
-          <t>not in the DB structure document; values: A1</t>
+          <t>RECEIVED_DT; values: 2026-10-06 06:30:21.103</t>
         </is>
       </c>
     </row>
@@ -29012,28 +29133,28 @@
         </is>
       </c>
       <c r="B310" s="31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C310" s="32" t="inlineStr">
         <is>
-          <t>CANCEL_QTY</t>
+          <t>MANIFEST_LAST_SEQ</t>
         </is>
       </c>
       <c r="D310" s="32" t="inlineStr">
         <is>
-          <t>NUMERIC (inferred)</t>
+          <t>VARCHAR(2+) (inferred)</t>
         </is>
       </c>
       <c r="E310" s="32" t="inlineStr"/>
       <c r="F310" s="32" t="inlineStr"/>
       <c r="G310" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H310" s="32" t="inlineStr">
         <is>
-          <t>not in the DB structure document; values: 0</t>
+          <t>not in the DB structure document; values: A1</t>
         </is>
       </c>
     </row>
@@ -29044,28 +29165,28 @@
         </is>
       </c>
       <c r="B311" s="31" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C311" s="32" t="inlineStr">
         <is>
-          <t>CANCEL_DT</t>
+          <t>CANCEL_QTY</t>
         </is>
       </c>
       <c r="D311" s="32" t="inlineStr">
         <is>
-          <t>DATETIME (inferred)</t>
+          <t>NUMERIC (inferred)</t>
         </is>
       </c>
       <c r="E311" s="32" t="inlineStr"/>
       <c r="F311" s="32" t="inlineStr"/>
       <c r="G311" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H311" s="32" t="inlineStr">
         <is>
-          <t>not in the DB structure document</t>
+          <t>not in the DB structure document; values: 0</t>
         </is>
       </c>
     </row>
@@ -29076,16 +29197,16 @@
         </is>
       </c>
       <c r="B312" s="31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C312" s="32" t="inlineStr">
         <is>
-          <t>SEND_FLAG_MDI</t>
+          <t>CANCEL_DT</t>
         </is>
       </c>
       <c r="D312" s="32" t="inlineStr">
         <is>
-          <t>? (no data) (inferred)</t>
+          <t>DATETIME (inferred)</t>
         </is>
       </c>
       <c r="E312" s="32" t="inlineStr"/>
@@ -29108,11 +29229,11 @@
         </is>
       </c>
       <c r="B313" s="31" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C313" s="32" t="inlineStr">
         <is>
-          <t>SEND_DATE_MDI</t>
+          <t>SEND_FLAG_MDI</t>
         </is>
       </c>
       <c r="D313" s="32" t="inlineStr">
@@ -29136,32 +29257,32 @@
     <row r="314">
       <c r="A314" s="32" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_PART</t>
+          <t>TB_R_PRA_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B314" s="31" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C314" s="32" t="inlineStr">
         <is>
-          <t>PO_NO</t>
+          <t>SEND_DATE_MDI</t>
         </is>
       </c>
       <c r="D314" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>? (no data) (inferred)</t>
         </is>
       </c>
       <c r="E314" s="32" t="inlineStr"/>
       <c r="F314" s="32" t="inlineStr"/>
       <c r="G314" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H314" s="32" t="inlineStr">
         <is>
-          <t>PO number; PO NO</t>
+          <t>not in the DB structure document</t>
         </is>
       </c>
     </row>
@@ -29172,16 +29293,16 @@
         </is>
       </c>
       <c r="B315" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C315" s="32" t="inlineStr">
         <is>
-          <t>PO_ITEM</t>
+          <t>PO_NO</t>
         </is>
       </c>
       <c r="D315" s="32" t="inlineStr">
         <is>
-          <t>NUMERIC</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E315" s="32" t="inlineStr"/>
@@ -29193,7 +29314,7 @@
       </c>
       <c r="H315" s="32" t="inlineStr">
         <is>
-          <t>Item of the PO (can differ from MANIFEST_ITEM); PO ITEM</t>
+          <t>PO number; PO NO</t>
         </is>
       </c>
     </row>
@@ -29204,28 +29325,20 @@
         </is>
       </c>
       <c r="B316" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C316" s="32" t="inlineStr">
         <is>
-          <t>MANIFEST_NO</t>
+          <t>PO_ITEM</t>
         </is>
       </c>
       <c r="D316" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="E316" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F316" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="E316" s="32" t="inlineStr"/>
+      <c r="F316" s="32" t="inlineStr"/>
       <c r="G316" s="32" t="inlineStr">
         <is>
           <t>N</t>
@@ -29233,7 +29346,7 @@
       </c>
       <c r="H316" s="32" t="inlineStr">
         <is>
-          <t>Manifest number (TB_R_PRA_DAILY_ORDER_MANIFEST); MANIFEST NO</t>
+          <t>Item of the PO (can differ from MANIFEST_ITEM); PO ITEM</t>
         </is>
       </c>
     </row>
@@ -29244,16 +29357,16 @@
         </is>
       </c>
       <c r="B317" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C317" s="32" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM</t>
+          <t>MANIFEST_NO</t>
         </is>
       </c>
       <c r="D317" s="32" t="inlineStr">
         <is>
-          <t>NUMERIC</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E317" s="32" t="inlineStr">
@@ -29261,7 +29374,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F317" s="32" t="inlineStr"/>
+      <c r="F317" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G317" s="32" t="inlineStr">
         <is>
           <t>N</t>
@@ -29269,7 +29386,7 @@
       </c>
       <c r="H317" s="32" t="inlineStr">
         <is>
-          <t>Item of the manifest (0001 ...); MANIFEST ITEM</t>
+          <t>Manifest number (TB_R_PRA_DAILY_ORDER_MANIFEST); MANIFEST NO</t>
         </is>
       </c>
     </row>
@@ -29280,28 +29397,32 @@
         </is>
       </c>
       <c r="B318" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C318" s="32" t="inlineStr">
         <is>
-          <t>ORI_PART_NO</t>
+          <t>MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="D318" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
-        </is>
-      </c>
-      <c r="E318" s="32" t="inlineStr"/>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="E318" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F318" s="32" t="inlineStr"/>
       <c r="G318" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H318" s="32" t="inlineStr">
         <is>
-          <t>ORI PART NO</t>
+          <t>Item of the manifest (0001 ...); MANIFEST ITEM</t>
         </is>
       </c>
     </row>
@@ -29312,11 +29433,11 @@
         </is>
       </c>
       <c r="B319" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C319" s="32" t="inlineStr">
         <is>
-          <t>PART_NO</t>
+          <t>ORI_PART_NO</t>
         </is>
       </c>
       <c r="D319" s="32" t="inlineStr">
@@ -29333,7 +29454,7 @@
       </c>
       <c r="H319" s="32" t="inlineStr">
         <is>
-          <t>Part number; PART NO</t>
+          <t>ORI PART NO</t>
         </is>
       </c>
     </row>
@@ -29344,16 +29465,16 @@
         </is>
       </c>
       <c r="B320" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C320" s="32" t="inlineStr">
         <is>
-          <t>PART_NAME</t>
+          <t>PART_NO</t>
         </is>
       </c>
       <c r="D320" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(15)</t>
         </is>
       </c>
       <c r="E320" s="32" t="inlineStr"/>
@@ -29365,7 +29486,7 @@
       </c>
       <c r="H320" s="32" t="inlineStr">
         <is>
-          <t>Part name; PART NAME</t>
+          <t>Part number; PART NO</t>
         </is>
       </c>
     </row>
@@ -29376,16 +29497,16 @@
         </is>
       </c>
       <c r="B321" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C321" s="32" t="inlineStr">
         <is>
-          <t>QTY_PER_CONTAINER</t>
+          <t>PART_NAME</t>
         </is>
       </c>
       <c r="D321" s="32" t="inlineStr">
         <is>
-          <t>NUMERIC</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E321" s="32" t="inlineStr"/>
@@ -29397,7 +29518,7 @@
       </c>
       <c r="H321" s="32" t="inlineStr">
         <is>
-          <t>Qty per container of the PO (mostly 1; not the crossdock pcs/case); QTY PER CONTAINER</t>
+          <t>Part name; PART NAME</t>
         </is>
       </c>
     </row>
@@ -29408,11 +29529,11 @@
         </is>
       </c>
       <c r="B322" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C322" s="32" t="inlineStr">
         <is>
-          <t>ORDER_QTY</t>
+          <t>QTY_PER_CONTAINER</t>
         </is>
       </c>
       <c r="D322" s="32" t="inlineStr">
@@ -29429,7 +29550,7 @@
       </c>
       <c r="H322" s="32" t="inlineStr">
         <is>
-          <t>PO qty (pcs) — basis of the open qty for XD09 (ORDER_QTY - MAPPED_QTY); ORDER QTY</t>
+          <t>Qty per container of the PO (mostly 1; not the crossdock pcs/case); QTY PER CONTAINER</t>
         </is>
       </c>
     </row>
@@ -29440,11 +29561,11 @@
         </is>
       </c>
       <c r="B323" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C323" s="32" t="inlineStr">
         <is>
-          <t>ORDER_PLAN_QTY_LOT</t>
+          <t>ORDER_QTY</t>
         </is>
       </c>
       <c r="D323" s="32" t="inlineStr">
@@ -29461,7 +29582,7 @@
       </c>
       <c r="H323" s="32" t="inlineStr">
         <is>
-          <t>ORDER PLAN QTY LOT</t>
+          <t>PO qty (pcs) — basis of the open qty for XD09 (ORDER_QTY - MAPPED_QTY); ORDER QTY</t>
         </is>
       </c>
     </row>
@@ -29472,11 +29593,11 @@
         </is>
       </c>
       <c r="B324" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C324" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY_QTY</t>
+          <t>ORDER_PLAN_QTY_LOT</t>
         </is>
       </c>
       <c r="D324" s="32" t="inlineStr">
@@ -29493,7 +29614,7 @@
       </c>
       <c r="H324" s="32" t="inlineStr">
         <is>
-          <t>Delivered qty; DELIVERY QTY</t>
+          <t>ORDER PLAN QTY LOT</t>
         </is>
       </c>
     </row>
@@ -29504,11 +29625,11 @@
         </is>
       </c>
       <c r="B325" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C325" s="32" t="inlineStr">
         <is>
-          <t>RECEIVED_QTY</t>
+          <t>DELIVERY_QTY</t>
         </is>
       </c>
       <c r="D325" s="32" t="inlineStr">
@@ -29525,7 +29646,7 @@
       </c>
       <c r="H325" s="32" t="inlineStr">
         <is>
-          <t>RECEIVED QTY</t>
+          <t>Delivered qty; DELIVERY QTY</t>
         </is>
       </c>
     </row>
@@ -29536,11 +29657,11 @@
         </is>
       </c>
       <c r="B326" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C326" s="32" t="inlineStr">
         <is>
-          <t>REMAIN_QTY</t>
+          <t>RECEIVED_QTY</t>
         </is>
       </c>
       <c r="D326" s="32" t="inlineStr">
@@ -29557,7 +29678,7 @@
       </c>
       <c r="H326" s="32" t="inlineStr">
         <is>
-          <t>Remaining qty; REMAIN QTY</t>
+          <t>RECEIVED QTY</t>
         </is>
       </c>
     </row>
@@ -29568,16 +29689,16 @@
         </is>
       </c>
       <c r="B327" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C327" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY_DT</t>
+          <t>REMAIN_QTY</t>
         </is>
       </c>
       <c r="D327" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="E327" s="32" t="inlineStr"/>
@@ -29589,7 +29710,7 @@
       </c>
       <c r="H327" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY DT</t>
+          <t>Remaining qty; REMAIN QTY</t>
         </is>
       </c>
     </row>
@@ -29600,11 +29721,11 @@
         </is>
       </c>
       <c r="B328" s="31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C328" s="32" t="inlineStr">
         <is>
-          <t>RECEIVED_DT</t>
+          <t>DELIVERY_DT</t>
         </is>
       </c>
       <c r="D328" s="32" t="inlineStr">
@@ -29621,7 +29742,7 @@
       </c>
       <c r="H328" s="32" t="inlineStr">
         <is>
-          <t>RECEIVED DT</t>
+          <t>DELIVERY DT</t>
         </is>
       </c>
     </row>
@@ -29632,16 +29753,16 @@
         </is>
       </c>
       <c r="B329" s="31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C329" s="32" t="inlineStr">
         <is>
-          <t>KANBAN_NO</t>
+          <t>RECEIVED_DT</t>
         </is>
       </c>
       <c r="D329" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(5)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E329" s="32" t="inlineStr"/>
@@ -29653,7 +29774,7 @@
       </c>
       <c r="H329" s="32" t="inlineStr">
         <is>
-          <t>KANBAN NO</t>
+          <t>RECEIVED DT</t>
         </is>
       </c>
     </row>
@@ -29664,16 +29785,16 @@
         </is>
       </c>
       <c r="B330" s="31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C330" s="32" t="inlineStr">
         <is>
-          <t>PART_BARCODE</t>
+          <t>KANBAN_NO</t>
         </is>
       </c>
       <c r="D330" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
+          <t>VARCHAR(5)</t>
         </is>
       </c>
       <c r="E330" s="32" t="inlineStr"/>
@@ -29685,7 +29806,7 @@
       </c>
       <c r="H330" s="32" t="inlineStr">
         <is>
-          <t>PART BARCODE</t>
+          <t>KANBAN NO</t>
         </is>
       </c>
     </row>
@@ -29696,16 +29817,16 @@
         </is>
       </c>
       <c r="B331" s="31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C331" s="32" t="inlineStr">
         <is>
-          <t>RECEIVE_PLANT_NAME</t>
+          <t>PART_BARCODE</t>
         </is>
       </c>
       <c r="D331" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(4)</t>
+          <t>VARCHAR(15)</t>
         </is>
       </c>
       <c r="E331" s="32" t="inlineStr"/>
@@ -29717,7 +29838,7 @@
       </c>
       <c r="H331" s="32" t="inlineStr">
         <is>
-          <t>RECEIVE PLANT NAME; values: SUNTER 1</t>
+          <t>PART BARCODE</t>
         </is>
       </c>
     </row>
@@ -29728,16 +29849,16 @@
         </is>
       </c>
       <c r="B332" s="31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C332" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_INFO1</t>
+          <t>RECEIVE_PLANT_NAME</t>
         </is>
       </c>
       <c r="D332" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(4)</t>
         </is>
       </c>
       <c r="E332" s="32" t="inlineStr"/>
@@ -29749,7 +29870,7 @@
       </c>
       <c r="H332" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER INFO1</t>
+          <t>RECEIVE PLANT NAME; values: SUNTER 1</t>
         </is>
       </c>
     </row>
@@ -29760,11 +29881,11 @@
         </is>
       </c>
       <c r="B333" s="31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C333" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_INFO2</t>
+          <t>SUPPLIER_INFO1</t>
         </is>
       </c>
       <c r="D333" s="32" t="inlineStr">
@@ -29781,7 +29902,7 @@
       </c>
       <c r="H333" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER INFO2</t>
+          <t>SUPPLIER INFO1</t>
         </is>
       </c>
     </row>
@@ -29792,11 +29913,11 @@
         </is>
       </c>
       <c r="B334" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C334" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_INFO3</t>
+          <t>SUPPLIER_INFO2</t>
         </is>
       </c>
       <c r="D334" s="32" t="inlineStr">
@@ -29813,7 +29934,7 @@
       </c>
       <c r="H334" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER INFO3</t>
+          <t>SUPPLIER INFO2</t>
         </is>
       </c>
     </row>
@@ -29824,11 +29945,11 @@
         </is>
       </c>
       <c r="B335" s="31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C335" s="32" t="inlineStr">
         <is>
-          <t>IMPORTIR_INFO</t>
+          <t>SUPPLIER_INFO3</t>
         </is>
       </c>
       <c r="D335" s="32" t="inlineStr">
@@ -29845,7 +29966,7 @@
       </c>
       <c r="H335" s="32" t="inlineStr">
         <is>
-          <t>IMPORTIR INFO</t>
+          <t>SUPPLIER INFO3</t>
         </is>
       </c>
     </row>
@@ -29856,11 +29977,11 @@
         </is>
       </c>
       <c r="B336" s="31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C336" s="32" t="inlineStr">
         <is>
-          <t>IMPORTIR_INFO2</t>
+          <t>IMPORTIR_INFO</t>
         </is>
       </c>
       <c r="D336" s="32" t="inlineStr">
@@ -29877,7 +29998,7 @@
       </c>
       <c r="H336" s="32" t="inlineStr">
         <is>
-          <t>IMPORTIR INFO2</t>
+          <t>IMPORTIR INFO</t>
         </is>
       </c>
     </row>
@@ -29888,11 +30009,11 @@
         </is>
       </c>
       <c r="B337" s="31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C337" s="32" t="inlineStr">
         <is>
-          <t>IMPORTIR_INFO3</t>
+          <t>IMPORTIR_INFO2</t>
         </is>
       </c>
       <c r="D337" s="32" t="inlineStr">
@@ -29909,7 +30030,7 @@
       </c>
       <c r="H337" s="32" t="inlineStr">
         <is>
-          <t>IMPORTIR INFO3</t>
+          <t>IMPORTIR INFO2</t>
         </is>
       </c>
     </row>
@@ -29920,11 +30041,11 @@
         </is>
       </c>
       <c r="B338" s="31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C338" s="32" t="inlineStr">
         <is>
-          <t>IMPORTIR_INFO4</t>
+          <t>IMPORTIR_INFO3</t>
         </is>
       </c>
       <c r="D338" s="32" t="inlineStr">
@@ -29941,7 +30062,7 @@
       </c>
       <c r="H338" s="32" t="inlineStr">
         <is>
-          <t>IMPORTIR INFO4</t>
+          <t>IMPORTIR INFO3</t>
         </is>
       </c>
     </row>
@@ -29952,16 +30073,16 @@
         </is>
       </c>
       <c r="B339" s="31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C339" s="32" t="inlineStr">
         <is>
-          <t>MOD_DST_CD</t>
+          <t>IMPORTIR_INFO4</t>
         </is>
       </c>
       <c r="D339" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(5)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E339" s="32" t="inlineStr"/>
@@ -29973,7 +30094,7 @@
       </c>
       <c r="H339" s="32" t="inlineStr">
         <is>
-          <t>MOD DST CD</t>
+          <t>IMPORTIR INFO4</t>
         </is>
       </c>
     </row>
@@ -29984,16 +30105,16 @@
         </is>
       </c>
       <c r="B340" s="31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C340" s="32" t="inlineStr">
         <is>
-          <t>PLN_PCK_DT</t>
+          <t>MOD_DST_CD</t>
         </is>
       </c>
       <c r="D340" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(5)</t>
         </is>
       </c>
       <c r="E340" s="32" t="inlineStr"/>
@@ -30005,7 +30126,7 @@
       </c>
       <c r="H340" s="32" t="inlineStr">
         <is>
-          <t>PLN PCK DT</t>
+          <t>MOD DST CD</t>
         </is>
       </c>
     </row>
@@ -30016,16 +30137,16 @@
         </is>
       </c>
       <c r="B341" s="31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C341" s="32" t="inlineStr">
         <is>
-          <t>PART_ADDRESS</t>
+          <t>PLN_PCK_DT</t>
         </is>
       </c>
       <c r="D341" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E341" s="32" t="inlineStr"/>
@@ -30037,7 +30158,7 @@
       </c>
       <c r="H341" s="32" t="inlineStr">
         <is>
-          <t>PART ADDRESS</t>
+          <t>PLN PCK DT</t>
         </is>
       </c>
     </row>
@@ -30048,16 +30169,16 @@
         </is>
       </c>
       <c r="B342" s="31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C342" s="32" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>PART_ADDRESS</t>
         </is>
       </c>
       <c r="D342" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(2)</t>
+          <t>VARCHAR(15)</t>
         </is>
       </c>
       <c r="E342" s="32" t="inlineStr"/>
@@ -30069,7 +30190,7 @@
       </c>
       <c r="H342" s="32" t="inlineStr">
         <is>
-          <t>Status ('0' in the sample); STATUS; values: 0</t>
+          <t>PART ADDRESS</t>
         </is>
       </c>
     </row>
@@ -30080,16 +30201,16 @@
         </is>
       </c>
       <c r="B343" s="31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C343" s="32" t="inlineStr">
         <is>
-          <t>CREATED_BY</t>
+          <t>STATUS</t>
         </is>
       </c>
       <c r="D343" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(2)</t>
         </is>
       </c>
       <c r="E343" s="32" t="inlineStr"/>
@@ -30101,7 +30222,7 @@
       </c>
       <c r="H343" s="32" t="inlineStr">
         <is>
-          <t>CREATED BY</t>
+          <t>Status ('0' in the sample); STATUS; values: 0</t>
         </is>
       </c>
     </row>
@@ -30112,16 +30233,16 @@
         </is>
       </c>
       <c r="B344" s="31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C344" s="32" t="inlineStr">
         <is>
-          <t>CREATED_DT</t>
+          <t>CREATED_BY</t>
         </is>
       </c>
       <c r="D344" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E344" s="32" t="inlineStr"/>
@@ -30133,7 +30254,7 @@
       </c>
       <c r="H344" s="32" t="inlineStr">
         <is>
-          <t>CREATED DT</t>
+          <t>CREATED BY</t>
         </is>
       </c>
     </row>
@@ -30144,16 +30265,16 @@
         </is>
       </c>
       <c r="B345" s="31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C345" s="32" t="inlineStr">
         <is>
-          <t>CHANGED_BY</t>
+          <t>CREATED_DT</t>
         </is>
       </c>
       <c r="D345" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E345" s="32" t="inlineStr"/>
@@ -30165,7 +30286,7 @@
       </c>
       <c r="H345" s="32" t="inlineStr">
         <is>
-          <t>CHANGED BY</t>
+          <t>CREATED DT</t>
         </is>
       </c>
     </row>
@@ -30176,16 +30297,16 @@
         </is>
       </c>
       <c r="B346" s="31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C346" s="32" t="inlineStr">
         <is>
-          <t>CHANGED_DT</t>
+          <t>CHANGED_BY</t>
         </is>
       </c>
       <c r="D346" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E346" s="32" t="inlineStr"/>
@@ -30197,7 +30318,7 @@
       </c>
       <c r="H346" s="32" t="inlineStr">
         <is>
-          <t>CHANGED DT</t>
+          <t>CHANGED BY</t>
         </is>
       </c>
     </row>
@@ -30208,28 +30329,28 @@
         </is>
       </c>
       <c r="B347" s="31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C347" s="32" t="inlineStr">
         <is>
-          <t>DOCK_CD</t>
+          <t>CHANGED_DT</t>
         </is>
       </c>
       <c r="D347" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(2+) (inferred)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E347" s="32" t="inlineStr"/>
       <c r="F347" s="32" t="inlineStr"/>
       <c r="G347" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H347" s="32" t="inlineStr">
         <is>
-          <t>Receiving dock; not in the DB structure document; values: S1, S2, S3</t>
+          <t>CHANGED DT</t>
         </is>
       </c>
     </row>
@@ -30240,16 +30361,16 @@
         </is>
       </c>
       <c r="B348" s="31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C348" s="32" t="inlineStr">
         <is>
-          <t>CANCEL_QTY</t>
+          <t>DOCK_CD</t>
         </is>
       </c>
       <c r="D348" s="32" t="inlineStr">
         <is>
-          <t>NUMERIC (inferred)</t>
+          <t>VARCHAR(2+) (inferred)</t>
         </is>
       </c>
       <c r="E348" s="32" t="inlineStr"/>
@@ -30261,7 +30382,7 @@
       </c>
       <c r="H348" s="32" t="inlineStr">
         <is>
-          <t>not in the DB structure document; values: 0</t>
+          <t>Receiving dock; not in the DB structure document; values: S1, S2, S3</t>
         </is>
       </c>
     </row>
@@ -30272,28 +30393,28 @@
         </is>
       </c>
       <c r="B349" s="31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C349" s="32" t="inlineStr">
         <is>
-          <t>CANCEL_DT</t>
+          <t>CANCEL_QTY</t>
         </is>
       </c>
       <c r="D349" s="32" t="inlineStr">
         <is>
-          <t>DATETIME (inferred)</t>
+          <t>NUMERIC (inferred)</t>
         </is>
       </c>
       <c r="E349" s="32" t="inlineStr"/>
       <c r="F349" s="32" t="inlineStr"/>
       <c r="G349" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H349" s="32" t="inlineStr">
         <is>
-          <t>not in the DB structure document</t>
+          <t>not in the DB structure document; values: 0</t>
         </is>
       </c>
     </row>
@@ -30304,16 +30425,16 @@
         </is>
       </c>
       <c r="B350" s="31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C350" s="32" t="inlineStr">
         <is>
-          <t>SEND_FLAG_MDI</t>
+          <t>CANCEL_DT</t>
         </is>
       </c>
       <c r="D350" s="32" t="inlineStr">
         <is>
-          <t>? (no data) (inferred)</t>
+          <t>DATETIME (inferred)</t>
         </is>
       </c>
       <c r="E350" s="32" t="inlineStr"/>
@@ -30336,11 +30457,11 @@
         </is>
       </c>
       <c r="B351" s="31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C351" s="32" t="inlineStr">
         <is>
-          <t>SEND_DATE_MDI</t>
+          <t>SEND_FLAG_MDI</t>
         </is>
       </c>
       <c r="D351" s="32" t="inlineStr">
@@ -30364,36 +30485,32 @@
     <row r="352">
       <c r="A352" s="32" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_PRA_DAILY_ORDER_PART</t>
         </is>
       </c>
       <c r="B352" s="31" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C352" s="32" t="inlineStr">
         <is>
-          <t>PO_NO</t>
+          <t>SEND_DATE_MDI</t>
         </is>
       </c>
       <c r="D352" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
-        </is>
-      </c>
-      <c r="E352" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>? (no data) (inferred)</t>
+        </is>
+      </c>
+      <c r="E352" s="32" t="inlineStr"/>
       <c r="F352" s="32" t="inlineStr"/>
       <c r="G352" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H352" s="32" t="inlineStr">
         <is>
-          <t>PO number (Pra Daily Order Manifest)</t>
+          <t>not in the DB structure document</t>
         </is>
       </c>
     </row>
@@ -30404,11 +30521,11 @@
         </is>
       </c>
       <c r="B353" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C353" s="32" t="inlineStr">
         <is>
-          <t>MANIFEST_NO</t>
+          <t>PO_NO</t>
         </is>
       </c>
       <c r="D353" s="32" t="inlineStr">
@@ -30421,11 +30538,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F353" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F353" s="32" t="inlineStr"/>
       <c r="G353" s="32" t="inlineStr">
         <is>
           <t>N</t>
@@ -30433,7 +30546,7 @@
       </c>
       <c r="H353" s="32" t="inlineStr">
         <is>
-          <t>Manifest number</t>
+          <t>PO number (Pra Daily Order Manifest)</t>
         </is>
       </c>
     </row>
@@ -30444,11 +30557,11 @@
         </is>
       </c>
       <c r="B354" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C354" s="32" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM</t>
+          <t>MANIFEST_NO</t>
         </is>
       </c>
       <c r="D354" s="32" t="inlineStr">
@@ -30473,7 +30586,7 @@
       </c>
       <c r="H354" s="32" t="inlineStr">
         <is>
-          <t>Manifest item number (Pra Daily Order Part)</t>
+          <t>Manifest number</t>
         </is>
       </c>
     </row>
@@ -30484,20 +30597,28 @@
         </is>
       </c>
       <c r="B355" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C355" s="32" t="inlineStr">
         <is>
-          <t>PART_NO</t>
+          <t>MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="D355" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
-        </is>
-      </c>
-      <c r="E355" s="32" t="inlineStr"/>
-      <c r="F355" s="32" t="inlineStr"/>
+          <t>VARCHAR(TBD)</t>
+        </is>
+      </c>
+      <c r="E355" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F355" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G355" s="32" t="inlineStr">
         <is>
           <t>N</t>
@@ -30505,7 +30626,7 @@
       </c>
       <c r="H355" s="32" t="inlineStr">
         <is>
-          <t>Part number</t>
+          <t>Manifest item number (Pra Daily Order Part)</t>
         </is>
       </c>
     </row>
@@ -30516,16 +30637,16 @@
         </is>
       </c>
       <c r="B356" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C356" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_CD</t>
+          <t>PART_NO</t>
         </is>
       </c>
       <c r="D356" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>VARCHAR(15)</t>
         </is>
       </c>
       <c r="E356" s="32" t="inlineStr"/>
@@ -30537,7 +30658,7 @@
       </c>
       <c r="H356" s="32" t="inlineStr">
         <is>
-          <t>Supplier code</t>
+          <t>Part number</t>
         </is>
       </c>
     </row>
@@ -30548,11 +30669,11 @@
         </is>
       </c>
       <c r="B357" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C357" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_PLANT</t>
+          <t>SUPPLIER_CD</t>
         </is>
       </c>
       <c r="D357" s="32" t="inlineStr">
@@ -30569,7 +30690,7 @@
       </c>
       <c r="H357" s="32" t="inlineStr">
         <is>
-          <t>Supplier plant</t>
+          <t>Supplier code</t>
         </is>
       </c>
     </row>
@@ -30580,16 +30701,16 @@
         </is>
       </c>
       <c r="B358" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C358" s="32" t="inlineStr">
         <is>
-          <t>ORDER_QTY</t>
+          <t>SUPPLIER_PLANT</t>
         </is>
       </c>
       <c r="D358" s="32" t="inlineStr">
         <is>
-          <t>NUMBER(TBD)</t>
+          <t>VARCHAR(TBD)</t>
         </is>
       </c>
       <c r="E358" s="32" t="inlineStr"/>
@@ -30601,7 +30722,7 @@
       </c>
       <c r="H358" s="32" t="inlineStr">
         <is>
-          <t>PO qty of the part</t>
+          <t>Supplier plant</t>
         </is>
       </c>
     </row>
@@ -30612,11 +30733,11 @@
         </is>
       </c>
       <c r="B359" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C359" s="32" t="inlineStr">
         <is>
-          <t>MAPPED_QTY</t>
+          <t>ORDER_QTY</t>
         </is>
       </c>
       <c r="D359" s="32" t="inlineStr">
@@ -30633,7 +30754,7 @@
       </c>
       <c r="H359" s="32" t="inlineStr">
         <is>
-          <t>Qty already mapped to customer orders by [Create ASN]; open qty = ORDER_QTY - MAPPED_QTY</t>
+          <t>PO qty of the part</t>
         </is>
       </c>
     </row>
@@ -30644,16 +30765,16 @@
         </is>
       </c>
       <c r="B360" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C360" s="32" t="inlineStr">
         <is>
-          <t>CREATED_BY</t>
+          <t>MAPPED_QTY</t>
         </is>
       </c>
       <c r="D360" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>NUMBER(TBD)</t>
         </is>
       </c>
       <c r="E360" s="32" t="inlineStr"/>
@@ -30665,7 +30786,7 @@
       </c>
       <c r="H360" s="32" t="inlineStr">
         <is>
-          <t>User who created the record</t>
+          <t>Qty already mapped to customer orders by [Create ASN]; open qty = ORDER_QTY - MAPPED_QTY</t>
         </is>
       </c>
     </row>
@@ -30676,16 +30797,16 @@
         </is>
       </c>
       <c r="B361" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C361" s="32" t="inlineStr">
         <is>
-          <t>CREATED_DT</t>
+          <t>CREATED_BY</t>
         </is>
       </c>
       <c r="D361" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(TBD)</t>
         </is>
       </c>
       <c r="E361" s="32" t="inlineStr"/>
@@ -30697,7 +30818,7 @@
       </c>
       <c r="H361" s="32" t="inlineStr">
         <is>
-          <t>Created date and time</t>
+          <t>User who created the record</t>
         </is>
       </c>
     </row>
@@ -30708,16 +30829,16 @@
         </is>
       </c>
       <c r="B362" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C362" s="32" t="inlineStr">
         <is>
-          <t>CHANGED_BY</t>
+          <t>CREATED_DT</t>
         </is>
       </c>
       <c r="D362" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(TBD)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E362" s="32" t="inlineStr"/>
@@ -30729,7 +30850,7 @@
       </c>
       <c r="H362" s="32" t="inlineStr">
         <is>
-          <t>User who last changed the record</t>
+          <t>Created date and time</t>
         </is>
       </c>
     </row>
@@ -30740,16 +30861,16 @@
         </is>
       </c>
       <c r="B363" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C363" s="32" t="inlineStr">
         <is>
-          <t>CHANGED_DT</t>
+          <t>CHANGED_BY</t>
         </is>
       </c>
       <c r="D363" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(TBD)</t>
         </is>
       </c>
       <c r="E363" s="32" t="inlineStr"/>
@@ -30761,39 +30882,39 @@
       </c>
       <c r="H363" s="32" t="inlineStr">
         <is>
-          <t>Last changed date and time</t>
+          <t>User who last changed the record</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="32" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_MANIFEST</t>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
         </is>
       </c>
       <c r="B364" s="31" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C364" s="32" t="inlineStr">
         <is>
-          <t>DEPOT_CD</t>
+          <t>CHANGED_DT</t>
         </is>
       </c>
       <c r="D364" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E364" s="32" t="inlineStr"/>
       <c r="F364" s="32" t="inlineStr"/>
       <c r="G364" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H364" s="32" t="inlineStr">
         <is>
-          <t>Depot Code</t>
+          <t>Last changed date and time</t>
         </is>
       </c>
     </row>
@@ -30804,32 +30925,28 @@
         </is>
       </c>
       <c r="B365" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C365" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_CD</t>
+          <t>DEPOT_CD</t>
         </is>
       </c>
       <c r="D365" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(4)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E365" s="32" t="inlineStr"/>
-      <c r="F365" s="32" t="inlineStr">
+      <c r="F365" s="32" t="inlineStr"/>
+      <c r="G365" s="32" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G365" s="32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="H365" s="32" t="inlineStr">
         <is>
-          <t>Supplier Code</t>
+          <t>Depot Code</t>
         </is>
       </c>
     </row>
@@ -30840,16 +30957,16 @@
         </is>
       </c>
       <c r="B366" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C366" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_PLANT</t>
+          <t>SUPPLIER_CD</t>
         </is>
       </c>
       <c r="D366" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(1)</t>
+          <t>VARCHAR(4)</t>
         </is>
       </c>
       <c r="E366" s="32" t="inlineStr"/>
@@ -30865,7 +30982,7 @@
       </c>
       <c r="H366" s="32" t="inlineStr">
         <is>
-          <t>Supplier Plant Code</t>
+          <t>Supplier Code</t>
         </is>
       </c>
     </row>
@@ -30876,28 +30993,32 @@
         </is>
       </c>
       <c r="B367" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C367" s="32" t="inlineStr">
         <is>
-          <t>SUB_SUPP_CD</t>
+          <t>SUPPLIER_PLANT</t>
         </is>
       </c>
       <c r="D367" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(4)</t>
+          <t>VARCHAR(1)</t>
         </is>
       </c>
       <c r="E367" s="32" t="inlineStr"/>
-      <c r="F367" s="32" t="inlineStr"/>
+      <c r="F367" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G367" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H367" s="32" t="inlineStr">
         <is>
-          <t>Sub Supplier Code</t>
+          <t>Supplier Plant Code</t>
         </is>
       </c>
     </row>
@@ -30908,16 +31029,16 @@
         </is>
       </c>
       <c r="B368" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C368" s="32" t="inlineStr">
         <is>
-          <t>SUB_SUPP_PLANT</t>
+          <t>SUB_SUPP_CD</t>
         </is>
       </c>
       <c r="D368" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(1)</t>
+          <t>VARCHAR(4)</t>
         </is>
       </c>
       <c r="E368" s="32" t="inlineStr"/>
@@ -30929,7 +31050,7 @@
       </c>
       <c r="H368" s="32" t="inlineStr">
         <is>
-          <t>Sub Supplier Plant Code</t>
+          <t>Sub Supplier Code</t>
         </is>
       </c>
     </row>
@@ -30940,16 +31061,16 @@
         </is>
       </c>
       <c r="B369" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C369" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_NAME</t>
+          <t>SUB_SUPP_PLANT</t>
         </is>
       </c>
       <c r="D369" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(1)</t>
         </is>
       </c>
       <c r="E369" s="32" t="inlineStr"/>
@@ -30961,7 +31082,7 @@
       </c>
       <c r="H369" s="32" t="inlineStr">
         <is>
-          <t>Supplier Name</t>
+          <t>Sub Supplier Plant Code</t>
         </is>
       </c>
     </row>
@@ -30972,28 +31093,28 @@
         </is>
       </c>
       <c r="B370" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C370" s="32" t="inlineStr">
         <is>
-          <t>PO_NO</t>
+          <t>SUPPLIER_NAME</t>
         </is>
       </c>
       <c r="D370" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E370" s="32" t="inlineStr"/>
       <c r="F370" s="32" t="inlineStr"/>
       <c r="G370" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H370" s="32" t="inlineStr">
         <is>
-          <t>PO Number</t>
+          <t>Supplier Name</t>
         </is>
       </c>
     </row>
@@ -31004,16 +31125,16 @@
         </is>
       </c>
       <c r="B371" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C371" s="32" t="inlineStr">
         <is>
-          <t>ASN_NO</t>
+          <t>PO_NO</t>
         </is>
       </c>
       <c r="D371" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E371" s="32" t="inlineStr"/>
@@ -31025,7 +31146,7 @@
       </c>
       <c r="H371" s="32" t="inlineStr">
         <is>
-          <t>ASN Number</t>
+          <t>PO Number</t>
         </is>
       </c>
     </row>
@@ -31036,11 +31157,11 @@
         </is>
       </c>
       <c r="B372" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C372" s="32" t="inlineStr">
         <is>
-          <t>INVOICE_NO</t>
+          <t>ASN_NO</t>
         </is>
       </c>
       <c r="D372" s="32" t="inlineStr">
@@ -31057,7 +31178,7 @@
       </c>
       <c r="H372" s="32" t="inlineStr">
         <is>
-          <t>Invoice Number</t>
+          <t>ASN Number</t>
         </is>
       </c>
     </row>
@@ -31068,16 +31189,16 @@
         </is>
       </c>
       <c r="B373" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C373" s="32" t="inlineStr">
         <is>
-          <t>PO_DATE</t>
+          <t>INVOICE_NO</t>
         </is>
       </c>
       <c r="D373" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(15)</t>
         </is>
       </c>
       <c r="E373" s="32" t="inlineStr"/>
@@ -31089,7 +31210,7 @@
       </c>
       <c r="H373" s="32" t="inlineStr">
         <is>
-          <t>PO Date</t>
+          <t>Invoice Number</t>
         </is>
       </c>
     </row>
@@ -31100,11 +31221,11 @@
         </is>
       </c>
       <c r="B374" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C374" s="32" t="inlineStr">
         <is>
-          <t>ASN_DATE</t>
+          <t>PO_DATE</t>
         </is>
       </c>
       <c r="D374" s="32" t="inlineStr">
@@ -31121,7 +31242,7 @@
       </c>
       <c r="H374" s="32" t="inlineStr">
         <is>
-          <t>ASN Date</t>
+          <t>PO Date</t>
         </is>
       </c>
     </row>
@@ -31132,23 +31253,19 @@
         </is>
       </c>
       <c r="B375" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C375" s="32" t="inlineStr">
         <is>
-          <t>SUB_MANIFEST_NO</t>
+          <t>ASN_DATE</t>
         </is>
       </c>
       <c r="D375" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="E375" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E375" s="32" t="inlineStr"/>
       <c r="F375" s="32" t="inlineStr"/>
       <c r="G375" s="32" t="inlineStr">
         <is>
@@ -31157,7 +31274,7 @@
       </c>
       <c r="H375" s="32" t="inlineStr">
         <is>
-          <t>Sub Manifest Number</t>
+          <t>ASN Date</t>
         </is>
       </c>
     </row>
@@ -31168,16 +31285,16 @@
         </is>
       </c>
       <c r="B376" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C376" s="32" t="inlineStr">
         <is>
-          <t>MANIFEST_NO</t>
+          <t>SUB_MANIFEST_NO</t>
         </is>
       </c>
       <c r="D376" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(16)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E376" s="32" t="inlineStr">
@@ -31185,11 +31302,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F376" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="F376" s="32" t="inlineStr"/>
       <c r="G376" s="32" t="inlineStr">
         <is>
           <t>N</t>
@@ -31197,7 +31310,7 @@
       </c>
       <c r="H376" s="32" t="inlineStr">
         <is>
-          <t>Manifest Number</t>
+          <t>Sub Manifest Number</t>
         </is>
       </c>
     </row>
@@ -31208,28 +31321,36 @@
         </is>
       </c>
       <c r="B377" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C377" s="32" t="inlineStr">
         <is>
-          <t>MAKER_CODE</t>
+          <t>MANIFEST_NO</t>
         </is>
       </c>
       <c r="D377" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="E377" s="32" t="inlineStr"/>
-      <c r="F377" s="32" t="inlineStr"/>
+          <t>VARCHAR(16)</t>
+        </is>
+      </c>
+      <c r="E377" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F377" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G377" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H377" s="32" t="inlineStr">
         <is>
-          <t>Maker Code</t>
+          <t>Manifest Number</t>
         </is>
       </c>
     </row>
@@ -31240,11 +31361,11 @@
         </is>
       </c>
       <c r="B378" s="31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C378" s="32" t="inlineStr">
         <is>
-          <t>PO_TRANSPORT_CD</t>
+          <t>MAKER_CODE</t>
         </is>
       </c>
       <c r="D378" s="32" t="inlineStr">
@@ -31261,7 +31382,7 @@
       </c>
       <c r="H378" s="32" t="inlineStr">
         <is>
-          <t>PO Transport Code</t>
+          <t>Maker Code</t>
         </is>
       </c>
     </row>
@@ -31272,16 +31393,16 @@
         </is>
       </c>
       <c r="B379" s="31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C379" s="32" t="inlineStr">
         <is>
-          <t>ORDER_TYPE</t>
+          <t>PO_TRANSPORT_CD</t>
         </is>
       </c>
       <c r="D379" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(1)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E379" s="32" t="inlineStr"/>
@@ -31293,7 +31414,7 @@
       </c>
       <c r="H379" s="32" t="inlineStr">
         <is>
-          <t>Order Type</t>
+          <t>PO Transport Code</t>
         </is>
       </c>
     </row>
@@ -31304,16 +31425,16 @@
         </is>
       </c>
       <c r="B380" s="31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C380" s="32" t="inlineStr">
         <is>
-          <t>CROSS_DOCK_FLAG</t>
+          <t>ORDER_TYPE</t>
         </is>
       </c>
       <c r="D380" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(3)</t>
+          <t>VARCHAR(1)</t>
         </is>
       </c>
       <c r="E380" s="32" t="inlineStr"/>
@@ -31325,7 +31446,7 @@
       </c>
       <c r="H380" s="32" t="inlineStr">
         <is>
-          <t>Cross Dock Flag</t>
+          <t>Order Type</t>
         </is>
       </c>
     </row>
@@ -31336,16 +31457,16 @@
         </is>
       </c>
       <c r="B381" s="31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C381" s="32" t="inlineStr">
         <is>
-          <t>COMPANY_CD</t>
+          <t>CROSS_DOCK_FLAG</t>
         </is>
       </c>
       <c r="D381" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(4)</t>
+          <t>VARCHAR(3)</t>
         </is>
       </c>
       <c r="E381" s="32" t="inlineStr"/>
@@ -31357,7 +31478,7 @@
       </c>
       <c r="H381" s="32" t="inlineStr">
         <is>
-          <t>Company Code</t>
+          <t>Cross Dock Flag</t>
         </is>
       </c>
     </row>
@@ -31368,16 +31489,16 @@
         </is>
       </c>
       <c r="B382" s="31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C382" s="32" t="inlineStr">
         <is>
-          <t>RCV_PLANT_CD</t>
+          <t>COMPANY_CD</t>
         </is>
       </c>
       <c r="D382" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(1)</t>
+          <t>VARCHAR(4)</t>
         </is>
       </c>
       <c r="E382" s="32" t="inlineStr"/>
@@ -31389,7 +31510,7 @@
       </c>
       <c r="H382" s="32" t="inlineStr">
         <is>
-          <t>Receive Plant Code</t>
+          <t>Company Code</t>
         </is>
       </c>
     </row>
@@ -31400,16 +31521,16 @@
         </is>
       </c>
       <c r="B383" s="31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C383" s="32" t="inlineStr">
         <is>
-          <t>DOCK_CD</t>
+          <t>RCV_PLANT_CD</t>
         </is>
       </c>
       <c r="D383" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(2)</t>
+          <t>VARCHAR(1)</t>
         </is>
       </c>
       <c r="E383" s="32" t="inlineStr"/>
@@ -31421,7 +31542,7 @@
       </c>
       <c r="H383" s="32" t="inlineStr">
         <is>
-          <t>Dock Code</t>
+          <t>Receive Plant Code</t>
         </is>
       </c>
     </row>
@@ -31432,28 +31553,28 @@
         </is>
       </c>
       <c r="B384" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C384" s="32" t="inlineStr">
         <is>
-          <t>TOTAL_ITEM</t>
+          <t>DOCK_CD</t>
         </is>
       </c>
       <c r="D384" s="32" t="inlineStr">
         <is>
-          <t>NUMERIC</t>
+          <t>VARCHAR(2)</t>
         </is>
       </c>
       <c r="E384" s="32" t="inlineStr"/>
       <c r="F384" s="32" t="inlineStr"/>
       <c r="G384" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H384" s="32" t="inlineStr">
         <is>
-          <t>Total Item</t>
+          <t>Dock Code</t>
         </is>
       </c>
     </row>
@@ -31464,11 +31585,11 @@
         </is>
       </c>
       <c r="B385" s="31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C385" s="32" t="inlineStr">
         <is>
-          <t>TOTAL_QTY</t>
+          <t>TOTAL_ITEM</t>
         </is>
       </c>
       <c r="D385" s="32" t="inlineStr">
@@ -31485,7 +31606,7 @@
       </c>
       <c r="H385" s="32" t="inlineStr">
         <is>
-          <t>Total Quantity</t>
+          <t>Total Item</t>
         </is>
       </c>
     </row>
@@ -31496,28 +31617,28 @@
         </is>
       </c>
       <c r="B386" s="31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C386" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY_DT_ORI</t>
+          <t>TOTAL_QTY</t>
         </is>
       </c>
       <c r="D386" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="E386" s="32" t="inlineStr"/>
       <c r="F386" s="32" t="inlineStr"/>
       <c r="G386" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H386" s="32" t="inlineStr">
         <is>
-          <t>Delivery Date Original</t>
+          <t>Total Quantity</t>
         </is>
       </c>
     </row>
@@ -31528,11 +31649,11 @@
         </is>
       </c>
       <c r="B387" s="31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C387" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY_DT_ADJUST</t>
+          <t>DELIVERY_DT_ORI</t>
         </is>
       </c>
       <c r="D387" s="32" t="inlineStr">
@@ -31549,7 +31670,7 @@
       </c>
       <c r="H387" s="32" t="inlineStr">
         <is>
-          <t>Delivery Date Adjust</t>
+          <t>Delivery Date Original</t>
         </is>
       </c>
     </row>
@@ -31560,11 +31681,11 @@
         </is>
       </c>
       <c r="B388" s="31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C388" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY_DT_ACTUAL</t>
+          <t>DELIVERY_DT_ADJUST</t>
         </is>
       </c>
       <c r="D388" s="32" t="inlineStr">
@@ -31581,7 +31702,7 @@
       </c>
       <c r="H388" s="32" t="inlineStr">
         <is>
-          <t>Delivery Date Actual</t>
+          <t>Delivery Date Adjust</t>
         </is>
       </c>
     </row>
@@ -31592,16 +31713,16 @@
         </is>
       </c>
       <c r="B389" s="31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C389" s="32" t="inlineStr">
         <is>
-          <t>SHIPPING_DOCK</t>
+          <t>DELIVERY_DT_ACTUAL</t>
         </is>
       </c>
       <c r="D389" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(3)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E389" s="32" t="inlineStr"/>
@@ -31613,7 +31734,7 @@
       </c>
       <c r="H389" s="32" t="inlineStr">
         <is>
-          <t>Shipping Dock</t>
+          <t>Delivery Date Actual</t>
         </is>
       </c>
     </row>
@@ -31624,16 +31745,16 @@
         </is>
       </c>
       <c r="B390" s="31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C390" s="32" t="inlineStr">
         <is>
-          <t>SHIPPING_DT</t>
+          <t>SHIPPING_DOCK</t>
         </is>
       </c>
       <c r="D390" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(3)</t>
         </is>
       </c>
       <c r="E390" s="32" t="inlineStr"/>
@@ -31645,7 +31766,7 @@
       </c>
       <c r="H390" s="32" t="inlineStr">
         <is>
-          <t>Shipping Date</t>
+          <t>Shipping Dock</t>
         </is>
       </c>
     </row>
@@ -31656,16 +31777,16 @@
         </is>
       </c>
       <c r="B391" s="31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C391" s="32" t="inlineStr">
         <is>
-          <t>SUPP_REFF_1</t>
+          <t>SHIPPING_DT</t>
         </is>
       </c>
       <c r="D391" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(25)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E391" s="32" t="inlineStr"/>
@@ -31677,7 +31798,7 @@
       </c>
       <c r="H391" s="32" t="inlineStr">
         <is>
-          <t>Supplier Reff 1</t>
+          <t>Shipping Date</t>
         </is>
       </c>
     </row>
@@ -31688,11 +31809,11 @@
         </is>
       </c>
       <c r="B392" s="31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C392" s="32" t="inlineStr">
         <is>
-          <t>SUPP_REFF_2</t>
+          <t>SUPP_REFF_1</t>
         </is>
       </c>
       <c r="D392" s="32" t="inlineStr">
@@ -31709,7 +31830,7 @@
       </c>
       <c r="H392" s="32" t="inlineStr">
         <is>
-          <t>Supplier Reff 2</t>
+          <t>Supplier Reff 1</t>
         </is>
       </c>
     </row>
@@ -31720,28 +31841,28 @@
         </is>
       </c>
       <c r="B393" s="31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C393" s="32" t="inlineStr">
         <is>
-          <t>SUB_ROUTE_CD</t>
+          <t>SUPP_REFF_2</t>
         </is>
       </c>
       <c r="D393" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>VARCHAR(25)</t>
         </is>
       </c>
       <c r="E393" s="32" t="inlineStr"/>
       <c r="F393" s="32" t="inlineStr"/>
       <c r="G393" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H393" s="32" t="inlineStr">
         <is>
-          <t>Sub Route Code</t>
+          <t>Supplier Reff 2</t>
         </is>
       </c>
     </row>
@@ -31752,16 +31873,16 @@
         </is>
       </c>
       <c r="B394" s="31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C394" s="32" t="inlineStr">
         <is>
-          <t>SUB_ROUTE_SEQ</t>
+          <t>SUB_ROUTE_CD</t>
         </is>
       </c>
       <c r="D394" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(2)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E394" s="32" t="inlineStr"/>
@@ -31773,7 +31894,7 @@
       </c>
       <c r="H394" s="32" t="inlineStr">
         <is>
-          <t>Sub Route Seq</t>
+          <t>Sub Route Code</t>
         </is>
       </c>
     </row>
@@ -31784,28 +31905,28 @@
         </is>
       </c>
       <c r="B395" s="31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C395" s="32" t="inlineStr">
         <is>
-          <t>SUB_ROUTE_DT</t>
+          <t>SUB_ROUTE_SEQ</t>
         </is>
       </c>
       <c r="D395" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(2)</t>
         </is>
       </c>
       <c r="E395" s="32" t="inlineStr"/>
       <c r="F395" s="32" t="inlineStr"/>
       <c r="G395" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H395" s="32" t="inlineStr">
         <is>
-          <t>Sub Route Date</t>
+          <t>Sub Route Seq</t>
         </is>
       </c>
     </row>
@@ -31816,16 +31937,16 @@
         </is>
       </c>
       <c r="B396" s="31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C396" s="32" t="inlineStr">
         <is>
-          <t>FST_X_DOC_CD</t>
+          <t>SUB_ROUTE_DT</t>
         </is>
       </c>
       <c r="D396" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E396" s="32" t="inlineStr"/>
@@ -31837,7 +31958,7 @@
       </c>
       <c r="H396" s="32" t="inlineStr">
         <is>
-          <t>Fst X Doc Code</t>
+          <t>Sub Route Date</t>
         </is>
       </c>
     </row>
@@ -31848,16 +31969,16 @@
         </is>
       </c>
       <c r="B397" s="31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C397" s="32" t="inlineStr">
         <is>
-          <t>FST_X_PLANT_CD</t>
+          <t>FST_X_DOC_CD</t>
         </is>
       </c>
       <c r="D397" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(15)</t>
         </is>
       </c>
       <c r="E397" s="32" t="inlineStr"/>
@@ -31869,7 +31990,7 @@
       </c>
       <c r="H397" s="32" t="inlineStr">
         <is>
-          <t>Fst X Plant Date</t>
+          <t>Fst X Doc Code</t>
         </is>
       </c>
     </row>
@@ -31880,16 +32001,16 @@
         </is>
       </c>
       <c r="B398" s="31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C398" s="32" t="inlineStr">
         <is>
-          <t>FST_X_SHIPPING_DOCK_CD</t>
+          <t>FST_X_PLANT_CD</t>
         </is>
       </c>
       <c r="D398" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E398" s="32" t="inlineStr"/>
@@ -31901,7 +32022,7 @@
       </c>
       <c r="H398" s="32" t="inlineStr">
         <is>
-          <t>Fst X Shipping Dock Code</t>
+          <t>Fst X Plant Date</t>
         </is>
       </c>
     </row>
@@ -31912,16 +32033,16 @@
         </is>
       </c>
       <c r="B399" s="31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C399" s="32" t="inlineStr">
         <is>
-          <t>FST_X_DOCK_ARRIVAL_DT</t>
+          <t>FST_X_SHIPPING_DOCK_CD</t>
         </is>
       </c>
       <c r="D399" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E399" s="32" t="inlineStr"/>
@@ -31933,7 +32054,7 @@
       </c>
       <c r="H399" s="32" t="inlineStr">
         <is>
-          <t>Fst X Dock Arrival Date</t>
+          <t>Fst X Shipping Dock Code</t>
         </is>
       </c>
     </row>
@@ -31944,11 +32065,11 @@
         </is>
       </c>
       <c r="B400" s="31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C400" s="32" t="inlineStr">
         <is>
-          <t>FST_X_DOCK_DEPART_DT</t>
+          <t>FST_X_DOCK_ARRIVAL_DT</t>
         </is>
       </c>
       <c r="D400" s="32" t="inlineStr">
@@ -31965,7 +32086,7 @@
       </c>
       <c r="H400" s="32" t="inlineStr">
         <is>
-          <t>Fst X Dock Depart Date</t>
+          <t>Fst X Dock Arrival Date</t>
         </is>
       </c>
     </row>
@@ -31976,16 +32097,16 @@
         </is>
       </c>
       <c r="B401" s="31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C401" s="32" t="inlineStr">
         <is>
-          <t>FST_X_DOCK_ROUTE_GRP_CD</t>
+          <t>FST_X_DOCK_DEPART_DT</t>
         </is>
       </c>
       <c r="D401" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E401" s="32" t="inlineStr"/>
@@ -31997,7 +32118,7 @@
       </c>
       <c r="H401" s="32" t="inlineStr">
         <is>
-          <t>Fst X Dock Route Grp Code</t>
+          <t>Fst X Dock Depart Date</t>
         </is>
       </c>
     </row>
@@ -32008,16 +32129,16 @@
         </is>
       </c>
       <c r="B402" s="31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C402" s="32" t="inlineStr">
         <is>
-          <t>FST_X_DOCK_SEQ_NO</t>
+          <t>FST_X_DOCK_ROUTE_GRP_CD</t>
         </is>
       </c>
       <c r="D402" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(2)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E402" s="32" t="inlineStr"/>
@@ -32029,7 +32150,7 @@
       </c>
       <c r="H402" s="32" t="inlineStr">
         <is>
-          <t>Fst X Dock Seq Number</t>
+          <t>Fst X Dock Route Grp Code</t>
         </is>
       </c>
     </row>
@@ -32040,16 +32161,16 @@
         </is>
       </c>
       <c r="B403" s="31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C403" s="32" t="inlineStr">
         <is>
-          <t>FST_X_ROUTE_DT</t>
+          <t>FST_X_DOCK_SEQ_NO</t>
         </is>
       </c>
       <c r="D403" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(2)</t>
         </is>
       </c>
       <c r="E403" s="32" t="inlineStr"/>
@@ -32061,7 +32182,7 @@
       </c>
       <c r="H403" s="32" t="inlineStr">
         <is>
-          <t>Fst X Route Date</t>
+          <t>Fst X Dock Seq Number</t>
         </is>
       </c>
     </row>
@@ -32072,16 +32193,16 @@
         </is>
       </c>
       <c r="B404" s="31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C404" s="32" t="inlineStr">
         <is>
-          <t>FTP_FLAG</t>
+          <t>FST_X_ROUTE_DT</t>
         </is>
       </c>
       <c r="D404" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(3)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E404" s="32" t="inlineStr"/>
@@ -32093,7 +32214,7 @@
       </c>
       <c r="H404" s="32" t="inlineStr">
         <is>
-          <t>FTP Flag</t>
+          <t>Fst X Route Date</t>
         </is>
       </c>
     </row>
@@ -32104,11 +32225,11 @@
         </is>
       </c>
       <c r="B405" s="31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C405" s="32" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>FTP_FLAG</t>
         </is>
       </c>
       <c r="D405" s="32" t="inlineStr">
@@ -32120,12 +32241,12 @@
       <c r="F405" s="32" t="inlineStr"/>
       <c r="G405" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H405" s="32" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>FTP Flag</t>
         </is>
       </c>
     </row>
@@ -32136,28 +32257,28 @@
         </is>
       </c>
       <c r="B406" s="31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C406" s="32" t="inlineStr">
         <is>
-          <t>REMARK</t>
+          <t>STATUS</t>
         </is>
       </c>
       <c r="D406" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(3)</t>
         </is>
       </c>
       <c r="E406" s="32" t="inlineStr"/>
       <c r="F406" s="32" t="inlineStr"/>
       <c r="G406" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H406" s="32" t="inlineStr">
         <is>
-          <t>Remark</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
@@ -32168,16 +32289,16 @@
         </is>
       </c>
       <c r="B407" s="31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C407" s="32" t="inlineStr">
         <is>
-          <t>SEND_ASN_FLAG</t>
+          <t>REMARK</t>
         </is>
       </c>
       <c r="D407" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(3)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E407" s="32" t="inlineStr"/>
@@ -32189,7 +32310,7 @@
       </c>
       <c r="H407" s="32" t="inlineStr">
         <is>
-          <t>Send ASN Flag</t>
+          <t>Remark</t>
         </is>
       </c>
     </row>
@@ -32200,16 +32321,16 @@
         </is>
       </c>
       <c r="B408" s="31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C408" s="32" t="inlineStr">
         <is>
-          <t>SEND_ASN_DATE</t>
+          <t>SEND_ASN_FLAG</t>
         </is>
       </c>
       <c r="D408" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(3)</t>
         </is>
       </c>
       <c r="E408" s="32" t="inlineStr"/>
@@ -32221,7 +32342,7 @@
       </c>
       <c r="H408" s="32" t="inlineStr">
         <is>
-          <t>Send ASN Date</t>
+          <t>Send ASN Flag</t>
         </is>
       </c>
     </row>
@@ -32232,16 +32353,16 @@
         </is>
       </c>
       <c r="B409" s="31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C409" s="32" t="inlineStr">
         <is>
-          <t>SEND_GR_ADM_FLAG</t>
+          <t>SEND_ASN_DATE</t>
         </is>
       </c>
       <c r="D409" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(3)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E409" s="32" t="inlineStr"/>
@@ -32253,7 +32374,7 @@
       </c>
       <c r="H409" s="32" t="inlineStr">
         <is>
-          <t>Send GR Adm Flag</t>
+          <t>Send ASN Date</t>
         </is>
       </c>
     </row>
@@ -32264,16 +32385,16 @@
         </is>
       </c>
       <c r="B410" s="31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C410" s="32" t="inlineStr">
         <is>
-          <t>SEND_GR_ADM_DATE</t>
+          <t>SEND_GR_ADM_FLAG</t>
         </is>
       </c>
       <c r="D410" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(3)</t>
         </is>
       </c>
       <c r="E410" s="32" t="inlineStr"/>
@@ -32285,7 +32406,7 @@
       </c>
       <c r="H410" s="32" t="inlineStr">
         <is>
-          <t>Send GR Adm Date</t>
+          <t>Send GR Adm Flag</t>
         </is>
       </c>
     </row>
@@ -32296,16 +32417,16 @@
         </is>
       </c>
       <c r="B411" s="31" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C411" s="32" t="inlineStr">
         <is>
-          <t>MANIFEST_LAST_SEQ</t>
+          <t>SEND_GR_ADM_DATE</t>
         </is>
       </c>
       <c r="D411" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(2)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E411" s="32" t="inlineStr"/>
@@ -32317,7 +32438,7 @@
       </c>
       <c r="H411" s="32" t="inlineStr">
         <is>
-          <t>Manifest Last Sequence</t>
+          <t>Send GR Adm Date</t>
         </is>
       </c>
     </row>
@@ -32328,28 +32449,28 @@
         </is>
       </c>
       <c r="B412" s="31" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C412" s="32" t="inlineStr">
         <is>
-          <t>CREATED_BY</t>
+          <t>MANIFEST_LAST_SEQ</t>
         </is>
       </c>
       <c r="D412" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(2)</t>
         </is>
       </c>
       <c r="E412" s="32" t="inlineStr"/>
       <c r="F412" s="32" t="inlineStr"/>
       <c r="G412" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H412" s="32" t="inlineStr">
         <is>
-          <t>Created By</t>
+          <t>Manifest Last Sequence</t>
         </is>
       </c>
     </row>
@@ -32360,16 +32481,16 @@
         </is>
       </c>
       <c r="B413" s="31" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C413" s="32" t="inlineStr">
         <is>
-          <t>CREATED_DT</t>
+          <t>CREATED_BY</t>
         </is>
       </c>
       <c r="D413" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E413" s="32" t="inlineStr"/>
@@ -32381,7 +32502,7 @@
       </c>
       <c r="H413" s="32" t="inlineStr">
         <is>
-          <t>Created Date</t>
+          <t>Created By</t>
         </is>
       </c>
     </row>
@@ -32392,28 +32513,28 @@
         </is>
       </c>
       <c r="B414" s="31" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C414" s="32" t="inlineStr">
         <is>
-          <t>CHANGED_BY</t>
+          <t>CREATED_DT</t>
         </is>
       </c>
       <c r="D414" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E414" s="32" t="inlineStr"/>
       <c r="F414" s="32" t="inlineStr"/>
       <c r="G414" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H414" s="32" t="inlineStr">
         <is>
-          <t>Changed By</t>
+          <t>Created Date</t>
         </is>
       </c>
     </row>
@@ -32424,16 +32545,16 @@
         </is>
       </c>
       <c r="B415" s="31" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C415" s="32" t="inlineStr">
         <is>
-          <t>CHANGED_DT</t>
+          <t>CHANGED_BY</t>
         </is>
       </c>
       <c r="D415" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E415" s="32" t="inlineStr"/>
@@ -32445,7 +32566,7 @@
       </c>
       <c r="H415" s="32" t="inlineStr">
         <is>
-          <t>Changed Date</t>
+          <t>Changed By</t>
         </is>
       </c>
     </row>
@@ -32456,16 +32577,16 @@
         </is>
       </c>
       <c r="B416" s="31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C416" s="32" t="inlineStr">
         <is>
-          <t>CASE_DELIVERED</t>
+          <t>CHANGED_DT</t>
         </is>
       </c>
       <c r="D416" s="32" t="inlineStr">
         <is>
-          <t>NUMERIC</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E416" s="32" t="inlineStr"/>
@@ -32477,7 +32598,7 @@
       </c>
       <c r="H416" s="32" t="inlineStr">
         <is>
-          <t>Case Delivered</t>
+          <t>Changed Date</t>
         </is>
       </c>
     </row>
@@ -32488,11 +32609,11 @@
         </is>
       </c>
       <c r="B417" s="31" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C417" s="32" t="inlineStr">
         <is>
-          <t>ITEM_DELIVERED</t>
+          <t>CASE_DELIVERED</t>
         </is>
       </c>
       <c r="D417" s="32" t="inlineStr">
@@ -32509,7 +32630,7 @@
       </c>
       <c r="H417" s="32" t="inlineStr">
         <is>
-          <t>Item Delivered</t>
+          <t>Case Delivered</t>
         </is>
       </c>
     </row>
@@ -32520,11 +32641,11 @@
         </is>
       </c>
       <c r="B418" s="31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C418" s="32" t="inlineStr">
         <is>
-          <t>QTY_DELIVERED</t>
+          <t>ITEM_DELIVERED</t>
         </is>
       </c>
       <c r="D418" s="32" t="inlineStr">
@@ -32541,7 +32662,7 @@
       </c>
       <c r="H418" s="32" t="inlineStr">
         <is>
-          <t>Qty Delivered</t>
+          <t>Item Delivered</t>
         </is>
       </c>
     </row>
@@ -32552,11 +32673,11 @@
         </is>
       </c>
       <c r="B419" s="31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C419" s="32" t="inlineStr">
         <is>
-          <t>CASE_RECEIVED</t>
+          <t>QTY_DELIVERED</t>
         </is>
       </c>
       <c r="D419" s="32" t="inlineStr">
@@ -32573,7 +32694,7 @@
       </c>
       <c r="H419" s="32" t="inlineStr">
         <is>
-          <t>Case Received</t>
+          <t>Qty Delivered</t>
         </is>
       </c>
     </row>
@@ -32584,11 +32705,11 @@
         </is>
       </c>
       <c r="B420" s="31" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C420" s="32" t="inlineStr">
         <is>
-          <t>ITEM_RECEIVED</t>
+          <t>CASE_RECEIVED</t>
         </is>
       </c>
       <c r="D420" s="32" t="inlineStr">
@@ -32605,7 +32726,7 @@
       </c>
       <c r="H420" s="32" t="inlineStr">
         <is>
-          <t>Item Received</t>
+          <t>Case Received</t>
         </is>
       </c>
     </row>
@@ -32616,11 +32737,11 @@
         </is>
       </c>
       <c r="B421" s="31" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C421" s="32" t="inlineStr">
         <is>
-          <t>QTY_RECEIVED</t>
+          <t>ITEM_RECEIVED</t>
         </is>
       </c>
       <c r="D421" s="32" t="inlineStr">
@@ -32637,7 +32758,7 @@
       </c>
       <c r="H421" s="32" t="inlineStr">
         <is>
-          <t>Qty Received</t>
+          <t>Item Received</t>
         </is>
       </c>
     </row>
@@ -32648,16 +32769,16 @@
         </is>
       </c>
       <c r="B422" s="31" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C422" s="32" t="inlineStr">
         <is>
-          <t>COMPLETE_DATE</t>
+          <t>QTY_RECEIVED</t>
         </is>
       </c>
       <c r="D422" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="E422" s="32" t="inlineStr"/>
@@ -32669,39 +32790,39 @@
       </c>
       <c r="H422" s="32" t="inlineStr">
         <is>
-          <t>Complete Date</t>
+          <t>Qty Received</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="32" t="inlineStr">
         <is>
-          <t>TB_R_DAILY_ORDER_PART</t>
+          <t>TB_R_DAILY_ORDER_MANIFEST</t>
         </is>
       </c>
       <c r="B423" s="31" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="C423" s="32" t="inlineStr">
         <is>
-          <t>PO_NO</t>
+          <t>COMPLETE_DATE</t>
         </is>
       </c>
       <c r="D423" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E423" s="32" t="inlineStr"/>
       <c r="F423" s="32" t="inlineStr"/>
       <c r="G423" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H423" s="32" t="inlineStr">
         <is>
-          <t>PO Number</t>
+          <t>Complete Date</t>
         </is>
       </c>
     </row>
@@ -32712,16 +32833,16 @@
         </is>
       </c>
       <c r="B424" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C424" s="32" t="inlineStr">
         <is>
-          <t>PO_ITEM</t>
+          <t>PO_NO</t>
         </is>
       </c>
       <c r="D424" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(4)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E424" s="32" t="inlineStr"/>
@@ -32733,7 +32854,7 @@
       </c>
       <c r="H424" s="32" t="inlineStr">
         <is>
-          <t>PO Item</t>
+          <t>PO Number</t>
         </is>
       </c>
     </row>
@@ -32744,28 +32865,20 @@
         </is>
       </c>
       <c r="B425" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C425" s="32" t="inlineStr">
         <is>
-          <t>SUB_MANIFEST_NO</t>
+          <t>PO_ITEM</t>
         </is>
       </c>
       <c r="D425" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="E425" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F425" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>VARCHAR(4)</t>
+        </is>
+      </c>
+      <c r="E425" s="32" t="inlineStr"/>
+      <c r="F425" s="32" t="inlineStr"/>
       <c r="G425" s="32" t="inlineStr">
         <is>
           <t>N</t>
@@ -32773,7 +32886,7 @@
       </c>
       <c r="H425" s="32" t="inlineStr">
         <is>
-          <t>Sub Manifest Number</t>
+          <t>PO Item</t>
         </is>
       </c>
     </row>
@@ -32784,20 +32897,28 @@
         </is>
       </c>
       <c r="B426" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C426" s="32" t="inlineStr">
         <is>
-          <t>SUB_MANIFEST_ITEM</t>
+          <t>SUB_MANIFEST_NO</t>
         </is>
       </c>
       <c r="D426" s="32" t="inlineStr">
         <is>
-          <t>NUMERIC</t>
-        </is>
-      </c>
-      <c r="E426" s="32" t="inlineStr"/>
-      <c r="F426" s="32" t="inlineStr"/>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="E426" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F426" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G426" s="32" t="inlineStr">
         <is>
           <t>N</t>
@@ -32805,7 +32926,7 @@
       </c>
       <c r="H426" s="32" t="inlineStr">
         <is>
-          <t>Sub Manifest Item</t>
+          <t>Sub Manifest Number</t>
         </is>
       </c>
     </row>
@@ -32816,28 +32937,20 @@
         </is>
       </c>
       <c r="B427" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C427" s="32" t="inlineStr">
         <is>
-          <t>MANIFEST_NO</t>
+          <t>SUB_MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="D427" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(16)</t>
-        </is>
-      </c>
-      <c r="E427" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F427" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="E427" s="32" t="inlineStr"/>
+      <c r="F427" s="32" t="inlineStr"/>
       <c r="G427" s="32" t="inlineStr">
         <is>
           <t>N</t>
@@ -32845,7 +32958,7 @@
       </c>
       <c r="H427" s="32" t="inlineStr">
         <is>
-          <t>Manifest Number</t>
+          <t>Sub Manifest Item</t>
         </is>
       </c>
     </row>
@@ -32856,16 +32969,16 @@
         </is>
       </c>
       <c r="B428" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C428" s="32" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM</t>
+          <t>MANIFEST_NO</t>
         </is>
       </c>
       <c r="D428" s="32" t="inlineStr">
         <is>
-          <t>NUMERIC</t>
+          <t>VARCHAR(16)</t>
         </is>
       </c>
       <c r="E428" s="32" t="inlineStr">
@@ -32873,7 +32986,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="F428" s="32" t="inlineStr"/>
+      <c r="F428" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="G428" s="32" t="inlineStr">
         <is>
           <t>N</t>
@@ -32881,7 +32998,7 @@
       </c>
       <c r="H428" s="32" t="inlineStr">
         <is>
-          <t>Manifest Item</t>
+          <t>Manifest Number</t>
         </is>
       </c>
     </row>
@@ -32892,16 +33009,16 @@
         </is>
       </c>
       <c r="B429" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C429" s="32" t="inlineStr">
         <is>
-          <t>CASE_NO</t>
+          <t>MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="D429" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(9)</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="E429" s="32" t="inlineStr">
@@ -32917,7 +33034,7 @@
       </c>
       <c r="H429" s="32" t="inlineStr">
         <is>
-          <t>Case Number</t>
+          <t>Manifest Item</t>
         </is>
       </c>
     </row>
@@ -32928,19 +33045,23 @@
         </is>
       </c>
       <c r="B430" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C430" s="32" t="inlineStr">
         <is>
-          <t>ASN_NO</t>
+          <t>CASE_NO</t>
         </is>
       </c>
       <c r="D430" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
-        </is>
-      </c>
-      <c r="E430" s="32" t="inlineStr"/>
+          <t>VARCHAR(9)</t>
+        </is>
+      </c>
+      <c r="E430" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F430" s="32" t="inlineStr"/>
       <c r="G430" s="32" t="inlineStr">
         <is>
@@ -32949,7 +33070,7 @@
       </c>
       <c r="H430" s="32" t="inlineStr">
         <is>
-          <t>ASN Number</t>
+          <t>Case Number</t>
         </is>
       </c>
     </row>
@@ -32960,16 +33081,16 @@
         </is>
       </c>
       <c r="B431" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C431" s="32" t="inlineStr">
         <is>
-          <t>ASN_DATE</t>
+          <t>ASN_NO</t>
         </is>
       </c>
       <c r="D431" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(15)</t>
         </is>
       </c>
       <c r="E431" s="32" t="inlineStr"/>
@@ -32981,7 +33102,7 @@
       </c>
       <c r="H431" s="32" t="inlineStr">
         <is>
-          <t>ASN Date</t>
+          <t>ASN Number</t>
         </is>
       </c>
     </row>
@@ -32992,16 +33113,16 @@
         </is>
       </c>
       <c r="B432" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C432" s="32" t="inlineStr">
         <is>
-          <t>PART_NO</t>
+          <t>ASN_DATE</t>
         </is>
       </c>
       <c r="D432" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E432" s="32" t="inlineStr"/>
@@ -33013,7 +33134,7 @@
       </c>
       <c r="H432" s="32" t="inlineStr">
         <is>
-          <t>Part Number</t>
+          <t>ASN Date</t>
         </is>
       </c>
     </row>
@@ -33024,16 +33145,16 @@
         </is>
       </c>
       <c r="B433" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C433" s="32" t="inlineStr">
         <is>
-          <t>PART_NAME</t>
+          <t>PART_NO</t>
         </is>
       </c>
       <c r="D433" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E433" s="32" t="inlineStr"/>
@@ -33045,7 +33166,7 @@
       </c>
       <c r="H433" s="32" t="inlineStr">
         <is>
-          <t>Part Name</t>
+          <t>Part Number</t>
         </is>
       </c>
     </row>
@@ -33056,16 +33177,16 @@
         </is>
       </c>
       <c r="B434" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C434" s="32" t="inlineStr">
         <is>
-          <t>PO_QTY</t>
+          <t>PART_NAME</t>
         </is>
       </c>
       <c r="D434" s="32" t="inlineStr">
         <is>
-          <t>NUMERIC</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E434" s="32" t="inlineStr"/>
@@ -33077,7 +33198,7 @@
       </c>
       <c r="H434" s="32" t="inlineStr">
         <is>
-          <t>PO Quantity</t>
+          <t>Part Name</t>
         </is>
       </c>
     </row>
@@ -33088,11 +33209,11 @@
         </is>
       </c>
       <c r="B435" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C435" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY_QTY</t>
+          <t>PO_QTY</t>
         </is>
       </c>
       <c r="D435" s="32" t="inlineStr">
@@ -33109,7 +33230,7 @@
       </c>
       <c r="H435" s="32" t="inlineStr">
         <is>
-          <t>Delivery Quantity</t>
+          <t>PO Quantity</t>
         </is>
       </c>
     </row>
@@ -33120,11 +33241,11 @@
         </is>
       </c>
       <c r="B436" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C436" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY_QTY_ACTUAL</t>
+          <t>DELIVERY_QTY</t>
         </is>
       </c>
       <c r="D436" s="32" t="inlineStr">
@@ -33136,12 +33257,12 @@
       <c r="F436" s="32" t="inlineStr"/>
       <c r="G436" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H436" s="32" t="inlineStr">
         <is>
-          <t>Delivery Quantity Actual</t>
+          <t>Delivery Quantity</t>
         </is>
       </c>
     </row>
@@ -33152,11 +33273,11 @@
         </is>
       </c>
       <c r="B437" s="31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C437" s="32" t="inlineStr">
         <is>
-          <t>QTY_PER_CONTAINER</t>
+          <t>DELIVERY_QTY_ACTUAL</t>
         </is>
       </c>
       <c r="D437" s="32" t="inlineStr">
@@ -33168,12 +33289,12 @@
       <c r="F437" s="32" t="inlineStr"/>
       <c r="G437" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H437" s="32" t="inlineStr">
         <is>
-          <t>Quantity Per Container</t>
+          <t>Delivery Quantity Actual</t>
         </is>
       </c>
     </row>
@@ -33184,11 +33305,11 @@
         </is>
       </c>
       <c r="B438" s="31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C438" s="32" t="inlineStr">
         <is>
-          <t>ORDER_PLAN_QTY_LOT</t>
+          <t>QTY_PER_CONTAINER</t>
         </is>
       </c>
       <c r="D438" s="32" t="inlineStr">
@@ -33205,7 +33326,7 @@
       </c>
       <c r="H438" s="32" t="inlineStr">
         <is>
-          <t>Order Plan Quantity Lot</t>
+          <t>Quantity Per Container</t>
         </is>
       </c>
     </row>
@@ -33216,28 +33337,28 @@
         </is>
       </c>
       <c r="B439" s="31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C439" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY_DT_ORI</t>
+          <t>ORDER_PLAN_QTY_LOT</t>
         </is>
       </c>
       <c r="D439" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>NUMERIC</t>
         </is>
       </c>
       <c r="E439" s="32" t="inlineStr"/>
       <c r="F439" s="32" t="inlineStr"/>
       <c r="G439" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H439" s="32" t="inlineStr">
         <is>
-          <t>Delivery Date Original</t>
+          <t>Order Plan Quantity Lot</t>
         </is>
       </c>
     </row>
@@ -33248,11 +33369,11 @@
         </is>
       </c>
       <c r="B440" s="31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C440" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY_DT_ADJUST</t>
+          <t>DELIVERY_DT_ORI</t>
         </is>
       </c>
       <c r="D440" s="32" t="inlineStr">
@@ -33269,7 +33390,7 @@
       </c>
       <c r="H440" s="32" t="inlineStr">
         <is>
-          <t>Delivery Date Adjust</t>
+          <t>Delivery Date Original</t>
         </is>
       </c>
     </row>
@@ -33280,11 +33401,11 @@
         </is>
       </c>
       <c r="B441" s="31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C441" s="32" t="inlineStr">
         <is>
-          <t>DELIVERY_DT_ACTUAL</t>
+          <t>DELIVERY_DT_ADJUST</t>
         </is>
       </c>
       <c r="D441" s="32" t="inlineStr">
@@ -33301,7 +33422,7 @@
       </c>
       <c r="H441" s="32" t="inlineStr">
         <is>
-          <t>Delivery Date Actual</t>
+          <t>Delivery Date Adjust</t>
         </is>
       </c>
     </row>
@@ -33312,16 +33433,16 @@
         </is>
       </c>
       <c r="B442" s="31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C442" s="32" t="inlineStr">
         <is>
-          <t>KANBAN_NO</t>
+          <t>DELIVERY_DT_ACTUAL</t>
         </is>
       </c>
       <c r="D442" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(4)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E442" s="32" t="inlineStr"/>
@@ -33333,7 +33454,7 @@
       </c>
       <c r="H442" s="32" t="inlineStr">
         <is>
-          <t>Kanban Number</t>
+          <t>Delivery Date Actual</t>
         </is>
       </c>
     </row>
@@ -33344,16 +33465,16 @@
         </is>
       </c>
       <c r="B443" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C443" s="32" t="inlineStr">
         <is>
-          <t>PART_BARCODE</t>
+          <t>KANBAN_NO</t>
         </is>
       </c>
       <c r="D443" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(25)</t>
+          <t>VARCHAR(4)</t>
         </is>
       </c>
       <c r="E443" s="32" t="inlineStr"/>
@@ -33365,7 +33486,7 @@
       </c>
       <c r="H443" s="32" t="inlineStr">
         <is>
-          <t>Part Barcode</t>
+          <t>Kanban Number</t>
         </is>
       </c>
     </row>
@@ -33376,11 +33497,11 @@
         </is>
       </c>
       <c r="B444" s="31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C444" s="32" t="inlineStr">
         <is>
-          <t>RECEIVE_PLANT_NAME</t>
+          <t>PART_BARCODE</t>
         </is>
       </c>
       <c r="D444" s="32" t="inlineStr">
@@ -33397,7 +33518,7 @@
       </c>
       <c r="H444" s="32" t="inlineStr">
         <is>
-          <t>Receive Plant Name</t>
+          <t>Part Barcode</t>
         </is>
       </c>
     </row>
@@ -33408,16 +33529,16 @@
         </is>
       </c>
       <c r="B445" s="31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C445" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_INFO1</t>
+          <t>RECEIVE_PLANT_NAME</t>
         </is>
       </c>
       <c r="D445" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
+          <t>VARCHAR(25)</t>
         </is>
       </c>
       <c r="E445" s="32" t="inlineStr"/>
@@ -33429,7 +33550,7 @@
       </c>
       <c r="H445" s="32" t="inlineStr">
         <is>
-          <t>Supplier Info 1</t>
+          <t>Receive Plant Name</t>
         </is>
       </c>
     </row>
@@ -33440,11 +33561,11 @@
         </is>
       </c>
       <c r="B446" s="31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C446" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_INFO2</t>
+          <t>SUPPLIER_INFO1</t>
         </is>
       </c>
       <c r="D446" s="32" t="inlineStr">
@@ -33456,12 +33577,12 @@
       <c r="F446" s="32" t="inlineStr"/>
       <c r="G446" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H446" s="32" t="inlineStr">
         <is>
-          <t>Supplier Info 2</t>
+          <t>Supplier Info 1</t>
         </is>
       </c>
     </row>
@@ -33472,11 +33593,11 @@
         </is>
       </c>
       <c r="B447" s="31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C447" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_INFO3</t>
+          <t>SUPPLIER_INFO2</t>
         </is>
       </c>
       <c r="D447" s="32" t="inlineStr">
@@ -33488,12 +33609,12 @@
       <c r="F447" s="32" t="inlineStr"/>
       <c r="G447" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H447" s="32" t="inlineStr">
         <is>
-          <t>Supplier Info 3</t>
+          <t>Supplier Info 2</t>
         </is>
       </c>
     </row>
@@ -33504,16 +33625,16 @@
         </is>
       </c>
       <c r="B448" s="31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C448" s="32" t="inlineStr">
         <is>
-          <t>IMPORTIR_INFO</t>
+          <t>SUPPLIER_INFO3</t>
         </is>
       </c>
       <c r="D448" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>VARCHAR(15)</t>
         </is>
       </c>
       <c r="E448" s="32" t="inlineStr"/>
@@ -33525,7 +33646,7 @@
       </c>
       <c r="H448" s="32" t="inlineStr">
         <is>
-          <t>Importir Info</t>
+          <t>Supplier Info 3</t>
         </is>
       </c>
     </row>
@@ -33536,11 +33657,11 @@
         </is>
       </c>
       <c r="B449" s="31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C449" s="32" t="inlineStr">
         <is>
-          <t>IMPORTIR_INFO2</t>
+          <t>IMPORTIR_INFO</t>
         </is>
       </c>
       <c r="D449" s="32" t="inlineStr">
@@ -33557,7 +33678,7 @@
       </c>
       <c r="H449" s="32" t="inlineStr">
         <is>
-          <t>Importir Info 2</t>
+          <t>Importir Info</t>
         </is>
       </c>
     </row>
@@ -33568,11 +33689,11 @@
         </is>
       </c>
       <c r="B450" s="31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C450" s="32" t="inlineStr">
         <is>
-          <t>IMPORTIR_INFO3</t>
+          <t>IMPORTIR_INFO2</t>
         </is>
       </c>
       <c r="D450" s="32" t="inlineStr">
@@ -33589,7 +33710,7 @@
       </c>
       <c r="H450" s="32" t="inlineStr">
         <is>
-          <t>Importir Info 3</t>
+          <t>Importir Info 2</t>
         </is>
       </c>
     </row>
@@ -33600,11 +33721,11 @@
         </is>
       </c>
       <c r="B451" s="31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C451" s="32" t="inlineStr">
         <is>
-          <t>IMPORTIR_INFO4</t>
+          <t>IMPORTIR_INFO3</t>
         </is>
       </c>
       <c r="D451" s="32" t="inlineStr">
@@ -33621,7 +33742,7 @@
       </c>
       <c r="H451" s="32" t="inlineStr">
         <is>
-          <t>Importir Info 4</t>
+          <t>Importir Info 3</t>
         </is>
       </c>
     </row>
@@ -33632,28 +33753,28 @@
         </is>
       </c>
       <c r="B452" s="31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C452" s="32" t="inlineStr">
         <is>
-          <t>MOD_DST_CD</t>
+          <t>IMPORTIR_INFO4</t>
         </is>
       </c>
       <c r="D452" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(4)</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E452" s="32" t="inlineStr"/>
       <c r="F452" s="32" t="inlineStr"/>
       <c r="G452" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H452" s="32" t="inlineStr">
         <is>
-          <t>Mod Dst Code</t>
+          <t>Importir Info 4</t>
         </is>
       </c>
     </row>
@@ -33664,28 +33785,28 @@
         </is>
       </c>
       <c r="B453" s="31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C453" s="32" t="inlineStr">
         <is>
-          <t>PLN_PCK_DT</t>
+          <t>MOD_DST_CD</t>
         </is>
       </c>
       <c r="D453" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(4)</t>
         </is>
       </c>
       <c r="E453" s="32" t="inlineStr"/>
       <c r="F453" s="32" t="inlineStr"/>
       <c r="G453" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H453" s="32" t="inlineStr">
         <is>
-          <t>Pln Pck Code</t>
+          <t>Mod Dst Code</t>
         </is>
       </c>
     </row>
@@ -33696,16 +33817,16 @@
         </is>
       </c>
       <c r="B454" s="31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C454" s="32" t="inlineStr">
         <is>
-          <t>PART_ADDRESS</t>
+          <t>PLN_PCK_DT</t>
         </is>
       </c>
       <c r="D454" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(15)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E454" s="32" t="inlineStr"/>
@@ -33717,7 +33838,7 @@
       </c>
       <c r="H454" s="32" t="inlineStr">
         <is>
-          <t>Part Address</t>
+          <t>Pln Pck Code</t>
         </is>
       </c>
     </row>
@@ -33728,28 +33849,28 @@
         </is>
       </c>
       <c r="B455" s="31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C455" s="32" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>PART_ADDRESS</t>
         </is>
       </c>
       <c r="D455" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(3)</t>
+          <t>VARCHAR(15)</t>
         </is>
       </c>
       <c r="E455" s="32" t="inlineStr"/>
       <c r="F455" s="32" t="inlineStr"/>
       <c r="G455" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H455" s="32" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Part Address</t>
         </is>
       </c>
     </row>
@@ -33760,16 +33881,16 @@
         </is>
       </c>
       <c r="B456" s="31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C456" s="32" t="inlineStr">
         <is>
-          <t>CREATED_BY</t>
+          <t>STATUS</t>
         </is>
       </c>
       <c r="D456" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(3)</t>
         </is>
       </c>
       <c r="E456" s="32" t="inlineStr"/>
@@ -33781,7 +33902,7 @@
       </c>
       <c r="H456" s="32" t="inlineStr">
         <is>
-          <t>Created By</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
@@ -33792,16 +33913,16 @@
         </is>
       </c>
       <c r="B457" s="31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C457" s="32" t="inlineStr">
         <is>
-          <t>CREATED_DT</t>
+          <t>CREATED_BY</t>
         </is>
       </c>
       <c r="D457" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E457" s="32" t="inlineStr"/>
@@ -33813,7 +33934,7 @@
       </c>
       <c r="H457" s="32" t="inlineStr">
         <is>
-          <t>Created Date</t>
+          <t>Created By</t>
         </is>
       </c>
     </row>
@@ -33824,28 +33945,28 @@
         </is>
       </c>
       <c r="B458" s="31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C458" s="32" t="inlineStr">
         <is>
-          <t>CHANGED_BY</t>
+          <t>CREATED_DT</t>
         </is>
       </c>
       <c r="D458" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E458" s="32" t="inlineStr"/>
       <c r="F458" s="32" t="inlineStr"/>
       <c r="G458" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H458" s="32" t="inlineStr">
         <is>
-          <t>Changed By</t>
+          <t>Created Date</t>
         </is>
       </c>
     </row>
@@ -33856,16 +33977,16 @@
         </is>
       </c>
       <c r="B459" s="31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C459" s="32" t="inlineStr">
         <is>
-          <t>CHANGED_DT</t>
+          <t>CHANGED_BY</t>
         </is>
       </c>
       <c r="D459" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E459" s="32" t="inlineStr"/>
@@ -33877,43 +33998,39 @@
       </c>
       <c r="H459" s="32" t="inlineStr">
         <is>
-          <t>Changed Date</t>
+          <t>Changed By</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="32" t="inlineStr">
         <is>
-          <t>TB_R_CASE_LABEL_LAST_SEQ</t>
+          <t>TB_R_DAILY_ORDER_PART</t>
         </is>
       </c>
       <c r="B460" s="31" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C460" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_CD</t>
+          <t>CHANGED_DT</t>
         </is>
       </c>
       <c r="D460" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(5)</t>
-        </is>
-      </c>
-      <c r="E460" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E460" s="32" t="inlineStr"/>
       <c r="F460" s="32" t="inlineStr"/>
       <c r="G460" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H460" s="32" t="inlineStr">
         <is>
-          <t>Supplier Code</t>
+          <t>Changed Date</t>
         </is>
       </c>
     </row>
@@ -33924,16 +34041,16 @@
         </is>
       </c>
       <c r="B461" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C461" s="32" t="inlineStr">
         <is>
-          <t>SUPPLIER_PLANT_CD</t>
+          <t>SUPPLIER_CD</t>
         </is>
       </c>
       <c r="D461" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(1)</t>
+          <t>VARCHAR(5)</t>
         </is>
       </c>
       <c r="E461" s="32" t="inlineStr">
@@ -33949,7 +34066,7 @@
       </c>
       <c r="H461" s="32" t="inlineStr">
         <is>
-          <t>Supplier Plant Code</t>
+          <t>Supplier Code</t>
         </is>
       </c>
     </row>
@@ -33960,28 +34077,32 @@
         </is>
       </c>
       <c r="B462" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C462" s="32" t="inlineStr">
         <is>
-          <t>CASE_LABEL_LAST_SEQ</t>
+          <t>SUPPLIER_PLANT_CD</t>
         </is>
       </c>
       <c r="D462" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(3)</t>
-        </is>
-      </c>
-      <c r="E462" s="32" t="inlineStr"/>
+          <t>VARCHAR(1)</t>
+        </is>
+      </c>
+      <c r="E462" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F462" s="32" t="inlineStr"/>
       <c r="G462" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H462" s="32" t="inlineStr">
         <is>
-          <t>Case Label Last Seq No</t>
+          <t>Supplier Plant Code</t>
         </is>
       </c>
     </row>
@@ -33992,11 +34113,11 @@
         </is>
       </c>
       <c r="B463" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C463" s="32" t="inlineStr">
         <is>
-          <t>ASN_LAST_SEQ</t>
+          <t>CASE_LABEL_LAST_SEQ</t>
         </is>
       </c>
       <c r="D463" s="32" t="inlineStr">
@@ -34013,7 +34134,7 @@
       </c>
       <c r="H463" s="32" t="inlineStr">
         <is>
-          <t>ASN Last Seq No</t>
+          <t>Case Label Last Seq No</t>
         </is>
       </c>
     </row>
@@ -34024,28 +34145,28 @@
         </is>
       </c>
       <c r="B464" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C464" s="32" t="inlineStr">
         <is>
-          <t>CREATED_BY</t>
+          <t>ASN_LAST_SEQ</t>
         </is>
       </c>
       <c r="D464" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(3)</t>
         </is>
       </c>
       <c r="E464" s="32" t="inlineStr"/>
       <c r="F464" s="32" t="inlineStr"/>
       <c r="G464" s="32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H464" s="32" t="inlineStr">
         <is>
-          <t>Created By</t>
+          <t>ASN Last Seq No</t>
         </is>
       </c>
     </row>
@@ -34056,16 +34177,16 @@
         </is>
       </c>
       <c r="B465" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C465" s="32" t="inlineStr">
         <is>
-          <t>CREATED_DT</t>
+          <t>CREATED_BY</t>
         </is>
       </c>
       <c r="D465" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E465" s="32" t="inlineStr"/>
@@ -34077,7 +34198,7 @@
       </c>
       <c r="H465" s="32" t="inlineStr">
         <is>
-          <t>Created Date</t>
+          <t>Created By</t>
         </is>
       </c>
     </row>
@@ -34088,28 +34209,28 @@
         </is>
       </c>
       <c r="B466" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C466" s="32" t="inlineStr">
         <is>
-          <t>CHANGED_BY</t>
+          <t>CREATED_DT</t>
         </is>
       </c>
       <c r="D466" s="32" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DATETIME</t>
         </is>
       </c>
       <c r="E466" s="32" t="inlineStr"/>
       <c r="F466" s="32" t="inlineStr"/>
       <c r="G466" s="32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H466" s="32" t="inlineStr">
         <is>
-          <t>Changed By</t>
+          <t>Created Date</t>
         </is>
       </c>
     </row>
@@ -34120,16 +34241,16 @@
         </is>
       </c>
       <c r="B467" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C467" s="32" t="inlineStr">
         <is>
-          <t>CHANGED_DT</t>
+          <t>CHANGED_BY</t>
         </is>
       </c>
       <c r="D467" s="32" t="inlineStr">
         <is>
-          <t>DATETIME</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E467" s="32" t="inlineStr"/>
@@ -34141,12 +34262,44 @@
       </c>
       <c r="H467" s="32" t="inlineStr">
         <is>
+          <t>Changed By</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="32" t="inlineStr">
+        <is>
+          <t>TB_R_CASE_LABEL_LAST_SEQ</t>
+        </is>
+      </c>
+      <c r="B468" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C468" s="32" t="inlineStr">
+        <is>
+          <t>CHANGED_DT</t>
+        </is>
+      </c>
+      <c r="D468" s="32" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E468" s="32" t="inlineStr"/>
+      <c r="F468" s="32" t="inlineStr"/>
+      <c r="G468" s="32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H468" s="32" t="inlineStr">
+        <is>
           <t>Changed Date</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H467"/>
+  <autoFilter ref="A3:H468"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -36997,7 +37150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:P94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -37014,7 +37167,8 @@
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37129,6 +37283,7 @@
       <c r="M9" s="46" t="n"/>
       <c r="N9" s="46" t="n"/>
       <c r="O9" s="46" t="n"/>
+      <c r="P9" s="46" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -37564,6 +37719,7 @@
       <c r="M18" s="46" t="n"/>
       <c r="N18" s="46" t="n"/>
       <c r="O18" s="46" t="n"/>
+      <c r="P18" s="46" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
@@ -37969,6 +38125,7 @@
       <c r="M31" s="46" t="n"/>
       <c r="N31" s="46" t="n"/>
       <c r="O31" s="46" t="n"/>
+      <c r="P31" s="46" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="35" t="inlineStr">
@@ -38040,20 +38197,25 @@
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
+          <t>SEQ_QTY</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
           <t>CUT_FLAG</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr">
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>GROUP_SEQ</t>
         </is>
       </c>
-      <c r="N33" s="9" t="inlineStr">
+      <c r="O33" s="9" t="inlineStr">
         <is>
           <t>CROSSDOCK_STATUS</t>
         </is>
       </c>
-      <c r="O33" s="9" t="inlineStr">
+      <c r="P33" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -38105,20 +38267,23 @@
       <c r="K34" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L34" s="65" t="inlineStr">
+      <c r="L34" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M34" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M34" s="63" t="n">
+      <c r="N34" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="49" t="inlineStr">
+      <c r="O34" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O34" s="64" t="inlineStr"/>
+      <c r="P34" s="64" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="62" t="inlineStr">
@@ -38166,20 +38331,23 @@
       <c r="K35" s="63" t="n">
         <v>10</v>
       </c>
-      <c r="L35" s="64" t="inlineStr">
+      <c r="L35" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="M35" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M35" s="63" t="n">
+      <c r="N35" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N35" s="49" t="inlineStr">
+      <c r="O35" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O35" s="64" t="inlineStr"/>
+      <c r="P35" s="64" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="62" t="inlineStr">
@@ -38227,20 +38395,23 @@
       <c r="K36" s="63" t="n">
         <v>12</v>
       </c>
-      <c r="L36" s="65" t="inlineStr">
+      <c r="L36" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M36" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M36" s="63" t="n">
+      <c r="N36" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N36" s="49" t="inlineStr">
+      <c r="O36" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O36" s="64" t="inlineStr"/>
+      <c r="P36" s="64" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="62" t="inlineStr">
@@ -38288,20 +38459,23 @@
       <c r="K37" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="L37" s="64" t="inlineStr">
+      <c r="L37" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M37" s="63" t="n">
+      <c r="N37" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N37" s="49" t="inlineStr">
+      <c r="O37" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O37" s="64" t="inlineStr"/>
+      <c r="P37" s="64" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="62" t="inlineStr">
@@ -38349,20 +38523,23 @@
       <c r="K38" s="63" t="n">
         <v>18</v>
       </c>
-      <c r="L38" s="65" t="inlineStr">
+      <c r="L38" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M38" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M38" s="63" t="n">
+      <c r="N38" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N38" s="49" t="inlineStr">
+      <c r="O38" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O38" s="64" t="inlineStr"/>
+      <c r="P38" s="64" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="62" t="inlineStr">
@@ -38410,20 +38587,23 @@
       <c r="K39" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L39" s="65" t="inlineStr">
+      <c r="L39" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M39" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M39" s="63" t="n">
+      <c r="N39" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="N39" s="49" t="inlineStr">
+      <c r="O39" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O39" s="64" t="inlineStr"/>
+      <c r="P39" s="64" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="62" t="inlineStr">
@@ -38471,20 +38651,23 @@
       <c r="K40" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L40" s="65" t="inlineStr">
+      <c r="L40" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M40" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M40" s="63" t="n">
+      <c r="N40" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="49" t="inlineStr">
+      <c r="O40" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O40" s="64" t="inlineStr"/>
+      <c r="P40" s="64" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="45" t="inlineStr">
@@ -38506,6 +38689,7 @@
       <c r="M42" s="46" t="n"/>
       <c r="N42" s="46" t="n"/>
       <c r="O42" s="46" t="n"/>
+      <c r="P42" s="46" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="35" t="inlineStr">
@@ -39585,6 +39769,7 @@
       <c r="M67" s="46" t="n"/>
       <c r="N67" s="46" t="n"/>
       <c r="O67" s="46" t="n"/>
+      <c r="P67" s="46" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="35" t="inlineStr">
@@ -40868,7 +41053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -40885,7 +41070,8 @@
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41000,6 +41186,7 @@
       <c r="M9" s="46" t="n"/>
       <c r="N9" s="46" t="n"/>
       <c r="O9" s="46" t="n"/>
+      <c r="P9" s="46" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -41147,6 +41334,7 @@
       <c r="M15" s="46" t="n"/>
       <c r="N15" s="46" t="n"/>
       <c r="O15" s="46" t="n"/>
+      <c r="P15" s="46" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
@@ -41218,20 +41406,25 @@
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
+          <t>SEQ_QTY</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
           <t>CUT_FLAG</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="N17" s="9" t="inlineStr">
         <is>
           <t>GROUP_SEQ</t>
         </is>
       </c>
-      <c r="N17" s="9" t="inlineStr">
+      <c r="O17" s="9" t="inlineStr">
         <is>
           <t>CROSSDOCK_STATUS</t>
         </is>
       </c>
-      <c r="O17" s="9" t="inlineStr">
+      <c r="P17" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -41283,20 +41476,23 @@
       <c r="K18" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L18" s="65" t="inlineStr">
+      <c r="L18" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M18" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M18" s="63" t="n">
+      <c r="N18" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N18" s="49" t="inlineStr">
+      <c r="O18" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O18" s="64" t="inlineStr"/>
+      <c r="P18" s="64" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="62" t="inlineStr">
@@ -41344,20 +41540,23 @@
       <c r="K19" s="63" t="n">
         <v>10</v>
       </c>
-      <c r="L19" s="64" t="inlineStr">
+      <c r="L19" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M19" s="63" t="n">
+      <c r="N19" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N19" s="49" t="inlineStr">
+      <c r="O19" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O19" s="64" t="inlineStr"/>
+      <c r="P19" s="64" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="62" t="inlineStr">
@@ -41405,20 +41604,23 @@
       <c r="K20" s="63" t="n">
         <v>12</v>
       </c>
-      <c r="L20" s="65" t="inlineStr">
+      <c r="L20" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M20" s="63" t="n">
+      <c r="N20" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N20" s="49" t="inlineStr">
+      <c r="O20" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O20" s="64" t="inlineStr"/>
+      <c r="P20" s="64" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="62" t="inlineStr">
@@ -41466,20 +41668,23 @@
       <c r="K21" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="L21" s="64" t="inlineStr">
+      <c r="L21" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M21" s="63" t="n">
+      <c r="N21" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N21" s="49" t="inlineStr">
+      <c r="O21" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O21" s="64" t="inlineStr"/>
+      <c r="P21" s="64" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="62" t="inlineStr">
@@ -41527,20 +41732,23 @@
       <c r="K22" s="63" t="n">
         <v>18</v>
       </c>
-      <c r="L22" s="65" t="inlineStr">
+      <c r="L22" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M22" s="63" t="n">
+      <c r="N22" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N22" s="49" t="inlineStr">
+      <c r="O22" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O22" s="64" t="inlineStr"/>
+      <c r="P22" s="64" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="62" t="inlineStr">
@@ -41584,20 +41792,23 @@
       <c r="K23" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L23" s="65" t="inlineStr">
+      <c r="L23" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M23" s="63" t="n">
+      <c r="N23" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="N23" s="66" t="inlineStr">
+      <c r="O23" s="66" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O23" s="64" t="inlineStr">
+      <c r="P23" s="64" t="inlineStr">
         <is>
           <t>No PO left: block 4 Not Ready, blocks 1-3 Ready</t>
         </is>
@@ -41623,6 +41834,7 @@
       <c r="M25" s="46" t="n"/>
       <c r="N25" s="46" t="n"/>
       <c r="O25" s="46" t="n"/>
+      <c r="P25" s="46" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="35" t="inlineStr">
@@ -41854,6 +42066,7 @@
       <c r="M34" s="46" t="n"/>
       <c r="N34" s="46" t="n"/>
       <c r="O34" s="46" t="n"/>
+      <c r="P34" s="46" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="35" t="inlineStr">
@@ -41925,20 +42138,25 @@
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
+          <t>SEQ_QTY</t>
+        </is>
+      </c>
+      <c r="M36" s="9" t="inlineStr">
+        <is>
           <t>CUT_FLAG</t>
         </is>
       </c>
-      <c r="M36" s="9" t="inlineStr">
+      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>GROUP_SEQ</t>
         </is>
       </c>
-      <c r="N36" s="9" t="inlineStr">
+      <c r="O36" s="9" t="inlineStr">
         <is>
           <t>CROSSDOCK_STATUS</t>
         </is>
       </c>
-      <c r="O36" s="9" t="inlineStr">
+      <c r="P36" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -41990,20 +42208,23 @@
       <c r="K37" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="65" t="inlineStr">
+      <c r="L37" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M37" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M37" s="63" t="n">
+      <c r="N37" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="49" t="inlineStr">
+      <c r="O37" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O37" s="64" t="inlineStr"/>
+      <c r="P37" s="64" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="62" t="inlineStr">
@@ -42051,20 +42272,23 @@
       <c r="K38" s="63" t="n">
         <v>10</v>
       </c>
-      <c r="L38" s="64" t="inlineStr">
+      <c r="L38" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="M38" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M38" s="63" t="n">
+      <c r="N38" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N38" s="49" t="inlineStr">
+      <c r="O38" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O38" s="64" t="inlineStr"/>
+      <c r="P38" s="64" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="62" t="inlineStr">
@@ -42112,20 +42336,23 @@
       <c r="K39" s="63" t="n">
         <v>12</v>
       </c>
-      <c r="L39" s="65" t="inlineStr">
+      <c r="L39" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M39" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M39" s="63" t="n">
+      <c r="N39" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N39" s="49" t="inlineStr">
+      <c r="O39" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O39" s="64" t="inlineStr"/>
+      <c r="P39" s="64" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="62" t="inlineStr">
@@ -42173,20 +42400,23 @@
       <c r="K40" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="L40" s="64" t="inlineStr">
+      <c r="L40" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M40" s="63" t="n">
+      <c r="N40" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N40" s="49" t="inlineStr">
+      <c r="O40" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O40" s="64" t="inlineStr"/>
+      <c r="P40" s="64" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="62" t="inlineStr">
@@ -42234,20 +42464,23 @@
       <c r="K41" s="63" t="n">
         <v>18</v>
       </c>
-      <c r="L41" s="65" t="inlineStr">
+      <c r="L41" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M41" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M41" s="63" t="n">
+      <c r="N41" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N41" s="49" t="inlineStr">
+      <c r="O41" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O41" s="64" t="inlineStr"/>
+      <c r="P41" s="64" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="62" t="inlineStr">
@@ -42295,20 +42528,23 @@
       <c r="K42" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L42" s="65" t="inlineStr">
+      <c r="L42" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M42" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M42" s="63" t="n">
+      <c r="N42" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="N42" s="60" t="inlineStr">
+      <c r="O42" s="60" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O42" s="64" t="inlineStr">
+      <c r="P42" s="64" t="inlineStr">
         <is>
           <t>PO T0410001: unit Ready</t>
         </is>
@@ -42326,7 +42562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -42343,7 +42579,8 @@
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42458,6 +42695,7 @@
       <c r="M9" s="46" t="n"/>
       <c r="N9" s="46" t="n"/>
       <c r="O9" s="46" t="n"/>
+      <c r="P9" s="46" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -42831,6 +43069,7 @@
       <c r="M17" s="46" t="n"/>
       <c r="N17" s="46" t="n"/>
       <c r="O17" s="46" t="n"/>
+      <c r="P17" s="46" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
@@ -42902,20 +43141,25 @@
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
+          <t>SEQ_QTY</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
           <t>CUT_FLAG</t>
         </is>
       </c>
-      <c r="M19" s="9" t="inlineStr">
+      <c r="N19" s="9" t="inlineStr">
         <is>
           <t>GROUP_SEQ</t>
         </is>
       </c>
-      <c r="N19" s="9" t="inlineStr">
+      <c r="O19" s="9" t="inlineStr">
         <is>
           <t>CROSSDOCK_STATUS</t>
         </is>
       </c>
-      <c r="O19" s="9" t="inlineStr">
+      <c r="P19" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -42967,20 +43211,23 @@
       <c r="K20" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="L20" s="65" t="inlineStr">
+      <c r="L20" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M20" s="63" t="n">
+      <c r="N20" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="N20" s="49" t="inlineStr">
+      <c r="O20" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O20" s="64" t="inlineStr"/>
+      <c r="P20" s="64" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="62" t="inlineStr">
@@ -43028,20 +43275,23 @@
       <c r="K21" s="63" t="n">
         <v>10</v>
       </c>
-      <c r="L21" s="64" t="inlineStr">
+      <c r="L21" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M21" s="63" t="n">
+      <c r="N21" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N21" s="49" t="inlineStr">
+      <c r="O21" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O21" s="64" t="inlineStr"/>
+      <c r="P21" s="64" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="62" t="inlineStr">
@@ -43089,20 +43339,23 @@
       <c r="K22" s="63" t="n">
         <v>12</v>
       </c>
-      <c r="L22" s="65" t="inlineStr">
+      <c r="L22" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M22" s="63" t="n">
+      <c r="N22" s="63" t="n">
         <v>2</v>
       </c>
-      <c r="N22" s="49" t="inlineStr">
+      <c r="O22" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O22" s="64" t="inlineStr"/>
+      <c r="P22" s="64" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="62" t="inlineStr">
@@ -43150,20 +43403,23 @@
       <c r="K23" s="63" t="n">
         <v>14</v>
       </c>
-      <c r="L23" s="64" t="inlineStr">
+      <c r="L23" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" s="64" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M23" s="63" t="n">
+      <c r="N23" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N23" s="49" t="inlineStr">
+      <c r="O23" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O23" s="64" t="inlineStr"/>
+      <c r="P23" s="64" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="62" t="inlineStr">
@@ -43211,20 +43467,23 @@
       <c r="K24" s="63" t="n">
         <v>18</v>
       </c>
-      <c r="L24" s="65" t="inlineStr">
+      <c r="L24" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M24" s="65" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M24" s="63" t="n">
+      <c r="N24" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="N24" s="49" t="inlineStr">
+      <c r="O24" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O24" s="64" t="inlineStr"/>
+      <c r="P24" s="64" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="45" t="inlineStr">
@@ -43246,6 +43505,7 @@
       <c r="M26" s="46" t="n"/>
       <c r="N26" s="46" t="n"/>
       <c r="O26" s="46" t="n"/>
+      <c r="P26" s="46" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="35" t="inlineStr">
@@ -43381,6 +43641,7 @@
       <c r="M31" s="46" t="n"/>
       <c r="N31" s="46" t="n"/>
       <c r="O31" s="46" t="n"/>
+      <c r="P31" s="46" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="35" t="inlineStr">

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -20,6 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-6" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-7" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-8" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-9" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Column Definition'!$A$3:$H$468</definedName>
@@ -17573,6 +17574,1485 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SIM-9 XD10 case check boxes: cases 1-2 not possible, 1-3 sent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>BPF F2 · Functions: XD09, XD10 (Select case, Create ASN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>• Same unit as SIM-7 (PART-A 14-Oct: V01 VN 10, T01 TH 6, V02 VN 14; 6 pcs/case) but all 5 cases have a PO (p1 24 + p2 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>• XD10 shows one check box per supplier case. The supplier wants cases 1 and 2 only: case 2 = VN 4 + TH 2 ends with VN 10 / TH 2 (CUT_FLAG N), so the warehouse could not close the VN and TH cases. XD10 ticks case 3 too (message no. 10): cases 1-3 = 18 pcs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>• [Create ASN] inserts the slices of cases 1-3; V01 and T01 are complete (PO_MAPPED_FLAG Y), V02 keeps 12 pcs open for a later ASN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>NEW row</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>UPD row</t>
+        </is>
+      </c>
+      <c r="D7" s="38" t="inlineStr">
+        <is>
+          <t>DEL row</t>
+        </is>
+      </c>
+      <c r="E7" s="39" t="inlineStr">
+        <is>
+          <t>READ row</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>TEMP row</t>
+        </is>
+      </c>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>Changed cell</t>
+        </is>
+      </c>
+      <c r="H7" s="42" t="inlineStr">
+        <is>
+          <t>PK column</t>
+        </is>
+      </c>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>Status OK</t>
+        </is>
+      </c>
+      <c r="J7" s="43" t="inlineStr">
+        <is>
+          <t>Status attention</t>
+        </is>
+      </c>
+      <c r="K7" s="44" t="inlineStr">
+        <is>
+          <t>Status NG / cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>1. [Search] → XD09: all cases with PO; CUT_FLAG Y after cases 1, 3, 4, 5</t>
+        </is>
+      </c>
+      <c r="B9" s="46" t="n"/>
+      <c r="C9" s="46" t="n"/>
+      <c r="D9" s="46" t="n"/>
+      <c r="E9" s="46" t="n"/>
+      <c r="F9" s="46" t="n"/>
+      <c r="G9" s="46" t="n"/>
+      <c r="H9" s="46" t="n"/>
+      <c r="I9" s="46" t="n"/>
+      <c r="J9" s="46" t="n"/>
+      <c r="K9" s="46" t="n"/>
+      <c r="L9" s="46" t="n"/>
+      <c r="M9" s="46" t="n"/>
+      <c r="N9" s="46" t="n"/>
+      <c r="O9" s="46" t="n"/>
+      <c r="P9" s="46" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>#TEMP_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>Temporary (session)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>SORT_SEQ</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>OPEN_ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>ASSIGNED_QTY</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>CUM_DEST_QTY</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>SEQ_QTY</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>CUT_FLAG</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>GROUP_SEQ</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>CROSSDOCK_STATUS</t>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="64" t="inlineStr">
+        <is>
+          <t>CUST-A</t>
+        </is>
+      </c>
+      <c r="D12" s="64" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="E12" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F12" s="64" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="G12" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="64" t="inlineStr">
+        <is>
+          <t>T0409011</t>
+        </is>
+      </c>
+      <c r="I12" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N12" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P12" s="64" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="64" t="inlineStr">
+        <is>
+          <t>CUST-A</t>
+        </is>
+      </c>
+      <c r="D13" s="64" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="E13" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F13" s="64" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="G13" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="64" t="inlineStr">
+        <is>
+          <t>T0409011</t>
+        </is>
+      </c>
+      <c r="I13" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N13" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P13" s="64" t="inlineStr">
+        <is>
+          <t>Case 2 = VN 4 + TH 2: CUT N (VN 10, TH 2) → cannot be the last case</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="64" t="inlineStr">
+        <is>
+          <t>CUST-B</t>
+        </is>
+      </c>
+      <c r="D14" s="64" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="E14" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F14" s="64" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="G14" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" s="64" t="inlineStr">
+        <is>
+          <t>T0409011</t>
+        </is>
+      </c>
+      <c r="I14" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N14" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P14" s="64" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="64" t="inlineStr">
+        <is>
+          <t>CUST-B</t>
+        </is>
+      </c>
+      <c r="D15" s="64" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="E15" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F15" s="64" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="G15" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="64" t="inlineStr">
+        <is>
+          <t>T0409011</t>
+        </is>
+      </c>
+      <c r="I15" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N15" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P15" s="64" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="64" t="inlineStr">
+        <is>
+          <t>CUST-C</t>
+        </is>
+      </c>
+      <c r="D16" s="64" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="E16" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F16" s="64" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="G16" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" s="64" t="inlineStr">
+        <is>
+          <t>T0409011</t>
+        </is>
+      </c>
+      <c r="I16" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="L16" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N16" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P16" s="64" t="inlineStr">
+        <is>
+          <t>Case 3: CUT Y (VN 12, TH 6) → ticked together with case 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="64" t="inlineStr">
+        <is>
+          <t>CUST-C</t>
+        </is>
+      </c>
+      <c r="D17" s="64" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="E17" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F17" s="64" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="G17" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" s="64" t="inlineStr">
+        <is>
+          <t>T0409011</t>
+        </is>
+      </c>
+      <c r="I17" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="63" t="n">
+        <v>18</v>
+      </c>
+      <c r="L17" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M17" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N17" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P17" s="64" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B18" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="64" t="inlineStr">
+        <is>
+          <t>CUST-C</t>
+        </is>
+      </c>
+      <c r="D18" s="64" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="E18" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F18" s="64" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="G18" s="63" t="n">
+        <v>14</v>
+      </c>
+      <c r="H18" s="64" t="inlineStr">
+        <is>
+          <t>T0410011</t>
+        </is>
+      </c>
+      <c r="I18" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" s="63" t="n">
+        <v>24</v>
+      </c>
+      <c r="L18" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M18" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N18" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="O18" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P18" s="64" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>2. Supplier ticks cases 1-2 → XD10 ticks case 3 too (MSG10) → [Create ASN] cases 1-3</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="n"/>
+      <c r="C20" s="46" t="n"/>
+      <c r="D20" s="46" t="n"/>
+      <c r="E20" s="46" t="n"/>
+      <c r="F20" s="46" t="n"/>
+      <c r="G20" s="46" t="n"/>
+      <c r="H20" s="46" t="n"/>
+      <c r="I20" s="46" t="n"/>
+      <c r="J20" s="46" t="n"/>
+      <c r="K20" s="46" t="n"/>
+      <c r="L20" s="46" t="n"/>
+      <c r="M20" s="46" t="n"/>
+      <c r="N20" s="46" t="n"/>
+      <c r="O20" s="46" t="n"/>
+      <c r="P20" s="46" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D21" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>LINE_SEQ</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B23" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G23" s="49" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="H23" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I23" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" s="49" t="inlineStr">
+        <is>
+          <t>T0409011</t>
+        </is>
+      </c>
+      <c r="K23" s="49" t="inlineStr">
+        <is>
+          <t>3126035911</t>
+        </is>
+      </c>
+      <c r="L23" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M23" s="49" t="n"/>
+      <c r="N23" s="49" t="n"/>
+      <c r="O23" s="49" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B24" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="F24" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G24" s="49" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="H24" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I24" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" s="49" t="inlineStr">
+        <is>
+          <t>T0409011</t>
+        </is>
+      </c>
+      <c r="K24" s="49" t="inlineStr">
+        <is>
+          <t>3126035911</t>
+        </is>
+      </c>
+      <c r="L24" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M24" s="49" t="n"/>
+      <c r="N24" s="49" t="n"/>
+      <c r="O24" s="49" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B25" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="49" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="F25" s="49" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="G25" s="49" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="H25" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I25" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="49" t="inlineStr">
+        <is>
+          <t>T0409011</t>
+        </is>
+      </c>
+      <c r="K25" s="49" t="inlineStr">
+        <is>
+          <t>3126035911</t>
+        </is>
+      </c>
+      <c r="L25" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M25" s="49" t="n"/>
+      <c r="N25" s="49" t="n"/>
+      <c r="O25" s="49" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B26" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="G26" s="49" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="H26" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I26" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" s="49" t="inlineStr">
+        <is>
+          <t>T0409011</t>
+        </is>
+      </c>
+      <c r="K26" s="49" t="inlineStr">
+        <is>
+          <t>3126035911</t>
+        </is>
+      </c>
+      <c r="L26" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M26" s="49" t="n"/>
+      <c r="N26" s="49" t="n"/>
+      <c r="O26" s="49" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B27" s="53" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G27" s="49" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="H27" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I27" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="49" t="inlineStr">
+        <is>
+          <t>T0409011</t>
+        </is>
+      </c>
+      <c r="K27" s="49" t="inlineStr">
+        <is>
+          <t>3126035911</t>
+        </is>
+      </c>
+      <c r="L27" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M27" s="49" t="n"/>
+      <c r="N27" s="49" t="n"/>
+      <c r="O27" s="49" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+        </is>
+      </c>
+      <c r="D29" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B30" s="42" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="C30" s="42" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="D30" s="42" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>MAPPED_QTY</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>T0409011</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="inlineStr">
+        <is>
+          <t>3126035911</t>
+        </is>
+      </c>
+      <c r="D31" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E31" s="49" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="F31" s="53" t="n">
+        <v>24</v>
+      </c>
+      <c r="G31" s="53" t="n">
+        <v>18</v>
+      </c>
+      <c r="H31" s="49" t="inlineStr">
+        <is>
+          <t>18 of 24 used; 6 left for case 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D33" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B34" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C34" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E34" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F34" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G34" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>CANCEL_STATUS</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B35" s="58" t="inlineStr">
+        <is>
+          <t>CUST-A</t>
+        </is>
+      </c>
+      <c r="C35" s="58" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="D35" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E35" s="58" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F35" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G35" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H35" s="58" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="I35" s="59" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K35" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L35" s="60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M35" s="58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="58" t="inlineStr">
+        <is>
+          <t>Whole line in cases 1-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B36" s="58" t="inlineStr">
+        <is>
+          <t>CUST-B</t>
+        </is>
+      </c>
+      <c r="C36" s="58" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="D36" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E36" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F36" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G36" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H36" s="58" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="I36" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K36" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L36" s="60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M36" s="58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="58" t="inlineStr">
+        <is>
+          <t>Whole line in cases 2-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B37" s="51" t="inlineStr">
+        <is>
+          <t>CUST-C</t>
+        </is>
+      </c>
+      <c r="C37" s="51" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="D37" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E37" s="51" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F37" s="51" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G37" s="51" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H37" s="51" t="inlineStr">
+        <is>
+          <t>PART-A</t>
+        </is>
+      </c>
+      <c r="I37" s="52" t="n">
+        <v>14</v>
+      </c>
+      <c r="J37" s="51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K37" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L37" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M37" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="51" t="inlineStr">
+        <is>
+          <t>2 of 14 sent: stays N, open qty 12 (cases 4-5 at the next Search)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -17895,7 +19375,7 @@
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-4, SIM-5, SIM-6, SIM-7, SIM-8</t>
+          <t>SIM-2, SIM-4, SIM-5, SIM-6, SIM-7, SIM-8, SIM-9</t>
         </is>
       </c>
     </row>
@@ -17955,7 +19435,7 @@
       </c>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-4, SIM-5, SIM-6, SIM-7, SIM-8</t>
+          <t>SIM-2, SIM-4, SIM-5, SIM-6, SIM-7, SIM-8, SIM-9</t>
         </is>
       </c>
     </row>
@@ -17985,7 +19465,7 @@
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-3, SIM-4, SIM-7, SIM-8</t>
+          <t>SIM-2, SIM-3, SIM-4, SIM-7, SIM-8, SIM-9</t>
         </is>
       </c>
     </row>
@@ -18075,7 +19555,7 @@
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-5, SIM-6, SIM-7, SIM-8</t>
+          <t>SIM-2, SIM-5, SIM-6, SIM-7, SIM-8, SIM-9</t>
         </is>
       </c>
     </row>
@@ -34311,7 +35791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -34621,6 +36101,38 @@
       <c r="F12" s="32" t="inlineStr">
         <is>
           <t>PART-B, 6 pcs/case. Scan order = G-System allocation order with Allocation Priority = Customer Order Date: 1) Allocation Priority, 2) Customer Code, 3) Customer Order No, 4) Order Date, 5) Order Time, 6) Destination, 7) Detailed Item No, 8) Serial No. Keys 2-8 are the PK of the H0253 replicate; XD09 reads with ORDER BY Part, Allocation Priority + the PK columns (query in XD09 Appendix). SORT_SEQ = row number per unit. Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. A-0201 (15-Oct) comes after all 14-Oct lines (Allocation Priority) and is the next unit. 15-Oct: PO1 20 pcs → blocks 1-2 Ready, block 3 (case 4) only 2 of 6 pcs with PO → Not Ready. The supplier sends option 1 case only. 16-Oct: PO2 10 pcs. The open qty (24) is cut again from case 1 in the same SORT_SEQ: the cases are the same as before. Unit 15-Oct (A-0201) comes after unit 14-Oct (way B), so it gets no PO yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>SIM-9</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>XD10 case check boxes: cases 1-2 not possible, 1-3 sent</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>BPF F2</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>XD09, XD10 (Select case, Create ASN)</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>#TEMP_INSTRUCTION, TB_R_INSTRUCTION, TB_R_PRA_DAILY_ORDER_MAPPED, TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>Same unit as SIM-7 (PART-A 14-Oct: V01 VN 10, T01 TH 6, V02 VN 14; 6 pcs/case) but all 5 cases have a PO (p1 24 + p2 6). XD10 shows one check box per supplier case. The supplier wants cases 1 and 2 only: case 2 = VN 4 + TH 2 ends with VN 10 / TH 2 (CUT_FLAG N), so the warehouse could not close the VN and TH cases. XD10 ticks case 3 too (message no. 10): cases 1-3 = 18 pcs. [Create ASN] inserts the slices of cases 1-3; V01 and T01 are complete (PO_MAPPED_FLAG Y), V02 keeps 12 pcs open for a later ASN.</t>
         </is>
       </c>
     </row>

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -8022,7 +8022,7 @@
       <c r="L61" s="19" t="inlineStr"/>
       <c r="N61" s="18" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="O61" s="18" t="inlineStr">
@@ -10560,7 +10560,7 @@
     <row r="19">
       <c r="A19" s="45" t="inlineStr">
         <is>
-          <t>2. XD12 27:30: status 2 row of the line (CANCEL_STATUS P)</t>
+          <t>2. XD12 27:30: status 2 row of the line (UPD_STATUS P)</t>
         </is>
       </c>
       <c r="B19" s="46" t="n"/>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
@@ -11951,7 +11951,7 @@
     <row r="14">
       <c r="A14" s="45" t="inlineStr">
         <is>
-          <t>2. XD12 27:30: status 2 (CANCEL_STATUS P)</t>
+          <t>2. XD12 27:30: status 2 (UPD_STATUS P)</t>
         </is>
       </c>
       <c r="B14" s="46" t="n"/>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr">
@@ -15549,7 +15549,7 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr">
@@ -18828,7 +18828,7 @@
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="D12" s="32" t="inlineStr">
         <is>
-          <t>Order control data, pre-order picking info (I/F H02-53, DVJO950) replicated from DB Surrounding by XD08 / XD12. Structure from the G-System I/F layout; physical names follow the existing table. Key (PK) = unique key of the I/F layout. NSP keeps the rows with status 7, 6 and 2 (insert / update); rows with status 6 / 2 are kept for tracking only (retention optional, TBC). CANCEL_STATUS is a new NSP column (proposed).</t>
+          <t>Order control data, pre-order picking info (I/F H02-53, DVJO950) replicated from DB Surrounding by XD08 / XD12. Structure from the G-System I/F layout; physical names follow the existing table. Key (PK) = unique key of the I/F layout. NSP keeps the rows with status 7, 6 and 2 (insert / update); rows with status 6 / 2 are kept for tracking only (retention optional, TBC). UPD_STATUS is a new NSP column (proposed).</t>
         </is>
       </c>
       <c r="E12" s="32" t="inlineStr">
@@ -26193,7 +26193,7 @@
       </c>
       <c r="C176" s="32" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="D176" s="32" t="inlineStr">
@@ -28998,7 +28998,7 @@
       </c>
       <c r="H259" s="32" t="inlineStr">
         <is>
-          <t>Block (ASN option) of the slice: the cases up to and including a valid cut</t>
+          <t>Case Group (block) of the slice: the cases up to and including a valid cut; the cases of a group are sent together</t>
         </is>
       </c>
     </row>
@@ -38872,7 +38872,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -40922,7 +40922,7 @@
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr">
@@ -44284,7 +44284,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>CANCEL_STATUS</t>
+          <t>UPD_STATUS</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr">

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -10395,12 +10395,12 @@
       </c>
       <c r="J12" s="51" t="inlineStr">
         <is>
-          <t>T0409004</t>
+          <t>PO-DMY-09004</t>
         </is>
       </c>
       <c r="K12" s="51" t="inlineStr">
         <is>
-          <t>3126035904</t>
+          <t>MF-DMY-09004</t>
         </is>
       </c>
       <c r="L12" s="51" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="J13" s="51" t="inlineStr">
         <is>
-          <t>T0409004</t>
+          <t>PO-DMY-09004</t>
         </is>
       </c>
       <c r="K13" s="51" t="inlineStr">
         <is>
-          <t>3126035904</t>
+          <t>MF-DMY-09004</t>
         </is>
       </c>
       <c r="L13" s="51" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B17" s="51" t="inlineStr">
         <is>
-          <t>T0409004</t>
+          <t>PO-DMY-09004</t>
         </is>
       </c>
       <c r="C17" s="51" t="inlineStr">
         <is>
-          <t>3126035904</t>
+          <t>MF-DMY-09004</t>
         </is>
       </c>
       <c r="D17" s="51" t="inlineStr">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="J28" s="68" t="inlineStr">
         <is>
-          <t>T0409004</t>
+          <t>PO-DMY-09004</t>
         </is>
       </c>
       <c r="K28" s="68" t="inlineStr">
         <is>
-          <t>3126035904</t>
+          <t>MF-DMY-09004</t>
         </is>
       </c>
       <c r="L28" s="68" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="J29" s="68" t="inlineStr">
         <is>
-          <t>T0409004</t>
+          <t>PO-DMY-09004</t>
         </is>
       </c>
       <c r="K29" s="68" t="inlineStr">
         <is>
-          <t>3126035904</t>
+          <t>MF-DMY-09004</t>
         </is>
       </c>
       <c r="L29" s="68" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="B33" s="58" t="inlineStr">
         <is>
-          <t>T0409004</t>
+          <t>PO-DMY-09004</t>
         </is>
       </c>
       <c r="C33" s="58" t="inlineStr">
         <is>
-          <t>3126035904</t>
+          <t>MF-DMY-09004</t>
         </is>
       </c>
       <c r="D33" s="58" t="inlineStr">
@@ -11923,12 +11923,12 @@
       </c>
       <c r="J12" s="51" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="K12" s="51" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="L12" s="51" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="J22" s="51" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="K22" s="51" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="L22" s="51" t="inlineStr">
@@ -12364,12 +12364,12 @@
       </c>
       <c r="B26" s="51" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="C26" s="51" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="D26" s="51" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="B18" s="51" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="C18" s="51" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="D18" s="51" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="E18" s="51" t="inlineStr">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="H23" s="64" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="I23" s="63" t="n">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="H24" s="64" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="I24" s="63" t="n">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="H25" s="64" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="I25" s="63" t="n">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="H26" s="64" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="I26" s="63" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="H27" s="64" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="I27" s="63" t="n">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="H28" s="64" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="I28" s="63" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="J34" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K34" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L34" s="49" t="inlineStr">
@@ -13987,12 +13987,12 @@
       </c>
       <c r="J35" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K35" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L35" s="49" t="inlineStr">
@@ -14044,12 +14044,12 @@
       </c>
       <c r="J36" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K36" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L36" s="49" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="J37" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K37" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L37" s="49" t="inlineStr">
@@ -14158,12 +14158,12 @@
       </c>
       <c r="J38" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K38" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L38" s="49" t="inlineStr">
@@ -14215,12 +14215,12 @@
       </c>
       <c r="J39" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K39" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L39" s="49" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="B43" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="C43" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="D43" s="49" t="inlineStr">
@@ -14698,7 +14698,7 @@
       </c>
       <c r="B54" s="49" t="inlineStr">
         <is>
-          <t>3126036011</t>
+          <t>MF-DMY-10011</t>
         </is>
       </c>
       <c r="C54" s="49" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="D54" s="49" t="inlineStr">
         <is>
-          <t>T0410011</t>
+          <t>PO-DMY-10011</t>
         </is>
       </c>
       <c r="E54" s="49" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="H59" s="64" t="inlineStr">
         <is>
-          <t>T0410011</t>
+          <t>PO-DMY-10011</t>
         </is>
       </c>
       <c r="I59" s="63" t="n">
@@ -15061,12 +15061,12 @@
       </c>
       <c r="J64" s="49" t="inlineStr">
         <is>
-          <t>T0410011</t>
+          <t>PO-DMY-10011</t>
         </is>
       </c>
       <c r="K64" s="49" t="inlineStr">
         <is>
-          <t>3126036011</t>
+          <t>MF-DMY-10011</t>
         </is>
       </c>
       <c r="L64" s="49" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="B68" s="49" t="inlineStr">
         <is>
-          <t>T0410011</t>
+          <t>PO-DMY-10011</t>
         </is>
       </c>
       <c r="C68" s="49" t="inlineStr">
         <is>
-          <t>3126036011</t>
+          <t>MF-DMY-10011</t>
         </is>
       </c>
       <c r="D68" s="49" t="inlineStr">
@@ -16058,7 +16058,7 @@
       </c>
       <c r="H22" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I22" s="63" t="n">
@@ -16126,7 +16126,7 @@
       </c>
       <c r="H23" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I23" s="63" t="n">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="H24" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I24" s="63" t="n">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="H25" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I25" s="63" t="n">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="H26" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I26" s="63" t="n">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="H27" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I27" s="63" t="n">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="H28" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I28" s="63" t="n">
@@ -16759,12 +16759,12 @@
       </c>
       <c r="J35" s="49" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="K35" s="49" t="inlineStr">
         <is>
-          <t>3126035921</t>
+          <t>MF-DMY-09021</t>
         </is>
       </c>
       <c r="L35" s="49" t="inlineStr">
@@ -16842,12 +16842,12 @@
       </c>
       <c r="B39" s="49" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="C39" s="49" t="inlineStr">
         <is>
-          <t>3126035921</t>
+          <t>MF-DMY-09021</t>
         </is>
       </c>
       <c r="D39" s="49" t="inlineStr">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="H44" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I44" s="63" t="n">
@@ -17086,7 +17086,7 @@
       </c>
       <c r="H45" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I45" s="63" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="H46" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I46" s="63" t="n">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="H47" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I47" s="63" t="n">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="H48" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I48" s="63" t="n">
@@ -17342,7 +17342,7 @@
       </c>
       <c r="H49" s="64" t="inlineStr">
         <is>
-          <t>T0409021</t>
+          <t>PO-DMY-09021</t>
         </is>
       </c>
       <c r="I49" s="63" t="n">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="H50" s="64" t="inlineStr">
         <is>
-          <t>T0410021</t>
+          <t>PO-DMY-10021</t>
         </is>
       </c>
       <c r="I50" s="63" t="n">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="H51" s="64" t="inlineStr">
         <is>
-          <t>T0410021</t>
+          <t>PO-DMY-10021</t>
         </is>
       </c>
       <c r="I51" s="63" t="n">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="H12" s="64" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="I12" s="63" t="n">
@@ -17907,7 +17907,7 @@
       </c>
       <c r="H13" s="64" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="I13" s="63" t="n">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="H14" s="64" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="I14" s="63" t="n">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="H15" s="64" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="I15" s="63" t="n">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="H16" s="64" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="I16" s="63" t="n">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="H17" s="64" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="I17" s="63" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="H18" s="64" t="inlineStr">
         <is>
-          <t>T0410011</t>
+          <t>PO-DMY-10011</t>
         </is>
       </c>
       <c r="I18" s="63" t="n">
@@ -18416,12 +18416,12 @@
       </c>
       <c r="J23" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K23" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L23" s="49" t="inlineStr">
@@ -18473,12 +18473,12 @@
       </c>
       <c r="J24" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K24" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L24" s="49" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="J25" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K25" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L25" s="49" t="inlineStr">
@@ -18587,12 +18587,12 @@
       </c>
       <c r="J26" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K26" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L26" s="49" t="inlineStr">
@@ -18644,12 +18644,12 @@
       </c>
       <c r="J27" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K27" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L27" s="49" t="inlineStr">
@@ -18723,12 +18723,12 @@
       </c>
       <c r="B31" s="49" t="inlineStr">
         <is>
-          <t>T0409011</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="C31" s="49" t="inlineStr">
         <is>
-          <t>3126035911</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="D31" s="49" t="inlineStr">
@@ -35940,7 +35940,7 @@
       </c>
       <c r="F7" s="32" t="inlineStr">
         <is>
-          <t>PART-X 14-Oct needs 24 pcs (VN 18, TH 6) but only 18 pcs of crossdock PO are released on 15-Oct (T0409001 12 + T0409002 6). Scan order VN (CO-14101..14103) then TH (CO-14104): cases 1-3 (VN) have a PO, case 4 (TH) has none. Every case ends a valid cut, so blocks 1-3 are Ready and block 4 Not Ready: the unit is Partially Ready (ASN options 1 / 2 / 3 cases). In this simulation the supplier waits: on 16-Oct a new crossdock manifest (T0410001, 6 pcs) is released → [Search] again → block 4 Ready.</t>
+          <t>PART-X 14-Oct needs 24 pcs (VN 18, TH 6) but only 18 pcs of crossdock PO are released on 15-Oct (PO-DMY-09001 12 + PO-DMY-09002 6). Scan order VN (CO-14101..14103) then TH (CO-14104): cases 1-3 (VN) have a PO, case 4 (TH) has none. Every case ends a valid cut, so blocks 1-3 are Ready and block 4 Not Ready: the unit is Partially Ready (ASN options 1 / 2 / 3 cases). In this simulation the supplier waits: on 16-Oct a new crossdock manifest (PO-DMY-10001, 6 pcs) is released → [Search] again → block 4 Ready.</t>
         </is>
       </c>
     </row>
@@ -39310,12 +39310,12 @@
       </c>
       <c r="B21" s="51" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="C21" s="51" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="D21" s="51" t="inlineStr">
@@ -39361,12 +39361,12 @@
       </c>
       <c r="B22" s="51" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="C22" s="51" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="D22" s="51" t="inlineStr">
@@ -39412,12 +39412,12 @@
       </c>
       <c r="B23" s="51" t="inlineStr">
         <is>
-          <t>3126035903</t>
+          <t>MF-DMY-09003</t>
         </is>
       </c>
       <c r="C23" s="51" t="inlineStr">
         <is>
-          <t>T0409003</t>
+          <t>PO-DMY-09003</t>
         </is>
       </c>
       <c r="D23" s="51" t="inlineStr">
@@ -39517,7 +39517,7 @@
       </c>
       <c r="B27" s="51" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="C27" s="51" t="inlineStr">
@@ -39527,7 +39527,7 @@
       </c>
       <c r="D27" s="51" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="E27" s="51" t="inlineStr">
@@ -39553,7 +39553,7 @@
       </c>
       <c r="B28" s="51" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="C28" s="51" t="inlineStr">
@@ -39563,7 +39563,7 @@
       </c>
       <c r="D28" s="51" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="E28" s="51" t="inlineStr">
@@ -39589,7 +39589,7 @@
       </c>
       <c r="B29" s="51" t="inlineStr">
         <is>
-          <t>3126035903</t>
+          <t>MF-DMY-09003</t>
         </is>
       </c>
       <c r="C29" s="51" t="inlineStr">
@@ -39599,7 +39599,7 @@
       </c>
       <c r="D29" s="51" t="inlineStr">
         <is>
-          <t>T0409003</t>
+          <t>PO-DMY-09003</t>
         </is>
       </c>
       <c r="E29" s="51" t="inlineStr">
@@ -39767,7 +39767,7 @@
       </c>
       <c r="H34" s="64" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="I34" s="63" t="n">
@@ -39831,7 +39831,7 @@
       </c>
       <c r="H35" s="64" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="I35" s="63" t="n">
@@ -39895,7 +39895,7 @@
       </c>
       <c r="H36" s="64" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="I36" s="63" t="n">
@@ -39959,7 +39959,7 @@
       </c>
       <c r="H37" s="64" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="I37" s="63" t="n">
@@ -40023,7 +40023,7 @@
       </c>
       <c r="H38" s="64" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="I38" s="63" t="n">
@@ -40087,7 +40087,7 @@
       </c>
       <c r="H39" s="64" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="I39" s="63" t="n">
@@ -40151,7 +40151,7 @@
       </c>
       <c r="H40" s="64" t="inlineStr">
         <is>
-          <t>T0409003</t>
+          <t>PO-DMY-09003</t>
         </is>
       </c>
       <c r="I40" s="63" t="n">
@@ -40332,12 +40332,12 @@
       </c>
       <c r="J45" s="49" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="K45" s="49" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="L45" s="49" t="inlineStr">
@@ -40389,12 +40389,12 @@
       </c>
       <c r="J46" s="49" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="K46" s="49" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="L46" s="49" t="inlineStr">
@@ -40446,12 +40446,12 @@
       </c>
       <c r="J47" s="49" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="K47" s="49" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="L47" s="49" t="inlineStr">
@@ -40503,12 +40503,12 @@
       </c>
       <c r="J48" s="49" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="K48" s="49" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="L48" s="49" t="inlineStr">
@@ -40560,12 +40560,12 @@
       </c>
       <c r="J49" s="49" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="K49" s="49" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="L49" s="49" t="inlineStr">
@@ -40617,12 +40617,12 @@
       </c>
       <c r="J50" s="49" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="K50" s="49" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="L50" s="49" t="inlineStr">
@@ -40674,12 +40674,12 @@
       </c>
       <c r="J51" s="49" t="inlineStr">
         <is>
-          <t>T0409003</t>
+          <t>PO-DMY-09003</t>
         </is>
       </c>
       <c r="K51" s="49" t="inlineStr">
         <is>
-          <t>3126035903</t>
+          <t>MF-DMY-09003</t>
         </is>
       </c>
       <c r="L51" s="49" t="inlineStr">
@@ -40753,12 +40753,12 @@
       </c>
       <c r="B55" s="49" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="C55" s="49" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="D55" s="49" t="inlineStr">
@@ -40787,12 +40787,12 @@
       </c>
       <c r="B56" s="49" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="C56" s="49" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="D56" s="49" t="inlineStr">
@@ -40821,12 +40821,12 @@
       </c>
       <c r="B57" s="49" t="inlineStr">
         <is>
-          <t>T0409003</t>
+          <t>PO-DMY-09003</t>
         </is>
       </c>
       <c r="C57" s="49" t="inlineStr">
         <is>
-          <t>3126035903</t>
+          <t>MF-DMY-09003</t>
         </is>
       </c>
       <c r="D57" s="49" t="inlineStr">
@@ -41375,12 +41375,12 @@
       </c>
       <c r="B70" s="49" t="inlineStr">
         <is>
-          <t>3126035901A1</t>
+          <t>MF-DMY-09001A1</t>
         </is>
       </c>
       <c r="C70" s="49" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="D70" s="49" t="inlineStr">
@@ -41400,7 +41400,7 @@
       </c>
       <c r="G70" s="49" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="H70" s="61" t="inlineStr">
@@ -41439,12 +41439,12 @@
       </c>
       <c r="B71" s="49" t="inlineStr">
         <is>
-          <t>3126035902A1</t>
+          <t>MF-DMY-09002A1</t>
         </is>
       </c>
       <c r="C71" s="49" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="D71" s="49" t="inlineStr">
@@ -41464,7 +41464,7 @@
       </c>
       <c r="G71" s="49" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="H71" s="61" t="inlineStr">
@@ -41503,12 +41503,12 @@
       </c>
       <c r="B72" s="49" t="inlineStr">
         <is>
-          <t>3126035903A1</t>
+          <t>MF-DMY-09003A1</t>
         </is>
       </c>
       <c r="C72" s="49" t="inlineStr">
         <is>
-          <t>3126035903</t>
+          <t>MF-DMY-09003</t>
         </is>
       </c>
       <c r="D72" s="49" t="inlineStr">
@@ -41528,7 +41528,7 @@
       </c>
       <c r="G72" s="49" t="inlineStr">
         <is>
-          <t>T0409003</t>
+          <t>PO-DMY-09003</t>
         </is>
       </c>
       <c r="H72" s="61" t="inlineStr">
@@ -41646,12 +41646,12 @@
       </c>
       <c r="B76" s="49" t="inlineStr">
         <is>
-          <t>3126035901A1</t>
+          <t>MF-DMY-09001A1</t>
         </is>
       </c>
       <c r="C76" s="49" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="D76" s="49" t="inlineStr">
@@ -41666,7 +41666,7 @@
       </c>
       <c r="F76" s="49" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="G76" s="49" t="inlineStr">
@@ -41705,12 +41705,12 @@
       </c>
       <c r="B77" s="49" t="inlineStr">
         <is>
-          <t>3126035901A1</t>
+          <t>MF-DMY-09001A1</t>
         </is>
       </c>
       <c r="C77" s="49" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="D77" s="49" t="inlineStr">
@@ -41725,7 +41725,7 @@
       </c>
       <c r="F77" s="49" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="G77" s="49" t="inlineStr">
@@ -41764,12 +41764,12 @@
       </c>
       <c r="B78" s="49" t="inlineStr">
         <is>
-          <t>3126035902A1</t>
+          <t>MF-DMY-09002A1</t>
         </is>
       </c>
       <c r="C78" s="49" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="D78" s="49" t="inlineStr">
@@ -41784,7 +41784,7 @@
       </c>
       <c r="F78" s="49" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="G78" s="49" t="inlineStr">
@@ -41823,12 +41823,12 @@
       </c>
       <c r="B79" s="49" t="inlineStr">
         <is>
-          <t>3126035902A1</t>
+          <t>MF-DMY-09002A1</t>
         </is>
       </c>
       <c r="C79" s="49" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="D79" s="49" t="inlineStr">
@@ -41843,7 +41843,7 @@
       </c>
       <c r="F79" s="49" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="G79" s="49" t="inlineStr">
@@ -41882,12 +41882,12 @@
       </c>
       <c r="B80" s="49" t="inlineStr">
         <is>
-          <t>3126035903A1</t>
+          <t>MF-DMY-09003A1</t>
         </is>
       </c>
       <c r="C80" s="49" t="inlineStr">
         <is>
-          <t>3126035903</t>
+          <t>MF-DMY-09003</t>
         </is>
       </c>
       <c r="D80" s="49" t="inlineStr">
@@ -41902,7 +41902,7 @@
       </c>
       <c r="F80" s="49" t="inlineStr">
         <is>
-          <t>T0409003</t>
+          <t>PO-DMY-09003</t>
         </is>
       </c>
       <c r="G80" s="49" t="inlineStr">
@@ -42138,12 +42138,12 @@
       </c>
       <c r="J88" s="58" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="K88" s="58" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="L88" s="58" t="inlineStr">
@@ -42203,12 +42203,12 @@
       </c>
       <c r="J89" s="58" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="K89" s="58" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="L89" s="58" t="inlineStr">
@@ -42268,12 +42268,12 @@
       </c>
       <c r="J90" s="58" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="K90" s="58" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="L90" s="58" t="inlineStr">
@@ -42333,12 +42333,12 @@
       </c>
       <c r="J91" s="58" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="K91" s="58" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="L91" s="58" t="inlineStr">
@@ -42398,12 +42398,12 @@
       </c>
       <c r="J92" s="58" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="K92" s="58" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="L92" s="58" t="inlineStr">
@@ -42463,12 +42463,12 @@
       </c>
       <c r="J93" s="58" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="K93" s="58" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="L93" s="58" t="inlineStr">
@@ -42528,12 +42528,12 @@
       </c>
       <c r="J94" s="58" t="inlineStr">
         <is>
-          <t>T0409003</t>
+          <t>PO-DMY-09003</t>
         </is>
       </c>
       <c r="K94" s="58" t="inlineStr">
         <is>
-          <t>3126035903</t>
+          <t>MF-DMY-09003</t>
         </is>
       </c>
       <c r="L94" s="58" t="inlineStr">
@@ -42603,7 +42603,7 @@
     <row r="3">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>• PART-X 14-Oct needs 24 pcs (VN 18, TH 6) but only 18 pcs of crossdock PO are released on 15-Oct (T0409001 12 + T0409002 6).</t>
+          <t>• PART-X 14-Oct needs 24 pcs (VN 18, TH 6) but only 18 pcs of crossdock PO are released on 15-Oct (PO-DMY-09001 12 + PO-DMY-09002 6).</t>
         </is>
       </c>
     </row>
@@ -42617,7 +42617,7 @@
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
         <is>
-          <t>• In this simulation the supplier waits: on 16-Oct a new crossdock manifest (T0410001, 6 pcs) is released → [Search] again → block 4 Ready.</t>
+          <t>• In this simulation the supplier waits: on 16-Oct a new crossdock manifest (PO-DMY-10001, 6 pcs) is released → [Search] again → block 4 Ready.</t>
         </is>
       </c>
     </row>
@@ -42762,7 +42762,7 @@
       </c>
       <c r="B12" s="51" t="inlineStr">
         <is>
-          <t>3126035901</t>
+          <t>MF-DMY-09001</t>
         </is>
       </c>
       <c r="C12" s="51" t="inlineStr">
@@ -42772,7 +42772,7 @@
       </c>
       <c r="D12" s="51" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="E12" s="51" t="inlineStr">
@@ -42798,7 +42798,7 @@
       </c>
       <c r="B13" s="51" t="inlineStr">
         <is>
-          <t>3126035902</t>
+          <t>MF-DMY-09002</t>
         </is>
       </c>
       <c r="C13" s="51" t="inlineStr">
@@ -42808,7 +42808,7 @@
       </c>
       <c r="D13" s="51" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="E13" s="51" t="inlineStr">
@@ -42976,7 +42976,7 @@
       </c>
       <c r="H18" s="64" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="I18" s="63" t="n">
@@ -43040,7 +43040,7 @@
       </c>
       <c r="H19" s="64" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="I19" s="63" t="n">
@@ -43104,7 +43104,7 @@
       </c>
       <c r="H20" s="64" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="I20" s="63" t="n">
@@ -43168,7 +43168,7 @@
       </c>
       <c r="H21" s="64" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="I21" s="63" t="n">
@@ -43232,7 +43232,7 @@
       </c>
       <c r="H22" s="64" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="I22" s="63" t="n">
@@ -43425,12 +43425,12 @@
       </c>
       <c r="B28" s="49" t="inlineStr">
         <is>
-          <t>3126036001</t>
+          <t>MF-DMY-10001</t>
         </is>
       </c>
       <c r="C28" s="49" t="inlineStr">
         <is>
-          <t>T0410001</t>
+          <t>PO-DMY-10001</t>
         </is>
       </c>
       <c r="D28" s="49" t="inlineStr">
@@ -43530,7 +43530,7 @@
       </c>
       <c r="B32" s="49" t="inlineStr">
         <is>
-          <t>3126036001</t>
+          <t>MF-DMY-10001</t>
         </is>
       </c>
       <c r="C32" s="49" t="inlineStr">
@@ -43540,7 +43540,7 @@
       </c>
       <c r="D32" s="49" t="inlineStr">
         <is>
-          <t>T0410001</t>
+          <t>PO-DMY-10001</t>
         </is>
       </c>
       <c r="E32" s="49" t="inlineStr">
@@ -43708,7 +43708,7 @@
       </c>
       <c r="H37" s="64" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="I37" s="63" t="n">
@@ -43772,7 +43772,7 @@
       </c>
       <c r="H38" s="64" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="I38" s="63" t="n">
@@ -43836,7 +43836,7 @@
       </c>
       <c r="H39" s="64" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="I39" s="63" t="n">
@@ -43900,7 +43900,7 @@
       </c>
       <c r="H40" s="64" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="I40" s="63" t="n">
@@ -43964,7 +43964,7 @@
       </c>
       <c r="H41" s="64" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="I41" s="63" t="n">
@@ -44028,7 +44028,7 @@
       </c>
       <c r="H42" s="60" t="inlineStr">
         <is>
-          <t>T0410001</t>
+          <t>PO-DMY-10001</t>
         </is>
       </c>
       <c r="I42" s="63" t="n">
@@ -44058,7 +44058,7 @@
       </c>
       <c r="P42" s="64" t="inlineStr">
         <is>
-          <t>PO T0410001: unit Ready</t>
+          <t>PO PO-DMY-10001: unit Ready</t>
         </is>
       </c>
     </row>
@@ -44711,7 +44711,7 @@
       </c>
       <c r="H20" s="64" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="I20" s="63" t="n">
@@ -44775,7 +44775,7 @@
       </c>
       <c r="H21" s="64" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="I21" s="63" t="n">
@@ -44839,7 +44839,7 @@
       </c>
       <c r="H22" s="64" t="inlineStr">
         <is>
-          <t>T0409001</t>
+          <t>PO-DMY-09001</t>
         </is>
       </c>
       <c r="I22" s="63" t="n">
@@ -44903,7 +44903,7 @@
       </c>
       <c r="H23" s="64" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="I23" s="63" t="n">
@@ -44967,7 +44967,7 @@
       </c>
       <c r="H24" s="64" t="inlineStr">
         <is>
-          <t>T0409002</t>
+          <t>PO-DMY-09002</t>
         </is>
       </c>
       <c r="I24" s="63" t="n">

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -10132,7 +10132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -10149,7 +10149,8 @@
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10176,21 +10177,21 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>• 15-Oct CO-14101 VN → ASN0001, CO-14102 TH on hold. 16-Oct CO-14101 received (6), CO-14102 cancelled (2, no ASN: nothing else), CO-14103 → ASN00002.</t>
+          <t>• 16-Oct CO-14101 VN → ASN0001, CO-14102 TH on hold. 17-Oct CO-14101 received (6), CO-14102 cancelled (2, no ASN: nothing else), CO-14103 → ASN0002.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
         <is>
-          <t>• 17-Oct CO-14103 received; CO-14104 TH → ASN00003. 18-Oct CO-14104 cancelled although in ASN00003, CO-14105 VN received without ASN (6, PO_MAPPED N).</t>
+          <t>• 18-Oct order date 17-Oct: scan order CO-14105, CO-14106 + CO-14107, CO-14104 (customer code 9715300 before 9722D10); all 3 cases Ready, sent together in ASN0003. CO-14108 (order date 18-Oct) gets no PO (Not Ready).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
         <is>
-          <t>• The D/S team moves the 6 pcs of ASN00003 from CO-14104 to CO-14105 in Change Order Number (XD11); history in TB_H_CROSSDOCK_ORDER_CHANGE.</t>
+          <t>• 19-Oct ASN0003 received; CO-14104 cancelled although in case 3, its pcs go to CO-14108 in G-System (6, PO_MAPPED N, no ASN). The D/S team moves case 3 from CO-14104 to CO-14108 in Change Order Number (XD11); history in TB_H_CROSSDOCK_ORDER_CHANGE.</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10255,7 @@
     <row r="10">
       <c r="A10" s="45" t="inlineStr">
         <is>
-          <t>1. 15-Oct XD08: first replication</t>
+          <t>1. 16-Oct XD08: first replication</t>
         </is>
       </c>
       <c r="B10" s="46" t="n"/>
@@ -10271,6 +10272,7 @@
       <c r="M10" s="46" t="n"/>
       <c r="N10" s="46" t="n"/>
       <c r="O10" s="46" t="n"/>
+      <c r="P10" s="46" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -10374,7 +10376,7 @@
       </c>
       <c r="D13" s="49" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E13" s="49" t="inlineStr">
@@ -10440,7 +10442,7 @@
       </c>
       <c r="D14" s="49" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E14" s="49" t="inlineStr">
@@ -10491,7 +10493,7 @@
     <row r="16">
       <c r="A16" s="45" t="inlineStr">
         <is>
-          <t>2. 15-Oct D/S holds CO-14102; supplier creates and submits ASN0001 (CO-14101)</t>
+          <t>2. 16-Oct D/S holds CO-14102; supplier creates and submits ASN0001 (CO-14101)</t>
         </is>
       </c>
       <c r="B16" s="46" t="n"/>
@@ -10508,6 +10510,7 @@
       <c r="M16" s="46" t="n"/>
       <c r="N16" s="46" t="n"/>
       <c r="O16" s="46" t="n"/>
+      <c r="P16" s="46" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
@@ -10638,12 +10641,12 @@
       </c>
       <c r="J19" s="49" t="inlineStr">
         <is>
-          <t>PO-DMY-09051</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K19" s="49" t="inlineStr">
         <is>
-          <t>MF-DMY-09051</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L19" s="49" t="inlineStr">
@@ -10765,7 +10768,7 @@
       </c>
       <c r="D23" s="58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E23" s="58" t="inlineStr">
@@ -10831,7 +10834,7 @@
       </c>
       <c r="D24" s="58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E24" s="58" t="inlineStr">
@@ -10875,14 +10878,14 @@
       <c r="M24" s="58" t="n"/>
       <c r="N24" s="58" t="inlineStr">
         <is>
-          <t>Hold by D/S (screen)</t>
+          <t>Hold by D/S (screen); PO-DMY-09012 stays open</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="45" t="inlineStr">
         <is>
-          <t>3. 16-Oct XD08: source CO-14101 → 6, CO-14102 → 2, CO-14103 new</t>
+          <t>3. 17-Oct XD08: source CO-14101 → 6, CO-14102 → 2, CO-14103 new</t>
         </is>
       </c>
       <c r="B26" s="46" t="n"/>
@@ -10899,6 +10902,7 @@
       <c r="M26" s="46" t="n"/>
       <c r="N26" s="46" t="n"/>
       <c r="O26" s="46" t="n"/>
+      <c r="P26" s="46" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="35" t="inlineStr">
@@ -11002,7 +11006,7 @@
       </c>
       <c r="D29" s="58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E29" s="58" t="inlineStr">
@@ -11072,7 +11076,7 @@
       </c>
       <c r="D30" s="58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E30" s="58" t="inlineStr">
@@ -11193,7 +11197,7 @@
     <row r="33">
       <c r="A33" s="45" t="inlineStr">
         <is>
-          <t>4. 16-Oct CO-14103 → ASN00002</t>
+          <t>4. 17-Oct CO-14103 → ASN0002 (PO-DMY-09012)</t>
         </is>
       </c>
       <c r="B33" s="46" t="n"/>
@@ -11210,6 +11214,7 @@
       <c r="M33" s="46" t="n"/>
       <c r="N33" s="46" t="n"/>
       <c r="O33" s="46" t="n"/>
+      <c r="P33" s="46" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="35" t="inlineStr">
@@ -11340,12 +11345,12 @@
       </c>
       <c r="J36" s="49" t="inlineStr">
         <is>
-          <t>PO-DMY-10052</t>
+          <t>PO-DMY-09012</t>
         </is>
       </c>
       <c r="K36" s="49" t="inlineStr">
         <is>
-          <t>MF-DMY-10052</t>
+          <t>MF-DMY-09012</t>
         </is>
       </c>
       <c r="L36" s="49" t="inlineStr">
@@ -11355,7 +11360,7 @@
       </c>
       <c r="M36" s="49" t="inlineStr">
         <is>
-          <t>ASN00002</t>
+          <t>ASN0002</t>
         </is>
       </c>
       <c r="N36" s="49" t="inlineStr">
@@ -11514,7 +11519,7 @@
     <row r="42">
       <c r="A42" s="45" t="inlineStr">
         <is>
-          <t>5. 17-Oct XD08: CO-14103 → 6, CO-14104 and CO-14105 new; CO-14104 → ASN00003</t>
+          <t>5. 18-Oct XD08: CO-14103 → 6; CO-14104 … CO-14108 new (rows in scan order)</t>
         </is>
       </c>
       <c r="B42" s="46" t="n"/>
@@ -11531,6 +11536,7 @@
       <c r="M42" s="46" t="n"/>
       <c r="N42" s="46" t="n"/>
       <c r="O42" s="46" t="n"/>
+      <c r="P42" s="46" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="35" t="inlineStr">
@@ -11694,12 +11700,12 @@
       </c>
       <c r="B46" s="49" t="inlineStr">
         <is>
-          <t>9722D10</t>
+          <t>9715300</t>
         </is>
       </c>
       <c r="C46" s="49" t="inlineStr">
         <is>
-          <t>CO-14104</t>
+          <t>CO-14105</t>
         </is>
       </c>
       <c r="D46" s="49" t="inlineStr">
@@ -11709,7 +11715,7 @@
       </c>
       <c r="E46" s="49" t="inlineStr">
         <is>
-          <t>9722D10</t>
+          <t>9715310</t>
         </is>
       </c>
       <c r="F46" s="49" t="inlineStr">
@@ -11756,12 +11762,12 @@
       </c>
       <c r="B47" s="49" t="inlineStr">
         <is>
-          <t>9722D10</t>
+          <t>9715300</t>
         </is>
       </c>
       <c r="C47" s="49" t="inlineStr">
         <is>
-          <t>CO-14105</t>
+          <t>CO-14106</t>
         </is>
       </c>
       <c r="D47" s="49" t="inlineStr">
@@ -11790,7 +11796,7 @@
         </is>
       </c>
       <c r="I47" s="53" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J47" s="49" t="inlineStr">
         <is>
@@ -11810,816 +11816,1015 @@
       <c r="M47" s="49" t="n"/>
       <c r="N47" s="49" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B48" s="49" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C48" s="49" t="inlineStr">
+        <is>
+          <t>CO-14107</t>
+        </is>
+      </c>
+      <c r="D48" s="49" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E48" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F48" s="49" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G48" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H48" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I48" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" s="49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K48" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L48" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M48" s="49" t="n"/>
+      <c r="N48" s="49" t="inlineStr"/>
+    </row>
     <row r="49">
-      <c r="A49" s="35" t="inlineStr">
+      <c r="A49" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B49" s="49" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="C49" s="49" t="inlineStr">
+        <is>
+          <t>CO-14104</t>
+        </is>
+      </c>
+      <c r="D49" s="49" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E49" s="49" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F49" s="49" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G49" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H49" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I49" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J49" s="49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K49" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L49" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M49" s="49" t="n"/>
+      <c r="N49" s="49" t="inlineStr">
+        <is>
+          <t>Customer code 9722D10 after 9715300</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B50" s="49" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="C50" s="49" t="inlineStr">
+        <is>
+          <t>CO-14108</t>
+        </is>
+      </c>
+      <c r="D50" s="49" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E50" s="49" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F50" s="49" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G50" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H50" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I50" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J50" s="49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K50" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L50" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M50" s="49" t="n"/>
+      <c r="N50" s="49" t="inlineStr">
+        <is>
+          <t>Order date 18-Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="45" t="inlineStr">
+        <is>
+          <t>6. 18-Oct [Search] → XD09 (unit 17-Oct: 3 cases Ready; unit 18-Oct: no PO)</t>
+        </is>
+      </c>
+      <c r="B52" s="46" t="n"/>
+      <c r="C52" s="46" t="n"/>
+      <c r="D52" s="46" t="n"/>
+      <c r="E52" s="46" t="n"/>
+      <c r="F52" s="46" t="n"/>
+      <c r="G52" s="46" t="n"/>
+      <c r="H52" s="46" t="n"/>
+      <c r="I52" s="46" t="n"/>
+      <c r="J52" s="46" t="n"/>
+      <c r="K52" s="46" t="n"/>
+      <c r="L52" s="46" t="n"/>
+      <c r="M52" s="46" t="n"/>
+      <c r="N52" s="46" t="n"/>
+      <c r="O52" s="46" t="n"/>
+      <c r="P52" s="46" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="35" t="inlineStr">
+        <is>
+          <t>#TEMP_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D53" s="47" t="inlineStr">
+        <is>
+          <t>Temporary (session)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>SORT_SEQ</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>OPEN_ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>ASSIGNED_QTY</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>CUM_DEST_QTY</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>SEQ_QTY</t>
+        </is>
+      </c>
+      <c r="M54" s="9" t="inlineStr">
+        <is>
+          <t>CUT_FLAG</t>
+        </is>
+      </c>
+      <c r="N54" s="9" t="inlineStr">
+        <is>
+          <t>GROUP_SEQ</t>
+        </is>
+      </c>
+      <c r="O54" s="9" t="inlineStr">
+        <is>
+          <t>CROSSDOCK_STATUS</t>
+        </is>
+      </c>
+      <c r="P54" s="9" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B55" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D55" s="64" t="inlineStr">
+        <is>
+          <t>CO-14105</t>
+        </is>
+      </c>
+      <c r="E55" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F55" s="64" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="G55" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H55" s="64" t="inlineStr">
+        <is>
+          <t>PO-DMY-09013</t>
+        </is>
+      </c>
+      <c r="I55" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J55" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L55" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N55" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P55" s="64" t="inlineStr">
+        <is>
+          <t>Cases 1-3 ticked → ASN0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B56" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D56" s="64" t="inlineStr">
+        <is>
+          <t>CO-14106</t>
+        </is>
+      </c>
+      <c r="E56" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F56" s="64" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="G56" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="64" t="inlineStr">
+        <is>
+          <t>PO-DMY-09014</t>
+        </is>
+      </c>
+      <c r="I56" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K56" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="L56" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="M56" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N56" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P56" s="64" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B57" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D57" s="64" t="inlineStr">
+        <is>
+          <t>CO-14107</t>
+        </is>
+      </c>
+      <c r="E57" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F57" s="64" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="G57" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" s="64" t="inlineStr">
+        <is>
+          <t>PO-DMY-09014</t>
+        </is>
+      </c>
+      <c r="I57" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K57" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="L57" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N57" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="O57" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P57" s="64" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B58" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="D58" s="64" t="inlineStr">
+        <is>
+          <t>CO-14104</t>
+        </is>
+      </c>
+      <c r="E58" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F58" s="64" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="G58" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H58" s="64" t="inlineStr">
+        <is>
+          <t>PO-DMY-09014</t>
+        </is>
+      </c>
+      <c r="I58" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J58" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L58" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M58" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N58" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P58" s="64" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B59" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="D59" s="64" t="inlineStr">
+        <is>
+          <t>CO-14108</t>
+        </is>
+      </c>
+      <c r="E59" s="64" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F59" s="64" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="G59" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" s="64" t="n"/>
+      <c r="I59" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J59" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L59" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M59" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N59" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P59" s="64" t="inlineStr">
+        <is>
+          <t>Not Ready (no PO left)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="45" t="inlineStr">
+        <is>
+          <t>7. 18-Oct ASN0003 = cases 1-3 (whole order date 17-Oct)</t>
+        </is>
+      </c>
+      <c r="B61" s="46" t="n"/>
+      <c r="C61" s="46" t="n"/>
+      <c r="D61" s="46" t="n"/>
+      <c r="E61" s="46" t="n"/>
+      <c r="F61" s="46" t="n"/>
+      <c r="G61" s="46" t="n"/>
+      <c r="H61" s="46" t="n"/>
+      <c r="I61" s="46" t="n"/>
+      <c r="J61" s="46" t="n"/>
+      <c r="K61" s="46" t="n"/>
+      <c r="L61" s="46" t="n"/>
+      <c r="M61" s="46" t="n"/>
+      <c r="N61" s="46" t="n"/>
+      <c r="O61" s="46" t="n"/>
+      <c r="P61" s="46" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="35" t="inlineStr">
         <is>
           <t>TB_R_INSTRUCTION</t>
         </is>
       </c>
-      <c r="D49" s="47" t="inlineStr">
+      <c r="D62" s="47" t="inlineStr">
         <is>
           <t>New table (Crossdock)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B50" s="42" t="inlineStr">
+      <c r="B63" s="42" t="inlineStr">
         <is>
           <t>INSTRUCTION_ID</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>CASE_SEQ</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>LINE_SEQ</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>PART_NO</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>DESTINATION_CD</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>CUSTOMER_ORDER_NO</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>SERIAL_NO</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>QTY</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>PO_NO</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="K63" s="3" t="inlineStr">
         <is>
           <t>MANIFEST_NO</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="L63" s="3" t="inlineStr">
         <is>
           <t>MANIFEST_ITEM</t>
         </is>
       </c>
-      <c r="M50" s="3" t="inlineStr">
+      <c r="M63" s="3" t="inlineStr">
         <is>
           <t>ASN_NO</t>
         </is>
       </c>
-      <c r="N50" s="3" t="inlineStr">
+      <c r="N63" s="3" t="inlineStr">
         <is>
           <t>CASE_NO</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
+      <c r="O63" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="48" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="48" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="B51" s="53" t="n">
+      <c r="B64" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="C51" s="53" t="n">
+      <c r="C64" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="53" t="n">
+      <c r="D64" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E51" s="49" t="inlineStr">
+      <c r="E64" s="49" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="F51" s="49" t="inlineStr">
+      <c r="F64" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G64" s="49" t="inlineStr">
+        <is>
+          <t>CO-14105</t>
+        </is>
+      </c>
+      <c r="H64" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I64" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J64" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09013</t>
+        </is>
+      </c>
+      <c r="K64" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09013</t>
+        </is>
+      </c>
+      <c r="L64" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M64" s="49" t="inlineStr">
+        <is>
+          <t>ASN0003</t>
+        </is>
+      </c>
+      <c r="N64" s="49" t="inlineStr">
+        <is>
+          <t>C-0003-01</t>
+        </is>
+      </c>
+      <c r="O64" s="49" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B65" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F65" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G65" s="49" t="inlineStr">
+        <is>
+          <t>CO-14106</t>
+        </is>
+      </c>
+      <c r="H65" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I65" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J65" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09014</t>
+        </is>
+      </c>
+      <c r="K65" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09014</t>
+        </is>
+      </c>
+      <c r="L65" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M65" s="49" t="inlineStr">
+        <is>
+          <t>ASN0003</t>
+        </is>
+      </c>
+      <c r="N65" s="49" t="inlineStr">
+        <is>
+          <t>C-0003-02</t>
+        </is>
+      </c>
+      <c r="O65" s="49" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B66" s="53" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F66" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G66" s="49" t="inlineStr">
+        <is>
+          <t>CO-14107</t>
+        </is>
+      </c>
+      <c r="H66" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I66" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J66" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09014</t>
+        </is>
+      </c>
+      <c r="K66" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09014</t>
+        </is>
+      </c>
+      <c r="L66" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M66" s="49" t="inlineStr">
+        <is>
+          <t>ASN0003</t>
+        </is>
+      </c>
+      <c r="N66" s="49" t="inlineStr">
+        <is>
+          <t>C-0003-02</t>
+        </is>
+      </c>
+      <c r="O66" s="49" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B67" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F67" s="49" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="G51" s="49" t="inlineStr">
+      <c r="G67" s="49" t="inlineStr">
         <is>
           <t>CO-14104</t>
         </is>
       </c>
-      <c r="H51" s="49" t="inlineStr">
+      <c r="H67" s="49" t="inlineStr">
         <is>
           <t>0000001</t>
         </is>
       </c>
-      <c r="I51" s="53" t="n">
+      <c r="I67" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="J51" s="49" t="inlineStr">
-        <is>
-          <t>PO-DMY-10053</t>
-        </is>
-      </c>
-      <c r="K51" s="49" t="inlineStr">
-        <is>
-          <t>MF-DMY-10053</t>
-        </is>
-      </c>
-      <c r="L51" s="49" t="inlineStr">
+      <c r="J67" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09014</t>
+        </is>
+      </c>
+      <c r="K67" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09014</t>
+        </is>
+      </c>
+      <c r="L67" s="49" t="inlineStr">
         <is>
           <t>0001</t>
         </is>
       </c>
-      <c r="M51" s="49" t="inlineStr">
-        <is>
-          <t>ASN00003</t>
-        </is>
-      </c>
-      <c r="N51" s="49" t="inlineStr">
-        <is>
-          <t>C-0003-01</t>
-        </is>
-      </c>
-      <c r="O51" s="49" t="inlineStr">
-        <is>
-          <t>CO-14105: no PO yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="45" t="inlineStr">
-        <is>
-          <t>6. 18-Oct XD08: CO-14104 → 2 (in ASN00003), CO-14105 → 6</t>
-        </is>
-      </c>
-      <c r="B53" s="46" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
-      <c r="E53" s="46" t="n"/>
-      <c r="F53" s="46" t="n"/>
-      <c r="G53" s="46" t="n"/>
-      <c r="H53" s="46" t="n"/>
-      <c r="I53" s="46" t="n"/>
-      <c r="J53" s="46" t="n"/>
-      <c r="K53" s="46" t="n"/>
-      <c r="L53" s="46" t="n"/>
-      <c r="M53" s="46" t="n"/>
-      <c r="N53" s="46" t="n"/>
-      <c r="O53" s="46" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
-        </is>
-      </c>
-      <c r="D54" s="47" t="inlineStr">
-        <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B55" s="42" t="inlineStr">
-        <is>
-          <t>CUSTOMER_CD</t>
-        </is>
-      </c>
-      <c r="C55" s="42" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="D55" s="42" t="inlineStr">
-        <is>
-          <t>ORDER_DT</t>
-        </is>
-      </c>
-      <c r="E55" s="42" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="F55" s="42" t="inlineStr">
-        <is>
-          <t>DETAILED_ITEM_NO</t>
-        </is>
-      </c>
-      <c r="G55" s="42" t="inlineStr">
-        <is>
-          <t>SERIAL_NO</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>SHIPPING_PART_NO</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS_QTY</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>HOLD_FLAG</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>PO_MAPPED_FLAG</t>
-        </is>
-      </c>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>UPD_STATUS</t>
-        </is>
-      </c>
-      <c r="N55" s="5" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B56" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="C56" s="58" t="inlineStr">
-        <is>
-          <t>CO-14104</t>
-        </is>
-      </c>
-      <c r="D56" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E56" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F56" s="58" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G56" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H56" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I56" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="J56" s="58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K56" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L56" s="58" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M56" s="60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N56" s="58" t="inlineStr">
-        <is>
-          <t>Cancel after ASN: LOG5, listed in XD11; ASN not changed</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B57" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="C57" s="58" t="inlineStr">
-        <is>
-          <t>CO-14105</t>
-        </is>
-      </c>
-      <c r="D57" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E57" s="58" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F57" s="58" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G57" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H57" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I57" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="J57" s="58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K57" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L57" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M57" s="60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N57" s="58" t="inlineStr">
-        <is>
-          <t>Received without ASN (allocated by G-System): candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="45" t="inlineStr">
-        <is>
-          <t>7. 18-Oct XD11 Change Order Number: ASN00003 6 pcs → CO-14105</t>
-        </is>
-      </c>
-      <c r="B59" s="46" t="n"/>
-      <c r="C59" s="46" t="n"/>
-      <c r="D59" s="46" t="n"/>
-      <c r="E59" s="46" t="n"/>
-      <c r="F59" s="46" t="n"/>
-      <c r="G59" s="46" t="n"/>
-      <c r="H59" s="46" t="n"/>
-      <c r="I59" s="46" t="n"/>
-      <c r="J59" s="46" t="n"/>
-      <c r="K59" s="46" t="n"/>
-      <c r="L59" s="46" t="n"/>
-      <c r="M59" s="46" t="n"/>
-      <c r="N59" s="46" t="n"/>
-      <c r="O59" s="46" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_INSTRUCTION</t>
-        </is>
-      </c>
-      <c r="D60" s="47" t="inlineStr">
-        <is>
-          <t>New table (Crossdock)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B61" s="42" t="inlineStr">
-        <is>
-          <t>INSTRUCTION_ID</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>CASE_SEQ</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>LINE_SEQ</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>SERIAL_NO</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>QTY</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>PO_NO</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_NO</t>
-        </is>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_ITEM</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="inlineStr">
-        <is>
-          <t>ASN_NO</t>
-        </is>
-      </c>
-      <c r="N61" s="3" t="inlineStr">
-        <is>
-          <t>CASE_NO</t>
-        </is>
-      </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B62" s="59" t="n">
-        <v>3</v>
-      </c>
-      <c r="C62" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="F62" s="60" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="G62" s="60" t="inlineStr">
-        <is>
-          <t>CO-14105</t>
-        </is>
-      </c>
-      <c r="H62" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="I62" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="J62" s="58" t="inlineStr">
-        <is>
-          <t>PO-DMY-10053</t>
-        </is>
-      </c>
-      <c r="K62" s="58" t="inlineStr">
-        <is>
-          <t>MF-DMY-10053</t>
-        </is>
-      </c>
-      <c r="L62" s="58" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="M62" s="58" t="inlineStr">
-        <is>
-          <t>ASN00003</t>
-        </is>
-      </c>
-      <c r="N62" s="58" t="inlineStr">
-        <is>
-          <t>C-0003-01</t>
-        </is>
-      </c>
-      <c r="O62" s="58" t="inlineStr">
-        <is>
-          <t>Whole row moved; case, PO and ASN not changed</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
-        </is>
-      </c>
-      <c r="D64" s="47" t="inlineStr">
-        <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="26" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B65" s="42" t="inlineStr">
-        <is>
-          <t>CUSTOMER_CD</t>
-        </is>
-      </c>
-      <c r="C65" s="42" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="D65" s="42" t="inlineStr">
-        <is>
-          <t>ORDER_DT</t>
-        </is>
-      </c>
-      <c r="E65" s="42" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="F65" s="42" t="inlineStr">
-        <is>
-          <t>DETAILED_ITEM_NO</t>
-        </is>
-      </c>
-      <c r="G65" s="42" t="inlineStr">
-        <is>
-          <t>SERIAL_NO</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>SHIPPING_PART_NO</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS_QTY</t>
-        </is>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>HOLD_FLAG</t>
-        </is>
-      </c>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>PO_MAPPED_FLAG</t>
-        </is>
-      </c>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t>UPD_STATUS</t>
-        </is>
-      </c>
-      <c r="N65" s="5" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="50" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-      <c r="B66" s="51" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="C66" s="51" t="inlineStr">
-        <is>
-          <t>CO-14104</t>
-        </is>
-      </c>
-      <c r="D66" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E66" s="51" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F66" s="51" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G66" s="51" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H66" s="51" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I66" s="52" t="n">
-        <v>6</v>
-      </c>
-      <c r="J66" s="51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K66" s="51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L66" s="51" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M66" s="66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N66" s="51" t="inlineStr">
-        <is>
-          <t>Not changed (PO_MAPPED_FLAG stays Y)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B67" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="C67" s="58" t="inlineStr">
-        <is>
-          <t>CO-14105</t>
-        </is>
-      </c>
-      <c r="D67" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E67" s="58" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F67" s="58" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G67" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H67" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I67" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="J67" s="58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K67" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L67" s="60" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="M67" s="49" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N67" s="58" t="inlineStr">
-        <is>
-          <t>PO and ASN through ASN00003</t>
-        </is>
-      </c>
+          <t>ASN0003</t>
+        </is>
+      </c>
+      <c r="N67" s="49" t="inlineStr">
+        <is>
+          <t>C-0003-03</t>
+        </is>
+      </c>
+      <c r="O67" s="49" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="35" t="inlineStr">
         <is>
-          <t>TB_H_CROSSDOCK_ORDER_CHANGE</t>
+          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
         </is>
       </c>
       <c r="D69" s="47" t="inlineStr">
@@ -12636,17 +12841,17 @@
       </c>
       <c r="B70" s="42" t="inlineStr">
         <is>
-          <t>HIST_ID</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>ASN_NO</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>CASE_NO</t>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="C70" s="42" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="D70" s="42" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -12656,40 +12861,15 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>FROM_CUSTOMER_ORDER_NO</t>
+          <t>ORDER_QTY</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>FROM_SERIAL_NO</t>
+          <t>MAPPED_QTY</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>TO_CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>TO_DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>QTY</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>FROM_INSTRUCTION_ID</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>TO_INSTRUCTION_ID</t>
-        </is>
-      </c>
-      <c r="M70" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -12701,54 +12881,1393 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="B71" s="53" t="n">
+      <c r="B71" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09013</t>
+        </is>
+      </c>
+      <c r="C71" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09013</t>
+        </is>
+      </c>
+      <c r="D71" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E71" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F71" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="H71" s="49" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B72" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09014</t>
+        </is>
+      </c>
+      <c r="C72" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09014</t>
+        </is>
+      </c>
+      <c r="D72" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E72" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F72" s="53" t="n">
+        <v>12</v>
+      </c>
+      <c r="G72" s="53" t="n">
+        <v>12</v>
+      </c>
+      <c r="H72" s="49" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D74" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="26" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B75" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C75" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D75" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E75" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F75" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G75" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>UPD_STATUS</t>
+        </is>
+      </c>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B76" s="58" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C76" s="58" t="inlineStr">
+        <is>
+          <t>CO-14105</t>
+        </is>
+      </c>
+      <c r="D76" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E76" s="58" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F76" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G76" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H76" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I76" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J76" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K76" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L76" s="60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M76" s="58" t="n"/>
+      <c r="N76" s="58" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B77" s="58" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C77" s="58" t="inlineStr">
+        <is>
+          <t>CO-14106</t>
+        </is>
+      </c>
+      <c r="D77" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E77" s="58" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F77" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G77" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H77" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I77" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="J77" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K77" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L77" s="60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M77" s="58" t="n"/>
+      <c r="N77" s="58" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B78" s="58" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C78" s="58" t="inlineStr">
+        <is>
+          <t>CO-14107</t>
+        </is>
+      </c>
+      <c r="D78" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E78" s="58" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F78" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G78" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H78" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I78" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="J78" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K78" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L78" s="60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M78" s="58" t="n"/>
+      <c r="N78" s="58" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B79" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="C79" s="58" t="inlineStr">
+        <is>
+          <t>CO-14104</t>
+        </is>
+      </c>
+      <c r="D79" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E79" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F79" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G79" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H79" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I79" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J79" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K79" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L79" s="60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M79" s="58" t="n"/>
+      <c r="N79" s="58" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="45" t="inlineStr">
+        <is>
+          <t>8. 19-Oct XD08: ASN0003 received, CO-14104 → 2 (in case 3), CO-14108 → 6</t>
+        </is>
+      </c>
+      <c r="B81" s="46" t="n"/>
+      <c r="C81" s="46" t="n"/>
+      <c r="D81" s="46" t="n"/>
+      <c r="E81" s="46" t="n"/>
+      <c r="F81" s="46" t="n"/>
+      <c r="G81" s="46" t="n"/>
+      <c r="H81" s="46" t="n"/>
+      <c r="I81" s="46" t="n"/>
+      <c r="J81" s="46" t="n"/>
+      <c r="K81" s="46" t="n"/>
+      <c r="L81" s="46" t="n"/>
+      <c r="M81" s="46" t="n"/>
+      <c r="N81" s="46" t="n"/>
+      <c r="O81" s="46" t="n"/>
+      <c r="P81" s="46" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D82" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="26" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B83" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C83" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D83" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E83" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F83" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G83" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>UPD_STATUS</t>
+        </is>
+      </c>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B84" s="58" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C84" s="58" t="inlineStr">
+        <is>
+          <t>CO-14105</t>
+        </is>
+      </c>
+      <c r="D84" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E84" s="58" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F84" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G84" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H84" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I84" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J84" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K84" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L84" s="58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M84" s="60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N84" s="58" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B85" s="58" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C85" s="58" t="inlineStr">
+        <is>
+          <t>CO-14106</t>
+        </is>
+      </c>
+      <c r="D85" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E85" s="58" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F85" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G85" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H85" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I85" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="J85" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K85" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L85" s="58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M85" s="60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N85" s="58" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B86" s="58" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C86" s="58" t="inlineStr">
+        <is>
+          <t>CO-14107</t>
+        </is>
+      </c>
+      <c r="D86" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E86" s="58" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F86" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G86" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H86" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I86" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="J86" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K86" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L86" s="58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M86" s="60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N86" s="58" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B87" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="C87" s="58" t="inlineStr">
+        <is>
+          <t>CO-14104</t>
+        </is>
+      </c>
+      <c r="D87" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E87" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F87" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G87" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H87" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I87" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J87" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K87" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L87" s="58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M87" s="60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N87" s="58" t="inlineStr">
+        <is>
+          <t>Cancel after ASN: LOG5, listed in XD11; ASN not changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B88" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="C88" s="58" t="inlineStr">
+        <is>
+          <t>CO-14108</t>
+        </is>
+      </c>
+      <c r="D88" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E88" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F88" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G88" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H88" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I88" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J88" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K88" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L88" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M88" s="60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N88" s="58" t="inlineStr">
+        <is>
+          <t>Received without ASN (pcs of case 3 allocated by G-System): candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="45" t="inlineStr">
+        <is>
+          <t>9. 19-Oct XD11 Change Order Number: ASN0003 case 3 → CO-14108</t>
+        </is>
+      </c>
+      <c r="B90" s="46" t="n"/>
+      <c r="C90" s="46" t="n"/>
+      <c r="D90" s="46" t="n"/>
+      <c r="E90" s="46" t="n"/>
+      <c r="F90" s="46" t="n"/>
+      <c r="G90" s="46" t="n"/>
+      <c r="H90" s="46" t="n"/>
+      <c r="I90" s="46" t="n"/>
+      <c r="J90" s="46" t="n"/>
+      <c r="K90" s="46" t="n"/>
+      <c r="L90" s="46" t="n"/>
+      <c r="M90" s="46" t="n"/>
+      <c r="N90" s="46" t="n"/>
+      <c r="O90" s="46" t="n"/>
+      <c r="P90" s="46" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D91" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B92" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>LINE_SEQ</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="O92" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B93" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="C93" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="C71" s="49" t="inlineStr">
-        <is>
-          <t>ASN00003</t>
-        </is>
-      </c>
-      <c r="D71" s="49" t="inlineStr">
-        <is>
-          <t>C-0003-01</t>
-        </is>
-      </c>
-      <c r="E71" s="49" t="inlineStr">
+      <c r="E93" s="58" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="F71" s="49" t="inlineStr">
+      <c r="F93" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="G93" s="60" t="inlineStr">
+        <is>
+          <t>CO-14108</t>
+        </is>
+      </c>
+      <c r="H93" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I93" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J93" s="58" t="inlineStr">
+        <is>
+          <t>PO-DMY-09014</t>
+        </is>
+      </c>
+      <c r="K93" s="58" t="inlineStr">
+        <is>
+          <t>MF-DMY-09014</t>
+        </is>
+      </c>
+      <c r="L93" s="58" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M93" s="58" t="inlineStr">
+        <is>
+          <t>ASN0003</t>
+        </is>
+      </c>
+      <c r="N93" s="58" t="inlineStr">
+        <is>
+          <t>C-0003-03</t>
+        </is>
+      </c>
+      <c r="O93" s="58" t="inlineStr">
+        <is>
+          <t>Whole row moved; case, PO and ASN not changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D95" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="26" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B96" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C96" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D96" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E96" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F96" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G96" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M96" s="5" t="inlineStr">
+        <is>
+          <t>UPD_STATUS</t>
+        </is>
+      </c>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B97" s="51" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="C97" s="51" t="inlineStr">
         <is>
           <t>CO-14104</t>
         </is>
       </c>
-      <c r="G71" s="49" t="inlineStr">
+      <c r="D97" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E97" s="51" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F97" s="51" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G97" s="51" t="inlineStr">
         <is>
           <t>0000001</t>
         </is>
       </c>
-      <c r="H71" s="49" t="inlineStr">
-        <is>
-          <t>CO-14105</t>
-        </is>
-      </c>
-      <c r="I71" s="49" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="J71" s="53" t="n">
+      <c r="H97" s="51" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I97" s="52" t="n">
         <v>6</v>
       </c>
-      <c r="K71" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="L71" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="M71" s="49" t="inlineStr"/>
+      <c r="J97" s="51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K97" s="51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L97" s="51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M97" s="66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N97" s="51" t="inlineStr">
+        <is>
+          <t>Not changed (PO_MAPPED_FLAG stays Y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B98" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="C98" s="58" t="inlineStr">
+        <is>
+          <t>CO-14108</t>
+        </is>
+      </c>
+      <c r="D98" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E98" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F98" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G98" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H98" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I98" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J98" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K98" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L98" s="60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M98" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N98" s="58" t="inlineStr">
+        <is>
+          <t>PO and ASN through ASN0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="35" t="inlineStr">
+        <is>
+          <t>TB_H_CROSSDOCK_ORDER_CHANGE</t>
+        </is>
+      </c>
+      <c r="D100" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="26" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B101" s="42" t="inlineStr">
+        <is>
+          <t>HIST_ID</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>FROM_CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>FROM_SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>TO_CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>TO_DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>FROM_INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>TO_INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B102" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="49" t="inlineStr">
+        <is>
+          <t>ASN0003</t>
+        </is>
+      </c>
+      <c r="D102" s="49" t="inlineStr">
+        <is>
+          <t>C-0003-03</t>
+        </is>
+      </c>
+      <c r="E102" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F102" s="49" t="inlineStr">
+        <is>
+          <t>CO-14104</t>
+        </is>
+      </c>
+      <c r="G102" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H102" s="49" t="inlineStr">
+        <is>
+          <t>CO-14108</t>
+        </is>
+      </c>
+      <c r="I102" s="49" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="J102" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="K102" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="L102" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="M102" s="49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21984,7 +23503,7 @@
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-3, SIM-4, SIM-7, SIM-8, SIM-9</t>
+          <t>SIM-2, SIM-3, SIM-4, SIM-5, SIM-7, SIM-8, SIM-9</t>
         </is>
       </c>
     </row>
@@ -22074,7 +23593,7 @@
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-6, SIM-7, SIM-8, SIM-9</t>
+          <t>SIM-2, SIM-5, SIM-6, SIM-7, SIM-8, SIM-9</t>
         </is>
       </c>
     </row>
@@ -38534,12 +40053,12 @@
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
-          <t>TB_R_H0253_ORDER_CONTROL_PRE, TB_R_INSTRUCTION, TB_H_CROSSDOCK_ORDER_CHANGE</t>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE, TB_R_INSTRUCTION, #TEMP_INSTRUCTION, TB_R_PRA_DAILY_ORDER_MAPPED, TB_H_CROSSDOCK_ORDER_CHANGE</t>
         </is>
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>PART-X, 6 pcs/case. ORDER_STATUS of the replicate keeps the first value (7); a change in G-System is written to UPD_STATUS: 6 received, 2 cancel. 15-Oct CO-14101 VN → ASN0001, CO-14102 TH on hold. 16-Oct CO-14101 received (6), CO-14102 cancelled (2, no ASN: nothing else), CO-14103 → ASN00002. 17-Oct CO-14103 received; CO-14104 TH → ASN00003. 18-Oct CO-14104 cancelled although in ASN00003, CO-14105 VN received without ASN (6, PO_MAPPED N). The D/S team moves the 6 pcs of ASN00003 from CO-14104 to CO-14105 in Change Order Number (XD11); history in TB_H_CROSSDOCK_ORDER_CHANGE.</t>
+          <t>PART-X, 6 pcs/case. ORDER_STATUS of the replicate keeps the first value (7); a change in G-System is written to UPD_STATUS: 6 received, 2 cancel. 16-Oct CO-14101 VN → ASN0001, CO-14102 TH on hold. 17-Oct CO-14101 received (6), CO-14102 cancelled (2, no ASN: nothing else), CO-14103 → ASN0002. 18-Oct order date 17-Oct: scan order CO-14105, CO-14106 + CO-14107, CO-14104 (customer code 9715300 before 9722D10); all 3 cases Ready, sent together in ASN0003. CO-14108 (order date 18-Oct) gets no PO (Not Ready). 19-Oct ASN0003 received; CO-14104 cancelled although in case 3, its pcs go to CO-14108 in G-System (6, PO_MAPPED N, no ASN). The D/S team moves case 3 from CO-14104 to CO-14108 in Change Order Number (XD11); history in TB_H_CROSSDOCK_ORDER_CHANGE.</t>
         </is>
       </c>
     </row>

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -10132,7 +10132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:P95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -10156,7 +10156,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIM-5 UPD_STATUS day by day; cancel after ASN → Change Order Number (simulasi_asn.xlsx)</t>
+          <t>SIM-5 One PO per order date (short PO → split PO); cancel of a middle row after ASN → Change Order Number (simulasi_asn.xlsx)</t>
         </is>
       </c>
     </row>
@@ -10170,28 +10170,28 @@
     <row r="3">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>• PART-X, 6 pcs/case. ORDER_STATUS of the replicate keeps the first value (7); a change in G-System is written to UPD_STATUS: 6 received, 2 cancel.</t>
+          <t>• PART-X, 6 pcs/case. One PO per customer order date: PO_DT = order date + 1, qty = total order qty of the date (all destinations). PO qty &lt; order qty is an abnormality: the rest comes in a split PO. ORDER_STATUS of the replicate keeps 7; changes go to UPD_STATUS.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>• 16-Oct CO-14101 VN → ASN0001, CO-14102 TH on hold. 17-Oct CO-14101 received (6), CO-14102 cancelled (2, no ASN: nothing else), CO-14103 → ASN0002.</t>
+          <t>• Order date 15-Oct (12) → PO-DMY-09011; CO-14102 on hold then cancelled, so its 6 pcs of PO-DMY-09011 go to CO-14103 (older PO_DT first).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
         <is>
-          <t>• 18-Oct order date 17-Oct: scan order CO-14105, CO-14106 + CO-14107, CO-14104 (customer code 9715300 before 9722D10); all 3 cases Ready, sent together in ASN0003. CO-14108 (order date 18-Oct) gets no PO (Not Ready).</t>
+          <t>• Order date 17-Oct: 4 destinations, 30 pcs, PO-DMY-09013 only 18 (abnormal) → case 5 Not Ready until the split PO-DMY-09014 (12, 19-Oct). Cases 1-4 → ASN0003; CO-14104 (middle row, case 3) is cancelled after the ASN.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
         <is>
-          <t>• 19-Oct ASN0003 received; CO-14104 cancelled although in case 3, its pcs go to CO-14108 in G-System (6, PO_MAPPED N, no ASN). The D/S team moves case 3 from CO-14104 to CO-14108 in Change Order Number (XD11); history in TB_H_CROSSDOCK_ORDER_CHANGE.</t>
+          <t>• 21-Oct G-System allocates the pcs of case 3 to CO-14111 (UPD_STATUS 6, no ASN): the D/S team moves case 3 to CO-14111 (XD11). Open PO qty at the end (12) = cancelled qty (CO-14102 + CO-14104).</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
     <row r="10">
       <c r="A10" s="45" t="inlineStr">
         <is>
-          <t>1. 16-Oct XD08: first replication</t>
+          <t>1. 16-Oct XD08 (order date 15-Oct; PO-DMY-09011 PO_DT 16-Oct, 12)</t>
         </is>
       </c>
       <c r="B10" s="46" t="n"/>
@@ -10418,11 +10418,7 @@
         </is>
       </c>
       <c r="M13" s="49" t="n"/>
-      <c r="N13" s="49" t="inlineStr">
-        <is>
-          <t>Source status 7</t>
-        </is>
-      </c>
+      <c r="N13" s="49" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="48" t="inlineStr">
@@ -10484,16 +10480,12 @@
         </is>
       </c>
       <c r="M14" s="49" t="n"/>
-      <c r="N14" s="49" t="inlineStr">
-        <is>
-          <t>Source status 7</t>
-        </is>
-      </c>
+      <c r="N14" s="49" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="45" t="inlineStr">
         <is>
-          <t>2. 16-Oct D/S holds CO-14102; supplier creates and submits ASN0001 (CO-14101)</t>
+          <t>2. 16-Oct D/S holds CO-14102; CO-14101 → ASN0001</t>
         </is>
       </c>
       <c r="B16" s="46" t="n"/>
@@ -10810,11 +10802,7 @@
         </is>
       </c>
       <c r="M23" s="58" t="n"/>
-      <c r="N23" s="58" t="inlineStr">
-        <is>
-          <t>In ASN0001</t>
-        </is>
-      </c>
+      <c r="N23" s="58" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="57" t="inlineStr">
@@ -10878,14 +10866,14 @@
       <c r="M24" s="58" t="n"/>
       <c r="N24" s="58" t="inlineStr">
         <is>
-          <t>Hold by D/S (screen); PO-DMY-09012 stays open</t>
+          <t>6 pcs of PO-DMY-09011 stay open</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="45" t="inlineStr">
         <is>
-          <t>3. 17-Oct XD08: source CO-14101 → 6, CO-14102 → 2, CO-14103 new</t>
+          <t>3. 17-Oct XD08: CO-14101 → 6, CO-14102 → 2, CO-14103 new (PO-DMY-09012 PO_DT 17-Oct, 6)</t>
         </is>
       </c>
       <c r="B26" s="46" t="n"/>
@@ -11054,7 +11042,7 @@
       </c>
       <c r="N29" s="58" t="inlineStr">
         <is>
-          <t>Received in G-System; ORDER_STATUS stays 7</t>
+          <t>Received</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11112,7 @@
       </c>
       <c r="N30" s="58" t="inlineStr">
         <is>
-          <t>Cancelled, no ASN: ignored (PO_MAPPED_FLAG stays N)</t>
+          <t>Cancelled, no ASN (PO_MAPPED_FLAG stays N)</t>
         </is>
       </c>
     </row>
@@ -11188,16 +11176,12 @@
         </is>
       </c>
       <c r="M31" s="49" t="n"/>
-      <c r="N31" s="49" t="inlineStr">
-        <is>
-          <t>Source status 7</t>
-        </is>
-      </c>
+      <c r="N31" s="49" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="45" t="inlineStr">
         <is>
-          <t>4. 17-Oct CO-14103 → ASN0002 (PO-DMY-09012)</t>
+          <t>4. 17-Oct CO-14103 → ASN0002 with the rest of PO-DMY-09011 (older PO_DT)</t>
         </is>
       </c>
       <c r="B33" s="46" t="n"/>
@@ -11345,12 +11329,12 @@
       </c>
       <c r="J36" s="49" t="inlineStr">
         <is>
-          <t>PO-DMY-09012</t>
+          <t>PO-DMY-09011</t>
         </is>
       </c>
       <c r="K36" s="49" t="inlineStr">
         <is>
-          <t>MF-DMY-09012</t>
+          <t>MF-DMY-09011</t>
         </is>
       </c>
       <c r="L36" s="49" t="inlineStr">
@@ -11368,327 +11352,437 @@
           <t>C-0002-01</t>
         </is>
       </c>
-      <c r="O36" s="49" t="inlineStr"/>
+      <c r="O36" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09012 stays open</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="A38" s="45" t="inlineStr">
+        <is>
+          <t>5. 18-Oct XD08: order date 17-Oct, 4 destinations, 30 pcs; PO-DMY-09013 only 18 (abnormal)</t>
+        </is>
+      </c>
+      <c r="B38" s="46" t="n"/>
+      <c r="C38" s="46" t="n"/>
+      <c r="D38" s="46" t="n"/>
+      <c r="E38" s="46" t="n"/>
+      <c r="F38" s="46" t="n"/>
+      <c r="G38" s="46" t="n"/>
+      <c r="H38" s="46" t="n"/>
+      <c r="I38" s="46" t="n"/>
+      <c r="J38" s="46" t="n"/>
+      <c r="K38" s="46" t="n"/>
+      <c r="L38" s="46" t="n"/>
+      <c r="M38" s="46" t="n"/>
+      <c r="N38" s="46" t="n"/>
+      <c r="O38" s="46" t="n"/>
+      <c r="P38" s="46" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
         </is>
       </c>
-      <c r="D38" s="47" t="inlineStr">
+      <c r="D39" s="47" t="inlineStr">
         <is>
           <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B39" s="42" t="inlineStr">
+      <c r="B40" s="42" t="inlineStr">
         <is>
           <t>CUSTOMER_CD</t>
         </is>
       </c>
-      <c r="C39" s="42" t="inlineStr">
+      <c r="C40" s="42" t="inlineStr">
         <is>
           <t>CUSTOMER_ORDER_NO</t>
         </is>
       </c>
-      <c r="D39" s="42" t="inlineStr">
+      <c r="D40" s="42" t="inlineStr">
         <is>
           <t>ORDER_DT</t>
         </is>
       </c>
-      <c r="E39" s="42" t="inlineStr">
+      <c r="E40" s="42" t="inlineStr">
         <is>
           <t>DESTINATION_CD</t>
         </is>
       </c>
-      <c r="F39" s="42" t="inlineStr">
+      <c r="F40" s="42" t="inlineStr">
         <is>
           <t>DETAILED_ITEM_NO</t>
         </is>
       </c>
-      <c r="G39" s="42" t="inlineStr">
+      <c r="G40" s="42" t="inlineStr">
         <is>
           <t>SERIAL_NO</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>SHIPPING_PART_NO</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>ORDER_STATUS_QTY</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>ORDER_STATUS</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>HOLD_FLAG</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>PO_MAPPED_FLAG</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>UPD_STATUS</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="57" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="57" t="inlineStr">
         <is>
           <t>UPD</t>
         </is>
       </c>
-      <c r="B40" s="58" t="inlineStr">
+      <c r="B41" s="58" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="C40" s="58" t="inlineStr">
+      <c r="C41" s="58" t="inlineStr">
         <is>
           <t>CO-14103</t>
         </is>
       </c>
-      <c r="D40" s="58" t="inlineStr">
+      <c r="D41" s="58" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="E40" s="58" t="inlineStr">
+      <c r="E41" s="58" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="F40" s="58" t="inlineStr">
+      <c r="F41" s="58" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="G40" s="58" t="inlineStr">
+      <c r="G41" s="58" t="inlineStr">
         <is>
           <t>0000001</t>
         </is>
       </c>
-      <c r="H40" s="58" t="inlineStr">
+      <c r="H41" s="58" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="I40" s="59" t="n">
+      <c r="I41" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="58" t="inlineStr">
+      <c r="J41" s="58" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K40" s="58" t="inlineStr">
+      <c r="K41" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L40" s="60" t="inlineStr">
+      <c r="L41" s="58" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M40" s="58" t="n"/>
-      <c r="N40" s="58" t="inlineStr"/>
+      <c r="M41" s="60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N41" s="58" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="45" t="inlineStr">
-        <is>
-          <t>5. 18-Oct XD08: CO-14103 → 6; CO-14104 … CO-14108 new (rows in scan order)</t>
-        </is>
-      </c>
-      <c r="B42" s="46" t="n"/>
-      <c r="C42" s="46" t="n"/>
-      <c r="D42" s="46" t="n"/>
-      <c r="E42" s="46" t="n"/>
-      <c r="F42" s="46" t="n"/>
-      <c r="G42" s="46" t="n"/>
-      <c r="H42" s="46" t="n"/>
-      <c r="I42" s="46" t="n"/>
-      <c r="J42" s="46" t="n"/>
-      <c r="K42" s="46" t="n"/>
-      <c r="L42" s="46" t="n"/>
-      <c r="M42" s="46" t="n"/>
-      <c r="N42" s="46" t="n"/>
-      <c r="O42" s="46" t="n"/>
-      <c r="P42" s="46" t="n"/>
+      <c r="A42" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B42" s="49" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C42" s="49" t="inlineStr">
+        <is>
+          <t>CO-14105</t>
+        </is>
+      </c>
+      <c r="D42" s="49" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E42" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F42" s="49" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G42" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H42" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I42" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J42" s="49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K42" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L42" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M42" s="49" t="n"/>
+      <c r="N42" s="49" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
-        </is>
-      </c>
-      <c r="D43" s="47" t="inlineStr">
-        <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B44" s="42" t="inlineStr">
-        <is>
-          <t>CUSTOMER_CD</t>
-        </is>
-      </c>
-      <c r="C44" s="42" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="D44" s="42" t="inlineStr">
-        <is>
-          <t>ORDER_DT</t>
-        </is>
-      </c>
-      <c r="E44" s="42" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="F44" s="42" t="inlineStr">
-        <is>
-          <t>DETAILED_ITEM_NO</t>
-        </is>
-      </c>
-      <c r="G44" s="42" t="inlineStr">
-        <is>
-          <t>SERIAL_NO</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>SHIPPING_PART_NO</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS_QTY</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>HOLD_FLAG</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>PO_MAPPED_FLAG</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>UPD_STATUS</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
+      <c r="A43" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B43" s="49" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C43" s="49" t="inlineStr">
+        <is>
+          <t>CO-14106</t>
+        </is>
+      </c>
+      <c r="D43" s="49" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E43" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F43" s="49" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G43" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H43" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I43" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" s="49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K43" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L43" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M43" s="49" t="n"/>
+      <c r="N43" s="49" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B44" s="49" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C44" s="49" t="inlineStr">
+        <is>
+          <t>CO-14107</t>
+        </is>
+      </c>
+      <c r="D44" s="49" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E44" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F44" s="49" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G44" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H44" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I44" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K44" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L44" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M44" s="49" t="n"/>
+      <c r="N44" s="49" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B45" s="58" t="inlineStr">
+      <c r="A45" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B45" s="49" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="C45" s="58" t="inlineStr">
-        <is>
-          <t>CO-14103</t>
-        </is>
-      </c>
-      <c r="D45" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E45" s="58" t="inlineStr">
+      <c r="C45" s="49" t="inlineStr">
+        <is>
+          <t>CO-14104</t>
+        </is>
+      </c>
+      <c r="D45" s="49" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E45" s="49" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="F45" s="58" t="inlineStr">
+      <c r="F45" s="49" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="G45" s="58" t="inlineStr">
+      <c r="G45" s="49" t="inlineStr">
         <is>
           <t>0000001</t>
         </is>
       </c>
-      <c r="H45" s="58" t="inlineStr">
+      <c r="H45" s="49" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="I45" s="59" t="n">
+      <c r="I45" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="J45" s="58" t="inlineStr">
+      <c r="J45" s="49" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K45" s="58" t="inlineStr">
+      <c r="K45" s="49" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L45" s="58" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M45" s="60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N45" s="58" t="inlineStr">
-        <is>
-          <t>Received</t>
+      <c r="L45" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M45" s="49" t="n"/>
+      <c r="N45" s="49" t="inlineStr">
+        <is>
+          <t>Middle row</t>
         </is>
       </c>
     </row>
@@ -11700,12 +11794,12 @@
       </c>
       <c r="B46" s="49" t="inlineStr">
         <is>
-          <t>9715300</t>
+          <t>9811100</t>
         </is>
       </c>
       <c r="C46" s="49" t="inlineStr">
         <is>
-          <t>CO-14105</t>
+          <t>CO-14109</t>
         </is>
       </c>
       <c r="D46" s="49" t="inlineStr">
@@ -11715,7 +11809,7 @@
       </c>
       <c r="E46" s="49" t="inlineStr">
         <is>
-          <t>9715310</t>
+          <t>9811110</t>
         </is>
       </c>
       <c r="F46" s="49" t="inlineStr">
@@ -11762,12 +11856,12 @@
       </c>
       <c r="B47" s="49" t="inlineStr">
         <is>
-          <t>9715300</t>
+          <t>982200</t>
         </is>
       </c>
       <c r="C47" s="49" t="inlineStr">
         <is>
-          <t>CO-14106</t>
+          <t>CO-14110</t>
         </is>
       </c>
       <c r="D47" s="49" t="inlineStr">
@@ -11777,7 +11871,7 @@
       </c>
       <c r="E47" s="49" t="inlineStr">
         <is>
-          <t>9715310</t>
+          <t>982220</t>
         </is>
       </c>
       <c r="F47" s="49" t="inlineStr">
@@ -11796,7 +11890,7 @@
         </is>
       </c>
       <c r="I47" s="53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J47" s="49" t="inlineStr">
         <is>
@@ -11816,315 +11910,317 @@
       <c r="M47" s="49" t="n"/>
       <c r="N47" s="49" t="inlineStr"/>
     </row>
-    <row r="48">
-      <c r="A48" s="48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B48" s="49" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="45" t="inlineStr">
+        <is>
+          <t>6. 18-Oct [Search] → XD09: 24 of 30 pcs with PO, case 5 Not Ready</t>
+        </is>
+      </c>
+      <c r="B49" s="46" t="n"/>
+      <c r="C49" s="46" t="n"/>
+      <c r="D49" s="46" t="n"/>
+      <c r="E49" s="46" t="n"/>
+      <c r="F49" s="46" t="n"/>
+      <c r="G49" s="46" t="n"/>
+      <c r="H49" s="46" t="n"/>
+      <c r="I49" s="46" t="n"/>
+      <c r="J49" s="46" t="n"/>
+      <c r="K49" s="46" t="n"/>
+      <c r="L49" s="46" t="n"/>
+      <c r="M49" s="46" t="n"/>
+      <c r="N49" s="46" t="n"/>
+      <c r="O49" s="46" t="n"/>
+      <c r="P49" s="46" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="35" t="inlineStr">
+        <is>
+          <t>#TEMP_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D50" s="47" t="inlineStr">
+        <is>
+          <t>Temporary (session)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>SORT_SEQ</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>OPEN_ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>ASSIGNED_QTY</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>CUM_DEST_QTY</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>SEQ_QTY</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
+        <is>
+          <t>CUT_FLAG</t>
+        </is>
+      </c>
+      <c r="N51" s="9" t="inlineStr">
+        <is>
+          <t>GROUP_SEQ</t>
+        </is>
+      </c>
+      <c r="O51" s="9" t="inlineStr">
+        <is>
+          <t>CROSSDOCK_STATUS</t>
+        </is>
+      </c>
+      <c r="P51" s="9" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B52" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="64" t="inlineStr">
         <is>
           <t>9715300</t>
         </is>
       </c>
-      <c r="C48" s="49" t="inlineStr">
+      <c r="D52" s="64" t="inlineStr">
+        <is>
+          <t>CO-14105</t>
+        </is>
+      </c>
+      <c r="E52" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F52" s="64" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="G52" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" s="64" t="inlineStr">
+        <is>
+          <t>PO-DMY-09012</t>
+        </is>
+      </c>
+      <c r="I52" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J52" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L52" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M52" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N52" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P52" s="64" t="inlineStr">
+        <is>
+          <t>Cases 1-4 ticked → ASN0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B53" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D53" s="64" t="inlineStr">
+        <is>
+          <t>CO-14106</t>
+        </is>
+      </c>
+      <c r="E53" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F53" s="64" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="G53" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="64" t="inlineStr">
+        <is>
+          <t>PO-DMY-09013</t>
+        </is>
+      </c>
+      <c r="I53" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="L53" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="M53" s="64" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N53" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="O53" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P53" s="64" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B54" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D54" s="64" t="inlineStr">
         <is>
           <t>CO-14107</t>
         </is>
       </c>
-      <c r="D48" s="49" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E48" s="49" t="inlineStr">
+      <c r="E54" s="64" t="inlineStr">
         <is>
           <t>9715310</t>
         </is>
       </c>
-      <c r="F48" s="49" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G48" s="49" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H48" s="49" t="inlineStr">
+      <c r="F54" s="64" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="I48" s="53" t="n">
+      <c r="G54" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="J48" s="49" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K48" s="49" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L48" s="49" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M48" s="49" t="n"/>
-      <c r="N48" s="49" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B49" s="49" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="C49" s="49" t="inlineStr">
-        <is>
-          <t>CO-14104</t>
-        </is>
-      </c>
-      <c r="D49" s="49" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E49" s="49" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F49" s="49" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G49" s="49" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H49" s="49" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I49" s="53" t="n">
+      <c r="H54" s="64" t="inlineStr">
+        <is>
+          <t>PO-DMY-09013</t>
+        </is>
+      </c>
+      <c r="I54" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K54" s="63" t="n">
+        <v>12</v>
+      </c>
+      <c r="L54" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="J49" s="49" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K49" s="49" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L49" s="49" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M49" s="49" t="n"/>
-      <c r="N49" s="49" t="inlineStr">
-        <is>
-          <t>Customer code 9722D10 after 9715300</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B50" s="49" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="C50" s="49" t="inlineStr">
-        <is>
-          <t>CO-14108</t>
-        </is>
-      </c>
-      <c r="D50" s="49" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="E50" s="49" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F50" s="49" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G50" s="49" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H50" s="49" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I50" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="J50" s="49" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K50" s="49" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L50" s="49" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M50" s="49" t="n"/>
-      <c r="N50" s="49" t="inlineStr">
-        <is>
-          <t>Order date 18-Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="45" t="inlineStr">
-        <is>
-          <t>6. 18-Oct [Search] → XD09 (unit 17-Oct: 3 cases Ready; unit 18-Oct: no PO)</t>
-        </is>
-      </c>
-      <c r="B52" s="46" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
-      <c r="E52" s="46" t="n"/>
-      <c r="F52" s="46" t="n"/>
-      <c r="G52" s="46" t="n"/>
-      <c r="H52" s="46" t="n"/>
-      <c r="I52" s="46" t="n"/>
-      <c r="J52" s="46" t="n"/>
-      <c r="K52" s="46" t="n"/>
-      <c r="L52" s="46" t="n"/>
-      <c r="M52" s="46" t="n"/>
-      <c r="N52" s="46" t="n"/>
-      <c r="O52" s="46" t="n"/>
-      <c r="P52" s="46" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="35" t="inlineStr">
-        <is>
-          <t>#TEMP_INSTRUCTION</t>
-        </is>
-      </c>
-      <c r="D53" s="47" t="inlineStr">
-        <is>
-          <t>Temporary (session)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>SORT_SEQ</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>CUSTOMER_CD</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>OPEN_ORDER_QTY</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>PO_NO</t>
-        </is>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>ASSIGNED_QTY</t>
-        </is>
-      </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t>CASE_SEQ</t>
-        </is>
-      </c>
-      <c r="K54" s="9" t="inlineStr">
-        <is>
-          <t>CUM_DEST_QTY</t>
-        </is>
-      </c>
-      <c r="L54" s="9" t="inlineStr">
-        <is>
-          <t>SEQ_QTY</t>
-        </is>
-      </c>
-      <c r="M54" s="9" t="inlineStr">
-        <is>
-          <t>CUT_FLAG</t>
-        </is>
-      </c>
-      <c r="N54" s="9" t="inlineStr">
-        <is>
-          <t>GROUP_SEQ</t>
-        </is>
-      </c>
-      <c r="O54" s="9" t="inlineStr">
-        <is>
-          <t>CROSSDOCK_STATUS</t>
-        </is>
-      </c>
-      <c r="P54" s="9" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
+      <c r="M54" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N54" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="O54" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P54" s="64" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="62" t="inlineStr">
@@ -12133,21 +12229,21 @@
         </is>
       </c>
       <c r="B55" s="63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C55" s="64" t="inlineStr">
         <is>
-          <t>9715300</t>
+          <t>9722D10</t>
         </is>
       </c>
       <c r="D55" s="64" t="inlineStr">
         <is>
-          <t>CO-14105</t>
+          <t>CO-14104</t>
         </is>
       </c>
       <c r="E55" s="64" t="inlineStr">
         <is>
-          <t>9715310</t>
+          <t>9722D10</t>
         </is>
       </c>
       <c r="F55" s="64" t="inlineStr">
@@ -12167,7 +12263,7 @@
         <v>6</v>
       </c>
       <c r="J55" s="63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K55" s="63" t="n">
         <v>6</v>
@@ -12181,7 +12277,7 @@
         </is>
       </c>
       <c r="N55" s="63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O55" s="49" t="inlineStr">
         <is>
@@ -12190,7 +12286,7 @@
       </c>
       <c r="P55" s="64" t="inlineStr">
         <is>
-          <t>Cases 1-3 ticked → ASN0003</t>
+          <t>Middle row</t>
         </is>
       </c>
     </row>
@@ -12201,21 +12297,21 @@
         </is>
       </c>
       <c r="B56" s="63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C56" s="64" t="inlineStr">
         <is>
-          <t>9715300</t>
+          <t>9811100</t>
         </is>
       </c>
       <c r="D56" s="64" t="inlineStr">
         <is>
-          <t>CO-14106</t>
+          <t>CO-14109</t>
         </is>
       </c>
       <c r="E56" s="64" t="inlineStr">
         <is>
-          <t>9715310</t>
+          <t>9811110</t>
         </is>
       </c>
       <c r="F56" s="64" t="inlineStr">
@@ -12224,32 +12320,32 @@
         </is>
       </c>
       <c r="G56" s="63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H56" s="64" t="inlineStr">
         <is>
-          <t>PO-DMY-09014</t>
+          <t>PO-DMY-09013</t>
         </is>
       </c>
       <c r="I56" s="63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J56" s="63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K56" s="63" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L56" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="M56" s="64" t="inlineStr">
-        <is>
-          <t>N</t>
+        <v>6</v>
+      </c>
+      <c r="M56" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="N56" s="63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O56" s="49" t="inlineStr">
         <is>
@@ -12265,21 +12361,21 @@
         </is>
       </c>
       <c r="B57" s="63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C57" s="64" t="inlineStr">
         <is>
-          <t>9715300</t>
+          <t>982200</t>
         </is>
       </c>
       <c r="D57" s="64" t="inlineStr">
         <is>
-          <t>CO-14107</t>
+          <t>CO-14110</t>
         </is>
       </c>
       <c r="E57" s="64" t="inlineStr">
         <is>
-          <t>9715310</t>
+          <t>982220</t>
         </is>
       </c>
       <c r="F57" s="64" t="inlineStr">
@@ -12288,21 +12384,17 @@
         </is>
       </c>
       <c r="G57" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="64" t="inlineStr">
-        <is>
-          <t>PO-DMY-09014</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H57" s="64" t="n"/>
       <c r="I57" s="63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J57" s="63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K57" s="63" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L57" s="63" t="n">
         <v>6</v>
@@ -12313,253 +12405,259 @@
         </is>
       </c>
       <c r="N57" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="O57" s="66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P57" s="64" t="inlineStr">
+        <is>
+          <t>Not Ready (PO short)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="45" t="inlineStr">
+        <is>
+          <t>7. 18-Oct ASN0003 = cases 1-4</t>
+        </is>
+      </c>
+      <c r="B59" s="46" t="n"/>
+      <c r="C59" s="46" t="n"/>
+      <c r="D59" s="46" t="n"/>
+      <c r="E59" s="46" t="n"/>
+      <c r="F59" s="46" t="n"/>
+      <c r="G59" s="46" t="n"/>
+      <c r="H59" s="46" t="n"/>
+      <c r="I59" s="46" t="n"/>
+      <c r="J59" s="46" t="n"/>
+      <c r="K59" s="46" t="n"/>
+      <c r="L59" s="46" t="n"/>
+      <c r="M59" s="46" t="n"/>
+      <c r="N59" s="46" t="n"/>
+      <c r="O59" s="46" t="n"/>
+      <c r="P59" s="46" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D60" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B61" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>LINE_SEQ</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B62" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F62" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G62" s="49" t="inlineStr">
+        <is>
+          <t>CO-14105</t>
+        </is>
+      </c>
+      <c r="H62" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I62" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J62" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09012</t>
+        </is>
+      </c>
+      <c r="K62" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09012</t>
+        </is>
+      </c>
+      <c r="L62" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M62" s="49" t="inlineStr">
+        <is>
+          <t>ASN0003</t>
+        </is>
+      </c>
+      <c r="N62" s="49" t="inlineStr">
+        <is>
+          <t>C-0003-01</t>
+        </is>
+      </c>
+      <c r="O62" s="49" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B63" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="O57" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P57" s="64" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B58" s="63" t="n">
-        <v>4</v>
-      </c>
-      <c r="C58" s="64" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="D58" s="64" t="inlineStr">
-        <is>
-          <t>CO-14104</t>
-        </is>
-      </c>
-      <c r="E58" s="64" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F58" s="64" t="inlineStr">
+      <c r="D63" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="49" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="G58" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="H58" s="64" t="inlineStr">
-        <is>
-          <t>PO-DMY-09014</t>
-        </is>
-      </c>
-      <c r="I58" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="J58" s="63" t="n">
+      <c r="F63" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G63" s="49" t="inlineStr">
+        <is>
+          <t>CO-14106</t>
+        </is>
+      </c>
+      <c r="H63" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I63" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="K58" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="L58" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="M58" s="65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N58" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="O58" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P58" s="64" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="62" t="inlineStr">
-        <is>
-          <t>TEMP</t>
-        </is>
-      </c>
-      <c r="B59" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="64" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="D59" s="64" t="inlineStr">
-        <is>
-          <t>CO-14108</t>
-        </is>
-      </c>
-      <c r="E59" s="64" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F59" s="64" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="G59" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="H59" s="64" t="n"/>
-      <c r="I59" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="J59" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K59" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="L59" s="63" t="n">
-        <v>6</v>
-      </c>
-      <c r="M59" s="65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="N59" s="63" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" s="66" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="P59" s="64" t="inlineStr">
-        <is>
-          <t>Not Ready (no PO left)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="45" t="inlineStr">
-        <is>
-          <t>7. 18-Oct ASN0003 = cases 1-3 (whole order date 17-Oct)</t>
-        </is>
-      </c>
-      <c r="B61" s="46" t="n"/>
-      <c r="C61" s="46" t="n"/>
-      <c r="D61" s="46" t="n"/>
-      <c r="E61" s="46" t="n"/>
-      <c r="F61" s="46" t="n"/>
-      <c r="G61" s="46" t="n"/>
-      <c r="H61" s="46" t="n"/>
-      <c r="I61" s="46" t="n"/>
-      <c r="J61" s="46" t="n"/>
-      <c r="K61" s="46" t="n"/>
-      <c r="L61" s="46" t="n"/>
-      <c r="M61" s="46" t="n"/>
-      <c r="N61" s="46" t="n"/>
-      <c r="O61" s="46" t="n"/>
-      <c r="P61" s="46" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_INSTRUCTION</t>
-        </is>
-      </c>
-      <c r="D62" s="47" t="inlineStr">
-        <is>
-          <t>New table (Crossdock)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B63" s="42" t="inlineStr">
-        <is>
-          <t>INSTRUCTION_ID</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>CASE_SEQ</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>LINE_SEQ</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>SERIAL_NO</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>QTY</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>PO_NO</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_NO</t>
-        </is>
-      </c>
-      <c r="L63" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_ITEM</t>
-        </is>
-      </c>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>ASN_NO</t>
-        </is>
-      </c>
-      <c r="N63" s="3" t="inlineStr">
-        <is>
-          <t>CASE_NO</t>
-        </is>
-      </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
+      <c r="J63" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09013</t>
+        </is>
+      </c>
+      <c r="K63" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09013</t>
+        </is>
+      </c>
+      <c r="L63" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M63" s="49" t="inlineStr">
+        <is>
+          <t>ASN0003</t>
+        </is>
+      </c>
+      <c r="N63" s="49" t="inlineStr">
+        <is>
+          <t>C-0003-02</t>
+        </is>
+      </c>
+      <c r="O63" s="49" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="48" t="inlineStr">
@@ -12568,37 +12666,37 @@
         </is>
       </c>
       <c r="B64" s="53" t="n">
+        <v>5</v>
+      </c>
+      <c r="C64" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F64" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G64" s="49" t="inlineStr">
+        <is>
+          <t>CO-14107</t>
+        </is>
+      </c>
+      <c r="H64" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I64" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="C64" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="49" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="F64" s="49" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="G64" s="49" t="inlineStr">
-        <is>
-          <t>CO-14105</t>
-        </is>
-      </c>
-      <c r="H64" s="49" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="I64" s="53" t="n">
-        <v>6</v>
-      </c>
       <c r="J64" s="49" t="inlineStr">
         <is>
           <t>PO-DMY-09013</t>
@@ -12621,7 +12719,7 @@
       </c>
       <c r="N64" s="49" t="inlineStr">
         <is>
-          <t>C-0003-01</t>
+          <t>C-0003-02</t>
         </is>
       </c>
       <c r="O64" s="49" t="inlineStr"/>
@@ -12633,10 +12731,10 @@
         </is>
       </c>
       <c r="B65" s="53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C65" s="53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65" s="53" t="n">
         <v>1</v>
@@ -12648,12 +12746,12 @@
       </c>
       <c r="F65" s="49" t="inlineStr">
         <is>
-          <t>9715310</t>
+          <t>9722D10</t>
         </is>
       </c>
       <c r="G65" s="49" t="inlineStr">
         <is>
-          <t>CO-14106</t>
+          <t>CO-14104</t>
         </is>
       </c>
       <c r="H65" s="49" t="inlineStr">
@@ -12662,16 +12760,16 @@
         </is>
       </c>
       <c r="I65" s="53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J65" s="49" t="inlineStr">
         <is>
-          <t>PO-DMY-09014</t>
+          <t>PO-DMY-09013</t>
         </is>
       </c>
       <c r="K65" s="49" t="inlineStr">
         <is>
-          <t>MF-DMY-09014</t>
+          <t>MF-DMY-09013</t>
         </is>
       </c>
       <c r="L65" s="49" t="inlineStr">
@@ -12686,7 +12784,7 @@
       </c>
       <c r="N65" s="49" t="inlineStr">
         <is>
-          <t>C-0003-02</t>
+          <t>C-0003-03</t>
         </is>
       </c>
       <c r="O65" s="49" t="inlineStr"/>
@@ -12698,13 +12796,13 @@
         </is>
       </c>
       <c r="B66" s="53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C66" s="53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D66" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="49" t="inlineStr">
         <is>
@@ -12713,12 +12811,12 @@
       </c>
       <c r="F66" s="49" t="inlineStr">
         <is>
-          <t>9715310</t>
+          <t>9811110</t>
         </is>
       </c>
       <c r="G66" s="49" t="inlineStr">
         <is>
-          <t>CO-14107</t>
+          <t>CO-14109</t>
         </is>
       </c>
       <c r="H66" s="49" t="inlineStr">
@@ -12727,16 +12825,16 @@
         </is>
       </c>
       <c r="I66" s="53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J66" s="49" t="inlineStr">
         <is>
-          <t>PO-DMY-09014</t>
+          <t>PO-DMY-09013</t>
         </is>
       </c>
       <c r="K66" s="49" t="inlineStr">
         <is>
-          <t>MF-DMY-09014</t>
+          <t>MF-DMY-09013</t>
         </is>
       </c>
       <c r="L66" s="49" t="inlineStr">
@@ -12751,773 +12849,651 @@
       </c>
       <c r="N66" s="49" t="inlineStr">
         <is>
-          <t>C-0003-02</t>
+          <t>C-0003-04</t>
         </is>
       </c>
       <c r="O66" s="49" t="inlineStr"/>
     </row>
-    <row r="67">
-      <c r="A67" s="48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B67" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="C67" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="D67" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="49" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="F67" s="49" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="G67" s="49" t="inlineStr">
-        <is>
-          <t>CO-14104</t>
-        </is>
-      </c>
-      <c r="H67" s="49" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="I67" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="J67" s="49" t="inlineStr">
-        <is>
-          <t>PO-DMY-09014</t>
-        </is>
-      </c>
-      <c r="K67" s="49" t="inlineStr">
-        <is>
-          <t>MF-DMY-09014</t>
-        </is>
-      </c>
-      <c r="L67" s="49" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="M67" s="49" t="inlineStr">
-        <is>
-          <t>ASN0003</t>
-        </is>
-      </c>
-      <c r="N67" s="49" t="inlineStr">
-        <is>
-          <t>C-0003-03</t>
-        </is>
-      </c>
-      <c r="O67" s="49" t="inlineStr"/>
+    <row r="68">
+      <c r="A68" s="45" t="inlineStr">
+        <is>
+          <t>8. 19-Oct XD08: ASN0003 received, CO-14104 → 2 (middle row, in case 3); split PO-DMY-09014 (PO_DT 19-Oct, 12)</t>
+        </is>
+      </c>
+      <c r="B68" s="46" t="n"/>
+      <c r="C68" s="46" t="n"/>
+      <c r="D68" s="46" t="n"/>
+      <c r="E68" s="46" t="n"/>
+      <c r="F68" s="46" t="n"/>
+      <c r="G68" s="46" t="n"/>
+      <c r="H68" s="46" t="n"/>
+      <c r="I68" s="46" t="n"/>
+      <c r="J68" s="46" t="n"/>
+      <c r="K68" s="46" t="n"/>
+      <c r="L68" s="46" t="n"/>
+      <c r="M68" s="46" t="n"/>
+      <c r="N68" s="46" t="n"/>
+      <c r="O68" s="46" t="n"/>
+      <c r="P68" s="46" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="35" t="inlineStr">
         <is>
-          <t>TB_R_PRA_DAILY_ORDER_MAPPED</t>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
         </is>
       </c>
       <c r="D69" s="47" t="inlineStr">
         <is>
-          <t>New table (Crossdock)</t>
+          <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
     <row r="70" ht="26" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
       <c r="B70" s="42" t="inlineStr">
         <is>
-          <t>PO_NO</t>
+          <t>CUSTOMER_CD</t>
         </is>
       </c>
       <c r="C70" s="42" t="inlineStr">
         <is>
-          <t>MANIFEST_NO</t>
+          <t>CUSTOMER_ORDER_NO</t>
         </is>
       </c>
       <c r="D70" s="42" t="inlineStr">
         <is>
-          <t>MANIFEST_ITEM</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>ORDER_QTY</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>MAPPED_QTY</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E70" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F70" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G70" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>UPD_STATUS</t>
+        </is>
+      </c>
+      <c r="N70" s="5" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B71" s="49" t="inlineStr">
-        <is>
-          <t>PO-DMY-09013</t>
-        </is>
-      </c>
-      <c r="C71" s="49" t="inlineStr">
-        <is>
-          <t>MF-DMY-09013</t>
-        </is>
-      </c>
-      <c r="D71" s="49" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="E71" s="49" t="inlineStr">
+      <c r="A71" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B71" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="C71" s="58" t="inlineStr">
+        <is>
+          <t>CO-14104</t>
+        </is>
+      </c>
+      <c r="D71" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E71" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F71" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G71" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H71" s="58" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="F71" s="53" t="n">
+      <c r="I71" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="G71" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="H71" s="49" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B72" s="49" t="inlineStr">
-        <is>
-          <t>PO-DMY-09014</t>
-        </is>
-      </c>
-      <c r="C72" s="49" t="inlineStr">
-        <is>
-          <t>MF-DMY-09014</t>
-        </is>
-      </c>
-      <c r="D72" s="49" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="E72" s="49" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="F72" s="53" t="n">
-        <v>12</v>
-      </c>
-      <c r="G72" s="53" t="n">
-        <v>12</v>
-      </c>
-      <c r="H72" s="49" t="inlineStr"/>
+      <c r="J71" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K71" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L71" s="58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M71" s="60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N71" s="58" t="inlineStr">
+        <is>
+          <t>Cancel after ASN: LOG5, listed in XD11 (waiting for a candidate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="45" t="inlineStr">
+        <is>
+          <t>9. 19-Oct CO-14110 → ASN0004 with the split PO</t>
+        </is>
+      </c>
+      <c r="B73" s="46" t="n"/>
+      <c r="C73" s="46" t="n"/>
+      <c r="D73" s="46" t="n"/>
+      <c r="E73" s="46" t="n"/>
+      <c r="F73" s="46" t="n"/>
+      <c r="G73" s="46" t="n"/>
+      <c r="H73" s="46" t="n"/>
+      <c r="I73" s="46" t="n"/>
+      <c r="J73" s="46" t="n"/>
+      <c r="K73" s="46" t="n"/>
+      <c r="L73" s="46" t="n"/>
+      <c r="M73" s="46" t="n"/>
+      <c r="N73" s="46" t="n"/>
+      <c r="O73" s="46" t="n"/>
+      <c r="P73" s="46" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="35" t="inlineStr">
         <is>
+          <t>TB_R_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D74" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="26" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B75" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>LINE_SEQ</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B76" s="53" t="n">
+        <v>8</v>
+      </c>
+      <c r="C76" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F76" s="49" t="inlineStr">
+        <is>
+          <t>982220</t>
+        </is>
+      </c>
+      <c r="G76" s="49" t="inlineStr">
+        <is>
+          <t>CO-14110</t>
+        </is>
+      </c>
+      <c r="H76" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I76" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J76" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09014</t>
+        </is>
+      </c>
+      <c r="K76" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09014</t>
+        </is>
+      </c>
+      <c r="L76" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M76" s="49" t="inlineStr">
+        <is>
+          <t>ASN0004</t>
+        </is>
+      </c>
+      <c r="N76" s="49" t="inlineStr">
+        <is>
+          <t>C-0004-01</t>
+        </is>
+      </c>
+      <c r="O76" s="49" t="inlineStr">
+        <is>
+          <t>6 pcs of the split PO stay open</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="45" t="inlineStr">
+        <is>
+          <t>10. 20-Oct XD08: CO-14111 new (order date 19-Oct, PO-DMY-09015); 21-Oct → 6 (pcs of case 3 allocated by G-System)</t>
+        </is>
+      </c>
+      <c r="B78" s="46" t="n"/>
+      <c r="C78" s="46" t="n"/>
+      <c r="D78" s="46" t="n"/>
+      <c r="E78" s="46" t="n"/>
+      <c r="F78" s="46" t="n"/>
+      <c r="G78" s="46" t="n"/>
+      <c r="H78" s="46" t="n"/>
+      <c r="I78" s="46" t="n"/>
+      <c r="J78" s="46" t="n"/>
+      <c r="K78" s="46" t="n"/>
+      <c r="L78" s="46" t="n"/>
+      <c r="M78" s="46" t="n"/>
+      <c r="N78" s="46" t="n"/>
+      <c r="O78" s="46" t="n"/>
+      <c r="P78" s="46" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="35" t="inlineStr">
+        <is>
           <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
         </is>
       </c>
-      <c r="D74" s="47" t="inlineStr">
+      <c r="D79" s="47" t="inlineStr">
         <is>
           <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="26" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
+    <row r="80" ht="26" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B75" s="42" t="inlineStr">
+      <c r="B80" s="42" t="inlineStr">
         <is>
           <t>CUSTOMER_CD</t>
         </is>
       </c>
-      <c r="C75" s="42" t="inlineStr">
+      <c r="C80" s="42" t="inlineStr">
         <is>
           <t>CUSTOMER_ORDER_NO</t>
         </is>
       </c>
-      <c r="D75" s="42" t="inlineStr">
+      <c r="D80" s="42" t="inlineStr">
         <is>
           <t>ORDER_DT</t>
         </is>
       </c>
-      <c r="E75" s="42" t="inlineStr">
+      <c r="E80" s="42" t="inlineStr">
         <is>
           <t>DESTINATION_CD</t>
         </is>
       </c>
-      <c r="F75" s="42" t="inlineStr">
+      <c r="F80" s="42" t="inlineStr">
         <is>
           <t>DETAILED_ITEM_NO</t>
         </is>
       </c>
-      <c r="G75" s="42" t="inlineStr">
+      <c r="G80" s="42" t="inlineStr">
         <is>
           <t>SERIAL_NO</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H80" s="5" t="inlineStr">
         <is>
           <t>SHIPPING_PART_NO</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>ORDER_STATUS_QTY</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>ORDER_STATUS</t>
         </is>
       </c>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr">
         <is>
           <t>HOLD_FLAG</t>
         </is>
       </c>
-      <c r="L75" s="5" t="inlineStr">
+      <c r="L80" s="5" t="inlineStr">
         <is>
           <t>PO_MAPPED_FLAG</t>
         </is>
       </c>
-      <c r="M75" s="5" t="inlineStr">
+      <c r="M80" s="5" t="inlineStr">
         <is>
           <t>UPD_STATUS</t>
         </is>
       </c>
-      <c r="N75" s="5" t="inlineStr">
+      <c r="N80" s="5" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="57" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="57" t="inlineStr">
         <is>
           <t>UPD</t>
         </is>
       </c>
-      <c r="B76" s="58" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="C76" s="58" t="inlineStr">
-        <is>
-          <t>CO-14105</t>
-        </is>
-      </c>
-      <c r="D76" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E76" s="58" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F76" s="58" t="inlineStr">
+      <c r="B81" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="C81" s="58" t="inlineStr">
+        <is>
+          <t>CO-14111</t>
+        </is>
+      </c>
+      <c r="D81" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E81" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F81" s="58" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="G76" s="58" t="inlineStr">
+      <c r="G81" s="58" t="inlineStr">
         <is>
           <t>0000001</t>
         </is>
       </c>
-      <c r="H76" s="58" t="inlineStr">
+      <c r="H81" s="58" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="I76" s="59" t="n">
+      <c r="I81" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="J76" s="58" t="inlineStr">
+      <c r="J81" s="58" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K76" s="58" t="inlineStr">
+      <c r="K81" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L76" s="60" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M76" s="58" t="n"/>
-      <c r="N76" s="58" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B77" s="58" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="C77" s="58" t="inlineStr">
-        <is>
-          <t>CO-14106</t>
-        </is>
-      </c>
-      <c r="D77" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E77" s="58" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F77" s="58" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G77" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H77" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I77" s="59" t="n">
-        <v>3</v>
-      </c>
-      <c r="J77" s="58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K77" s="58" t="inlineStr">
+      <c r="L81" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L77" s="60" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M77" s="58" t="n"/>
-      <c r="N77" s="58" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B78" s="58" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="C78" s="58" t="inlineStr">
-        <is>
-          <t>CO-14107</t>
-        </is>
-      </c>
-      <c r="D78" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E78" s="58" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F78" s="58" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G78" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H78" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I78" s="59" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" s="58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K78" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L78" s="60" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M78" s="58" t="n"/>
-      <c r="N78" s="58" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B79" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="C79" s="58" t="inlineStr">
-        <is>
-          <t>CO-14104</t>
-        </is>
-      </c>
-      <c r="D79" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E79" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F79" s="58" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G79" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H79" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I79" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="J79" s="58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K79" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L79" s="60" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M79" s="58" t="n"/>
-      <c r="N79" s="58" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="45" t="inlineStr">
-        <is>
-          <t>8. 19-Oct XD08: ASN0003 received, CO-14104 → 2 (in case 3), CO-14108 → 6</t>
-        </is>
-      </c>
-      <c r="B81" s="46" t="n"/>
-      <c r="C81" s="46" t="n"/>
-      <c r="D81" s="46" t="n"/>
-      <c r="E81" s="46" t="n"/>
-      <c r="F81" s="46" t="n"/>
-      <c r="G81" s="46" t="n"/>
-      <c r="H81" s="46" t="n"/>
-      <c r="I81" s="46" t="n"/>
-      <c r="J81" s="46" t="n"/>
-      <c r="K81" s="46" t="n"/>
-      <c r="L81" s="46" t="n"/>
-      <c r="M81" s="46" t="n"/>
-      <c r="N81" s="46" t="n"/>
-      <c r="O81" s="46" t="n"/>
-      <c r="P81" s="46" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
-        </is>
-      </c>
-      <c r="D82" s="47" t="inlineStr">
-        <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="26" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="M81" s="60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N81" s="58" t="inlineStr">
+        <is>
+          <t>Received without ASN: candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="45" t="inlineStr">
+        <is>
+          <t>11. 21-Oct XD11 Change Order Number: ASN0003 case 3 → CO-14111</t>
+        </is>
+      </c>
+      <c r="B83" s="46" t="n"/>
+      <c r="C83" s="46" t="n"/>
+      <c r="D83" s="46" t="n"/>
+      <c r="E83" s="46" t="n"/>
+      <c r="F83" s="46" t="n"/>
+      <c r="G83" s="46" t="n"/>
+      <c r="H83" s="46" t="n"/>
+      <c r="I83" s="46" t="n"/>
+      <c r="J83" s="46" t="n"/>
+      <c r="K83" s="46" t="n"/>
+      <c r="L83" s="46" t="n"/>
+      <c r="M83" s="46" t="n"/>
+      <c r="N83" s="46" t="n"/>
+      <c r="O83" s="46" t="n"/>
+      <c r="P83" s="46" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D84" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B83" s="42" t="inlineStr">
-        <is>
-          <t>CUSTOMER_CD</t>
-        </is>
-      </c>
-      <c r="C83" s="42" t="inlineStr">
+      <c r="B85" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>LINE_SEQ</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
         <is>
           <t>CUSTOMER_ORDER_NO</t>
         </is>
       </c>
-      <c r="D83" s="42" t="inlineStr">
-        <is>
-          <t>ORDER_DT</t>
-        </is>
-      </c>
-      <c r="E83" s="42" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="F83" s="42" t="inlineStr">
-        <is>
-          <t>DETAILED_ITEM_NO</t>
-        </is>
-      </c>
-      <c r="G83" s="42" t="inlineStr">
+      <c r="H85" s="3" t="inlineStr">
         <is>
           <t>SERIAL_NO</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>SHIPPING_PART_NO</t>
-        </is>
-      </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS_QTY</t>
-        </is>
-      </c>
-      <c r="J83" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS</t>
-        </is>
-      </c>
-      <c r="K83" s="5" t="inlineStr">
-        <is>
-          <t>HOLD_FLAG</t>
-        </is>
-      </c>
-      <c r="L83" s="5" t="inlineStr">
-        <is>
-          <t>PO_MAPPED_FLAG</t>
-        </is>
-      </c>
-      <c r="M83" s="5" t="inlineStr">
-        <is>
-          <t>UPD_STATUS</t>
-        </is>
-      </c>
-      <c r="N83" s="5" t="inlineStr">
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="inlineStr">
         <is>
           <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B84" s="58" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="C84" s="58" t="inlineStr">
-        <is>
-          <t>CO-14105</t>
-        </is>
-      </c>
-      <c r="D84" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E84" s="58" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F84" s="58" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G84" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H84" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I84" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="J84" s="58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K84" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L84" s="58" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M84" s="60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N84" s="58" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B85" s="58" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="C85" s="58" t="inlineStr">
-        <is>
-          <t>CO-14106</t>
-        </is>
-      </c>
-      <c r="D85" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E85" s="58" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F85" s="58" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G85" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H85" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I85" s="59" t="n">
-        <v>3</v>
-      </c>
-      <c r="J85" s="58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K85" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L85" s="58" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M85" s="60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N85" s="58" t="inlineStr">
-        <is>
-          <t>Received</t>
         </is>
       </c>
     </row>
@@ -13527,747 +13503,426 @@
           <t>UPD</t>
         </is>
       </c>
-      <c r="B86" s="58" t="inlineStr">
-        <is>
-          <t>9715300</t>
-        </is>
-      </c>
-      <c r="C86" s="58" t="inlineStr">
-        <is>
-          <t>CO-14107</t>
-        </is>
-      </c>
-      <c r="D86" s="58" t="inlineStr">
+      <c r="B86" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="C86" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D86" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F86" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="G86" s="60" t="inlineStr">
+        <is>
+          <t>CO-14111</t>
+        </is>
+      </c>
+      <c r="H86" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I86" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J86" s="58" t="inlineStr">
+        <is>
+          <t>PO-DMY-09013</t>
+        </is>
+      </c>
+      <c r="K86" s="58" t="inlineStr">
+        <is>
+          <t>MF-DMY-09013</t>
+        </is>
+      </c>
+      <c r="L86" s="58" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M86" s="58" t="inlineStr">
+        <is>
+          <t>ASN0003</t>
+        </is>
+      </c>
+      <c r="N86" s="58" t="inlineStr">
+        <is>
+          <t>C-0003-03</t>
+        </is>
+      </c>
+      <c r="O86" s="58" t="inlineStr">
+        <is>
+          <t>Whole row moved; case, PO and ASN not changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D88" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="26" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B89" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C89" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D89" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E89" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F89" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G89" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t>UPD_STATUS</t>
+        </is>
+      </c>
+      <c r="N89" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B90" s="51" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="C90" s="51" t="inlineStr">
+        <is>
+          <t>CO-14104</t>
+        </is>
+      </c>
+      <c r="D90" s="51" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="E86" s="58" t="inlineStr">
-        <is>
-          <t>9715310</t>
-        </is>
-      </c>
-      <c r="F86" s="58" t="inlineStr">
+      <c r="E90" s="51" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F90" s="51" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="G86" s="58" t="inlineStr">
+      <c r="G90" s="51" t="inlineStr">
         <is>
           <t>0000001</t>
         </is>
       </c>
-      <c r="H86" s="58" t="inlineStr">
+      <c r="H90" s="51" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="I86" s="59" t="n">
-        <v>3</v>
-      </c>
-      <c r="J86" s="58" t="inlineStr">
+      <c r="I90" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="J90" s="51" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K86" s="58" t="inlineStr">
+      <c r="K90" s="51" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L86" s="58" t="inlineStr">
+      <c r="L90" s="51" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M86" s="60" t="inlineStr">
+      <c r="M90" s="66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N90" s="51" t="inlineStr">
+        <is>
+          <t>Not changed (PO_MAPPED_FLAG stays Y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B91" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="C91" s="58" t="inlineStr">
+        <is>
+          <t>CO-14111</t>
+        </is>
+      </c>
+      <c r="D91" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E91" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F91" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G91" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H91" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I91" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J91" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K91" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L91" s="60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M91" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N86" s="58" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B87" s="58" t="inlineStr">
+      <c r="N91" s="58" t="inlineStr">
+        <is>
+          <t>PO and ASN through ASN0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="35" t="inlineStr">
+        <is>
+          <t>TB_H_CROSSDOCK_ORDER_CHANGE</t>
+        </is>
+      </c>
+      <c r="D93" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B94" s="42" t="inlineStr">
+        <is>
+          <t>HIST_ID</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>FROM_CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>FROM_SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>TO_CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>TO_DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>FROM_INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>TO_INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B95" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="49" t="inlineStr">
+        <is>
+          <t>ASN0003</t>
+        </is>
+      </c>
+      <c r="D95" s="49" t="inlineStr">
+        <is>
+          <t>C-0003-03</t>
+        </is>
+      </c>
+      <c r="E95" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F95" s="49" t="inlineStr">
+        <is>
+          <t>CO-14104</t>
+        </is>
+      </c>
+      <c r="G95" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H95" s="49" t="inlineStr">
+        <is>
+          <t>CO-14111</t>
+        </is>
+      </c>
+      <c r="I95" s="49" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="C87" s="58" t="inlineStr">
-        <is>
-          <t>CO-14104</t>
-        </is>
-      </c>
-      <c r="D87" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E87" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F87" s="58" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G87" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H87" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I87" s="59" t="n">
+      <c r="J95" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="J87" s="58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K87" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L87" s="58" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M87" s="60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N87" s="58" t="inlineStr">
-        <is>
-          <t>Cancel after ASN: LOG5, listed in XD11; ASN not changed</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B88" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="C88" s="58" t="inlineStr">
-        <is>
-          <t>CO-14108</t>
-        </is>
-      </c>
-      <c r="D88" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="E88" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F88" s="58" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G88" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H88" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I88" s="59" t="n">
+      <c r="K95" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="J88" s="58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K88" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L88" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M88" s="60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N88" s="58" t="inlineStr">
-        <is>
-          <t>Received without ASN (pcs of case 3 allocated by G-System): candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="45" t="inlineStr">
-        <is>
-          <t>9. 19-Oct XD11 Change Order Number: ASN0003 case 3 → CO-14108</t>
-        </is>
-      </c>
-      <c r="B90" s="46" t="n"/>
-      <c r="C90" s="46" t="n"/>
-      <c r="D90" s="46" t="n"/>
-      <c r="E90" s="46" t="n"/>
-      <c r="F90" s="46" t="n"/>
-      <c r="G90" s="46" t="n"/>
-      <c r="H90" s="46" t="n"/>
-      <c r="I90" s="46" t="n"/>
-      <c r="J90" s="46" t="n"/>
-      <c r="K90" s="46" t="n"/>
-      <c r="L90" s="46" t="n"/>
-      <c r="M90" s="46" t="n"/>
-      <c r="N90" s="46" t="n"/>
-      <c r="O90" s="46" t="n"/>
-      <c r="P90" s="46" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_INSTRUCTION</t>
-        </is>
-      </c>
-      <c r="D91" s="47" t="inlineStr">
-        <is>
-          <t>New table (Crossdock)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="26" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B92" s="42" t="inlineStr">
-        <is>
-          <t>INSTRUCTION_ID</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>CASE_SEQ</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>LINE_SEQ</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>SERIAL_NO</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t>QTY</t>
-        </is>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>PO_NO</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_NO</t>
-        </is>
-      </c>
-      <c r="L92" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_ITEM</t>
-        </is>
-      </c>
-      <c r="M92" s="3" t="inlineStr">
-        <is>
-          <t>ASN_NO</t>
-        </is>
-      </c>
-      <c r="N92" s="3" t="inlineStr">
-        <is>
-          <t>CASE_NO</t>
-        </is>
-      </c>
-      <c r="O92" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B93" s="59" t="n">
+      <c r="L95" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="C93" s="59" t="n">
-        <v>3</v>
-      </c>
-      <c r="D93" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="F93" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="G93" s="60" t="inlineStr">
-        <is>
-          <t>CO-14108</t>
-        </is>
-      </c>
-      <c r="H93" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="I93" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="J93" s="58" t="inlineStr">
-        <is>
-          <t>PO-DMY-09014</t>
-        </is>
-      </c>
-      <c r="K93" s="58" t="inlineStr">
-        <is>
-          <t>MF-DMY-09014</t>
-        </is>
-      </c>
-      <c r="L93" s="58" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="M93" s="58" t="inlineStr">
-        <is>
-          <t>ASN0003</t>
-        </is>
-      </c>
-      <c r="N93" s="58" t="inlineStr">
-        <is>
-          <t>C-0003-03</t>
-        </is>
-      </c>
-      <c r="O93" s="58" t="inlineStr">
-        <is>
-          <t>Whole row moved; case, PO and ASN not changed</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
-        </is>
-      </c>
-      <c r="D95" s="47" t="inlineStr">
-        <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="26" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B96" s="42" t="inlineStr">
-        <is>
-          <t>CUSTOMER_CD</t>
-        </is>
-      </c>
-      <c r="C96" s="42" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="D96" s="42" t="inlineStr">
-        <is>
-          <t>ORDER_DT</t>
-        </is>
-      </c>
-      <c r="E96" s="42" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="F96" s="42" t="inlineStr">
-        <is>
-          <t>DETAILED_ITEM_NO</t>
-        </is>
-      </c>
-      <c r="G96" s="42" t="inlineStr">
-        <is>
-          <t>SERIAL_NO</t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t>SHIPPING_PART_NO</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS_QTY</t>
-        </is>
-      </c>
-      <c r="J96" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS</t>
-        </is>
-      </c>
-      <c r="K96" s="5" t="inlineStr">
-        <is>
-          <t>HOLD_FLAG</t>
-        </is>
-      </c>
-      <c r="L96" s="5" t="inlineStr">
-        <is>
-          <t>PO_MAPPED_FLAG</t>
-        </is>
-      </c>
-      <c r="M96" s="5" t="inlineStr">
-        <is>
-          <t>UPD_STATUS</t>
-        </is>
-      </c>
-      <c r="N96" s="5" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="50" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-      <c r="B97" s="51" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="C97" s="51" t="inlineStr">
-        <is>
-          <t>CO-14104</t>
-        </is>
-      </c>
-      <c r="D97" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="E97" s="51" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F97" s="51" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G97" s="51" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H97" s="51" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I97" s="52" t="n">
-        <v>6</v>
-      </c>
-      <c r="J97" s="51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K97" s="51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L97" s="51" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M97" s="66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N97" s="51" t="inlineStr">
-        <is>
-          <t>Not changed (PO_MAPPED_FLAG stays Y)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B98" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="C98" s="58" t="inlineStr">
-        <is>
-          <t>CO-14108</t>
-        </is>
-      </c>
-      <c r="D98" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="E98" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F98" s="58" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G98" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H98" s="58" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="I98" s="59" t="n">
-        <v>6</v>
-      </c>
-      <c r="J98" s="58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K98" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L98" s="60" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M98" s="49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N98" s="58" t="inlineStr">
-        <is>
-          <t>PO and ASN through ASN0003</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="35" t="inlineStr">
-        <is>
-          <t>TB_H_CROSSDOCK_ORDER_CHANGE</t>
-        </is>
-      </c>
-      <c r="D100" s="47" t="inlineStr">
-        <is>
-          <t>New table (Crossdock)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="26" customHeight="1">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B101" s="42" t="inlineStr">
-        <is>
-          <t>HIST_ID</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>ASN_NO</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>CASE_NO</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>FROM_CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>FROM_SERIAL_NO</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>TO_CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>TO_DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>QTY</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>FROM_INSTRUCTION_ID</t>
-        </is>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>TO_INSTRUCTION_ID</t>
-        </is>
-      </c>
-      <c r="M101" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B102" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C102" s="49" t="inlineStr">
-        <is>
-          <t>ASN0003</t>
-        </is>
-      </c>
-      <c r="D102" s="49" t="inlineStr">
-        <is>
-          <t>C-0003-03</t>
-        </is>
-      </c>
-      <c r="E102" s="49" t="inlineStr">
-        <is>
-          <t>PART-X</t>
-        </is>
-      </c>
-      <c r="F102" s="49" t="inlineStr">
-        <is>
-          <t>CO-14104</t>
-        </is>
-      </c>
-      <c r="G102" s="49" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H102" s="49" t="inlineStr">
-        <is>
-          <t>CO-14108</t>
-        </is>
-      </c>
-      <c r="I102" s="49" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="J102" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="K102" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="L102" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="M102" s="49" t="inlineStr"/>
+      <c r="M95" s="49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23593,7 +23248,7 @@
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-5, SIM-6, SIM-7, SIM-8, SIM-9</t>
+          <t>SIM-2, SIM-6, SIM-7, SIM-8, SIM-9</t>
         </is>
       </c>
     </row>
@@ -40038,7 +39693,7 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>UPD_STATUS day by day; cancel after ASN → Change Order Number (simulasi_asn.xlsx)</t>
+          <t>One PO per order date (short PO → split PO); cancel of a middle row after ASN → Change Order Number (simulasi_asn.xlsx)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -40053,12 +39708,12 @@
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
-          <t>TB_R_H0253_ORDER_CONTROL_PRE, TB_R_INSTRUCTION, #TEMP_INSTRUCTION, TB_R_PRA_DAILY_ORDER_MAPPED, TB_H_CROSSDOCK_ORDER_CHANGE</t>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE, TB_R_INSTRUCTION, #TEMP_INSTRUCTION, TB_H_CROSSDOCK_ORDER_CHANGE</t>
         </is>
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>PART-X, 6 pcs/case. ORDER_STATUS of the replicate keeps the first value (7); a change in G-System is written to UPD_STATUS: 6 received, 2 cancel. 16-Oct CO-14101 VN → ASN0001, CO-14102 TH on hold. 17-Oct CO-14101 received (6), CO-14102 cancelled (2, no ASN: nothing else), CO-14103 → ASN0002. 18-Oct order date 17-Oct: scan order CO-14105, CO-14106 + CO-14107, CO-14104 (customer code 9715300 before 9722D10); all 3 cases Ready, sent together in ASN0003. CO-14108 (order date 18-Oct) gets no PO (Not Ready). 19-Oct ASN0003 received; CO-14104 cancelled although in case 3, its pcs go to CO-14108 in G-System (6, PO_MAPPED N, no ASN). The D/S team moves case 3 from CO-14104 to CO-14108 in Change Order Number (XD11); history in TB_H_CROSSDOCK_ORDER_CHANGE.</t>
+          <t>PART-X, 6 pcs/case. One PO per customer order date: PO_DT = order date + 1, qty = total order qty of the date (all destinations). PO qty &lt; order qty is an abnormality: the rest comes in a split PO. ORDER_STATUS of the replicate keeps 7; changes go to UPD_STATUS. Order date 15-Oct (12) → PO-DMY-09011; CO-14102 on hold then cancelled, so its 6 pcs of PO-DMY-09011 go to CO-14103 (older PO_DT first). Order date 17-Oct: 4 destinations, 30 pcs, PO-DMY-09013 only 18 (abnormal) → case 5 Not Ready until the split PO-DMY-09014 (12, 19-Oct). Cases 1-4 → ASN0003; CO-14104 (middle row, case 3) is cancelled after the ASN. 21-Oct G-System allocates the pcs of case 3 to CO-14111 (UPD_STATUS 6, no ASN): the D/S team moves case 3 to CO-14111 (XD11). Open PO qty at the end (12) = cancelled qty (CO-14102 + CO-14104).</t>
         </is>
       </c>
     </row>

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -10132,7 +10132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P95"/>
+  <dimension ref="A1:P112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -10184,7 +10184,7 @@
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
         <is>
-          <t>• Order date 17-Oct: 4 destinations, 30 pcs, PO-DMY-09013 only 18 (abnormal) → case 5 Not Ready until the split PO-DMY-09014 (12, 19-Oct). Cases 1-4 → ASN0003; CO-14104 (middle row, case 3) is cancelled after the ASN.</t>
+          <t>• Order date 17-Oct: 4 destinations, 30 pcs, PO-DMY-09013 only 18 (abnormal) → case 5 Not Ready until the split PO-DMY-09014 (12, 19-Oct). Cases 1-4 → ASN0003; CO-14104 (middle row, case 3) is cancelled after the ASN. Order date 18-Oct: 3 destinations, 18 pcs, PO-DMY-09015 18 (OK) → ASN0005.</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
     <row r="68">
       <c r="A68" s="45" t="inlineStr">
         <is>
-          <t>8. 19-Oct XD08: ASN0003 received, CO-14104 → 2 (middle row, in case 3); split PO-DMY-09014 (PO_DT 19-Oct, 12)</t>
+          <t>8. 19-Oct XD08: ASN0003 received, CO-14104 → 2 (middle row, in case 3); split PO-DMY-09014 (PO_DT 19-Oct, 12); order date 18-Oct new</t>
         </is>
       </c>
       <c r="B68" s="46" t="n"/>
@@ -13031,113 +13031,152 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="45" t="inlineStr">
-        <is>
-          <t>9. 19-Oct CO-14110 → ASN0004 with the split PO</t>
-        </is>
-      </c>
-      <c r="B73" s="46" t="n"/>
-      <c r="C73" s="46" t="n"/>
-      <c r="D73" s="46" t="n"/>
-      <c r="E73" s="46" t="n"/>
-      <c r="F73" s="46" t="n"/>
-      <c r="G73" s="46" t="n"/>
-      <c r="H73" s="46" t="n"/>
-      <c r="I73" s="46" t="n"/>
-      <c r="J73" s="46" t="n"/>
-      <c r="K73" s="46" t="n"/>
-      <c r="L73" s="46" t="n"/>
-      <c r="M73" s="46" t="n"/>
-      <c r="N73" s="46" t="n"/>
-      <c r="O73" s="46" t="n"/>
-      <c r="P73" s="46" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_INSTRUCTION</t>
-        </is>
-      </c>
-      <c r="D74" s="47" t="inlineStr">
-        <is>
-          <t>New table (Crossdock)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="26" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A73" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D73" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B75" s="42" t="inlineStr">
-        <is>
-          <t>INSTRUCTION_ID</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>CASE_SEQ</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>LINE_SEQ</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="B74" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C74" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D74" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E74" s="42" t="inlineStr">
         <is>
           <t>DESTINATION_CD</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="F74" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G74" s="42" t="inlineStr">
         <is>
           <t>SERIAL_NO</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>QTY</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>PO_NO</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_NO</t>
-        </is>
-      </c>
-      <c r="L75" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_ITEM</t>
-        </is>
-      </c>
-      <c r="M75" s="3" t="inlineStr">
-        <is>
-          <t>ASN_NO</t>
-        </is>
-      </c>
-      <c r="N75" s="3" t="inlineStr">
-        <is>
-          <t>CASE_NO</t>
-        </is>
-      </c>
-      <c r="O75" s="3" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>UPD_STATUS</t>
+        </is>
+      </c>
+      <c r="N74" s="5" t="inlineStr">
         <is>
           <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B75" s="49" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C75" s="49" t="inlineStr">
+        <is>
+          <t>CO-14112</t>
+        </is>
+      </c>
+      <c r="D75" s="49" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E75" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F75" s="49" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G75" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H75" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I75" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" s="49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K75" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L75" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M75" s="49" t="n"/>
+      <c r="N75" s="49" t="inlineStr">
+        <is>
+          <t>Order date 18-Oct, 3 destinations (PO-DMY-09015, PO_DT 19-Oct, 18)</t>
         </is>
       </c>
     </row>
@@ -13147,33 +13186,39 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="B76" s="53" t="n">
-        <v>8</v>
-      </c>
-      <c r="C76" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" s="53" t="n">
-        <v>1</v>
+      <c r="B76" s="49" t="inlineStr">
+        <is>
+          <t>9811100</t>
+        </is>
+      </c>
+      <c r="C76" s="49" t="inlineStr">
+        <is>
+          <t>CO-14113</t>
+        </is>
+      </c>
+      <c r="D76" s="49" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
       </c>
       <c r="E76" s="49" t="inlineStr">
         <is>
+          <t>9811110</t>
+        </is>
+      </c>
+      <c r="F76" s="49" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G76" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H76" s="49" t="inlineStr">
+        <is>
           <t>PART-X</t>
-        </is>
-      </c>
-      <c r="F76" s="49" t="inlineStr">
-        <is>
-          <t>982220</t>
-        </is>
-      </c>
-      <c r="G76" s="49" t="inlineStr">
-        <is>
-          <t>CO-14110</t>
-        </is>
-      </c>
-      <c r="H76" s="49" t="inlineStr">
-        <is>
-          <t>0000001</t>
         </is>
       </c>
       <c r="I76" s="53" t="n">
@@ -13181,748 +13226,1556 @@
       </c>
       <c r="J76" s="49" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K76" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L76" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M76" s="49" t="n"/>
+      <c r="N76" s="49" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B77" s="49" t="inlineStr">
+        <is>
+          <t>982200</t>
+        </is>
+      </c>
+      <c r="C77" s="49" t="inlineStr">
+        <is>
+          <t>CO-14114</t>
+        </is>
+      </c>
+      <c r="D77" s="49" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E77" s="49" t="inlineStr">
+        <is>
+          <t>982220</t>
+        </is>
+      </c>
+      <c r="F77" s="49" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G77" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H77" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I77" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J77" s="49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K77" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L77" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M77" s="49" t="n"/>
+      <c r="N77" s="49" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>9. 19-Oct [Search] → XD09: rest of 17-Oct with the split PO, then 18-Oct</t>
+        </is>
+      </c>
+      <c r="B79" s="46" t="n"/>
+      <c r="C79" s="46" t="n"/>
+      <c r="D79" s="46" t="n"/>
+      <c r="E79" s="46" t="n"/>
+      <c r="F79" s="46" t="n"/>
+      <c r="G79" s="46" t="n"/>
+      <c r="H79" s="46" t="n"/>
+      <c r="I79" s="46" t="n"/>
+      <c r="J79" s="46" t="n"/>
+      <c r="K79" s="46" t="n"/>
+      <c r="L79" s="46" t="n"/>
+      <c r="M79" s="46" t="n"/>
+      <c r="N79" s="46" t="n"/>
+      <c r="O79" s="46" t="n"/>
+      <c r="P79" s="46" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="35" t="inlineStr">
+        <is>
+          <t>#TEMP_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D80" s="47" t="inlineStr">
+        <is>
+          <t>Temporary (session)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="26" customHeight="1">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>SORT_SEQ</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>OPEN_ORDER_QTY</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>ASSIGNED_QTY</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
+        <is>
+          <t>CUM_DEST_QTY</t>
+        </is>
+      </c>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>SEQ_QTY</t>
+        </is>
+      </c>
+      <c r="M81" s="9" t="inlineStr">
+        <is>
+          <t>CUT_FLAG</t>
+        </is>
+      </c>
+      <c r="N81" s="9" t="inlineStr">
+        <is>
+          <t>GROUP_SEQ</t>
+        </is>
+      </c>
+      <c r="O81" s="9" t="inlineStr">
+        <is>
+          <t>CROSSDOCK_STATUS</t>
+        </is>
+      </c>
+      <c r="P81" s="9" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B82" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="64" t="inlineStr">
+        <is>
+          <t>982200</t>
+        </is>
+      </c>
+      <c r="D82" s="64" t="inlineStr">
+        <is>
+          <t>CO-14110</t>
+        </is>
+      </c>
+      <c r="E82" s="64" t="inlineStr">
+        <is>
+          <t>982220</t>
+        </is>
+      </c>
+      <c r="F82" s="64" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="G82" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H82" s="64" t="inlineStr">
+        <is>
           <t>PO-DMY-09014</t>
         </is>
       </c>
-      <c r="K76" s="49" t="inlineStr">
-        <is>
-          <t>MF-DMY-09014</t>
-        </is>
-      </c>
-      <c r="L76" s="49" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="M76" s="49" t="inlineStr">
-        <is>
-          <t>ASN0004</t>
-        </is>
-      </c>
-      <c r="N76" s="49" t="inlineStr">
-        <is>
-          <t>C-0004-01</t>
-        </is>
-      </c>
-      <c r="O76" s="49" t="inlineStr">
-        <is>
-          <t>6 pcs of the split PO stay open</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="45" t="inlineStr">
-        <is>
-          <t>10. 20-Oct XD08: CO-14111 new (order date 19-Oct, PO-DMY-09015); 21-Oct → 6 (pcs of case 3 allocated by G-System)</t>
-        </is>
-      </c>
-      <c r="B78" s="46" t="n"/>
-      <c r="C78" s="46" t="n"/>
-      <c r="D78" s="46" t="n"/>
-      <c r="E78" s="46" t="n"/>
-      <c r="F78" s="46" t="n"/>
-      <c r="G78" s="46" t="n"/>
-      <c r="H78" s="46" t="n"/>
-      <c r="I78" s="46" t="n"/>
-      <c r="J78" s="46" t="n"/>
-      <c r="K78" s="46" t="n"/>
-      <c r="L78" s="46" t="n"/>
-      <c r="M78" s="46" t="n"/>
-      <c r="N78" s="46" t="n"/>
-      <c r="O78" s="46" t="n"/>
-      <c r="P78" s="46" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
-        </is>
-      </c>
-      <c r="D79" s="47" t="inlineStr">
-        <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="26" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B80" s="42" t="inlineStr">
-        <is>
-          <t>CUSTOMER_CD</t>
-        </is>
-      </c>
-      <c r="C80" s="42" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="D80" s="42" t="inlineStr">
-        <is>
-          <t>ORDER_DT</t>
-        </is>
-      </c>
-      <c r="E80" s="42" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="F80" s="42" t="inlineStr">
-        <is>
-          <t>DETAILED_ITEM_NO</t>
-        </is>
-      </c>
-      <c r="G80" s="42" t="inlineStr">
-        <is>
-          <t>SERIAL_NO</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>SHIPPING_PART_NO</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS_QTY</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>ORDER_STATUS</t>
-        </is>
-      </c>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t>HOLD_FLAG</t>
-        </is>
-      </c>
-      <c r="L80" s="5" t="inlineStr">
-        <is>
-          <t>PO_MAPPED_FLAG</t>
-        </is>
-      </c>
-      <c r="M80" s="5" t="inlineStr">
-        <is>
-          <t>UPD_STATUS</t>
-        </is>
-      </c>
-      <c r="N80" s="5" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B81" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="C81" s="58" t="inlineStr">
-        <is>
-          <t>CO-14111</t>
-        </is>
-      </c>
-      <c r="D81" s="58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="E81" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="F81" s="58" t="inlineStr">
-        <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="G81" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="H81" s="58" t="inlineStr">
+      <c r="I82" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J82" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L82" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M82" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N82" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P82" s="64" t="inlineStr">
+        <is>
+          <t>→ ASN0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B83" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="64" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="D83" s="64" t="inlineStr">
+        <is>
+          <t>CO-14112</t>
+        </is>
+      </c>
+      <c r="E83" s="64" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F83" s="64" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="I81" s="59" t="n">
+      <c r="G83" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="J81" s="58" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K81" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L81" s="58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M81" s="60" t="inlineStr">
+      <c r="H83" s="64" t="inlineStr">
+        <is>
+          <t>PO-DMY-09014</t>
+        </is>
+      </c>
+      <c r="I83" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J83" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L83" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M83" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N83" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N81" s="58" t="inlineStr">
-        <is>
-          <t>Received without ASN: candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="45" t="inlineStr">
-        <is>
-          <t>11. 21-Oct XD11 Change Order Number: ASN0003 case 3 → CO-14111</t>
-        </is>
-      </c>
-      <c r="B83" s="46" t="n"/>
-      <c r="C83" s="46" t="n"/>
-      <c r="D83" s="46" t="n"/>
-      <c r="E83" s="46" t="n"/>
-      <c r="F83" s="46" t="n"/>
-      <c r="G83" s="46" t="n"/>
-      <c r="H83" s="46" t="n"/>
-      <c r="I83" s="46" t="n"/>
-      <c r="J83" s="46" t="n"/>
-      <c r="K83" s="46" t="n"/>
-      <c r="L83" s="46" t="n"/>
-      <c r="M83" s="46" t="n"/>
-      <c r="N83" s="46" t="n"/>
-      <c r="O83" s="46" t="n"/>
-      <c r="P83" s="46" t="n"/>
+      <c r="P83" s="64" t="inlineStr">
+        <is>
+          <t>Rest of the split PO; cases 1-3 → ASN0005</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="35" t="inlineStr">
-        <is>
-          <t>TB_R_INSTRUCTION</t>
-        </is>
-      </c>
-      <c r="D84" s="47" t="inlineStr">
-        <is>
-          <t>New table (Crossdock)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="26" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B85" s="42" t="inlineStr">
-        <is>
-          <t>INSTRUCTION_ID</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>CASE_SEQ</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>LINE_SEQ</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>PART_NO</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>DESTINATION_CD</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOMER_ORDER_NO</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>SERIAL_NO</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>QTY</t>
-        </is>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>PO_NO</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_NO</t>
-        </is>
-      </c>
-      <c r="L85" s="3" t="inlineStr">
-        <is>
-          <t>MANIFEST_ITEM</t>
-        </is>
-      </c>
-      <c r="M85" s="3" t="inlineStr">
-        <is>
-          <t>ASN_NO</t>
-        </is>
-      </c>
-      <c r="N85" s="3" t="inlineStr">
-        <is>
-          <t>CASE_NO</t>
-        </is>
-      </c>
-      <c r="O85" s="3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="57" t="inlineStr">
-        <is>
-          <t>UPD</t>
-        </is>
-      </c>
-      <c r="B86" s="59" t="n">
+      <c r="A84" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B84" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" s="64" t="inlineStr">
+        <is>
+          <t>9811100</t>
+        </is>
+      </c>
+      <c r="D84" s="64" t="inlineStr">
+        <is>
+          <t>CO-14113</t>
+        </is>
+      </c>
+      <c r="E84" s="64" t="inlineStr">
+        <is>
+          <t>9811110</t>
+        </is>
+      </c>
+      <c r="F84" s="64" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="G84" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="C86" s="59" t="n">
+      <c r="H84" s="64" t="inlineStr">
+        <is>
+          <t>PO-DMY-09015</t>
+        </is>
+      </c>
+      <c r="I84" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J84" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K84" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L84" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M84" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N84" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="O84" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P84" s="64" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="62" t="inlineStr">
+        <is>
+          <t>TEMP</t>
+        </is>
+      </c>
+      <c r="B85" s="63" t="n">
         <v>3</v>
       </c>
-      <c r="D86" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="58" t="inlineStr">
+      <c r="C85" s="64" t="inlineStr">
+        <is>
+          <t>982200</t>
+        </is>
+      </c>
+      <c r="D85" s="64" t="inlineStr">
+        <is>
+          <t>CO-14114</t>
+        </is>
+      </c>
+      <c r="E85" s="64" t="inlineStr">
+        <is>
+          <t>982220</t>
+        </is>
+      </c>
+      <c r="F85" s="64" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="F86" s="58" t="inlineStr">
-        <is>
-          <t>9722D10</t>
-        </is>
-      </c>
-      <c r="G86" s="60" t="inlineStr">
-        <is>
-          <t>CO-14111</t>
-        </is>
-      </c>
-      <c r="H86" s="58" t="inlineStr">
-        <is>
-          <t>0000001</t>
-        </is>
-      </c>
-      <c r="I86" s="59" t="n">
+      <c r="G85" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="J86" s="58" t="inlineStr">
-        <is>
-          <t>PO-DMY-09013</t>
-        </is>
-      </c>
-      <c r="K86" s="58" t="inlineStr">
-        <is>
-          <t>MF-DMY-09013</t>
-        </is>
-      </c>
-      <c r="L86" s="58" t="inlineStr">
-        <is>
-          <t>0001</t>
-        </is>
-      </c>
-      <c r="M86" s="58" t="inlineStr">
-        <is>
-          <t>ASN0003</t>
-        </is>
-      </c>
-      <c r="N86" s="58" t="inlineStr">
-        <is>
-          <t>C-0003-03</t>
-        </is>
-      </c>
-      <c r="O86" s="58" t="inlineStr">
-        <is>
-          <t>Whole row moved; case, PO and ASN not changed</t>
-        </is>
-      </c>
+      <c r="H85" s="64" t="inlineStr">
+        <is>
+          <t>PO-DMY-09015</t>
+        </is>
+      </c>
+      <c r="I85" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="J85" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K85" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="L85" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="M85" s="65" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N85" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="O85" s="49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P85" s="64" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="45" t="inlineStr">
+        <is>
+          <t>10. 19-Oct ASN0004 (CO-14110) and ASN0005 (order date 18-Oct, cases 1-3)</t>
+        </is>
+      </c>
+      <c r="B87" s="46" t="n"/>
+      <c r="C87" s="46" t="n"/>
+      <c r="D87" s="46" t="n"/>
+      <c r="E87" s="46" t="n"/>
+      <c r="F87" s="46" t="n"/>
+      <c r="G87" s="46" t="n"/>
+      <c r="H87" s="46" t="n"/>
+      <c r="I87" s="46" t="n"/>
+      <c r="J87" s="46" t="n"/>
+      <c r="K87" s="46" t="n"/>
+      <c r="L87" s="46" t="n"/>
+      <c r="M87" s="46" t="n"/>
+      <c r="N87" s="46" t="n"/>
+      <c r="O87" s="46" t="n"/>
+      <c r="P87" s="46" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="35" t="inlineStr">
         <is>
+          <t>TB_R_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D88" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="26" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B89" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>LINE_SEQ</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B90" s="53" t="n">
+        <v>8</v>
+      </c>
+      <c r="C90" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F90" s="49" t="inlineStr">
+        <is>
+          <t>982220</t>
+        </is>
+      </c>
+      <c r="G90" s="49" t="inlineStr">
+        <is>
+          <t>CO-14110</t>
+        </is>
+      </c>
+      <c r="H90" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I90" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J90" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09014</t>
+        </is>
+      </c>
+      <c r="K90" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09014</t>
+        </is>
+      </c>
+      <c r="L90" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M90" s="49" t="inlineStr">
+        <is>
+          <t>ASN0004</t>
+        </is>
+      </c>
+      <c r="N90" s="49" t="inlineStr">
+        <is>
+          <t>C-0004-01</t>
+        </is>
+      </c>
+      <c r="O90" s="49" t="inlineStr">
+        <is>
+          <t>Split PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B91" s="53" t="n">
+        <v>9</v>
+      </c>
+      <c r="C91" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F91" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G91" s="49" t="inlineStr">
+        <is>
+          <t>CO-14112</t>
+        </is>
+      </c>
+      <c r="H91" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I91" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J91" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09014</t>
+        </is>
+      </c>
+      <c r="K91" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09014</t>
+        </is>
+      </c>
+      <c r="L91" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M91" s="49" t="inlineStr">
+        <is>
+          <t>ASN0005</t>
+        </is>
+      </c>
+      <c r="N91" s="49" t="inlineStr">
+        <is>
+          <t>C-0005-01</t>
+        </is>
+      </c>
+      <c r="O91" s="49" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B92" s="53" t="n">
+        <v>10</v>
+      </c>
+      <c r="C92" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F92" s="49" t="inlineStr">
+        <is>
+          <t>9811110</t>
+        </is>
+      </c>
+      <c r="G92" s="49" t="inlineStr">
+        <is>
+          <t>CO-14113</t>
+        </is>
+      </c>
+      <c r="H92" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I92" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J92" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09015</t>
+        </is>
+      </c>
+      <c r="K92" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09015</t>
+        </is>
+      </c>
+      <c r="L92" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M92" s="49" t="inlineStr">
+        <is>
+          <t>ASN0005</t>
+        </is>
+      </c>
+      <c r="N92" s="49" t="inlineStr">
+        <is>
+          <t>C-0005-02</t>
+        </is>
+      </c>
+      <c r="O92" s="49" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B93" s="53" t="n">
+        <v>11</v>
+      </c>
+      <c r="C93" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F93" s="49" t="inlineStr">
+        <is>
+          <t>982220</t>
+        </is>
+      </c>
+      <c r="G93" s="49" t="inlineStr">
+        <is>
+          <t>CO-14114</t>
+        </is>
+      </c>
+      <c r="H93" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I93" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J93" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09015</t>
+        </is>
+      </c>
+      <c r="K93" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09015</t>
+        </is>
+      </c>
+      <c r="L93" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M93" s="49" t="inlineStr">
+        <is>
+          <t>ASN0005</t>
+        </is>
+      </c>
+      <c r="N93" s="49" t="inlineStr">
+        <is>
+          <t>C-0005-03</t>
+        </is>
+      </c>
+      <c r="O93" s="49" t="inlineStr">
+        <is>
+          <t>6 pcs of PO-DMY-09015 stay open</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="45" t="inlineStr">
+        <is>
+          <t>11. 20-Oct XD08: CO-14111 new (order date 19-Oct, PO-DMY-09016); 21-Oct → 6 (pcs of case 3 allocated by G-System)</t>
+        </is>
+      </c>
+      <c r="B95" s="46" t="n"/>
+      <c r="C95" s="46" t="n"/>
+      <c r="D95" s="46" t="n"/>
+      <c r="E95" s="46" t="n"/>
+      <c r="F95" s="46" t="n"/>
+      <c r="G95" s="46" t="n"/>
+      <c r="H95" s="46" t="n"/>
+      <c r="I95" s="46" t="n"/>
+      <c r="J95" s="46" t="n"/>
+      <c r="K95" s="46" t="n"/>
+      <c r="L95" s="46" t="n"/>
+      <c r="M95" s="46" t="n"/>
+      <c r="N95" s="46" t="n"/>
+      <c r="O95" s="46" t="n"/>
+      <c r="P95" s="46" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="35" t="inlineStr">
+        <is>
           <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
         </is>
       </c>
-      <c r="D88" s="47" t="inlineStr">
+      <c r="D96" s="47" t="inlineStr">
         <is>
           <t>Replicated from DB Surrounding (G-System)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="26" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
+    <row r="97" ht="26" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B89" s="42" t="inlineStr">
+      <c r="B97" s="42" t="inlineStr">
         <is>
           <t>CUSTOMER_CD</t>
         </is>
       </c>
-      <c r="C89" s="42" t="inlineStr">
+      <c r="C97" s="42" t="inlineStr">
         <is>
           <t>CUSTOMER_ORDER_NO</t>
         </is>
       </c>
-      <c r="D89" s="42" t="inlineStr">
+      <c r="D97" s="42" t="inlineStr">
         <is>
           <t>ORDER_DT</t>
         </is>
       </c>
-      <c r="E89" s="42" t="inlineStr">
+      <c r="E97" s="42" t="inlineStr">
         <is>
           <t>DESTINATION_CD</t>
         </is>
       </c>
-      <c r="F89" s="42" t="inlineStr">
+      <c r="F97" s="42" t="inlineStr">
         <is>
           <t>DETAILED_ITEM_NO</t>
         </is>
       </c>
-      <c r="G89" s="42" t="inlineStr">
+      <c r="G97" s="42" t="inlineStr">
         <is>
           <t>SERIAL_NO</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H97" s="5" t="inlineStr">
         <is>
           <t>SHIPPING_PART_NO</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I97" s="5" t="inlineStr">
         <is>
           <t>ORDER_STATUS_QTY</t>
         </is>
       </c>
-      <c r="J89" s="5" t="inlineStr">
+      <c r="J97" s="5" t="inlineStr">
         <is>
           <t>ORDER_STATUS</t>
         </is>
       </c>
-      <c r="K89" s="5" t="inlineStr">
+      <c r="K97" s="5" t="inlineStr">
         <is>
           <t>HOLD_FLAG</t>
         </is>
       </c>
-      <c r="L89" s="5" t="inlineStr">
+      <c r="L97" s="5" t="inlineStr">
         <is>
           <t>PO_MAPPED_FLAG</t>
         </is>
       </c>
-      <c r="M89" s="5" t="inlineStr">
+      <c r="M97" s="5" t="inlineStr">
         <is>
           <t>UPD_STATUS</t>
         </is>
       </c>
-      <c r="N89" s="5" t="inlineStr">
+      <c r="N97" s="5" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="50" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B98" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="C98" s="58" t="inlineStr">
+        <is>
+          <t>CO-14111</t>
+        </is>
+      </c>
+      <c r="D98" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E98" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="F98" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G98" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H98" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I98" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J98" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K98" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L98" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M98" s="60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N98" s="58" t="inlineStr">
+        <is>
+          <t>Received without ASN: candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="45" t="inlineStr">
+        <is>
+          <t>12. 21-Oct XD11 Change Order Number: ASN0003 case 3 → CO-14111</t>
+        </is>
+      </c>
+      <c r="B100" s="46" t="n"/>
+      <c r="C100" s="46" t="n"/>
+      <c r="D100" s="46" t="n"/>
+      <c r="E100" s="46" t="n"/>
+      <c r="F100" s="46" t="n"/>
+      <c r="G100" s="46" t="n"/>
+      <c r="H100" s="46" t="n"/>
+      <c r="I100" s="46" t="n"/>
+      <c r="J100" s="46" t="n"/>
+      <c r="K100" s="46" t="n"/>
+      <c r="L100" s="46" t="n"/>
+      <c r="M100" s="46" t="n"/>
+      <c r="N100" s="46" t="n"/>
+      <c r="O100" s="46" t="n"/>
+      <c r="P100" s="46" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D101" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="26" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B102" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>LINE_SEQ</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="O102" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B103" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="C103" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F103" s="58" t="inlineStr">
+        <is>
+          <t>9722D10</t>
+        </is>
+      </c>
+      <c r="G103" s="60" t="inlineStr">
+        <is>
+          <t>CO-14111</t>
+        </is>
+      </c>
+      <c r="H103" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I103" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J103" s="58" t="inlineStr">
+        <is>
+          <t>PO-DMY-09013</t>
+        </is>
+      </c>
+      <c r="K103" s="58" t="inlineStr">
+        <is>
+          <t>MF-DMY-09013</t>
+        </is>
+      </c>
+      <c r="L103" s="58" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M103" s="58" t="inlineStr">
+        <is>
+          <t>ASN0003</t>
+        </is>
+      </c>
+      <c r="N103" s="58" t="inlineStr">
+        <is>
+          <t>C-0003-03</t>
+        </is>
+      </c>
+      <c r="O103" s="58" t="inlineStr">
+        <is>
+          <t>Whole row moved; case, PO and ASN not changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D105" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="26" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B106" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C106" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D106" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E106" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F106" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G106" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M106" s="5" t="inlineStr">
+        <is>
+          <t>UPD_STATUS</t>
+        </is>
+      </c>
+      <c r="N106" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="50" t="inlineStr">
         <is>
           <t>READ</t>
         </is>
       </c>
-      <c r="B90" s="51" t="inlineStr">
+      <c r="B107" s="51" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="C90" s="51" t="inlineStr">
+      <c r="C107" s="51" t="inlineStr">
         <is>
           <t>CO-14104</t>
         </is>
       </c>
-      <c r="D90" s="51" t="inlineStr">
+      <c r="D107" s="51" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="E90" s="51" t="inlineStr">
+      <c r="E107" s="51" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="F90" s="51" t="inlineStr">
+      <c r="F107" s="51" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="G90" s="51" t="inlineStr">
+      <c r="G107" s="51" t="inlineStr">
         <is>
           <t>0000001</t>
         </is>
       </c>
-      <c r="H90" s="51" t="inlineStr">
+      <c r="H107" s="51" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="I90" s="52" t="n">
+      <c r="I107" s="52" t="n">
         <v>6</v>
       </c>
-      <c r="J90" s="51" t="inlineStr">
+      <c r="J107" s="51" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K90" s="51" t="inlineStr">
+      <c r="K107" s="51" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L90" s="51" t="inlineStr">
+      <c r="L107" s="51" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M90" s="66" t="inlineStr">
+      <c r="M107" s="66" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N90" s="51" t="inlineStr">
+      <c r="N107" s="51" t="inlineStr">
         <is>
           <t>Not changed (PO_MAPPED_FLAG stays Y)</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="57" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="57" t="inlineStr">
         <is>
           <t>UPD</t>
         </is>
       </c>
-      <c r="B91" s="58" t="inlineStr">
+      <c r="B108" s="58" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="C91" s="58" t="inlineStr">
+      <c r="C108" s="58" t="inlineStr">
         <is>
           <t>CO-14111</t>
         </is>
       </c>
-      <c r="D91" s="58" t="inlineStr">
+      <c r="D108" s="58" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="E91" s="58" t="inlineStr">
+      <c r="E108" s="58" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="F91" s="58" t="inlineStr">
+      <c r="F108" s="58" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="G91" s="58" t="inlineStr">
+      <c r="G108" s="58" t="inlineStr">
         <is>
           <t>0000001</t>
         </is>
       </c>
-      <c r="H91" s="58" t="inlineStr">
+      <c r="H108" s="58" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="I91" s="59" t="n">
+      <c r="I108" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="J91" s="58" t="inlineStr">
+      <c r="J108" s="58" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K91" s="58" t="inlineStr">
+      <c r="K108" s="58" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L91" s="60" t="inlineStr">
+      <c r="L108" s="60" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="M91" s="49" t="inlineStr">
+      <c r="M108" s="49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N91" s="58" t="inlineStr">
+      <c r="N108" s="58" t="inlineStr">
         <is>
           <t>PO and ASN through ASN0003</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="35" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="35" t="inlineStr">
         <is>
           <t>TB_H_CROSSDOCK_ORDER_CHANGE</t>
         </is>
       </c>
-      <c r="D93" s="47" t="inlineStr">
+      <c r="D110" s="47" t="inlineStr">
         <is>
           <t>New table (Crossdock)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="26" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
+    <row r="111" ht="26" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B94" s="42" t="inlineStr">
+      <c r="B111" s="42" t="inlineStr">
         <is>
           <t>HIST_ID</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>ASN_NO</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>CASE_NO</t>
         </is>
       </c>
-      <c r="E94" s="3" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>PART_NO</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>FROM_CUSTOMER_ORDER_NO</t>
         </is>
       </c>
-      <c r="G94" s="3" t="inlineStr">
+      <c r="G111" s="3" t="inlineStr">
         <is>
           <t>FROM_SERIAL_NO</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H111" s="3" t="inlineStr">
         <is>
           <t>TO_CUSTOMER_ORDER_NO</t>
         </is>
       </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="I111" s="3" t="inlineStr">
         <is>
           <t>TO_DESTINATION_CD</t>
         </is>
       </c>
-      <c r="J94" s="3" t="inlineStr">
+      <c r="J111" s="3" t="inlineStr">
         <is>
           <t>QTY</t>
         </is>
       </c>
-      <c r="K94" s="3" t="inlineStr">
+      <c r="K111" s="3" t="inlineStr">
         <is>
           <t>FROM_INSTRUCTION_ID</t>
         </is>
       </c>
-      <c r="L94" s="3" t="inlineStr">
+      <c r="L111" s="3" t="inlineStr">
         <is>
           <t>TO_INSTRUCTION_ID</t>
         </is>
       </c>
-      <c r="M94" s="3" t="inlineStr">
+      <c r="M111" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="48" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="48" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="B95" s="53" t="n">
+      <c r="B112" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="C95" s="49" t="inlineStr">
+      <c r="C112" s="49" t="inlineStr">
         <is>
           <t>ASN0003</t>
         </is>
       </c>
-      <c r="D95" s="49" t="inlineStr">
+      <c r="D112" s="49" t="inlineStr">
         <is>
           <t>C-0003-03</t>
         </is>
       </c>
-      <c r="E95" s="49" t="inlineStr">
+      <c r="E112" s="49" t="inlineStr">
         <is>
           <t>PART-X</t>
         </is>
       </c>
-      <c r="F95" s="49" t="inlineStr">
+      <c r="F112" s="49" t="inlineStr">
         <is>
           <t>CO-14104</t>
         </is>
       </c>
-      <c r="G95" s="49" t="inlineStr">
+      <c r="G112" s="49" t="inlineStr">
         <is>
           <t>0000001</t>
         </is>
       </c>
-      <c r="H95" s="49" t="inlineStr">
+      <c r="H112" s="49" t="inlineStr">
         <is>
           <t>CO-14111</t>
         </is>
       </c>
-      <c r="I95" s="49" t="inlineStr">
+      <c r="I112" s="49" t="inlineStr">
         <is>
           <t>9722D10</t>
         </is>
       </c>
-      <c r="J95" s="53" t="n">
+      <c r="J112" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="K95" s="53" t="n">
+      <c r="K112" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="L95" s="53" t="n">
+      <c r="L112" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="M95" s="49" t="inlineStr"/>
+      <c r="M112" s="49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -39713,7 +40566,7 @@
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>PART-X, 6 pcs/case. One PO per customer order date: PO_DT = order date + 1, qty = total order qty of the date (all destinations). PO qty &lt; order qty is an abnormality: the rest comes in a split PO. ORDER_STATUS of the replicate keeps 7; changes go to UPD_STATUS. Order date 15-Oct (12) → PO-DMY-09011; CO-14102 on hold then cancelled, so its 6 pcs of PO-DMY-09011 go to CO-14103 (older PO_DT first). Order date 17-Oct: 4 destinations, 30 pcs, PO-DMY-09013 only 18 (abnormal) → case 5 Not Ready until the split PO-DMY-09014 (12, 19-Oct). Cases 1-4 → ASN0003; CO-14104 (middle row, case 3) is cancelled after the ASN. 21-Oct G-System allocates the pcs of case 3 to CO-14111 (UPD_STATUS 6, no ASN): the D/S team moves case 3 to CO-14111 (XD11). Open PO qty at the end (12) = cancelled qty (CO-14102 + CO-14104).</t>
+          <t>PART-X, 6 pcs/case. One PO per customer order date: PO_DT = order date + 1, qty = total order qty of the date (all destinations). PO qty &lt; order qty is an abnormality: the rest comes in a split PO. ORDER_STATUS of the replicate keeps 7; changes go to UPD_STATUS. Order date 15-Oct (12) → PO-DMY-09011; CO-14102 on hold then cancelled, so its 6 pcs of PO-DMY-09011 go to CO-14103 (older PO_DT first). Order date 17-Oct: 4 destinations, 30 pcs, PO-DMY-09013 only 18 (abnormal) → case 5 Not Ready until the split PO-DMY-09014 (12, 19-Oct). Cases 1-4 → ASN0003; CO-14104 (middle row, case 3) is cancelled after the ASN. Order date 18-Oct: 3 destinations, 18 pcs, PO-DMY-09015 18 (OK) → ASN0005. 21-Oct G-System allocates the pcs of case 3 to CO-14111 (UPD_STATUS 6, no ASN): the D/S team moves case 3 to CO-14111 (XD11). Open PO qty at the end (12) = cancelled qty (CO-14102 + CO-14104).</t>
         </is>
       </c>
     </row>

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -21,6 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-7" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-8" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-9" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIM-10" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Column Definition'!$A$3:$H$470</definedName>
@@ -23599,6 +23600,1334 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SIM-10 One line in 2 ASNs; partial receipt splits the serial → XD08 re-assigns TB_R_INSTRUCTION (simulasi_asn.xlsx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>BPF F2 · Functions: XD09, XD10, XD08 (serial split)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>• CO-14115 VN 12 pcs (order date 19-Oct), 6 pcs/case: case 1 → ASN0006 (rit 1), case 2 → ASN0007 (rit 2). One H0253 row, two TB_R_INSTRUCTION rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>• 21-Oct ASN0006 received: G-System splits the line into serial 0000001 6 pcs status 6 and serial 0000002 6 pcs status 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>• Upsert alone: serial 0000001 has 12 pcs in TB_R_INSTRUCTION for qty 6 and serial 0000002 looks open (6) → XD09 would map it again (double). XD08 re-assigns the rows: serial 0000001 = ASN0006 (oldest ASN = received), serial 0000002 = ASN0007; both PO_MAPPED_FLAG Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>NEW row</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>UPD row</t>
+        </is>
+      </c>
+      <c r="D7" s="38" t="inlineStr">
+        <is>
+          <t>DEL row</t>
+        </is>
+      </c>
+      <c r="E7" s="39" t="inlineStr">
+        <is>
+          <t>READ row</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>TEMP row</t>
+        </is>
+      </c>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>Changed cell</t>
+        </is>
+      </c>
+      <c r="H7" s="42" t="inlineStr">
+        <is>
+          <t>PK column</t>
+        </is>
+      </c>
+      <c r="I7" s="36" t="inlineStr">
+        <is>
+          <t>Status OK</t>
+        </is>
+      </c>
+      <c r="J7" s="43" t="inlineStr">
+        <is>
+          <t>Status attention</t>
+        </is>
+      </c>
+      <c r="K7" s="44" t="inlineStr">
+        <is>
+          <t>Status NG / cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>1. 20-Oct ASN0006 (case 1) and ASN0007 (case 2): one line in 2 ASNs</t>
+        </is>
+      </c>
+      <c r="B9" s="46" t="n"/>
+      <c r="C9" s="46" t="n"/>
+      <c r="D9" s="46" t="n"/>
+      <c r="E9" s="46" t="n"/>
+      <c r="F9" s="46" t="n"/>
+      <c r="G9" s="46" t="n"/>
+      <c r="H9" s="46" t="n"/>
+      <c r="I9" s="46" t="n"/>
+      <c r="J9" s="46" t="n"/>
+      <c r="K9" s="46" t="n"/>
+      <c r="L9" s="46" t="n"/>
+      <c r="M9" s="46" t="n"/>
+      <c r="N9" s="46" t="n"/>
+      <c r="O9" s="46" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>LINE_SEQ</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B12" s="53" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F12" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G12" s="49" t="inlineStr">
+        <is>
+          <t>CO-14115</t>
+        </is>
+      </c>
+      <c r="H12" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I12" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09015</t>
+        </is>
+      </c>
+      <c r="K12" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09015</t>
+        </is>
+      </c>
+      <c r="L12" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M12" s="49" t="inlineStr">
+        <is>
+          <t>ASN0006</t>
+        </is>
+      </c>
+      <c r="N12" s="49" t="inlineStr">
+        <is>
+          <t>C-0006-01</t>
+        </is>
+      </c>
+      <c r="O12" s="49" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="n">
+        <v>13</v>
+      </c>
+      <c r="C13" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F13" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G13" s="49" t="inlineStr">
+        <is>
+          <t>CO-14115</t>
+        </is>
+      </c>
+      <c r="H13" s="49" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I13" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="49" t="inlineStr">
+        <is>
+          <t>PO-DMY-09016</t>
+        </is>
+      </c>
+      <c r="K13" s="49" t="inlineStr">
+        <is>
+          <t>MF-DMY-09016</t>
+        </is>
+      </c>
+      <c r="L13" s="49" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M13" s="49" t="inlineStr">
+        <is>
+          <t>ASN0007</t>
+        </is>
+      </c>
+      <c r="N13" s="49" t="inlineStr">
+        <is>
+          <t>C-0007-01</t>
+        </is>
+      </c>
+      <c r="O13" s="49" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D15" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C16" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E16" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F16" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G16" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>UPD_STATUS</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B17" s="58" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C17" s="58" t="inlineStr">
+        <is>
+          <t>CO-14115</t>
+        </is>
+      </c>
+      <c r="D17" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E17" s="58" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F17" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G17" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H17" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I17" s="59" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K17" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L17" s="60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M17" s="58" t="n"/>
+      <c r="N17" s="58" t="inlineStr">
+        <is>
+          <t>N after ASN0006 (6 of 12), Y after ASN0007</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>2. 21-Oct XD08 upsert: ASN0006 received, G-System split the line</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="n"/>
+      <c r="C19" s="46" t="n"/>
+      <c r="D19" s="46" t="n"/>
+      <c r="E19" s="46" t="n"/>
+      <c r="F19" s="46" t="n"/>
+      <c r="G19" s="46" t="n"/>
+      <c r="H19" s="46" t="n"/>
+      <c r="I19" s="46" t="n"/>
+      <c r="J19" s="46" t="n"/>
+      <c r="K19" s="46" t="n"/>
+      <c r="L19" s="46" t="n"/>
+      <c r="M19" s="46" t="n"/>
+      <c r="N19" s="46" t="n"/>
+      <c r="O19" s="46" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D20" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C21" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E21" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F21" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G21" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>UPD_STATUS</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C22" s="58" t="inlineStr">
+        <is>
+          <t>CO-14115</t>
+        </is>
+      </c>
+      <c r="D22" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E22" s="58" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F22" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G22" s="58" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="H22" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I22" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K22" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L22" s="58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M22" s="60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N22" s="58" t="inlineStr">
+        <is>
+          <t>12 → 6, received</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>CO-14115</t>
+        </is>
+      </c>
+      <c r="D23" s="49" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G23" s="49" t="inlineStr">
+        <is>
+          <t>0000002</t>
+        </is>
+      </c>
+      <c r="H23" s="49" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I23" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" s="49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K23" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L23" s="49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M23" s="49" t="n"/>
+      <c r="N23" s="49" t="inlineStr">
+        <is>
+          <t>New serial, status 7: without step 3 open qty 6 = double mapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="45" t="inlineStr">
+        <is>
+          <t>3. 21-Oct XD08 serial split: rows re-assigned (LOG7)</t>
+        </is>
+      </c>
+      <c r="B25" s="46" t="n"/>
+      <c r="C25" s="46" t="n"/>
+      <c r="D25" s="46" t="n"/>
+      <c r="E25" s="46" t="n"/>
+      <c r="F25" s="46" t="n"/>
+      <c r="G25" s="46" t="n"/>
+      <c r="H25" s="46" t="n"/>
+      <c r="I25" s="46" t="n"/>
+      <c r="J25" s="46" t="n"/>
+      <c r="K25" s="46" t="n"/>
+      <c r="L25" s="46" t="n"/>
+      <c r="M25" s="46" t="n"/>
+      <c r="N25" s="46" t="n"/>
+      <c r="O25" s="46" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="D26" s="47" t="inlineStr">
+        <is>
+          <t>New table (Crossdock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B27" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCTION_ID</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>CASE_SEQ</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>LINE_SEQ</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>PART_NO</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>PO_NO</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_NO</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>MANIFEST_ITEM</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>ASN_NO</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>CASE_NO</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="B28" s="52" t="n">
+        <v>12</v>
+      </c>
+      <c r="C28" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="51" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F28" s="51" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G28" s="51" t="inlineStr">
+        <is>
+          <t>CO-14115</t>
+        </is>
+      </c>
+      <c r="H28" s="51" t="inlineStr">
+        <is>
+          <t>0000001</t>
+        </is>
+      </c>
+      <c r="I28" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" s="51" t="inlineStr">
+        <is>
+          <t>PO-DMY-09015</t>
+        </is>
+      </c>
+      <c r="K28" s="51" t="inlineStr">
+        <is>
+          <t>MF-DMY-09015</t>
+        </is>
+      </c>
+      <c r="L28" s="51" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M28" s="51" t="inlineStr">
+        <is>
+          <t>ASN0006</t>
+        </is>
+      </c>
+      <c r="N28" s="51" t="inlineStr">
+        <is>
+          <t>C-0006-01</t>
+        </is>
+      </c>
+      <c r="O28" s="51" t="inlineStr">
+        <is>
+          <t>Oldest ASN → serial with status 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B29" s="59" t="n">
+        <v>13</v>
+      </c>
+      <c r="C29" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="F29" s="58" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="G29" s="58" t="inlineStr">
+        <is>
+          <t>CO-14115</t>
+        </is>
+      </c>
+      <c r="H29" s="60" t="inlineStr">
+        <is>
+          <t>0000002</t>
+        </is>
+      </c>
+      <c r="I29" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J29" s="58" t="inlineStr">
+        <is>
+          <t>PO-DMY-09016</t>
+        </is>
+      </c>
+      <c r="K29" s="58" t="inlineStr">
+        <is>
+          <t>MF-DMY-09016</t>
+        </is>
+      </c>
+      <c r="L29" s="58" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="M29" s="58" t="inlineStr">
+        <is>
+          <t>ASN0007</t>
+        </is>
+      </c>
+      <c r="N29" s="58" t="inlineStr">
+        <is>
+          <t>C-0007-01</t>
+        </is>
+      </c>
+      <c r="O29" s="58" t="inlineStr">
+        <is>
+          <t>Next ASN → serial with status 7; case, PO, ASN not changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D31" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B32" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E32" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F32" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G32" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>UPD_STATUS</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B33" s="58" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C33" s="58" t="inlineStr">
+        <is>
+          <t>CO-14115</t>
+        </is>
+      </c>
+      <c r="D33" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E33" s="58" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F33" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G33" s="58" t="inlineStr">
+        <is>
+          <t>0000002</t>
+        </is>
+      </c>
+      <c r="H33" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I33" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J33" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K33" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L33" s="60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M33" s="58" t="n"/>
+      <c r="N33" s="58" t="inlineStr">
+        <is>
+          <t>Fully in TB_R_INSTRUCTION: not taken by XD09</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="45" t="inlineStr">
+        <is>
+          <t>4. 22-Oct XD08: ASN0007 received</t>
+        </is>
+      </c>
+      <c r="B35" s="46" t="n"/>
+      <c r="C35" s="46" t="n"/>
+      <c r="D35" s="46" t="n"/>
+      <c r="E35" s="46" t="n"/>
+      <c r="F35" s="46" t="n"/>
+      <c r="G35" s="46" t="n"/>
+      <c r="H35" s="46" t="n"/>
+      <c r="I35" s="46" t="n"/>
+      <c r="J35" s="46" t="n"/>
+      <c r="K35" s="46" t="n"/>
+      <c r="L35" s="46" t="n"/>
+      <c r="M35" s="46" t="n"/>
+      <c r="N35" s="46" t="n"/>
+      <c r="O35" s="46" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="35" t="inlineStr">
+        <is>
+          <t>TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="D36" s="47" t="inlineStr">
+        <is>
+          <t>Replicated from DB Surrounding (G-System)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B37" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CD</t>
+        </is>
+      </c>
+      <c r="C37" s="42" t="inlineStr">
+        <is>
+          <t>CUSTOMER_ORDER_NO</t>
+        </is>
+      </c>
+      <c r="D37" s="42" t="inlineStr">
+        <is>
+          <t>ORDER_DT</t>
+        </is>
+      </c>
+      <c r="E37" s="42" t="inlineStr">
+        <is>
+          <t>DESTINATION_CD</t>
+        </is>
+      </c>
+      <c r="F37" s="42" t="inlineStr">
+        <is>
+          <t>DETAILED_ITEM_NO</t>
+        </is>
+      </c>
+      <c r="G37" s="42" t="inlineStr">
+        <is>
+          <t>SERIAL_NO</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>SHIPPING_PART_NO</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS_QTY</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>ORDER_STATUS</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>HOLD_FLAG</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>PO_MAPPED_FLAG</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>UPD_STATUS</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="57" t="inlineStr">
+        <is>
+          <t>UPD</t>
+        </is>
+      </c>
+      <c r="B38" s="58" t="inlineStr">
+        <is>
+          <t>9715300</t>
+        </is>
+      </c>
+      <c r="C38" s="58" t="inlineStr">
+        <is>
+          <t>CO-14115</t>
+        </is>
+      </c>
+      <c r="D38" s="58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E38" s="58" t="inlineStr">
+        <is>
+          <t>9715310</t>
+        </is>
+      </c>
+      <c r="F38" s="58" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G38" s="58" t="inlineStr">
+        <is>
+          <t>0000002</t>
+        </is>
+      </c>
+      <c r="H38" s="58" t="inlineStr">
+        <is>
+          <t>PART-X</t>
+        </is>
+      </c>
+      <c r="I38" s="59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" s="58" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K38" s="58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L38" s="58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M38" s="60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N38" s="58" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -23921,7 +25250,7 @@
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-4, SIM-5, SIM-6, SIM-7, SIM-8, SIM-9</t>
+          <t>SIM-10, SIM-2, SIM-4, SIM-5, SIM-6, SIM-7, SIM-8, SIM-9</t>
         </is>
       </c>
     </row>
@@ -23981,7 +25310,7 @@
       </c>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>SIM-2, SIM-4, SIM-5, SIM-6, SIM-7, SIM-8, SIM-9</t>
+          <t>SIM-10, SIM-2, SIM-4, SIM-5, SIM-6, SIM-7, SIM-8, SIM-9</t>
         </is>
       </c>
     </row>
@@ -40353,7 +41682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -40695,6 +42024,38 @@
       <c r="F13" s="32" t="inlineStr">
         <is>
           <t>Same unit as SIM-7 (PART-A 14-Oct: V01 VN 10, T01 TH 6, V02 VN 14; 6 pcs/case) but all 5 cases have a PO (p1 24 + p2 6). XD10 shows one check box per supplier case. The supplier wants cases 1 and 2 only: case 2 = VN 4 + TH 2 ends with VN 10 / TH 2 (CUT_FLAG N), so the warehouse could not close the VN and TH cases. XD10 ticks case 3 too (message no. 10): cases 1-3 = 18 pcs. [Create ASN] inserts the slices of cases 1-3; V01 and T01 are complete (PO_MAPPED_FLAG Y), V02 keeps 12 pcs open for a later ASN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>SIM-10</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>One line in 2 ASNs; partial receipt splits the serial → XD08 re-assigns TB_R_INSTRUCTION (simulasi_asn.xlsx)</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>BPF F2</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>XD09, XD10, XD08 (serial split)</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>TB_R_INSTRUCTION, TB_R_H0253_ORDER_CONTROL_PRE</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>CO-14115 VN 12 pcs (order date 19-Oct), 6 pcs/case: case 1 → ASN0006 (rit 1), case 2 → ASN0007 (rit 2). One H0253 row, two TB_R_INSTRUCTION rows. 21-Oct ASN0006 received: G-System splits the line into serial 0000001 6 pcs status 6 and serial 0000002 6 pcs status 7. Upsert alone: serial 0000001 has 12 pcs in TB_R_INSTRUCTION for qty 6 and serial 0000002 looks open (6) → XD09 would map it again (double). XD08 re-assigns the rows: serial 0000001 = ASN0006 (oldest ASN = received), serial 0000002 = ASN0007; both PO_MAPPED_FLAG Y.</t>
         </is>
       </c>
     </row>

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -47268,7 +47268,7 @@
       </c>
       <c r="D70" s="49" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="E70" s="49" t="inlineStr">
@@ -47332,7 +47332,7 @@
       </c>
       <c r="D71" s="49" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="E71" s="49" t="inlineStr">
@@ -47396,7 +47396,7 @@
       </c>
       <c r="D72" s="49" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="E72" s="49" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="H76" s="49" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="I76" s="49" t="inlineStr">
@@ -47618,7 +47618,7 @@
       </c>
       <c r="H77" s="49" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="I77" s="49" t="inlineStr">
@@ -47677,7 +47677,7 @@
       </c>
       <c r="H78" s="49" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="I78" s="49" t="inlineStr">
@@ -47736,7 +47736,7 @@
       </c>
       <c r="H79" s="49" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="I79" s="49" t="inlineStr">
@@ -47795,7 +47795,7 @@
       </c>
       <c r="H80" s="49" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="I80" s="49" t="inlineStr">
@@ -48036,7 +48036,7 @@
       </c>
       <c r="M88" s="60" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="N88" s="60" t="inlineStr">
@@ -48101,7 +48101,7 @@
       </c>
       <c r="M89" s="60" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="N89" s="60" t="inlineStr">
@@ -48166,7 +48166,7 @@
       </c>
       <c r="M90" s="60" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="N90" s="60" t="inlineStr">
@@ -48231,7 +48231,7 @@
       </c>
       <c r="M91" s="60" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="N91" s="60" t="inlineStr">
@@ -48296,7 +48296,7 @@
       </c>
       <c r="M92" s="60" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="N92" s="60" t="inlineStr">
@@ -48361,7 +48361,7 @@
       </c>
       <c r="M93" s="60" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="N93" s="60" t="inlineStr">
@@ -48426,7 +48426,7 @@
       </c>
       <c r="M94" s="60" t="inlineStr">
         <is>
-          <t>ASN-50221-261016-001</t>
+          <t>ASN0101</t>
         </is>
       </c>
       <c r="N94" s="60" t="inlineStr">

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -17327,7 +17327,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIM-7 Scan order, supplier cases and ASN options (two ASNs)</t>
+          <t>SIM-7 H0253 order, supplier cases and ASN options (two ASNs)</t>
         </is>
       </c>
     </row>
@@ -17341,7 +17341,7 @@
     <row r="3">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>• PART-A 14-Oct, 6 pcs/case: V01 VN 10, T01 TH 6, V02 VN 14 (dummy customer codes CUST-A / B / C give this scan order).</t>
+          <t>• PART-A 14-Oct, 6 pcs/case: V01 VN 10, T01 TH 6, V02 VN 14 (dummy customer codes CUST-A / B / C give this H0253 order).</t>
         </is>
       </c>
     </row>
@@ -19935,7 +19935,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIM-8 SORT_SEQ: H0253 lines into scan order, partial send and re-cut</t>
+          <t>SIM-8 SORT_SEQ: H0253 lines into H0253 order, partial send and re-cut</t>
         </is>
       </c>
     </row>
@@ -19949,7 +19949,7 @@
     <row r="3">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>• PART-B, 6 pcs/case. Scan order = G-System allocation order with Allocation Priority = Customer Order Date: 1) Allocation Priority, 2) Customer Code, 3) Customer Order No, 4) Order Date, 5) Order Time, 6) Destination, 7) Detailed Item No, 8) Serial No. Keys 2-8 are the PK of the H0253 replicate; XD09 reads with ORDER BY Part, Allocation Priority + the PK columns (query in XD09 Appendix). SORT_SEQ = row number per unit.</t>
+          <t>• PART-B, 6 pcs/case. H0253 order (ORDER BY) with Allocation Priority = Customer Order Date: 1) Allocation Priority, 2) Customer Code, 3) Customer Order No, 4) Order Date, 5) Order Time, 6) Destination, 7) Detailed Item No, 8) Serial No. Keys 2-8 are the PK of the H0253 replicate; XD09 reads with ORDER BY Part, Allocation Priority + the PK columns (query in XD09 Appendix). SORT_SEQ = row number per unit.</t>
         </is>
       </c>
     </row>
@@ -20034,7 +20034,7 @@
     <row r="10">
       <c r="A10" s="45" t="inlineStr">
         <is>
-          <t>1. H0253 lines in scan order: ORDER BY Part, Allocation Priority (= Order Date), PK columns</t>
+          <t>1. H0253 lines in H0253 order: ORDER BY Part, Allocation Priority (= Order Date), PK columns</t>
         </is>
       </c>
       <c r="B10" s="46" t="n"/>
@@ -25330,7 +25330,7 @@
       </c>
       <c r="D15" s="32" t="inlineStr">
         <is>
-          <t>Temporary table of one Search run (session): the open qty of the customer order lines (H0253, order status 7, Hold Flag N) in scan order, pre-mapped to the supplier POs (Pra Daily Order) and cut into supplier cases and blocks. One row per line x PO x supplier case; PO_NO NULL for the qty still without a PO. Columns proposed.</t>
+          <t>Temporary table of one Search run (session): the open qty of the customer order lines (H0253, order status 7, Hold Flag N) in H0253 order, pre-mapped to the supplier POs (Pra Daily Order) and cut into supplier cases and blocks. One row per line x PO x supplier case; PO_NO NULL for the qty still without a PO. Columns proposed.</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr">
@@ -33865,7 +33865,7 @@
       </c>
       <c r="H230" s="32" t="inlineStr">
         <is>
-          <t>Scan order of the line within the unit (refer 4.1)</t>
+          <t>H0253 order of the line within the unit (refer 4.1)</t>
         </is>
       </c>
     </row>
@@ -33901,7 +33901,7 @@
       </c>
       <c r="H231" s="32" t="inlineStr">
         <is>
-          <t>H0253.CUSTOMER_CD (scan key 1)</t>
+          <t>H0253.CUSTOMER_CD (order key 1)</t>
         </is>
       </c>
     </row>
@@ -33937,7 +33937,7 @@
       </c>
       <c r="H232" s="32" t="inlineStr">
         <is>
-          <t>H0253.CUSTOMER_ORDER_NO (scan key 2)</t>
+          <t>H0253.CUSTOMER_ORDER_NO (order key 2)</t>
         </is>
       </c>
     </row>
@@ -33973,7 +33973,7 @@
       </c>
       <c r="H233" s="32" t="inlineStr">
         <is>
-          <t>Customer Order Date (H0253.ORDER_DT; unit and scan key 3)</t>
+          <t>Customer Order Date (H0253.ORDER_DT; unit and order key 3)</t>
         </is>
       </c>
     </row>
@@ -34005,7 +34005,7 @@
       </c>
       <c r="H234" s="32" t="inlineStr">
         <is>
-          <t>H0253.ORDER_TIME (scan key 4)</t>
+          <t>H0253.ORDER_TIME (order key 4)</t>
         </is>
       </c>
     </row>
@@ -34041,7 +34041,7 @@
       </c>
       <c r="H235" s="32" t="inlineStr">
         <is>
-          <t>H0253.DESTINATION_CD (scan key 5)</t>
+          <t>H0253.DESTINATION_CD (order key 5)</t>
         </is>
       </c>
     </row>
@@ -34077,7 +34077,7 @@
       </c>
       <c r="H236" s="32" t="inlineStr">
         <is>
-          <t>H0253.DETAILED_ITEM_NO (scan key 6)</t>
+          <t>H0253.DETAILED_ITEM_NO (order key 6)</t>
         </is>
       </c>
     </row>
@@ -34113,7 +34113,7 @@
       </c>
       <c r="H237" s="32" t="inlineStr">
         <is>
-          <t>H0253.SERIAL_NO (scan key 7)</t>
+          <t>H0253.SERIAL_NO (order key 7)</t>
         </is>
       </c>
     </row>
@@ -34729,7 +34729,7 @@
       </c>
       <c r="H256" s="32" t="inlineStr">
         <is>
-          <t>Supplier case of the slice within the unit (PCS_CASE pcs in scan order)</t>
+          <t>Supplier case of the slice within the unit (PCS_CASE pcs in H0253 order)</t>
         </is>
       </c>
     </row>
@@ -41799,7 +41799,7 @@
       </c>
       <c r="F6" s="32" t="inlineStr">
         <is>
-          <t>G-System releases crossdock orders 14-Oct (status 7); the supplier POs of 15-Oct are crossdock manifests (CROSS_DOCK_FLAG X). Supplier searches delivery 16-Oct Rit 1: PART-X (VN 18 + TH 6 = 4 cases in scan order, 4 blocks) and PART-Y (PH 6 = 1 case) are Ready; all blocks are chosen, Create ASN and Submit. Result: one ASN with 5 cases / 30 pcs, 3 ASN manifests (one per Pra manifest), 5 ASN part rows (manifest item x case).</t>
+          <t>G-System releases crossdock orders 14-Oct (status 7); the supplier POs of 15-Oct are crossdock manifests (CROSS_DOCK_FLAG X). Supplier searches delivery 16-Oct Rit 1: PART-X (VN 18 + TH 6 = 4 cases in H0253 order, 4 blocks) and PART-Y (PH 6 = 1 case) are Ready; all blocks are chosen, Create ASN and Submit. Result: one ASN with 5 cases / 30 pcs, 3 ASN manifests (one per Pra manifest), 5 ASN part rows (manifest item x case).</t>
         </is>
       </c>
     </row>
@@ -41831,7 +41831,7 @@
       </c>
       <c r="F7" s="32" t="inlineStr">
         <is>
-          <t>PART-X 14-Oct needs 24 pcs (VN 18, TH 6) but only 18 pcs of crossdock PO are released on 15-Oct (PO-DMY-09001 12 + PO-DMY-09002 6). Scan order VN (CO-14101..14103) then TH (CO-14104): cases 1-3 (VN) have a PO, case 4 (TH) has none. Every case ends a valid cut, so blocks 1-3 are Ready and block 4 Not Ready: the unit is Partially Ready (ASN options 1 / 2 / 3 cases). In this simulation the supplier waits: on 16-Oct a new crossdock manifest (PO-DMY-10001, 6 pcs) is released → [Search] again → block 4 Ready.</t>
+          <t>PART-X 14-Oct needs 24 pcs (VN 18, TH 6) but only 18 pcs of crossdock PO are released on 15-Oct (PO-DMY-09001 12 + PO-DMY-09002 6). H0253 order VN (CO-14101..14103) then TH (CO-14104): cases 1-3 (VN) have a PO, case 4 (TH) has none. Every case ends a valid cut, so blocks 1-3 are Ready and block 4 Not Ready: the unit is Partially Ready (ASN options 1 / 2 / 3 cases). In this simulation the supplier waits: on 16-Oct a new crossdock manifest (PO-DMY-10001, 6 pcs) is released → [Search] again → block 4 Ready.</t>
         </is>
       </c>
     </row>
@@ -41863,7 +41863,7 @@
       </c>
       <c r="F8" s="32" t="inlineStr">
         <is>
-          <t>The D/S team holds Thailand of PART-X 14-Oct: HOLD_FLAG Y on CO-14104. XD09 does not take held lines: the scan order and the blocks are computed with Vietnam only (18 pcs = 3 cases, 3 blocks) and the unit is Ready. If the supplier had ticked the unit before the hold, [Create ASN] fails for the whole selection (MSG8): nothing is inserted.</t>
+          <t>The D/S team holds Thailand of PART-X 14-Oct: HOLD_FLAG Y on CO-14104. XD09 does not take held lines: the H0253 order and the blocks are computed with Vietnam only (18 pcs = 3 cases, 3 blocks) and the unit is Ready. If the supplier had ticked the unit before the hold, [Create ASN] fails for the whole selection (MSG8): nothing is inserted.</t>
         </is>
       </c>
     </row>
@@ -41939,7 +41939,7 @@
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>Scan order, supplier cases and ASN options (two ASNs)</t>
+          <t>H0253 order, supplier cases and ASN options (two ASNs)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -41959,7 +41959,7 @@
       </c>
       <c r="F11" s="32" t="inlineStr">
         <is>
-          <t>PART-A 14-Oct, 6 pcs/case: V01 VN 10, T01 TH 6, V02 VN 14 (dummy customer codes CUST-A / B / C give this scan order). p1 (24 pcs) is released 15-Oct, p2 (6 pcs) 16-Oct. Cuts are valid after cases 1, 3, 4 and 5 (VN / TH multiples of 6): blocks case 1 | 2-3 | 4 | 5. 15-Oct: blocks 1-3 Ready, the supplier chooses option 4 cases (blocks 1-3, 24 pcs). 16-Oct: the open 6 pcs of V02 get p2 and go in a second ASN.</t>
+          <t>PART-A 14-Oct, 6 pcs/case: V01 VN 10, T01 TH 6, V02 VN 14 (dummy customer codes CUST-A / B / C give this H0253 order). p1 (24 pcs) is released 15-Oct, p2 (6 pcs) 16-Oct. Cuts are valid after cases 1, 3, 4 and 5 (VN / TH multiples of 6): blocks case 1 | 2-3 | 4 | 5. 15-Oct: blocks 1-3 Ready, the supplier chooses option 4 cases (blocks 1-3, 24 pcs). 16-Oct: the open 6 pcs of V02 get p2 and go in a second ASN.</t>
         </is>
       </c>
     </row>
@@ -41971,7 +41971,7 @@
       </c>
       <c r="B12" s="32" t="inlineStr">
         <is>
-          <t>SORT_SEQ: H0253 lines into scan order, partial send and re-cut</t>
+          <t>SORT_SEQ: H0253 lines into H0253 order, partial send and re-cut</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -41991,7 +41991,7 @@
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>PART-B, 6 pcs/case. Scan order = G-System allocation order with Allocation Priority = Customer Order Date: 1) Allocation Priority, 2) Customer Code, 3) Customer Order No, 4) Order Date, 5) Order Time, 6) Destination, 7) Detailed Item No, 8) Serial No. Keys 2-8 are the PK of the H0253 replicate; XD09 reads with ORDER BY Part, Allocation Priority + the PK columns (query in XD09 Appendix). SORT_SEQ = row number per unit. Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. A-0201 (15-Oct) comes after all 14-Oct lines (Allocation Priority) and is the next unit. 15-Oct: PO1 20 pcs → blocks 1-2 Ready, block 3 (case 4) only 2 of 6 pcs with PO → Not Ready. The supplier sends option 1 case only. 16-Oct: PO2 10 pcs. The open qty (24) is cut again from case 1 in the same SORT_SEQ: the cases are the same as before. Unit 15-Oct (A-0201) comes after unit 14-Oct (way B), so it gets no PO yet.</t>
+          <t>PART-B, 6 pcs/case. H0253 order (ORDER BY) with Allocation Priority = Customer Order Date: 1) Allocation Priority, 2) Customer Code, 3) Customer Order No, 4) Order Date, 5) Order Time, 6) Destination, 7) Detailed Item No, 8) Serial No. Keys 2-8 are the PK of the H0253 replicate; XD09 reads with ORDER BY Part, Allocation Priority + the PK columns (query in XD09 Appendix). SORT_SEQ = row number per unit. Unit 14-Oct: A-0101 item 001 VN 8 (seq 1), A-0101 item 002 VN 2 (seq 2), B-0102 TH 6 (seq 3), C-0103 VN 14 of a second VN customer 9730000 (seq 4). Order Time 07:00 of C-0103 does not move it up: Customer Code and Order No come first. A-0201 (15-Oct) comes after all 14-Oct lines (Allocation Priority) and is the next unit. 15-Oct: PO1 20 pcs → blocks 1-2 Ready, block 3 (case 4) only 2 of 6 pcs with PO → Not Ready. The supplier sends option 1 case only. 16-Oct: PO2 10 pcs. The open qty (24) is cut again from case 1 in the same SORT_SEQ: the cases are the same as before. Unit 15-Oct (A-0201) comes after unit 14-Oct (way B), so it gets no PO yet.</t>
         </is>
       </c>
     </row>
@@ -44630,7 +44630,7 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>• Supplier searches delivery 16-Oct Rit 1: PART-X (VN 18 + TH 6 = 4 cases in scan order, 4 blocks) and PART-Y (PH 6 = 1 case) are Ready; all blocks are chosen, Create ASN and Submit.</t>
+          <t>• Supplier searches delivery 16-Oct Rit 1: PART-X (VN 18 + TH 6 = 4 cases in H0253 order, 4 blocks) and PART-Y (PH 6 = 1 case) are Ready; all blocks are chosen, Create ASN and Submit.</t>
         </is>
       </c>
     </row>
@@ -45523,7 +45523,7 @@
     <row r="31">
       <c r="A31" s="45" t="inlineStr">
         <is>
-          <t>3. [Search] → XD09 pre-mapping in scan order: cases and blocks (session)</t>
+          <t>3. [Search] → XD09 pre-mapping in H0253 order: cases and blocks (session)</t>
         </is>
       </c>
       <c r="B31" s="46" t="n"/>
@@ -48493,7 +48493,7 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>• Scan order VN (CO-14101..14103) then TH (CO-14104): cases 1-3 (VN) have a PO, case 4 (TH) has none. Every case ends a valid cut, so blocks 1-3 are Ready and block 4 Not Ready: the unit is Partially Ready (ASN options 1 / 2 / 3 cases).</t>
+          <t>• H0253 order VN (CO-14101..14103) then TH (CO-14104): cases 1-3 (VN) have a PO, case 4 (TH) has none. Every case ends a valid cut, so blocks 1-3 are Ready and block 4 Not Ready: the unit is Partially Ready (ASN options 1 / 2 / 3 cases).</t>
         </is>
       </c>
     </row>
@@ -50002,7 +50002,7 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>• XD09 does not take held lines: the scan order and the blocks are computed with Vietnam only (18 pcs = 3 cases, 3 blocks) and the unit is Ready.</t>
+          <t>• XD09 does not take held lines: the H0253 order and the blocks are computed with Vietnam only (18 pcs = 3 cases, 3 blocks) and the unit is Ready.</t>
         </is>
       </c>
     </row>

--- a/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
+++ b/deliverables/function_list_v2/erd/Crossdock_ERD.xlsx
@@ -4307,7 +4307,7 @@
       <c r="D3" s="4" t="n"/>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
       <c r="G3" s="6" t="n"/>
@@ -10192,7 +10192,7 @@
     <row r="6">
       <c r="A6" s="34" t="inlineStr">
         <is>
-          <t>• 21-Oct G-System allocates the pcs of case 3 to CO-14111 (UPD_STATUS 6, no ASN): the D/S team moves case 3 to CO-14111 (XD11). Open PO qty at the end (12) = cancelled qty (CO-14102 + CO-14104).</t>
+          <t>• 21-Oct GTOPAS allocates the pcs of case 3 to CO-14111 (UPD_STATUS 6, no ASN): the D/S team moves case 3 to CO-14111 (XD11). Open PO qty at the end (12) = cancelled qty (CO-14102 + CO-14104).</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="D11" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="D21" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="D27" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="D39" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="D69" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="D73" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -14067,7 +14067,7 @@
     <row r="95">
       <c r="A95" s="45" t="inlineStr">
         <is>
-          <t>11. 20-Oct XD08: CO-14111 new (order date 19-Oct, PO-DMY-09016); 21-Oct → 6 (pcs of case 3 allocated by G-System)</t>
+          <t>11. 20-Oct XD08: CO-14111 new (order date 19-Oct, PO-DMY-09016); 21-Oct → 6 (pcs of case 3 allocated by GTOPAS)</t>
         </is>
       </c>
       <c r="B95" s="46" t="n"/>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="D96" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -14428,7 +14428,7 @@
       </c>
       <c r="D105" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -14834,7 +14834,7 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>• B: CO-B (PART-Y, VN, 8 pcs) is in ASN00020: case 1 = CO-A 2 + CO-B 4, case 2 = CO-B 4 + CO-C 2. G-System cancels 6 pcs (new serial 0000002, status 2).</t>
+          <t>• B: CO-B (PART-Y, VN, 8 pcs) is in ASN00020: case 1 = CO-A 2 + CO-B 4, case 2 = CO-B 4 + CO-C 2. GTOPAS cancels 6 pcs (new serial 0000002, status 2).</t>
         </is>
       </c>
     </row>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="D29" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -16087,7 +16087,7 @@
       </c>
       <c r="D42" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -16894,7 +16894,7 @@
       </c>
       <c r="D58" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="D10" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -18923,7 +18923,7 @@
       </c>
       <c r="D45" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="D70" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="D11" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -23320,7 +23320,7 @@
       </c>
       <c r="D33" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -23650,7 +23650,7 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>• 21-Oct ASN0006 received: G-System splits the line into serial 0000001 6 pcs status 6 and serial 0000002 6 pcs status 7.</t>
+          <t>• 21-Oct ASN0006 received: GTOPAS splits the line into serial 0000001 6 pcs status 6 and serial 0000002 6 pcs status 7.</t>
         </is>
       </c>
     </row>
@@ -23966,7 +23966,7 @@
       </c>
       <c r="D15" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -24111,7 +24111,7 @@
     <row r="19">
       <c r="A19" s="45" t="inlineStr">
         <is>
-          <t>2. 21-Oct XD08 upsert: ASN0006 received, G-System split the line</t>
+          <t>2. 21-Oct XD08 upsert: ASN0006 received, GTOPAS split the line</t>
         </is>
       </c>
       <c r="B19" s="46" t="n"/>
@@ -24137,7 +24137,7 @@
       </c>
       <c r="D20" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -24605,7 +24605,7 @@
       </c>
       <c r="D31" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -24776,7 +24776,7 @@
       </c>
       <c r="D36" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -24995,7 +24995,7 @@
       </c>
       <c r="C4" s="32" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
       <c r="D4" s="32" t="inlineStr">
@@ -25025,7 +25025,7 @@
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
       </c>
       <c r="D6" s="32" t="inlineStr">
         <is>
-          <t>Existing part master (MST-03); only PART_NAME is used (by PART_NO). Full structure: GSystem_SPS_DB_Structure_20240423 sheet MST-03.</t>
+          <t>Existing part master (MST-03); only PART_NAME is used (by PART_NO). Full structure: GTOPAS_SPS_DB_Structure_20240423 sheet MST-03.</t>
         </is>
       </c>
       <c r="E6" s="32" t="inlineStr">
@@ -25210,7 +25210,7 @@
       </c>
       <c r="D11" s="32" t="inlineStr">
         <is>
-          <t>Dummy table (proposed): send status of the cross dock master per part and target system (XD06 G-System, XD07 AP POLE). The real output is the interface data sent to the target (AP POLE: file by SFTP; G-System: existing interface). The overall Sync Status of the part stays in TB_M_PART_CANDIDATE.</t>
+          <t>Dummy table (proposed): send status of the cross dock master per part and target system (XD06 GTOPAS, XD07 AP POLE). The real output is the interface data sent to the target (AP POLE: file by SFTP; GTOPAS: existing interface). The overall Sync Status of the part stays in TB_M_PART_CANDIDATE.</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr">
@@ -25235,12 +25235,12 @@
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
         <is>
-          <t>Order control data, pre-order picking info (I/F H02-53, DVJO950) replicated from DB Surrounding by XD08. Structure from the G-System I/F layout; physical names follow the existing table. Key (PK) = unique key of the I/F layout. Rows with UPD_STATUS 6 / 2 are kept for tracking (retention optional, TBC). UPD_STATUS is a new NSP column (proposed).</t>
+          <t>Order control data, pre-order picking info (I/F H02-53, DVJO950) replicated from DB Surrounding by XD08. Structure from the GTOPAS I/F layout; physical names follow the existing table. Key (PK) = unique key of the I/F layout. Rows with UPD_STATUS 6 / 2 are kept for tracking (retention optional, TBC). UPD_STATUS is a new NSP column (proposed).</t>
         </is>
       </c>
       <c r="E12" s="32" t="inlineStr">
@@ -25360,7 +25360,7 @@
       </c>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>Existing Pra Daily Order manifest (supplier PO per manifest, 391 sample rows). MANIFEST_NO is unique; one PO_NO can have several manifests. CROSS_DOCK_FLAG is on the manifest. Columns from the data export (20-Oct), types from GSystem_SPS_DB_Structure_20240423.</t>
+          <t>Existing Pra Daily Order manifest (supplier PO per manifest, 391 sample rows). MANIFEST_NO is unique; one PO_NO can have several manifests. CROSS_DOCK_FLAG is on the manifest. Columns from the data export (20-Oct), types from GTOPAS_SPS_DB_Structure_20240423.</t>
         </is>
       </c>
       <c r="E16" s="32" t="inlineStr">
@@ -25390,7 +25390,7 @@
       </c>
       <c r="D17" s="32" t="inlineStr">
         <is>
-          <t>Existing Pra Daily Order part (one row per manifest item, 2353 sample rows). Key MANIFEST_NO + MANIFEST_ITEM (also PO_NO + PO_ITEM is unique; PO_ITEM can differ from MANIFEST_ITEM). Columns from the data export (20-Oct), types from GSystem_SPS_DB_Structure_20240423.</t>
+          <t>Existing Pra Daily Order part (one row per manifest item, 2353 sample rows). Key MANIFEST_NO + MANIFEST_ITEM (also PO_NO + PO_ITEM is unique; PO_ITEM can differ from MANIFEST_ITEM). Columns from the data export (20-Oct), types from GTOPAS_SPS_DB_Structure_20240423.</t>
         </is>
       </c>
       <c r="E17" s="32" t="inlineStr">
@@ -25450,7 +25450,7 @@
       </c>
       <c r="D19" s="32" t="inlineStr">
         <is>
-          <t>Existing ASN manifest (G-System SPS DB structure TR-01). Submit ASN: one row per Pra Daily Order manifest of the cases, all with the same ASN_NO. Only the columns used are listed. Full structure: GSystem_SPS_DB_Structure_20240423 sheet TR-01.</t>
+          <t>Existing ASN manifest (GTOPAS SPS DB structure TR-01). Submit ASN: one row per Pra Daily Order manifest of the cases, all with the same ASN_NO. Only the columns used are listed. Full structure: GTOPAS_SPS_DB_Structure_20240423 sheet TR-01.</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
@@ -25480,7 +25480,7 @@
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
-          <t>Existing ASN part (TR-02). Submit ASN: one row per manifest item and case (a case can hold several manifest items). Only the columns used are listed. Full structure: GSystem_SPS_DB_Structure_20240423 sheet TR-02.</t>
+          <t>Existing ASN part (TR-02). Submit ASN: one row per manifest item and case (a case can hold several manifest items). Only the columns used are listed. Full structure: GTOPAS_SPS_DB_Structure_20240423 sheet TR-02.</t>
         </is>
       </c>
       <c r="E20" s="32" t="inlineStr">
@@ -25510,7 +25510,7 @@
       </c>
       <c r="D21" s="32" t="inlineStr">
         <is>
-          <t>Existing last sequence per supplier + plant (TR-06): the case number (case label) and the ASN number are auto generated from it and the new last sequence is saved here. Full structure: GSystem_SPS_DB_Structure_20240423 sheet TR-06.</t>
+          <t>Existing last sequence per supplier + plant (TR-06): the case number (case label) and the ASN number are auto generated from it and the new last sequence is saved here. Full structure: GTOPAS_SPS_DB_Structure_20240423 sheet TR-06.</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="G9" s="32" t="inlineStr">
         <is>
-          <t>Send status per target system (G-System / APPOLE)</t>
+          <t>Send status per target system (GTOPAS / APPOLE)</t>
         </is>
       </c>
     </row>
@@ -30257,7 +30257,7 @@
       </c>
       <c r="H120" s="32" t="inlineStr">
         <is>
-          <t>'G-System' (XD06) / 'APPOLE' (XD07)</t>
+          <t>'GTOPAS' (XD06) / 'APPOLE' (XD07)</t>
         </is>
       </c>
     </row>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="H124" s="32" t="inlineStr">
         <is>
-          <t>Name of the interface file (AP POLE) or send ID (G-System)</t>
+          <t>Name of the interface file (AP POLE) or send ID (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -32085,7 +32085,7 @@
       </c>
       <c r="H176" s="32" t="inlineStr">
         <is>
-          <t>NSP column: status change in G-System after the first replication: NULL = no change (status 7) / '6' = received or allocated (source ORDER_STATUS 6) / '2' = cancelled (source ORDER_STATUS 2). Set by XD08; lines with UPD_STATUS are not taken by XD09</t>
+          <t>NSP column: status change in GTOPAS after the first replication: NULL = no change (status 7) / '6' = received or allocated (source ORDER_STATUS 6) / '2' = cancelled (source ORDER_STATUS 2). Set by XD08; lines with UPD_STATUS are not taken by XD09</t>
         </is>
       </c>
     </row>
@@ -41799,7 +41799,7 @@
       </c>
       <c r="F6" s="32" t="inlineStr">
         <is>
-          <t>G-System releases crossdock orders 14-Oct (status 7); the supplier POs of 15-Oct are crossdock manifests (CROSS_DOCK_FLAG X). Supplier searches delivery 16-Oct Rit 1: PART-X (VN 18 + TH 6 = 4 cases in H0253 order, 4 blocks) and PART-Y (PH 6 = 1 case) are Ready; all blocks are chosen, Create ASN and Submit. Result: one ASN with 5 cases / 30 pcs, 3 ASN manifests (one per Pra manifest), 5 ASN part rows (manifest item x case).</t>
+          <t>GTOPAS releases crossdock orders 14-Oct (status 7); the supplier POs of 15-Oct are crossdock manifests (CROSS_DOCK_FLAG X). Supplier searches delivery 16-Oct Rit 1: PART-X (VN 18 + TH 6 = 4 cases in H0253 order, 4 blocks) and PART-Y (PH 6 = 1 case) are Ready; all blocks are chosen, Create ASN and Submit. Result: one ASN with 5 cases / 30 pcs, 3 ASN manifests (one per Pra manifest), 5 ASN part rows (manifest item x case).</t>
         </is>
       </c>
     </row>
@@ -41895,7 +41895,7 @@
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>PART-X, 6 pcs/case. One PO per customer order date: PO_DT = order date + 1, qty = total order qty of the date (all destinations). PO qty &lt; order qty is an abnormality: the rest comes in a split PO. ORDER_STATUS of the replicate keeps 7; changes go to UPD_STATUS. Order date 15-Oct (12) → PO-DMY-09011; CO-14102 on hold then cancelled, so its 6 pcs of PO-DMY-09011 go to CO-14103 (older PO_DT first). Order date 17-Oct: 4 destinations, 30 pcs, PO-DMY-09013 only 18 (abnormal) → case 5 Not Ready until the split PO-DMY-09014 (12, 19-Oct). Cases 1-4 → ASN0003; CO-14104 (middle row, case 3) is cancelled after the ASN. Order date 18-Oct: 3 destinations, 18 pcs, PO-DMY-09015 18 (OK) → ASN0005. 21-Oct G-System allocates the pcs of case 3 to CO-14111 (UPD_STATUS 6, no ASN): the D/S team moves case 3 to CO-14111 (XD11). Open PO qty at the end (12) = cancelled qty (CO-14102 + CO-14104).</t>
+          <t>PART-X, 6 pcs/case. One PO per customer order date: PO_DT = order date + 1, qty = total order qty of the date (all destinations). PO qty &lt; order qty is an abnormality: the rest comes in a split PO. ORDER_STATUS of the replicate keeps 7; changes go to UPD_STATUS. Order date 15-Oct (12) → PO-DMY-09011; CO-14102 on hold then cancelled, so its 6 pcs of PO-DMY-09011 go to CO-14103 (older PO_DT first). Order date 17-Oct: 4 destinations, 30 pcs, PO-DMY-09013 only 18 (abnormal) → case 5 Not Ready until the split PO-DMY-09014 (12, 19-Oct). Cases 1-4 → ASN0003; CO-14104 (middle row, case 3) is cancelled after the ASN. Order date 18-Oct: 3 destinations, 18 pcs, PO-DMY-09015 18 (OK) → ASN0005. 21-Oct GTOPAS allocates the pcs of case 3 to CO-14111 (UPD_STATUS 6, no ASN): the D/S team moves case 3 to CO-14111 (XD11). Open PO qty at the end (12) = cancelled qty (CO-14102 + CO-14104).</t>
         </is>
       </c>
     </row>
@@ -41927,7 +41927,7 @@
       </c>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>A: CO-14110 (PART-Y, PH, 12 pcs) is in a draft (Create ASN done, not submitted). The next run of XD08 releases every draft, whatever changed: the rows are deleted, the mapped qty is given back and the cases come back in the delivery plan. B: CO-B (PART-Y, VN, 8 pcs) is in ASN00020: case 1 = CO-A 2 + CO-B 4, case 2 = CO-B 4 + CO-C 2. G-System cancels 6 pcs (new serial 0000002, status 2). Candidates (UPD_STATUS 6, PO_MAPPED_FLAG N, no ASN, oldest first): CO-E PH 4, CO-F VN 2. From the last case: case 2 CO-B 4 → CO-E; case 1: 2 of the 4 pcs → CO-F (row split), 2 pcs stay with CO-B.</t>
+          <t>A: CO-14110 (PART-Y, PH, 12 pcs) is in a draft (Create ASN done, not submitted). The next run of XD08 releases every draft, whatever changed: the rows are deleted, the mapped qty is given back and the cases come back in the delivery plan. B: CO-B (PART-Y, VN, 8 pcs) is in ASN00020: case 1 = CO-A 2 + CO-B 4, case 2 = CO-B 4 + CO-C 2. GTOPAS cancels 6 pcs (new serial 0000002, status 2). Candidates (UPD_STATUS 6, PO_MAPPED_FLAG N, no ASN, oldest first): CO-E PH 4, CO-F VN 2. From the last case: case 2 CO-B 4 → CO-E; case 1: 2 of the 4 pcs → CO-F (row split), 2 pcs stay with CO-B.</t>
         </is>
       </c>
     </row>
@@ -42055,7 +42055,7 @@
       </c>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>CO-14115 VN 12 pcs (order date 19-Oct), 6 pcs/case: case 1 → ASN0006 (rit 1), case 2 → ASN0007 (rit 2). One H0253 row, two TB_R_INSTRUCTION rows. 21-Oct ASN0006 received: G-System splits the line into serial 0000001 6 pcs status 6 and serial 0000002 6 pcs status 7. Upsert alone: serial 0000001 has 12 pcs in TB_R_INSTRUCTION for qty 6 and serial 0000002 looks open (6) → XD09 would map it again (double). XD08 re-assigns the rows: serial 0000001 = ASN0006 (oldest ASN = received), serial 0000002 = ASN0007; both PO_MAPPED_FLAG Y.</t>
+          <t>CO-14115 VN 12 pcs (order date 19-Oct), 6 pcs/case: case 1 → ASN0006 (rit 1), case 2 → ASN0007 (rit 2). One H0253 row, two TB_R_INSTRUCTION rows. 21-Oct ASN0006 received: GTOPAS splits the line into serial 0000001 6 pcs status 6 and serial 0000002 6 pcs status 7. Upsert alone: serial 0000001 has 12 pcs in TB_R_INSTRUCTION for qty 6 and serial 0000002 looks open (6) → XD09 would map it again (double). XD08 re-assigns the rows: serial 0000001 = ASN0006 (oldest ASN = received), serial 0000002 = ASN0007; both PO_MAPPED_FLAG Y.</t>
         </is>
       </c>
     </row>
@@ -42206,7 +42206,7 @@
       </c>
       <c r="D10" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -42742,7 +42742,7 @@
       </c>
       <c r="D30" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -44185,7 +44185,7 @@
     <row r="75">
       <c r="A75" s="45" t="inlineStr">
         <is>
-          <t>6. D/S [Sync] → XD06 (G-System) / XD07 (AP POLE)</t>
+          <t>6. D/S [Sync] → XD06 (GTOPAS) / XD07 (AP POLE)</t>
         </is>
       </c>
       <c r="B75" s="46" t="n"/>
@@ -44267,7 +44267,7 @@
       </c>
       <c r="C78" s="49" t="inlineStr">
         <is>
-          <t>G-System</t>
+          <t>GTOPAS</t>
         </is>
       </c>
       <c r="D78" s="49" t="inlineStr">
@@ -44343,7 +44343,7 @@
       </c>
       <c r="C80" s="49" t="inlineStr">
         <is>
-          <t>G-System</t>
+          <t>GTOPAS</t>
         </is>
       </c>
       <c r="D80" s="49" t="inlineStr">
@@ -44569,7 +44569,7 @@
       </c>
       <c r="K86" s="58" t="inlineStr">
         <is>
-          <t>No Sync → Success (inactive in G-System / AP POLE)</t>
+          <t>No Sync → Success (inactive in GTOPAS / AP POLE)</t>
         </is>
       </c>
     </row>
@@ -44623,7 +44623,7 @@
     <row r="3">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>• G-System releases crossdock orders 14-Oct (status 7); the supplier POs of 15-Oct are crossdock manifests (CROSS_DOCK_FLAG X).</t>
+          <t>• GTOPAS releases crossdock orders 14-Oct (status 7); the supplier POs of 15-Oct are crossdock manifests (CROSS_DOCK_FLAG X).</t>
         </is>
       </c>
     </row>
@@ -44728,7 +44728,7 @@
       </c>
       <c r="D10" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -46758,7 +46758,7 @@
       </c>
       <c r="D59" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -50100,7 +50100,7 @@
       </c>
       <c r="D10" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
@@ -51030,7 +51030,7 @@
       </c>
       <c r="D32" s="47" t="inlineStr">
         <is>
-          <t>Replicated from DB Surrounding (G-System)</t>
+          <t>Replicated from DB Surrounding (GTOPAS)</t>
         </is>
       </c>
     </row>
